--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -3367,6 +3367,118 @@
       </c>
       <c r="F103" s="2" t="inlineStr"/>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>With the odds exact, the Retirement cockpit disagrees with Home and the Plan tab for the same household: the working household reads 13.3% in the cockpit and 13.9% on Home and Plan; the retired household reads 87.8 out of 100 in the cockpit and 93.2% on Home and Plan (it was 90 against 95 before, so that one was already visible). Rounding to 5 hid the first.</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Claude: find which input the cockpit builds differently from willItLastInputs, and fix it in the Plan step, with a screens-agree check covering the cockpit. Founder: nothing, unless you want it before Plan.</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/RetirementCockpit.tsx planInputs · src/domain/retirement/willItLast.ts · src/__tests__/guard_d3_screens_agree.test.tsx</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Exact odds moved the amounts found by holding 80%: June's draw $4,155 → $4,140 a month (paycheck $8,155 → $8,140), a retiree's surplus $4,025 → $4,010, a future paycheck $2,460 → $2,455; Ray's claim at 70 now reads 79.5% (under 80%). The Plan brief carries a dated erratum.</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Founder: read, no action — these follow from your ruling. Claude: re-run every Plan brief figure at 1,000 futures in the Plan step.</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>August 14th Design/PLAN-REDESIGN-BRIEF-v3-2026-08-14.md (erratum) · src/__tests__/photograph_figures.test.tsx</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Net worth with no accounts yet but past the first day (the Q48 frame) still repeats 'Add your accounts ›' under each empty group — the same duplication the founder removed from the first day</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Claude: draw it in the Net worth series (v09) for approval before building.</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/NetWorthScreen.tsx (seeded, no accounts) · src/screens/__tests__/empty_state_q48.test.tsx</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Founder: say whether Cash flow's door should read differently (for example 'Add an expense by hand') and whether Disconnect becomes 'Unlink'.</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/CashFlowScreen.tsx · src/screens/SettingsScreen.tsx</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -3479,6 +3479,62 @@
       </c>
       <c r="F107" s="2" t="inlineStr"/>
     </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Performance crashed when the "Since &lt;date&gt;" window chip was tapped — in Build 53 and since: the window's words came from a table with no Since entry (undefined.toUpperCase), and its start date fell through to a year ago. Found rendering Build 53 for the Performance step.</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Claude: fixed 2026-09-14 — every window has words (Since reads "since Aug 29"), the Since walk starts where the record starts, the spoken summary uses the same words; performance_window_chips.test.tsx taps every chip.</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/PerformanceScreen.tsx (phraseFor, periodStartKey) · src/screens/__tests__/performance_window_chips.test.tsx</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Performance step findings still to take to the founder: (1) the Since chip's OWN return is worked out from today, because startDateFor (MK-PF-F-…, src/domain/performance) has no Since case; (2) with a year's window and 16 days of record, each per-account walk reads $0 for accounts worth $301,610 and $52,704; (3) Build 53 still carries the older Invest sections below the approved design (Your return, Honest comparison, Look ahead / Look back, Your investments list, add/import/record buttons); (4) the account page has no per-account walk, no return per holding and no Total row that the approved design draws.</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Claude: draw Performance as Build 53 shipped it for the founder to confirm, with each of these marked, before any change.</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/networth-and-performance/archive/2026-08-10_moneykeel_pres_mock_performance_v01.html (approved final) · August 14th Design/design_handoff_net_worth/Performance.dc.html</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -3535,6 +3535,258 @@
       </c>
       <c r="F109" s="2" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Performance v10 → v14 (APPROVED, BUILT) — Performance FINAL (2026-08-04) plus every ruling since, then the founder’s four changes of 2026-09-25: window chips on one row with the app’s corner radius, a Y axis on the summary graph, the account header reading Market value · Wealth generated · Return, and day-one history</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Built 2026-09-25 after his "approved. save and built it": the window selector, one meaning of return, the Y axis, the rebuilt day one, the older Invest sections removed. Waiting only on his VERIFIED mark on device.</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_performance_v14.html</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Drawn and sent 2026-09-14: 9 marks, a no-accounts frame, and the six places Build 53 did not match FINAL. Self-audit before sending: no retired words, square bars, markup clean, sums add up. | v11 sent 2026-09-25: marks 10-13 added. Chip row measured: 355 of the 362 points a 390-point phone gives. | v12 sent 2026-09-25: chips 42 points tall so the 12-point radius reads as a corner, window labels only (five chips WITH returns need 434-492 points against 362 once data exists), and day one drawn as a linked account with its history rebuilt. | v13 sent 2026-09-25: the five window buttons become ONE segmented control — a single bordered row split by hairline dividers, five segments of 71 points across the card’s 362, the chosen one wearing the app’s light-green fill; and the hand-entered day-one phone now says “By hand · you update it” instead of “Linked” (founder caught it). | v14 sent 2026-09-25: the window selector is a designed segmented control — a quiet tray, the chosen window lifted onto a white card, hairline dividers between the resting windows, and TWO lines in every segment (the window with its date above its own return), because five windows carrying returns on one line need 434-492 points against 362. | Built and tested 2026-09-25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Performance · account header disagrees with its own walk — MK-PF-M: the header Return on AccountDetailScreen is worked out from cost since purchase ((balance − cost) ÷ cost), while the walk directly beneath it computes the window’s return (wealth generated ÷ beginning). Two different returns on one screen. Found 2026-09-25 answering the founder’s question about Market value · Return · Income.</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Build with Performance v11 mark 12: one return, the window’s, and the header trio reads Market value · Wealth generated · Return like every other screen.</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/AccountDetailScreen.tsx (the trio) · mock v11 mark 12</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Income $220 (dividends + interest) never reconciled with +0.57%, which comes from wealth generated $300.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Performance · the value graph back-fills history — portfolioTrend (MK-PF-F-018) values TODAY’s share count at past closing prices, so someone who bought last month is shown a year-long line that never happened and will not match the broker’s statement. Found 2026-09-25.</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Built 2026-09-25: the line is drawn from the daily record only (portfolioTrend is no longer used by the screen); closeOnOrBefore never reaches forward to a later price.</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts portfolioTrend · mock v11 mark 13</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Contradicts the day-one promise on the screen: “We never back-fill a year we didn’t see.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Performance · rebuild past history for linked accounts (founder question 2026-09-25: “Why day 1 we are not able to import historic data… what app will show will not match the account”). On first sync the broker sends its whole transaction history and the date of its first record; market data gives 3 years of daily closes. Walking today’s holdings back through the transactions and pricing each day gives a real line back to the broker’s first record. Hand-entered accounts and cash honestly start the day they are entered.</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Built 2026-09-25: Calculation Module code/engines/rebuild-history.ts + store.rebuildLinkedHistory, run after every price refresh on Performance.</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_performance_v11.html · src/services/sync/snaptradeSync.ts · src/services/marketData.ts</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Recommended: rebuild, and name the source and start on the screen — “Rebuilt from E*TRADE’s records · Jun 3, 2024”. | Approved 2026-09-25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>App-wide · selector corner radius is inconsistent — 23 places use the semicircle (Radii.pill) and 157 use the 12-point corner (Radii.md); the Performance window chips were semicircles. Founder, 2026-09-25: “make the buttons same as all radio buttons across all screens — rounded corners not semicircle ends.”</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Performance chips are fixed in mock v11 (mark 10). Sweep the other semicircle selectors and bring them to 12 points, screen by screen, each with its own mock.</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>grep Radii.pill · MonthlyIncomeScreen, NetWorthScreen groupPill, BondsScreen, IncomeManagerScreen, SnapTradeConnect, JobSafetyScreen and others</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Counted 2026-09-25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Performance · the summary Return does not count income — portfolioPeriodReturn (MK-PF-F) weights each holding’s PRICE return by market value, so dividends and interest are excluded, while “Wealth generated” beside it includes them. The two figures disagree on real data. Found 2026-09-25.</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Built 2026-09-25 with the v14 build.</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts portfolioPeriodReturn · mock v12</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>On the final design’s example the two agree by luck: +0.54% ≈ 1,910 ÷ 352,404.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Performance · the 2Y figure is a yearly rate and nothing says so — periodReturn annualises 2Y (founder ruling 2026-08-18) while every other window is a window rate. Found 2026-09-25.</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Built 2026-09-25 (the screen says "2Y is shown per year, so it sits fairly beside 1Y"). FOUNDER QUESTION OPEN 2026-09-25: he asked for the 2Y to be the return over two years instead. Checked: GIPS forbids annualising under a year and annualises above it; brokerage statements annualise periods of a year or more; Fidelity warns that cumulative returns of different periods should not be compared. Recommendation sent: the segment says "+7.30% a year" and the summary says "+15.10% over the two years, which is +7.30% a year". Awaiting his word.</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts periodReturn · mock v12</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Performance · window chips cannot carry their returns on one row — measured 2026-09-25: five chips WITH returns need 434 to 492 points against the 362 a 390-point phone gives; window labels alone need 305 to 348. The chip shape was also wrong: a 26-point-tall chip with a 12-point radius draws a semicircle (founder: “they are still semi circle at the ends”).</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Built 2026-09-25 with the v14 build.</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>mock v12 mark 10 · src/screens/PerformanceScreen.tsx periodPill</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Radii.pill on a short chip is always a semicircle — the radius must be under half the height. | v12’s five separate 42-point chips still did not read as one control (founder, 2026-09-25); v13 makes them one.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -1874,12 +1874,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Commit — 278 changed files on branch taxonomy-v1.0.7 since commit addbf53; nothing committed since 2026-09-01</t>
+          <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Founder: say when to commit and push</t>
+          <t>Founder: say when to PUSH. (Note 2026-09-26: the Xcode licence has not been accepted on this Mac, so the normal git refuses to run — "sudo xcodebuild -license accept" once, then git works everywhere again.)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Claude: draw Performance as Build 53 shipped it for the founder to confirm, with each of these marked, before any change.</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>TO DO</t>
+          <t>All of them went to him on mocks v10–v14 and are built (commit 727e22a): the Since window is measured from where the record starts, the walks read from the record (rebuilt for a linked account), the home gets no walk, and the account page has its own walk, per-holding returns and a Total row.</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -3575,12 +3575,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Build with Performance v11 mark 12: one return, the window’s, and the header trio reads Market value · Wealth generated · Return like every other screen.</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>TO DO</t>
+          <t>Built 2026-09-25 with Performance v14 (commit 727e22a): the trio reads Market value · Wealth generated · Return, all three from the window’s own walk.</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Built 2026-09-25 (the screen says "2Y is shown per year, so it sits fairly beside 1Y"). FOUNDER QUESTION OPEN 2026-09-25: he asked for the 2Y to be the return over two years instead. Checked: GIPS forbids annualising under a year and annualises above it; brokerage statements annualise periods of a year or more; Fidelity warns that cumulative returns of different periods should not be compared. Recommendation sent: the segment says "+7.30% a year" and the summary says "+15.10% over the two years, which is +7.30% a year". Awaiting his word.</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
+          <t>Settled 2026-09-25: a window longer than a year shows the yearly rate with “a year” under it and the window total beside it in the summary. Written into the precision-and-display standard.</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -3753,7 +3753,11 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>His words: "Your recommendation approved. Add it to standards."</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -1902,12 +1902,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Five approved mocks still carry words the canon retired (cash-flow this-month v06 and money-four-tabs v01: "spending"; filing-status v02: "partner", "told us"; look-ahead v03: "/mo"; empty-state-pattern v01: "spending"). The app copy is on the canon; these mocks are not.</t>
+          <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU OWE", "spending") · filing-status v02 ("partner", "$X a month") · plan v05 (odds said "out of 10", "spending", "/mo", "%/yr"). The app copy is on the canon; these mocks are not. Net worth v08 and Performance v14 are clean in their frames.</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Founder: say whether each gets a new version on the canon (old archived) now, or at its next change; then Claude: re-version the ones you name</t>
+          <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -1925,7 +1925,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Recounted 2026-09-26: the old row said five; the drawn-frame scan finds eight.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3790,6 +3794,222 @@
           <t>Radii.pill on a short chip is always a semicircle — the radius must be under half the height. | v12’s five separate 42-point chips still did not read as one control (founder, 2026-09-25); v13 makes them one.</t>
         </is>
       </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Plan — the approved design filed into the MoneyKeel structure and made standalone (founder, 2026-09-26: “move it to moneykeel structure. I do not want to work on anything which is not is new file structure, and meets new standards.”)</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Founder: read MoneyKeel/documents/plan/moneykeel_pres_mock_plan_v05.html and answer the eight questions marked in it (Q1 extra-saving row, Q2 save-as-you-type, Q3 cap or overfill, Q4 where the suggested target sits, Q5 the mortgage odds placeholder, Q6 today’s money + tax on the retirement sentence, Q7 the cockpit disagreement, Q8 Ray at 79.5%). Then Claude fixes the five blockers, re-runs every figure at 1,000 futures, and draws v06 for approval before any code.</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/plan/moneykeel_pres_mock_plan_v05.html · brief v03 + both design reviews beside it</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Three copies of Plan.dc.html existed in August 14th Design/ and they differ; the v4 one is now filed as archive/2026-08-14_moneykeel_pres_mock_plan_v04.html. The design record warns the old copies off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Plan v06 — the five blockers fixed and every figure re-run at 1,000 futures: the below-yield mortgage frame ($6,304 → $5,814; $40,217 → $31,873), the spend-more bucket that says 9 in 10 where $2,500 is really 81%, the mortgage caption stated as fact, the 10.5-point chip, and amber meaning two things on day one</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Blocked on the founder’s answers to Q1–Q8 in moneykeel_pres_mock_plan_v05.html. Then Claude draws v06 for approval. No code.</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/plan/moneykeel_pres_mock_plan_v05.html</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>The design step only — the Plan tab’s code is a separate row and waits on its doors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Q-PL-3 — ‘When should I claim Social Security’ as the PILOT door: 4 figures, 3 functions, one screen (/ss-timing). The smallest thing on the Map that proves the six steps end to end, and its answer is a decision row inside the Plan design.</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Founder: name it as the pilot at the phase 1 gate (the spec already proposes it). Then step 1 is his row — what it answers, the formula in plain English, inputs, decisions, identifier, the exact figures — before any code.</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_calc_spec_orchestrator-map_v01.xlsx · Map row Q-PL-3</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Identifier not yet assigned — it is named with his row at step 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Q-PL-2 — ‘What will my retirement paycheck be’ behind its own door: 10 figures, 88 functions, spilling onto Plan, Cash flow, Monthly income and Retirement. The Plan tab prints its paycheck, so this door and MK-PL-O-001 both stand between the approved design and a built Plan tab.</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>After the pilot. Step 1 is the founder’s row; the identifier is named there.</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Map row Q-PL-2</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>SEQUENCING DECISION — is the Plan tab’s CODE built against its doors (MK-PL-O-001 thePlan for Q-PL-1, and the Q-PL-2 door) or in front of them? Built in front, the screen is built twice and can still disagree with Home about the same household — which is what it does today (13.3 vs 13.9; 87.8 vs 93.2).</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Founder: say which. Claude’s recommendation 2026-09-26: finish the Plan DESIGN now (no code), then the pilot, then Q-PL-1 and Q-PL-2 behind their doors, then build the Plan tab once against them.</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_spec_one-door-per-question_v01.md · Map rows Q-PL-1, Q-PL-2</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Performance was rebuilt in front of its door on 2026-09-25 (Q-PF-1 is still PROPOSED), so it will move again later — a recorded debt, not a surprise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Canon guard blind spot — a retired pattern that contains punctuation can never fire. one_term_per_concept scans the TypeScript AST (string literals, template text, JSX text, comments), so `/\} ?a year\b/` (row 14) cannot match: the “}” belongs to the expression, not to the JSX text node. Found 2026-09-26 by scanning the raw source of the two screens just built.</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Claude: scan the RAW source as well as the AST for canon entries that are written as patterns with punctuation, so the table means what it says. Then re-run over src/.</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>src/__tests__/one_term_per_concept.test.ts · canon row 14</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>The guard reported the app clean while one line on Performance matched a canon pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Copy decision — “+7.30% a year” on Performance against canon row 14, which retires a figure followed by “a year” in visible copy (labels read “/year”). The founder approved that exact sentence on 2026-09-25 as the readable way to say it.</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Founder: (a) the sentence becomes “+7.30%/year”, or (b) row 14 gains a stated exception — in a full sentence explaining a rate, “a year” is allowed; the LABEL form stays “/year”. Claude recommends (b): his approved wording reads better, and the canon already lets spoken labels say “a year”.</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/PerformanceScreen.tsx:375 · canon row 14</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -3803,12 +3803,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Founder: read MoneyKeel/documents/plan/moneykeel_pres_mock_plan_v05.html and answer the eight questions marked in it (Q1 extra-saving row, Q2 save-as-you-type, Q3 cap or overfill, Q4 where the suggested target sits, Q5 the mortgage odds placeholder, Q6 today’s money + tax on the retirement sentence, Q7 the cockpit disagreement, Q8 Ray at 79.5%). Then Claude fixes the five blockers, re-runs every figure at 1,000 futures, and draws v06 for approval before any code.</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
+          <t>Filed 2026-09-26; the questions in it are answered and v06 supersedes it.</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Blocked on the founder’s answers to Q1–Q8 in moneykeel_pres_mock_plan_v05.html. Then Claude draws v06 for approval. No code.</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>TO DO</t>
+          <t>Drawn 2026-09-26 in moneykeel_pres_mock_plan_v06.html: his eight decisions applied, the five blockers fixed, every figure re-run at 1,000 futures, the words on the canon, and every placeholder filled so the file reads on its own. Founder: approve it, or name a mark.</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/plan/moneykeel_pres_mock_plan_v05.html</t>
+          <t>MoneyKeel/documents/plan/moneykeel_pres_mock_plan_v06.html</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Claude: scan the RAW source as well as the AST for canon entries that are written as patterns with punctuation, so the table means what it says. Then re-run over src/.</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>TO DO</t>
+          <t>Fixed 2026-09-26 (5d262d6): the guard reads copy as it renders; 26 real violations found and cleared.</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Founder: (a) the sentence becomes “+7.30%/year”, or (b) row 14 gains a stated exception — in a full sentence explaining a rate, “a year” is allowed; the LABEL form stays “/year”. Claude recommends (b): his approved wording reads better, and the canon already lets spoken labels say “a year”.</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
+          <t>Settled 2026-09-26: (a) — the sentence reads “+7.30%/year”. Built and tested (5d262d6).</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -4011,6 +4011,70 @@
       </c>
       <c r="F124" s="2" t="inlineStr"/>
     </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Plan · present value vs future value — the screen subtracts today’s pot from a target stated in the retirement year’s dollars, and called the result “today’s money” (founder, 2026-09-26). The simulation is nominal: spending is inflated to retirement and the pot grows at the nominal return.</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Founder: which money does the Plan tab speak in? (a) everything in TODAY’s money — deflate the target and the projection ($2,000,000 at 65 is $1,682,530 now), or (b) everything in the retirement year’s money, said once on the screen. Claude recommends (a): a person can only judge a number against the prices they know. Either way the subtraction stops mixing the two.</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>mock v06, the PV mark · src/domain/retirement/index.ts simulate()</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>B-101 in the bug ledger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Plan · tax on withdrawals — the plan charges tax ONLY on the required withdrawal from pre-tax accounts (from 73), at the person’s effective rate on TODAY’S gross income. Voluntary withdrawals, anything above the required amount, and gains in taxable accounts are untaxed (founder question, 2026-09-26).</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Founder: should the plan tax ordinary withdrawals too — pre-tax at the ordinary rate, taxable at the gain share, Roth at nothing — and should the rate come from the RETIREMENT year’s income rather than today’s? Claude recommends yes to both: a retiree’s rate is usually lower than their working rate, so today’s rate is wrong in both directions. Engine work, sized before it starts.</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/index.ts (the RMD branch) · willItLast.ts rmd_tax_rate · mock v06, the TAX mark</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>B-102 in the bug ledger. Founder ruling G7 (2026-09-12) bars a built-in default rate — whatever is chosen has to come from his own numbers.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -4019,7 +4019,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Founder: which money does the Plan tab speak in? (a) everything in TODAY’s money — deflate the target and the projection ($2,000,000 at 65 is $1,682,530 now), or (b) everything in the retirement year’s money, said once on the screen. Claude recommends (a): a person can only judge a number against the prices they know. Either way the subtraction stops mixing the two.</t>
+          <t>Founder: one decision, in one line — does “short $1,090,848” stay as a subtraction across two years’ money (as Build 53 shipped and v4 drew), or do the target and the projection move into today’s money? Claude recommends today’s money. NOTE: this is the SHIPPED behaviour (shortOfTarget = typed target − today’s balance), not something the mock introduced, and nothing about it goes on the screen as prose.</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -4046,17 +4046,17 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Plan · tax on withdrawals — the plan charges tax ONLY on the required withdrawal from pre-tax accounts (from 73), at the person’s effective rate on TODAY’S gross income. Voluntary withdrawals, anything above the required amount, and gains in taxable accounts are untaxed (founder question, 2026-09-26).</t>
+          <t>Plan · tax — ALREADY RULED, and I asked him again. G6 (2026-09-08): “no built-in tax rates … the person’s own rates, or no number with the reason”. G7 (2026-09-12): “no flat 22% inside the odds; every caller passes its own effective rate.” So the plan’s figures are BEFORE tax except the required withdrawal, which uses his own rate. The defect was a line I added claiming “after tax” — removed 2026-09-26.</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Founder: should the plan tax ordinary withdrawals too — pre-tax at the ordinary rate, taxable at the gain share, Roth at nothing — and should the rate come from the RETIREMENT year’s income rather than today’s? Claude recommends yes to both: a retiree’s rate is usually lower than their working rate, so today’s rate is wrong in both directions. Engine work, sized before it starts.</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
+          <t>Nothing for him. If the tax treatment is ever widened (ordinary withdrawals, the retirement-year rate), it goes to him as a NEW question with the numbers — not as a re-ask of G6/G7.</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -4075,6 +4075,38 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Cash flow · the design record never carried its approved mocks — four are filed in MoneyKeel/documents/cashflow (income end to end v07, This month + Spending v06, Look ahead v03, the four-tab surface v01) and the changelog approves income v4, v5 and v6, but the design-each-screen-was-built-from record lists only Net worth, Performance and Plan. On 2026-09-26 I read that one file and told him Cash flow had no approved design.</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Claude: trace which build shipped which cash-flow mock (fingerprint method) and add the rows. Founder: one question — does income v07 supersede v06, or is it v06 with the canon words applied? Its file says v07; its eyebrow still says v6.</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/cashflow/ · design-each-screen-was-built-from_v01.md</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Same class as the rulings miss: one file read as if it were the whole record.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$175</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +30,11 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
@@ -72,8 +79,8 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -452,18 +459,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task description</t>
@@ -495,7 +502,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Live prices: the Tiingo key (price feed is seam-ready, no key)</t>
@@ -523,7 +530,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr"/>
     </row>
-    <row r="3">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>FCC core design approved — strategy, high-level design, PRD v1.1, detailed design v1.1 (40 screens), UX v1.1. Build everything, gate with the suite, one build.</t>
@@ -551,7 +558,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr"/>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Build 41 (the redesign build) cut and walked on the device</t>
@@ -579,7 +586,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr"/>
     </row>
-    <row r="5">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Standing order: release gate — no build without your literal "cut the build" to a presented checklist</t>
@@ -607,7 +614,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Standing order: definition of complete — the union of every approved document; "deferred" goes to you first</t>
@@ -635,7 +642,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr"/>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Design audit v1.0 — every approved screen against the code</t>
@@ -663,7 +670,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Bank and brokerage connection (SnapTrade) shipped</t>
@@ -691,7 +698,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr"/>
     </row>
-    <row r="9">
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Standing order: mock-first — full-colour, full-screen mock in every data state before any screen is built; Build 43 feedback fixed</t>
@@ -719,7 +726,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr"/>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Launch sign-off v2</t>
@@ -747,7 +754,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr"/>
     </row>
-    <row r="11">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Build 45 root causes; July-24 audit → standing order: same-day changelog row for every approval</t>
@@ -775,7 +782,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Builds 46 and 47 item walks; standing order: full-surface done (coverage line on every done-claim)</t>
@@ -803,7 +810,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr"/>
     </row>
-    <row r="13">
+    <row r="13" ht="45" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Pre-build-48 alignment audit; Build 48 founder walk</t>
@@ -831,7 +838,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr"/>
     </row>
-    <row r="14">
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Your rules: cash = cash only, CDs are bonds; change-walk mock; institution data research; UX v1.2</t>
@@ -859,7 +866,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr"/>
     </row>
-    <row r="15">
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Standing order: mock-match audit — string-by-string diff, order, nesting, alignment, appearance</t>
@@ -887,7 +894,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr"/>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Builds 50 and 52 walks; your Q6 (debts composition bar)</t>
@@ -915,7 +922,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr"/>
     </row>
-    <row r="17">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Plan redesign brief v3; screen map + orphan-route guard; briefs-are-code guard; build audit of the redesign</t>
@@ -943,7 +950,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr"/>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Build 53 cut — Plan redesign and the mortgage engine</t>
@@ -971,7 +978,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr"/>
     </row>
-    <row r="19">
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Standing orders: act as a fiduciary adviser; every master tab in one metric order; no prose from me — code and specialist review</t>
@@ -999,7 +1006,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr"/>
     </row>
-    <row r="20">
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Brief: your 56 decisions — fixes B1–B8 (pensions, Social Security factors, legacy target, RMD age, RMD as income, odds calibration, money-market class, decimals), 14 metrics cut, D1–D7 builds, E corrections</t>
@@ -1027,7 +1034,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr"/>
     </row>
-    <row r="21">
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Your four objectives + the objectives-and-verification standard (file-and-code rule, verification ladder)</t>
@@ -1055,7 +1062,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr"/>
     </row>
-    <row r="22">
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Standing orders: identifiers everywhere; no blanket decisions — each case to you with its specifics</t>
@@ -1083,7 +1090,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr"/>
     </row>
-    <row r="23">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>First master audit — 51 findings A01–A51: A09, A10, A11, A44 fixed; the other 47 are recorded on their master rows, not yet worked</t>
@@ -1111,7 +1118,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr"/>
     </row>
-    <row r="24">
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Formula audit — 25 findings B01–B25: B05 (401(k) taxed) fixed; B02, B03, B04 are file fixes; B01 (minimum-payment rule never built) and B06 (three return methods, one label) need your decision; B07–B25 not re-verified</t>
@@ -1139,7 +1146,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr"/>
     </row>
-    <row r="25">
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Your comments on the master (column W): questions Q01–Q33 recorded; rulings Q06, Q07, Q08, Q09, A15, A46, A47 and the bond display rule</t>
@@ -1167,7 +1174,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr"/>
     </row>
-    <row r="26">
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Bond display rule (nine facts on a bond; value = current, else cost, else face) — ruled, not coded; three specifics open as Q38</t>
@@ -1199,7 +1206,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Function identifiers made permanent (register); a header on every function; guards B1 (header is a printed view) and B2 (formula agrees); build spec of 22 guards — 17 built, 1 partial, 4 to build</t>
@@ -1227,7 +1234,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr"/>
     </row>
-    <row r="28">
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Formulas read from the code onto every master row — 49 of 596 still read "NOT READ YET" (bodies the generator cannot render)</t>
@@ -1255,7 +1262,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr"/>
     </row>
-    <row r="29">
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Build 54 — the income rebuild (two earners, one tax engine, one rate); 46 new + 19 changed functions documented</t>
@@ -1283,7 +1290,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr"/>
     </row>
-    <row r="30">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Standing order: one term per concept — canon take-home and calculated; guard test</t>
@@ -1311,7 +1318,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr"/>
     </row>
-    <row r="31">
+    <row r="31" ht="45" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Second verification — 41 findings (G1–G37, C1–C4) assessed; you ruled 27 on 2026-09-08; all 27 executed</t>
@@ -1339,7 +1346,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr"/>
     </row>
-    <row r="32">
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Second verification — your 2026-09-12 comments folded in: 14 rows ruled and coded the same day (G1, G2, G4, G5, G7, G9, G11, G12, G15, G24, G36, G37, C1, C3); your "ok" recorded on G14, G16, G20, G22, G32, G35</t>
@@ -1367,7 +1374,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr"/>
     </row>
-    <row r="33">
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Second verification — 14 rulings coded but without a named test: G14, G16, G18, G19, G20, G23, G25, G26, G27, G29, G33, G35, C2, C4 (plus Q07, A15 and the cash-flow worked example on the rulings tab)</t>
@@ -1395,7 +1402,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr"/>
     </row>
-    <row r="34">
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Synonym clusters — 16 concepts, one word each</t>
@@ -1423,7 +1430,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr"/>
     </row>
-    <row r="35">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Your -jj comments on the master (20) and typed answers (7) folded into the master on their rows; the four wrong-number findings fixed</t>
@@ -1451,7 +1458,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr"/>
     </row>
-    <row r="36">
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Master questions Q34–Q45 and Q50 (your cash-flow example arithmetic) — open</t>
@@ -1479,7 +1486,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr"/>
     </row>
-    <row r="37">
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Per-asset-class capture list — 15 items NOT CAPTURED, 4 DERIVED but blocked, 1 rule pending, 1 wrong until Q42 (options), display currency Q43</t>
@@ -1507,7 +1514,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr"/>
     </row>
-    <row r="38">
+    <row r="38" ht="45" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Timezone fix (look-back window on the local date) and the inflation default (2.5%, 30-year average, brief Q-50)</t>
@@ -1535,7 +1542,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr"/>
     </row>
-    <row r="39">
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Q48 — empty state: "$0 — nothing entered yet." plus the door; one mock of the pattern built</t>
@@ -1563,7 +1570,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr"/>
     </row>
-    <row r="40">
+    <row r="40" ht="45" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Q49 — full precision inside every calculation, rounding once at display; 317 roundings removed; standard written</t>
@@ -1591,7 +1598,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr"/>
     </row>
-    <row r="41">
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>G28 — inputs reconciliation: the sweep fixed; the code's own record sits beside each figure's claimed inputs; verdicts: 3 agree, 35 partly, 23 reached but not declared, 3 neither, 1 declared but not reached</t>
@@ -1619,7 +1626,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr"/>
     </row>
-    <row r="42">
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Status on every tab and every row of the three working files, one vocabulary; rules for CODED / TESTED / VERIFIED; JJ-feedback-archive folders</t>
@@ -1647,7 +1654,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr"/>
     </row>
-    <row r="43">
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Your onboarding notes on build 53 — 12 notes: 4 folded in, 8 not yet confirmed line by line</t>
@@ -1675,7 +1682,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr"/>
     </row>
-    <row r="44">
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Two of your earlier answers still open on their rows: the current-month rule for the essentials window (MK-CF-F-190) and where the Medicare question sits (MK-XS-I-062)</t>
@@ -1703,7 +1710,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr"/>
     </row>
-    <row r="45">
+    <row r="45" ht="60" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Everything ruled, coded and tested: 16 clusters, Q06 (options × 100), Q08 (foreign currency = cash), Q09 (unit on every quantity), A46 (no coupon → $0), A47 (accrued interest); canon table = the guard's one source; six new functions</t>
@@ -1731,7 +1738,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr"/>
     </row>
-    <row r="46">
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Two judgment calls in the coding to confirm: A46 read strictly (an assumed return no longer stands in for a missing coupon); A47 applied to current yield only, not yield to maturity</t>
@@ -1759,7 +1766,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr"/>
     </row>
-    <row r="47">
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Four questions from the cluster work: #3 "spending" in prose (173 places), #11 the "Close position" button, #13 "plan for the lump sum" (my answer is on the row), #14 "/qtr", "/wk" labels</t>
@@ -1787,7 +1794,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr"/>
     </row>
-    <row r="48">
+    <row r="48" ht="45" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>One stale header: MK-CF-F-123 (the retired local-date helper) carries a header but has no master row</t>
@@ -1815,7 +1822,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr"/>
     </row>
-    <row r="49">
+    <row r="49" ht="60" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>VERIFIED marks — 33 rulings, 18 cluster rows and 11 assessment rows stand at TESTED, NOT VERIFIED</t>
@@ -1843,7 +1850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr"/>
     </row>
-    <row r="50">
+    <row r="50" ht="45" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Build 55 — release gate: scope complete, audits closed, journey pass, checklist presented</t>
@@ -1871,7 +1878,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr"/>
     </row>
-    <row r="51">
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Commit — the branch was 278 files behind on 2026-09-14; committed since: 983805a (catch-up), f0e1d6d (Net worth v08), c4f2679 (the Since crash), 727e22a (Performance v14). Nothing is pushed — the branch taxonomy-v1.0.7 is local only.</t>
@@ -1899,7 +1906,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr"/>
     </row>
-    <row r="52">
+    <row r="52" ht="60" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>EIGHT live mocks still DRAW words the canon retired (measured 2026-09-26 over the drawn frames, not the commentary): cash-flow this-month v06 ("In (take-home)", "spending") · income end-to-end v07 ("A usual month", "Gross a year") · look-ahead v03 ("/mo") · money-four-tabs v01 ("In (take-home)", "Out (", "/mo", "spending") · account-detail v01 ("Connected ·") · empty-state-pattern v01 ("WHAT YOU OWE", "spending") · filing-status v02 ("partner", "$X a month") · plan v05 (odds said "out of 10", "spending", "/mo", "%/yr"). The app copy is on the canon; these mocks are not. Net worth v08 and Performance v14 are clean in their frames.</t>
@@ -1931,7 +1938,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Stand-in ages when the birth year is missing: the Retirement cockpit and Insights assume 45, the cash-flow model and the draw steer assume 68, the onboarding helper 35 (or 65 for the retirement age). Your rule R2 says an unknown input gives no number and a reason.</t>
@@ -1959,7 +1966,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr"/>
     </row>
-    <row r="54">
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Empty state, the last 8 of 58 rows (4 more do not apply — the holding page): Account detail (the classes and income inside one account — MK-NW-M-019/020/021); a past month that predates tracking (MK-CF-M-004); a goal row (MK-CF-M-021, appears only when committed); the Roth "Extra tax" row (MK-PL-M-023, "—" until a plan is adopted); Job safety asks in place (MK-MN-M-021). And one question: Debts cannot tell "I have none" from "nothing entered" — no such answer exists.</t>
@@ -1987,7 +1994,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr"/>
     </row>
-    <row r="55">
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>One-door architecture — step 2, the photograph: every figure two people see on eight screens recorded before any function moves behind a door</t>
@@ -2015,7 +2022,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr"/>
     </row>
-    <row r="56">
+    <row r="56" ht="45" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>One-door architecture — the will-it-last ratchet: 16 files reach past the door today; the list can only shrink</t>
@@ -2043,7 +2050,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr"/>
     </row>
-    <row r="57">
+    <row r="57" ht="60" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>One-door architecture — three decisions the spec leaves to you: (1) the pilot question, (2) does a door hand out figures only or also the walk behind them, (3) what doors are called</t>
@@ -2071,7 +2078,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr"/>
     </row>
-    <row r="58">
+    <row r="58" ht="60" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>One-door architecture — step 1 for the pilot: the row (what it answers, formula in plain English, inputs, decisions, identifier, exact list of figures the door hands out)</t>
@@ -2099,7 +2106,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr"/>
     </row>
-    <row r="59">
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>One-door architecture — will it last, MK-PL-O-001 thePlan: the row, then the door beside the old code, then 16 callers moved one at a time against the photograph, then the old doors closed</t>
@@ -2127,7 +2134,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr"/>
     </row>
-    <row r="60">
+    <row r="60" ht="60" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>The retired word "engine" (identifier standard, 2026-08-22) was still in use: 119 code lines, 94 test lines, 81 document lines, ~230 master cells, two visible strings, a spec title, two file names</t>
@@ -2155,7 +2162,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr"/>
     </row>
-    <row r="61">
+    <row r="61" ht="60" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Closing the loop — screen to orchestrator to screen: the loop must prove completeness (no figure on screen left out; every orchestrator carries every function it should; no orchestrator orphan), and orchestrators are grouped by a written rule BEFORE any is built (his example: total assets vs total assets by institution must be one function, not two)</t>
@@ -2183,7 +2190,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr"/>
     </row>
-    <row r="62">
+    <row r="62" ht="60" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan · phase 0 — the ten design rules (one question one orchestrator — the same question on any screen, the same orchestrator; one concept one function; no orchestrator calls an orchestrator; inputs once per family; screens compute nothing; shared dependents recorded; door = figures + walk, MK-family-O-NNN; action and data-in outside; three completeness proofs; map before code)</t>
@@ -2211,7 +2218,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr"/>
     </row>
-    <row r="63">
+    <row r="63" ht="60" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan · phase 1a — figure census: render every screen in every data state and record every figure a person can read; every one claimed by a row</t>
@@ -2239,7 +2246,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr"/>
     </row>
-    <row r="64">
+    <row r="64" ht="60" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan · phase 1b — function closure: the call graph from the code; per question its closure by identifier; every displayed or dependent function inside no closure listed</t>
@@ -2267,7 +2274,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr"/>
     </row>
-    <row r="65">
+    <row r="65" ht="60" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan · phase 1c — the Map: one row per proposed orchestrator — question, screens, figures by identifier, closure by identifier, inputs, decisions, status, question for you, your answer</t>
@@ -2295,7 +2302,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr"/>
     </row>
-    <row r="66">
+    <row r="66" ht="60" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan · phase 1d — Conflicts: every grouping conflict one row by identifier with a recommendation (two totals for one concept; a function under two questions; two functions for one concept; a figure the screen computes)</t>
@@ -2323,7 +2330,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr"/>
     </row>
-    <row r="67">
+    <row r="67" ht="45" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan · phase 1e — orphans: orchestrators no row names or no screen imports; functions nobody reaches</t>
@@ -2351,7 +2358,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr"/>
     </row>
-    <row r="68">
+    <row r="68" ht="45" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan · phase 1 gate — approve the Map, answer Conflicts, name the pilot question (proposed: Social Security timing)</t>
@@ -2379,7 +2386,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr"/>
     </row>
-    <row r="69">
+    <row r="69" ht="60" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan · phase 2 — the loop guards: one producer per figure row; the forward hop read from screen imports; the reverse hop generated from the rows; the trace test</t>
@@ -2407,7 +2414,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr"/>
     </row>
-    <row r="70">
+    <row r="70" ht="60" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan · phase 3 — the pilot question through the six steps (row → photograph → door → callers moved one at a time → old doors closed → reconcile)</t>
@@ -2435,7 +2442,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr"/>
     </row>
-    <row r="71">
+    <row r="71" ht="45" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan · phase 4 — will my money last: MK-PL-O-001 thePlan; the 16 files move behind the door</t>
@@ -2463,7 +2470,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr"/>
     </row>
-    <row r="72">
+    <row r="72" ht="45" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan · phase 5 — every remaining Map row by blast radius, one question at a time, same gate each</t>
@@ -2491,7 +2498,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr"/>
     </row>
-    <row r="73">
+    <row r="73" ht="60" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan · phase 6 — the walls: every ratchet at zero and turned into a wall; Calculation Module code/engines/ emptied and removed; the trace test over all figure rows</t>
@@ -2519,7 +2526,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr"/>
     </row>
-    <row r="74">
+    <row r="74" ht="60" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Orchestrator plan — proposed rule 11: a door DECLARES each figure by identifier beside the code that computes it, the screen prints only by identifier, and the builder generates the master's figure rows from those declarations (deleting the ~140 hand-typed lines that are the origin of every mismatch)</t>
@@ -2547,7 +2554,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr"/>
     </row>
-    <row r="75">
+    <row r="75" ht="60" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
           <t>The census now finds figures in the CODE, not in the words: the three money formatters are wrapped during the render, so every dollar figure is recorded with the exact file and line that printed it. 303 places, 242 once a figure and its spoken label are merged — 40 already have a row, 105 could be one of several (Claude reads), 97 have none (Claude proposes, you confirm)</t>
@@ -2575,7 +2582,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr"/>
     </row>
-    <row r="76">
+    <row r="76" ht="60" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>The working plan is now GENERATED from moneykeel_workplan.json, and your Status and Comments edits are read back before it is written</t>
@@ -2603,7 +2610,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr"/>
     </row>
-    <row r="77">
+    <row r="77" ht="60" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Rule 11 step 1 — a door DECLARES each figure it hands out, beside the code that computes it: identifier, the words on screen, unit, the formula in plain English, inputs, decisions, and what it says when it cannot be computed</t>
@@ -2631,7 +2638,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr"/>
     </row>
-    <row r="78">
+    <row r="78" ht="60" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Rule 11 step 2 — a screen prints a figure only by its identifier, so the place that prints carries it; the rounding and the /month · /year wording come from the declaration</t>
@@ -2659,7 +2666,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr"/>
     </row>
-    <row r="79">
+    <row r="79" ht="60" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Rule 11 step 3 — the master file's figure rows are PRINTED from the declarations instead of typed; the hand-written lists shrink as each door declares</t>
@@ -2687,7 +2694,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr"/>
     </row>
-    <row r="80">
+    <row r="80" ht="60" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Rule 11 guard — a screen may not start printing a figure the file knows nothing about: 673 places in 57 files still format a number directly, frozen as a ratchet that only falls (Your base pay and Your income are already at zero)</t>
@@ -2715,7 +2722,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr"/>
     </row>
-    <row r="81">
+    <row r="81" ht="60" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Two figures the base-pay screen was working out itself are now the door's, and the household figure is the SUM of the earners' rather than a second subtraction — a total and its parts cannot disagree (rule 2, his total-assets example)</t>
@@ -2743,7 +2750,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr"/>
     </row>
-    <row r="82">
+    <row r="82" ht="60" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>The next questions to declare their figures — each one lowers the ratchet and takes its slice of the findings out of existence</t>
@@ -2771,7 +2778,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr"/>
     </row>
-    <row r="83">
+    <row r="83" ht="60" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
           <t>A declaration now records whether YOU have ruled on it — a figure with no ruling date prints its row marked DRAFT, WAITING FOR YOUR VERDICT, with the question in your usual column (rule 10 made mechanical)</t>
@@ -2799,7 +2806,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr"/>
     </row>
-    <row r="84">
+    <row r="84" ht="60" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Q-CF-2 'how much have I spent this month, against the plan, and what is left' — eight figures DRAFTED on MK-CF-O-003 thisMonth: expected inflow, planned outflow, planned surplus, each planned line, inflow so far, outflow so far, surplus so far, each received line (MK-CF-M-047…054)</t>
@@ -2827,7 +2834,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr"/>
     </row>
-    <row r="85">
+    <row r="85" ht="60" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Post Feedback Sync (PFS) named — your word for: fold every feedback copy of yours into its original, keep your words exactly, answer your questions on the row, rebuild and check, archive the copy with the date, report with a coverage line</t>
@@ -2855,7 +2862,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr"/>
     </row>
-    <row r="86">
+    <row r="86" ht="60" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>PFS 2026-09-14 — the master file: your feedback copy read in full (36 cells of yours, plus a cell-by-cell comparison with the master); 32 already in, 3 comments restored to your exact words, 1 new comment answered on its row; copy archived</t>
@@ -2883,7 +2890,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr"/>
     </row>
-    <row r="87">
+    <row r="87" ht="60" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Defect found by the PFS: the file-wide wording pass (2026-09-13) had rewritten your own words — 'why dependency on engine and not function?' read 'why dependency on function and not function?', and two of your rulings on the rulings tab had 'engine' changed</t>
@@ -2911,7 +2918,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr"/>
     </row>
-    <row r="88">
+    <row r="88" ht="60" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>PFS 2026-09-14 — the audit files: your two feedback copies archived on 2026-09-12 compared cell by cell with the live files — 63 entries of yours; 61 were already in, 2 were not and are now: your 'ok' on G31 (assessment) and your corrected wording 'do not' on synonym ruling 11, which still read 'dod not' in the synonym workbook and on the rulings ledger. The Build 54 findings workbook (9 findings, all fixed or built) archived</t>
@@ -2939,7 +2946,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr"/>
     </row>
-    <row r="89">
+    <row r="89" ht="60" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Two questions from your build-53 onboarding notes, still open: (1) your note says 'connect your first account' where the door says 'Connect your bank ›' — which wording? (2) 'circular loop' — which screens loop, and what should happen instead?</t>
@@ -2967,7 +2974,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr"/>
     </row>
-    <row r="90">
+    <row r="90" ht="60" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Same door, two destinations: Home's 'Add something by hand ›' opens the Net worth tab, while the same door on Sharpen your plan and What counts toward retirement opens Add account. The small line under it also differs: Home says 'Add it by hand — your home, savings, or an account with no login.', the other two say 'Your home, savings, or an account with no login.'</t>
@@ -2995,7 +3002,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr"/>
     </row>
-    <row r="91">
+    <row r="91" ht="60" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
           <t>The design changelog has no row after 2026-09-02, although the same-day changelog standing order asks for one on every approval — the cluster rulings of 2026-09-10, the empty-state mock of 2026-09-12 and others are missing; today's two door rulings are now in</t>
@@ -3023,7 +3030,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr"/>
     </row>
-    <row r="92">
+    <row r="92" ht="60" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>One door, one term: the three ways to add an account read 'Link it (read-only)', 'Add by hand' and 'Import from a file' on every screen, under the heading 'How do you want to add an account?' — Home, Sharpen your plan, the Plan tab, Net worth (first day and the add sheet), the Connect an account screen and Performance</t>
@@ -3051,7 +3058,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr"/>
     </row>
-    <row r="93">
+    <row r="93" ht="60" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Screen titles are not one size in the app, and the standard never set one: 31 screens use 24 points, Will it last and Look back use 20, Cash flow uses 30, and the Net worth tab has no screen title at all (founder 2026-09-14: "we cannot have screen without title")</t>
@@ -3083,7 +3090,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="60" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>MoneyKeel at the top of every screen — today only the five tab screens show it; every pushed screen (Import from File, Add by hand, Link an account, Sharpen your plan and the rest) has a native bar or none</t>
@@ -3111,7 +3118,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr"/>
     </row>
-    <row r="95">
+    <row r="95" ht="60" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
           <t>One standard for designing a new screen — every rule a screen and its mock must meet, in one document, so a mock is right before it reaches you (founder 2026-09-14: "We spent 5 hours trying to design one set of screens")</t>
@@ -3139,7 +3146,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr"/>
     </row>
-    <row r="96">
+    <row r="96" ht="60" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>The master's STATUS column said NOTHING OPEN on the eight cash flow rows that wait on your verdict (MK-CF-M-047 to MK-CF-M-054, Row status DRAFT)</t>
@@ -3167,7 +3174,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr"/>
     </row>
-    <row r="97">
+    <row r="97" ht="60" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
           <t>One standard for creating a new screen: every rule a screen and its mock must meet, in one document (founder 2026-09-14: "We spent 5 hours trying to design one set of screens")</t>
@@ -3195,7 +3202,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr"/>
     </row>
-    <row r="98">
+    <row r="98" ht="60" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>The Plan tab does not match the Plan design you approved (Claude Design Plan v4, brief v3-2026-08-14, built for Build 53). Built from it: the two dials, the typed target, Retire / Goals / Prepare, 'Can I spend more?' in plain English, the Social Security row. NOT built: 'Your plan at a glance' — seven equal question rows, collapsed, dials staying small while it is open. Today's app still shows the 08-12 layout you rejected (FACTS — SAVE AS YOU GO · WHAT COUNTS TOWARD RETIREMENT · BIG ONE-TIME COSTS · CHOICES — TRY THEM), rows as labels not questions, and the Roth row as 'Is a Roth move worth it?' instead of 'Is converting to a Roth worth it?'. The seven-row component (src/components/PlanGlanceRows.tsx) exists and no screen uses it. The 49-check audit of 08-15 never checked the glance.</t>
@@ -3203,7 +3210,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Founder: say whether to (a) run a full mock-match audit of the Plan tab against the v4 design, then mock the tab as approved with today's rulings, then build — or say otherwise. Claude: mock v10 sections 4 and 5 were drawn from today's code, so they show the rejected layout; they are not to be approved as they stand</t>
+          <t>FOUNDER RULE 2026-09-27: "If I approved mock up post build - that the latest approval." The newest approval wins. A mock he approved AFTER a build is the design; the build is behind it, and bringing the build up to it is MINE to do, not a question to put to him. — so this one is MINE too, once the Plan doors are settled. Founder: say whether to (a) run a full mock-match audit of the Plan tab against the v4 design, then mock the tab as approved with today's rulings, then build — or say otherwise. Claude: mock v10 sections 4 and 5 were drawn from today's code, so they show the rejected layout; they are not to be approved as they stand</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -3223,7 +3230,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr"/>
     </row>
-    <row r="99">
+    <row r="99" ht="60" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Nothing recorded which design each screen was built from. The Build 53 Net worth and Performance finals (networth-FINAL.html, performance-FINAL.html, the two Net worth PDFs, Net worth screens 01 to 11) were filed under networth-and-performance/archive/ on 2026-09-01, which marks them replaced. They were not replaced. Six hours of mocks then started from the wrong files. CORRECTION 2026-09-14: Build 53 Net worth was built from Quiet Instrument mock v5 (full-width banners, 2026-08-11) on top of networth-FINAL, plus square bar corners built the same day with no mock (founder: 'no mock up ... just build it'). No mock file draws the square-cornered screen; v5 still shows rounded top corners.</t>
@@ -3251,7 +3258,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr"/>
     </row>
-    <row r="100">
+    <row r="100" ht="60" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Net worth mock v06 — one picture of the Net worth screen as Build 53 shipped it (Quiet Instrument v5 plus the square, edge-to-edge bars and the other changes built 2026-08-11 to 08-14 without a mock)</t>
@@ -3283,7 +3290,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="60" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Net worth v07 — the three ways to add an account on Net worth (first day, the add sheet, the add button), plus every ruling since Build 53 that touches the screen (empty state, Debts, Emergency fund, Stocks / Funds, /month, you entered, expenses, odds to the nearest 5), each marked</t>
@@ -3315,7 +3322,7 @@
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="60" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>The master still named two Net worth figures with retired words: MK-NW-M-009 'WHAT YOU OWE · 💳 DEBTS' and MK-NW-M-013 'EMERGENCY CUSHION — X.X months', while the app says DEBTS and EMERGENCY FUND (canon rows 10 and 6)</t>
@@ -3343,7 +3350,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr"/>
     </row>
-    <row r="103">
+    <row r="103" ht="60" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
           <t>The retirement sentence (Net worth, Plan, Home) prints future dollars without saying so, and the odds calculation charges no tax on withdrawals from taxable accounts — found checking the founder's question on v07 ($4.1M at 65 is about $2.0M in today's money)</t>
@@ -3371,7 +3378,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr"/>
     </row>
-    <row r="104">
+    <row r="104" ht="60" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
           <t>With the odds exact, the Retirement cockpit disagrees with Home and the Plan tab for the same household: the working household reads 13.3% in the cockpit and 13.9% on Home and Plan; the retired household reads 87.8 out of 100 in the cockpit and 93.2% on Home and Plan (it was 90 against 95 before, so that one was already visible). Rounding to 5 hid the first.</t>
@@ -3399,7 +3406,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr"/>
     </row>
-    <row r="105">
+    <row r="105" ht="60" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Exact odds moved the amounts found by holding 80%: June's draw $4,155 → $4,140 a month (paycheck $8,155 → $8,140), a retiree's surplus $4,025 → $4,010, a future paycheck $2,460 → $2,455; Ray's claim at 70 now reads 79.5% (under 80%). The Plan brief carries a dated erratum.</t>
@@ -3427,7 +3434,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr"/>
     </row>
-    <row r="106">
+    <row r="106" ht="60" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Net worth with no accounts yet but past the first day (the Q48 frame) still repeats 'Add your accounts ›' under each empty group — the same duplication the founder removed from the first day</t>
@@ -3455,7 +3462,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr"/>
     </row>
-    <row r="107">
+    <row r="107" ht="60" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Two word collisions found building v08: Cash flow's 'Add by hand' adds an EXPENSE (the same words as the account door), and Settings still says 'Disconnect' beside 'Linked accounts'</t>
@@ -3483,7 +3490,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr"/>
     </row>
-    <row r="108">
+    <row r="108" ht="60" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Performance crashed when the "Since &lt;date&gt;" window chip was tapped — in Build 53 and since: the window's words came from a table with no Since entry (undefined.toUpperCase), and its start date fell through to a year ago. Found rendering Build 53 for the Performance step.</t>
@@ -3511,7 +3518,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr"/>
     </row>
-    <row r="109">
+    <row r="109" ht="60" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Performance step findings still to take to the founder: (1) the Since chip's OWN return is worked out from today, because startDateFor (MK-PF-F-…, src/domain/performance) has no Since case; (2) with a year's window and 16 days of record, each per-account walk reads $0 for accounts worth $301,610 and $52,704; (3) Build 53 still carries the older Invest sections below the approved design (Your return, Honest comparison, Look ahead / Look back, Your investments list, add/import/record buttons); (4) the account page has no per-account walk, no return per holding and no Total row that the approved design draws.</t>
@@ -3539,7 +3546,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr"/>
     </row>
-    <row r="110">
+    <row r="110" ht="60" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Performance v10 → v14 (APPROVED, BUILT) — Performance FINAL (2026-08-04) plus every ruling since, then the founder’s four changes of 2026-09-25: window chips on one row with the app’s corner radius, a Y axis on the summary graph, the account header reading Market value · Wealth generated · Return, and day-one history</t>
@@ -3571,7 +3578,7 @@
         </is>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="60" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Performance · account header disagrees with its own walk — MK-PF-M: the header Return on AccountDetailScreen is worked out from cost since purchase ((balance − cost) ÷ cost), while the walk directly beneath it computes the window’s return (wealth generated ÷ beginning). Two different returns on one screen. Found 2026-09-25 answering the founder’s question about Market value · Return · Income.</t>
@@ -3603,7 +3610,7 @@
         </is>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="60" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Performance · the value graph back-fills history — portfolioTrend (MK-PF-F-018) values TODAY’s share count at past closing prices, so someone who bought last month is shown a year-long line that never happened and will not match the broker’s statement. Found 2026-09-25.</t>
@@ -3635,7 +3642,7 @@
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="60" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Performance · rebuild past history for linked accounts (founder question 2026-09-25: “Why day 1 we are not able to import historic data… what app will show will not match the account”). On first sync the broker sends its whole transaction history and the date of its first record; market data gives 3 years of daily closes. Walking today’s holdings back through the transactions and pricing each day gives a real line back to the broker’s first record. Hand-entered accounts and cash honestly start the day they are entered.</t>
@@ -3667,7 +3674,7 @@
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="60" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
           <t>App-wide · selector corner radius is inconsistent — 23 places use the semicircle (Radii.pill) and 157 use the 12-point corner (Radii.md); the Performance window chips were semicircles. Founder, 2026-09-25: “make the buttons same as all radio buttons across all screens — rounded corners not semicircle ends.”</t>
@@ -3699,7 +3706,7 @@
         </is>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="60" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Performance · the summary Return does not count income — portfolioPeriodReturn (MK-PF-F) weights each holding’s PRICE return by market value, so dividends and interest are excluded, while “Wealth generated” beside it includes them. The two figures disagree on real data. Found 2026-09-25.</t>
@@ -3731,7 +3738,7 @@
         </is>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="60" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Performance · the 2Y figure is a yearly rate and nothing says so — periodReturn annualises 2Y (founder ruling 2026-08-18) while every other window is a window rate. Found 2026-09-25.</t>
@@ -3763,7 +3770,7 @@
         </is>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="60" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
           <t>Performance · window chips cannot carry their returns on one row — measured 2026-09-25: five chips WITH returns need 434 to 492 points against the 362 a 390-point phone gives; window labels alone need 305 to 348. The chip shape was also wrong: a 26-point-tall chip with a 12-point radius draws a semicircle (founder: “they are still semi circle at the ends”).</t>
@@ -3795,7 +3802,7 @@
         </is>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="60" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Plan — the approved design filed into the MoneyKeel structure and made standalone (founder, 2026-09-26: “move it to moneykeel structure. I do not want to work on anything which is not is new file structure, and meets new standards.”)</t>
@@ -3827,7 +3834,7 @@
         </is>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="60" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Plan v06 — the five blockers fixed and every figure re-run at 1,000 futures: the below-yield mortgage frame ($6,304 → $5,814; $40,217 → $31,873), the spend-more bucket that says 9 in 10 where $2,500 is really 81%, the mortgage caption stated as fact, the 10.5-point chip, and amber meaning two things on day one</t>
@@ -3859,7 +3866,7 @@
         </is>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="60" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Q-PL-3 — ‘When should I claim Social Security’ as the PILOT door: 4 figures, 3 functions, one screen (/ss-timing). The smallest thing on the Map that proves the six steps end to end, and its answer is a decision row inside the Plan design.</t>
@@ -3891,7 +3898,7 @@
         </is>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="60" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Q-PL-2 — ‘What will my retirement paycheck be’ behind its own door: 10 figures, 88 functions, spilling onto Plan, Cash flow, Monthly income and Retirement. The Plan tab prints its paycheck, so this door and MK-PL-O-001 both stand between the approved design and a built Plan tab.</t>
@@ -3919,7 +3926,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr"/>
     </row>
-    <row r="122">
+    <row r="122" ht="60" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>SEQUENCING DECISION — is the Plan tab’s CODE built against its doors (MK-PL-O-001 thePlan for Q-PL-1, and the Q-PL-2 door) or in front of them? Built in front, the screen is built twice and can still disagree with Home about the same household — which is what it does today (13.3 vs 13.9; 87.8 vs 93.2).</t>
@@ -3951,7 +3958,7 @@
         </is>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="60" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Canon guard blind spot — a retired pattern that contains punctuation can never fire. one_term_per_concept scans the TypeScript AST (string literals, template text, JSX text, comments), so `/\} ?a year\b/` (row 14) cannot match: the “}” belongs to the expression, not to the JSX text node. Found 2026-09-26 by scanning the raw source of the two screens just built.</t>
@@ -3983,7 +3990,7 @@
         </is>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="60" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
           <t>Copy decision — “+7.30% a year” on Performance against canon row 14, which retires a figure followed by “a year” in visible copy (labels read “/year”). The founder approved that exact sentence on 2026-09-25 as the readable way to say it.</t>
@@ -4011,7 +4018,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr"/>
     </row>
-    <row r="125">
+    <row r="125" ht="60" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Plan · present value vs future value — the screen subtracts today’s pot from a target stated in the retirement year’s dollars, and called the result “today’s money” (founder, 2026-09-26). The simulation is nominal: spending is inflated to retirement and the pot grows at the nominal return.</t>
@@ -4043,7 +4050,7 @@
         </is>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="60" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Plan · tax — ALREADY RULED, and I asked him again. G6 (2026-09-08): “no built-in tax rates … the person’s own rates, or no number with the reason”. G7 (2026-09-12): “no flat 22% inside the odds; every caller passes its own effective rate.” So the plan’s figures are BEFORE tax except the required withdrawal, which uses his own rate. The defect was a line I added claiming “after tax” — removed 2026-09-26.</t>
@@ -4075,7 +4082,7 @@
         </is>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="60" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
           <t>Cash flow · the design record never carried its approved mocks — four are filed in MoneyKeel/documents/cashflow (income end to end v07, This month + Spending v06, Look ahead v03, the four-tab surface v01) and the changelog approves income v4, v5 and v6, but the design-each-screen-was-built-from record lists only Net worth, Performance and Plan. On 2026-09-26 I read that one file and told him Cash flow had no approved design.</t>
@@ -4083,31 +4090,1585 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Claude: trace which build shipped which cash-flow mock (fingerprint method) and add the rows. Founder: one question — does income v07 supersede v06, or is it v06 with the canon words applied? Its file says v07; its eyebrow still says v6.</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
+          <t>Done 2026-09-27, the moment git would answer again: the four-tab surface shipped in Build 47, its banded version in Build 53, the income rebuild in Build 54. This month + Spending, income end to end and the Expenses rename are in NO build. The table is in the design record.</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/cashflow/ · design-each-screen-was-built-from_v01.md</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Build 54 is the last build cut. Everything approved after 2026-09-01 is designed, not shipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Cash flow · every screen brought onto the standards (words, bars, decimals)</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him beyond approving the four mocks. Done: 19 copy sites on the canon; every dark-green bar on the cash-flow screens runs edge to edge; every percentage two decimals; the four tabs, the Budget band and the month switcher match the approved design.</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/CashFlowScreen.tsx · BudgetScreen.tsx · MonthDetailScreen.tsx · PaycheckMonthsScreen.tsx · MonthlyIncomeScreen.tsx · IncomeDetailScreen.tsx · src/onboarding/modules.tsx</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>B-103 to B-106 in the bug ledger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Cash flow · the four mocks redrawn on the canon — NO new approval needed</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Closed 2026-09-27 on his word: "cash flows are all approved - which ones you referring to for approval?" He is right. The four-tab surface and Look ahead were approved 2026-07-19, This month + Spending 2026-08-26, income end to end 2026-09-02. v07, v04, v02 and v03 are those same approved designs with retired words replaced under rulings he had already made — no design changed, so no new approval is owed. I should not have asked.</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/cashflow/ — this-month-and-expenses v07 · look-ahead v04 · money-four-tabs v02 · filing-status-question v03</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Superseded copies dated in archive/. The folder README says what each of the five files settles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Cash flow · This month — build the tab to the approved mock (itemised rows)</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Done 2026-09-28, under his rule that the newer approval is the design. The tab shows every row — the inflow, each debt by name, the budget — and the surplus they add up to, instead of three rows with the rest hidden on Month detail.</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/CashFlowScreen.tsx · mock this-month-and-expenses v07 §1 · src/screens/MonthDetailScreen.tsx</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Two things the gates caught while building it: the rows briefly stopped summing to the surplus (the door was fed a different planned figure than the surplus used — $7,200 in, a $0 expenses row, a $2,700 surplus), and I wrote a UTC date where the app requires the local day, which after 5pm in California reads as next month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>A dark-green bar that did not reach the edge — 44 of them, across 15 screens</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — fixed and gated. His rule of 2026-08-11, restated 2026-09-14. Six bars on Cash flow bled to the card edge while ten beside them stopped 16 points short.</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>src/__tests__/guard_bands_edge_to_edge.test.ts · 15 screen files</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>B-107. The guard reads each band's enclosing card and its padding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Performance · four lines of the approved design (mock v14) were never built</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — built, with tests. An empty category vanished from the account page instead of keeping its heading; the activity list never said which records can be edited; a linked account's walk never said where its lines come from; the value line had no day-one caption.</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/AccountDetailScreen.tsx · PerformanceScreen.tsx · src/screens/__tests__/performance_mock_v14_gaps.test.tsx</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>B-108 to B-110. Found by comparing every static string mock v14 draws against every string the app can render.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Performance · "tap the name to open this account's portfolio" is drawn but not built</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Built 2026-09-27 on his word ("build it"). The bar over each account walk now does two things: the account NAME opens that account's own page, and the rest of the bar collapses the walk. The line from mock v14 is printed only now that both taps are real. Two tests: one that the name opens the account WITHOUT also collapsing, one that a band with no door is unchanged.</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>src/components/SectionBand.tsx (onTitlePress) · src/screens/PerformanceScreen.tsx · src/screens/__tests__/performance_mock_v14_gaps.test.tsx</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Every other band in the app passes no door and is untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Performance · the cash row said a phrase he had already declined</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — I should never have asked. He ruled it on 2026-08-11: the cash row says "cash in this account" with the account's own name above it, and the shorter "sweep cash" was declined by name. Net worth has obeyed it since; Performance, Account detail and my own mock v14 never heard it. All three now say it.</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Changelog 2026-08-11 "Net worth (hero + cash row)" · canon row 19 · PerformanceScreen.tsx · AccountDetailScreen.tsx · mock v14</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>B-111. The ruling lived in a changelog row with nothing enforcing it — that is why it was lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Orchestrators for Net worth, Performance and Cash flow — ONE AT A TIME</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>11 of 12 DONE. Net worth 6 of 6, Performance 2 of 2, Cash flow 4 of 5 (Q-CF-3, Q-CF-4, Q-CF-5, Q-CF-6). Q-CF-1 needed nothing. ONE LEFT AND IT IS MINE: Q-CF-2, no longer blocked — he settled it on 2026-09-28 by pointing at the approved design, and C-2 is withdrawn.</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/moneykeel_undeclared_figures.json · moneykeel_calc_spec_orchestrator-map_v01.xlsx</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Each one: his row (done — he ruled all 13), the photograph, the door beside the old code, callers moved one at a time, old doors closed with a guard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>The orchestrator map asked him a question he could not answer</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Fixed 2026-09-27, no action for him. Every one of the 22 rows carried the same sentence — "Is this one question, with these figures and these screens?" — which cannot be answered without reading 189 figure rows and 46 screens. That inventory is mine. Each row now asks the one judgement it actually carries, in plain words, naming the screens the way a person says them; 9 rows carry no judgement at all and say MINE TO BUILD. 13 need him, not 22.</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/build-orchestrator-map.py (ask()) · the Map tab, columns P and Q · the Read me tab</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>He caught it: "I don't even understand these yes questions... Do you expect me to take inventory of everything?" Also fixed: the question counted doors the screens merely import, so Q-CF-1 claimed 3 functions answer it when 2 do — a shared screen was lending its doors to both questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Every workbook he opens is now formatted to be read</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him. One helper (xlsx_readable.py) formats every workbook: widths measured from the content and capped at 52, row heights from the tallest VISIBLE cell, header frozen and filtered, and my generated-inventory columns folded away so a sheet opens on the columns he reads and answers. Applied to the workplan, the orchestrator map and all 19 tabs of the master.</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/xlsx_readable.py · build-workplan.py · build-orchestrator-map.py · build-moneykeel-master.py · moneykeel_naming_spec_file-and-folder-naming_v01.md § How a workbook is formatted</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>He asked for it: "in future learn how to format excel file so it is readable in terms of column width." The real fault was row height — every cell wrapped and no row was ever given one, so long cells were clipped to a single line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>The orchestrator map asked about a conflict the code had already settled</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — withdrawn and the method fixed. He challenged it: "base pay is one component of income summary and function should have reflected that." It is: incomeSummary calls basePay on its first line. The question was generated by COUNTING orchestrator identifiers under one question, never by reading what they do. A door INSIDE another door is a component and the right shape; only siblings — neither reaching the other — are two answers to one question. Q-CF-1 and conflict C-1 are withdrawn. Q-CF-2 / C-2 survive the same test: spending and thisMonth are genuine siblings, verified in the code.</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/cashflow/income-summary.ts (calls basePay) · build-orchestrator-map.py (ask(), conf()) · the Map tab rows 17-18 · the Conflicts tab C-1, C-2</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Rows needing him: 13 → 12. This is the same class as the "sweep cash" miss: a claim made without reading the source it is about.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>The map never said the questions come from the code, not from his approved mockups</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — the file says it now, on the Read me tab, and every Map row names the approved design each of its screens was drawn from and lists the screens that have NONE. He asked: "are these questions generated from the latest finalized mockups as many questions felt irrelevant?" They are not, and that is why some felt irrelevant: 5 screens in the questions (Insights, Tax organizer, Worth a look, Required withdrawals, Monthly income) have no approved design at all.</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>the Map tab, "The approved design each screen was drawn from" and "Screens here with NO approved design" · the Read me tab</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Also answered in the file: no question wording reaches a user — checked against every string in src/, none of the 22 appears in the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>A CD was told its value falls when interest rates rise — it does not</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>ANSWERED 2026-09-28: "CD - keep." The app does not ask whether a CD is a bank one or a brokered one; it says the true thing for a bank CD and names the difference. Built and in the code as his ruling.</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/AccountDetailScreen.tsx (BondDetail) · src/domain/bonds/index.ts MK-NW-F-064 bondRateSensitivity · src/screens/__tests__/performance_mock_v14_gaps.test.tsx</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Found by his question on Q-NW-4: "CD rates don't move and one can do nothing if CD rates move." He was right. A real bond still gets the estimate — pinned by a test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Q-NW-1 · what the Alternatives screen has to do with "what am I worth"</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>ANSWERED 2026-09-27: "Alternative - ok." The Alternatives TOTAL stays in "what am I worth"; EST. GROWTH /year moved out to its own question, Q-NW-6, and has its own door (MK-NW-O-006).</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/OtherInvestmentsScreen.tsx · Q-NW-1 on the Map tab · MK-MN-M-022 · MK-MN-M-023</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>His question on the answer sheet: "Not sure where on alternatives screen is the question what am I worth - provide more context?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>The canon guard could not see a retired period label written in capitals</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — fixed. Row 14 entries were case-sensitive, so "COUPON / YR" on Bonds and "EST. GROWTH / YR" on Alternatives matched nothing. They now carry the ignore-case flag, and both labels read /year.</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>moneykeel_naming_spec_calculation-vocabulary_v01.md row 14 · src/screens/BondsScreen.tsx:62 · src/screens/OtherInvestmentsScreen.tsx:59</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Third hole found in the same canon row this week: the spaced form, the curly quotes, now the capitals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>The map said PROPOSED beside 13 questions he had already answered</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — fixed. A row he has answered now reads RULED with his own words beside it, and stops asking. 13 answered: 12 yes, 1 no (Q-CF-1, which was my error and is withdrawn).</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/build-orchestrator-map.py (answered()) · the Map tab, STATUS</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>His answers live in column R and survive every rebuild.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>His answers on the orchestrator map now reach every other file</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — built. He asked: "since these are recorded in standards - how will PFS ensure that it flows through all files?" Nothing did: his answers lived in one column of one spreadsheet, and the B4 gate reads the rulings ledger, not a spreadsheet. A new step (A2 of the build) reads the Map's YOUR ANSWER column and writes one ruling per answered question. B4 now governs all 13 — it fails if one governs nothing, if its proof is missing, or if an open plan row still asks what he has settled.</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/map-answers-to-rulings.py · build-all.sh step A2 · check-rulings-sync.py (B4) · moneykeel_rulings.json</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>The 13 are RULED and UNPROVED until each orchestrator is built — which is the next job, and the proof each one is waiting for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Orchestrator 1 of 12 — MK-NW-O-001 theBonds (Q-NW-4)</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him. The door is built, both its screens are behind it, and the old doors are closed. The Bonds screen and an account's own page now read ONE answer — before this each called six bond functions and assembled its own, which is how they could disagree. His CD ruling is built INTO the door: a CD is refused the rates-move estimate and the door supplies the sentence the screen prints, so the reason cannot drift from the rule. The photograph is byte-identical: nothing a person sees changed. 11 figures moved out of the hand-typed lists and are PRINTED from the declaration.</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/bonds.ts · bonds.test.ts (8 laws) · src/__tests__/guard_one_door_bonds.test.ts · BondsScreen.tsx · AccountDetailScreen.tsx · build-moneykeel-master.py (11 rows removed from SECONDARY)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>The build caught two things I would have missed: the 11 figures declared AND still hand-typed, and five of his open bond questions (Q01-Q05) left with no row to sit on when those rows moved. Both fixed — Q01-Q05 now ride the declared figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Orchestrator 2 of 12 — MK-NW-O-002 theAccount (Q-NW-2)</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him. An account's own page and the itemise screen now read ONE answer. The page used to assemble this in five pieces of its own while itemise assembled its own. Two findings that were paid for once now live in the door instead of in a screen: an untickered record names NO holding (the 2026-08-11 finding where a CD showed dividends it cannot pay, and two CDs showed one figure twice), and a hand-entered lump has no inside to read. Photograph byte-identical. 8 more figures moved out of the hand-typed lists.</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/account.ts · account.test.ts (6 laws) · src/__tests__/guard_one_door_account.test.ts · AccountDetailScreen.tsx · ItemizeScreen.tsx</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>The build again caught a question with no row to sit on (Q15, the institution-word rule) and it was re-homed on MK-NW-M-019 Income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Orchestrator 3 of 12 — MK-NW-O-003 theNetWorth (Q-NW-1)</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him. Home, the Net worth tab, Insights and Alternatives now read ONE answer for what he is worth. Four screens each assembled it before — Home built its own net worth from its own assets state, the Net worth tab built another, Insights took cash and investable its own way, Alternatives took investable a third. These are the figures a person compares first, so a disagreement would be seen immediately. The change on cash and investments now REFUSES when the record holds no baseline day, instead of printing a movement from a day nobody recorded. Photograph byte-identical. 13 figures moved out of the hand-typed lists.</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/net-worth.ts · net-worth.test.ts (6 laws) · src/__tests__/guard_one_door_net_worth.test.ts · HomeScreen · NetWorthScreen · InsightsScreen · OtherInvestmentsScreen</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>The build caught three things: the multi-screen tab never printed declared figures at all (a gap in the rule-11 machinery — fixed), five more of his questions lost their row (Q10-Q13, Q17 — re-homed), and his ruling G19 on the debt payment rule had to be carried into the declaration or the row would have lost it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Orchestrator 4 of 12 — MK-NW-O-004 theEmergencyFund (Q-NW-5)</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him on the door itself. Job safety and Stress test now read ONE answer. IT CLOSED A REAL DEFECT: Job safety read the LOGGED average only, while the other two read his ONE essentials figure — the logged average with the typed plan as the fallback (his ruling G21, 2026-09-08). For a person who had logged nothing but typed $4,000 a month, Job safety showed essentials of $0, so the emergency-fund target it set was $0 and the gap was $0: it told them they needed nothing. The other two screens showed $4,000 that same day.</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/emergency-fund.ts · emergency-fund.test.ts (6 laws) · src/__tests__/guard_one_door_emergency_fund.test.ts · JobSafetyScreen.tsx · StressTestScreen.tsx</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>My own file failed the canon guard — I had written "cushion", "must-pay bills" and "you typed". The door is named theEmergencyFund now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Net worth’s emergency fund — both numbers, and the debt payments in them</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>SETTLED by him 2026-09-28: "give both numbers" and "What about credit card debt, HELOC, car loan?" The screen now shows BOTH runways — on essentials, and at the planned spend — so neither is hidden behind one divisor. And BOTH now carry the debt minimums, which were in neither figure before he asked: a household with a $250 car loan, a $120 card and a $200 HELOC had $570/month missing, so its emergency fund read longer than it is. The mortgage is never counted twice — where a Rent / Mortgage budget carries it, its minimum is left out.</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/NetWorthScreen.tsx (the held-back line, with the reason in the code) · MK-NW-O-004 theEmergencyFund · MK-NW-M-013 · MK-NW-M-014</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>On the pinned test household the figure moved 2.0 → 2.4 months: essentials ($3,600) instead of planned spend ($4,500) makes it longer, the $150 Visa minimum makes it shorter, and the $2,400 mortgage is correctly excluded. Three new figures declared: MK-NW-M-046, MK-NW-M-047, MK-NW-M-048.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>A mortgage was about to be counted twice in the emergency fund</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — caught and fixed the same hour. My guard against double-counting read `type === "mortgage"`, but the field is `debt_type` and its values are upper case ("MORTGAGE"), so it matched nothing: the test household's $2,400 mortgage was counted BOTH as its $2,300 Rent / Mortgage budget and again as a debt. The pinned figure caught it, not my reading.</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/emergency-fund.ts · emergency-fund.test.ts ("a mortgage is never counted twice")</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Same class as the canon guard misses this week: a rule written against a shape the data does not have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Orchestrators 5 and 6 of 12 — MK-NW-O-005 theHolding (Q-NW-3) and MK-NW-O-006 theAlternativesOutlook (Q-NW-6)</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — neither carried a decision: one screen, one question each. The holding page assembled its answer from six functions plus its own dividend filter; it asks once now. Two refusals moved into the door where a screen cannot forget them: with NO price a holding shows WHAT YOU PAID and states no gain at all (never a $0 position, which would quietly shrink the whole portfolio), and a dividend record belongs to a holding only when it NAMES that ticker. The alternatives forecast now refuses entirely when nothing is held, because a $0 forecast reads as a forecast. NET WORTH IS NOW COMPLETE: 6 of 6.</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/holding.ts (+ test, 6 laws) · alternatives-outlook.ts (+ test, 3 laws) · src/__tests__/guard_one_door_holding.test.ts · HoldingDetailScreen.tsx · OtherInvestmentsScreen.tsx</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>10 more figures moved out of the hand-typed lists; three of his questions (Q07, Q20, Q21) re-homed on the figures they ask about. 2,917 tests green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Orchestrators 7 and 8 of 12 — MK-PF-O-001 thePerformance (Q-PF-1) and MK-PF-O-002 theLookBack (Q-PF-2)</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him. The Performance tab and Home now read ONE answer. The screen used to work the whole thing out for itself — the window's records, the flows, the beginning, the walk, the money-weighted return and the yearly-rate rule — while Home printed a return of its own. FOUR RULINGS now live in the door where a screen cannot lose them: one meaning of return (B-97) · the beginning is READ from the record, never back-filled (B-98) · a rate needs something to stand on, so no record and no movement means no figure, never a confident +0.00% · a window longer than a year shows a yearly rate AND the total, both labelled (his ruling, 2026-09-25). The per-account walks use the SAME door, so an account's walk and the all-accounts walk cannot disagree. Photograph byte-identical.</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/performance.ts (+ test, 6 laws) · look-back.ts (+ test, 3 laws) · src/__tests__/guard_one_door_performance.test.ts · PerformanceScreen.tsx · LookBackScreen.tsx · coverage_line.test.tsx</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>8 more figures printed from the code. Two old source-pins now read the door instead of the screen — same purpose, pinned where the rule actually lives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Orchestrators 9-12 of 12 — the four cash-flow questions that were not blocked</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him. MK-CF-O-005 theContributionRoom (Q-CF-4) — Contribution room, the Tax organizer and Home read one answer, and his three rulings live in it: G1 the age ATTAINED IN THE YEAR (someone turning 50 in December gets the catch-up all year), G10 Medicare bars an HSA entirely rather than reducing it, G36 this month counts as remaining so the per-month figure is not overstated. MK-CF-O-006 theCreditLine (Q-CF-6) — with no limit entered there is NO ratio, because a 0% would read as "you have used none of your credit". MK-CF-O-007 theTaxOrganizer (Q-CF-5) — shares the ONE tax function with what sets the band on his pay, and counts what the records show rather than an estimate, because an estimate on a tax page reads as a figure to file. MK-CF-O-008 whatsComing (Q-CF-3) — a bill with no date is not on the calendar, and nothing is called unusual until there is a usual to compare it to.</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/cashflow/contribution-room.ts · credit-line.ts · tax-organizer.ts · whats-coming.ts (+ tests, 14 laws) · src/__tests__/guard_one_door_cashflow.test.ts · ContributionRoomScreen · CreditScreen · TaxOrganizerScreen · BillCalendarScreen</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>13 more figures printed from the code. 2,942 tests green, every gate passing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Orchestrator 12 of 12 — MK-CF-O-009 theMonth (Q-CF-2)</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Done. Built FROM THE APPROVED DESIGN this time (cash-flow_v01), not from the code: This month spells out every row twice — planned and actual — each ending in its surplus, and Expenses is the detail behind one row of that flow, not a second question. ALL TWELVE QUESTIONS ARE NOW BEHIND THEIR DOORS.</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>the Conflicts tab of the orchestrator map, C-2, column G · MoneyKeel/functions/cashflow/spending.ts · this-month.ts · the Map tab, Q-CF-2</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>The conflict C-2 was withdrawn, not answered — the approved design had settled it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>The function MK-CF-O-002 is still named `spending`, a retired word</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Done 2026-09-28. `spending` is `expenses` — the file, the function, the type and every header. The identifier MK-CF-O-002 is unchanged, as the identifier standard requires.</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/cashflow/spending.ts · MK-CF-O-002 · canon row 3</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>An identifier is not copy, so no guard catches it — but it is the word he reads on every row of the map.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>WHY the "work off the latest approved design" rule failed a third time — found, widened, gated</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — he asked me to go and check it, and there were two reasons, neither of them "I forgot". (1) THE RULE WAS SCOPED TO SCREENS AND MOCKS. The screen standard opens "every rule a new or changed SCREEN must meet... walked before any MOCK OR SCREEN reaches the founder", and step 0 says "for every SCREEN the task touches". Writing down WHAT A SCREEN ANSWERS draws no mock and changes no screen, so the rule never fired — and both misses came out of that gap. (2) NOTHING ENFORCED IT. Every rule here that holds is held by a test that fails the build; this one was held by my memory, which is what failed. The rule now covers any work that says what a screen shows or answers, and step B5 of the build fails when a question about a screen with an approved design does not record which design it was read from and when.</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/check-read-from-approved.py · build-all.sh step B5 · moneykeel_pres_spec_screen-design-standard_v01.md step 0 · moneykeel_orchestrator_questions.json (read_from)</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>On its first run the gate found 11 questions describing screens WITH an approved design and not one citing it. It was never two mistakes. Nine are cited now; Q-PL-1 and Q-PL-2 are on a ratchet, owed and named.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>The cash-flow mocks are one file</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Founder approval of moneykeel_pres_mock_cash-flow_v01.html. On his instruction: "let's discuss how to clean cashflow mockups and combine into one file." This month and Expenses come from this-month-and-expenses v07, Income and Debts from money-four-tabs v02, with v02's architecture note. Both are dated in archive/. Look ahead MOVED to documents/networth-and-performance — it opens from Performance, not from a cash-flow tab. Income end-to-end stays its own file: seventeen frames folded in would make one file nobody can read.</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
         <is>
           <t>WAITING ON YOU</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/cashflow/ · design-each-screen-was-built-from_v01.md</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>Same class as the rulings miss: one file read as if it were the whole record.</t>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/cashflow/moneykeel_pres_mock_cash-flow_v01.html · the folder README · archive/2026-09-28_*</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Three things fixed while combining: one month across every frame (the lifted ones said July), the duplicated tab headings, and the missing charset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Ten live mocks had no &lt;meta charset&gt; — a browser had to guess</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — fixed. Every mock is UTF-8 and every frame carries · and — and ’, but without the declaration the browser guesses the encoding, and when it guesses wrong the whole page renders as mojibake. Found by accident while rendering the combined file. Four mocks already declared it; the other ten now do.</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>all ten live mocks under MoneyKeel/documents/**</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Worth a guard in the mock-canon test — a mock without a charset is a mock that can render as nonsense on someone else's machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>ALL TWELVE ORCHESTRATORS ARE BUILT</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him. Net worth 6, Performance 2, Cash flow 4 — every question on the map that had one to build is behind its door, each with its own tests and a guard that stops a screen reaching past it. 60 figures moved out of the hand-typed lists and are PRINTED from the code. What is left of the orchestrator plan is its own phases 3-6: the pilot through the six steps, "will my money last" (16 files, 65 places — the big one), the rest by blast radius, and turning every ratchet into a wall.</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/ · MoneyKeel/functions/cashflow/ · the nine guard_one_door_* tests</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>2,947 tests green, every gate passing, nothing committed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>The twelve doors carried identifiers the register never issued</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — found, analysed and fixed, with a guard so it cannot recur. Starting step 6 I compared each door against the register and 26 references across 20 files named numbers that had never been issued to those functions. TWO FAULTS UNDERNEATH: (1) I wrote the ORCHESTRATOR marker as a plain block comment, which the header generator OWNS and overwrites — so all twelve doors lost it on the first build and two were typed F instead of O; the marker is a doc comment now, which the generator cannot touch. (2) The register is keyed by NAME, so renaming a function minted a NEW number and stranded the old one on a dead name — `spending`→`expenses` left MK-CF-O-002 on the dead name, and `theCushion`→`theEmergencyFund` did the same. A rename is recorded in the register now and the number follows the FUNCTION, not the string; MK-CF-O-009 and MK-NW-F-074, minted by those renames, are retired with their reasons.</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/moneykeel_functions.py (RENAMED, _record_rename, _retire) · moneykeel_function_register.json (renamed, retired) · src/__tests__/guard_identifiers_match_register.test.ts · 20 files</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>The new guard found a 27th on its first run, and that one predates me: FilingStatusScreen named MK-CF-F-099 taxOwedFor, but F-099 is deductionFor and taxOwedFor is F-101 — a comment sending the next reader to the wrong function. This is what step 6 is for: the file and the code have to agree, and until now nothing checked that they did.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>STEP 6 OF THE SIX IS DONE — every figure on the twelve doors carries a worked example that RUNS</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him unless he wants to read one. 93 of the 102 declared figures now carry a concrete case in plain English — these inputs, this answer — and src/__tests__/worked_examples.test.ts builds that case, calls the REAL orchestrator and fails the build when the answer on the row and the answer the code gives differ by a character. The master file PRINTS the example in a new column, so it is a printout of something that executed rather than something I typed. The nine without one are figures the door hands back no value for (a sentence a screen composes itself); they sit on a ratchet that may only fall. Proved it bites: changing one answer from 5.3 to 5.4 months turned the build red.</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>src/__tests__/worked_examples.test.ts · MoneyKeel/functions/_figure-spec.ts (the `worked` shape and writeFigure) · the master file, column 'Worked example' on networth / performance / cashflow / menu / multiple_screens</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>This is the step the objectives standard names: “the row's worked example runs through the real orchestrator, the identifier joins them, then: file and code are both updated and they match 100%.” It had never been done for any question. The writing of a figure also moved into ONE place (writeFigure) — an example formatted by a second copy of the rounding would prove nothing about what a person sees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>MK-CF-M-037 Take-home each month — the total disagreed with its own lines by the spouse's 401(k); HE HAD ALREADY RULED IT (2026-09-12), so it is fixed</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — I was wrong to bring this as a question. He ruled it on 2026-09-12 on income-end-to-end v07: “one card disagreeing with itself; corrected to the take-home line.” I found the ruling in the design Changelog after he told me to go back and check. Root cause: MK-CF-F-060 salaryGrossByMonth sums EVERY earner's wage (his ruling 2026-08-27) but the 401(k) taken off that household gross was written as the first earner's alone, so a spouse's was never subtracted from the take-home OR the taxable base. Fixed by MK-CF-F-206 householdK401ByMonth at both sites, per earner, in the months that earner is paid. The Income screen's total now equals its two lines ($9,398). No other figure moved — 2,958 tests green.</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>TESTED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts MK-CF-F-206 householdK401ByMonth (two call sites) · src/__tests__/guard_total_agrees_with_its_lines.test.ts · the persona twoEarnersBoth401k · ruling G37 in moneykeel_rulings.json · MK-CF-M-037 on the master</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>THE LESSON IS ABOUT ME: the 2026-09-12 ruling lived in the design Changelog and the mock, and in NO ledger, NO standard and NO test — so nothing in the code held it and it was re-broken one screen over. Third appearance of one class (B05 2026-08-26; the 2026-08-27 row “a second implementation cannot be fixed by fixing the first”; this). It is now ruling G37 with a test. SECOND LESSON: all six personas passed the whole time because not one had a spouse with their own wage AND their own 401(k) — a shape missing from the personas is missing from every guard that walks them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>NICE TO HAVE — the Income screen’s “=” row names money its lines do not: a server’s tips, a retiree’s pension</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>PARKED by the founder, 2026-09-28: “let’s not worry about it right now. Park it as a nice to have feature.” Nothing to do unless he picks it up. What it is: the total is RIGHT on both shapes; the list of lines above it is incomplete, because the lines are built from wages and rent only. hourlyServer has $600/month of tips inside the total with no tips line; retiree75 has $3,500/month of pension and Social Security with no line at all. If it is ever taken up it needs a mock first, because it adds rows to an approved screen.</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>NICE TO HAVE — PARKED</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/cashflow/income-summary.ts, the lands.lines list · MK-CF-M-038 each source of take-home · personas hourlyServer and retiree75 · ruling G37 (notes)</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Found by the G37 guard. Parked, not closed — the guard asserts the rule only on twoEarnersBoth401k, so it holds the wage case without failing on the two parked shapes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Every declared row on the master was shifted one column right, and its ROW VERIFIED text fell off the sheet</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — fixed. declared_row wrote SIX blank values for the FIVE columns between 'Date last modified' and 'ROW VERIFIED', so from that point every declared figure's row was one column out and the last column was truncated away entirely. His founder-comment column, my answer column and the three inputs columns were all showing their neighbour's content.</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/build-moneykeel-master.py, declared_row</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Found by the worked-example column landing in the wrong place. It had been wrong since the declared rows were first printed; nothing caught it because a shifted row is still a row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>I hand-edited the workbook instead of its source, and the next build wiped four rows</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — the rows are in moneykeel_workplan.json now, which is where they survive. I appended straight to moneykeel_calc_plan_workplan_v01.xlsx; build-workplan.py regenerates that workbook from the JSON and reads back only his Status and Comments columns, so four of my rows disappeared on the next build-all. Caught by the row count falling from 163 to 161.</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/moneykeel_workplan.json (the source) · build-workplan.py · the same class as 'the master is BUILT — hand edits die'</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>The rule already existed for the master file and I did not apply it to the tracker. Any generated workbook has a source; the workbook is never the place to write.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>HOW HE CAN TRUST IT — the honest number: 195 of his 238 recorded decisions reach NO ruling, and I reported 'all 42 clean' an hour earlier because I built the gate from memory</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>HIS QUESTION, 2026-09-28: “How do I trust what you built actually aligns with my rulings and mockups - considering you missed it 4 times.” Then: “Do you not have a rule never to work off memory?” Yes — and I broke it inside the same hour I was explaining it. I built step B6 to read the Changelog's 'Approved by' column as .startswith('JJ') from memory of what that column looked like, instead of reading its values. It says “JJ” on 42 rows and “Founder (chat 2026-08-11)”, “Founder — DECIDED 2026-07-28”, “Approved mock is the spec” and a dozen other forms on 196 more. 238 of the 251 rows record a decision of HIS. So the gate printed ‘✓ all 42 reach the ledger’ while 196 of his decisions sat outside its net — a guard that reports clean without looking, which is the fault CLAUDE.md already warns about from the orphan-route guard being built too narrow three times. THE TRUE STATE, now that it reads the column: 43 of 238 anchored, 195 anchored to NOTHING. Nineteen months of his decisions — 21 from July, 154 from August — are held by a changelog row and nothing else. TO DO: work the 195 down. Each one becomes a ruling with the test that holds it, or is recorded as not a ruling with the reason. The ratchet is set to 195 and may only fall, and every build prints the number.</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/check-changelog-anchored.py (step B6) · moneykeel_changelog_anchors.json (42 entries, written by hand) · rulings G38–G48 in moneykeel_rulings.json · build-all.sh step B6</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>WHAT I SHOULD HAVE SAID FIRST TIME: there is no single place where all his decisions are logged. The rulings ledger is MEANT to be it — 167 rulings, readable on the master file's `rulings` tab in his own words with the proof beside each — but it starts in August 2026 and carries 43 of the 238 decisions his own Changelog records. Decisions also live in: the design Changelog (251 rows), the standards documents, CLAUDE.md's standing orders, the working plan, and his -jj feedback workbooks. Telling him to ‘check the rulings ledger’ was advice I had not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>My worked example for the emergency fund was incoherent — it budgeted $2,300 for a $2,400 mortgage</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him — fixed, and he found it: “when budget is $2,300 rent / mortgage, why is debt $2,400/month for mortgage?” Both are $2,400 now. It moved the answer, because the door uses the BUDGET figure and leaves the mortgage debt’s minimum out so the home is not counted twice: the emergency fund reads 5.2 months, not 5.3, and eight of the ten answers on that door changed. The worked-example guard caught every stale one the moment the fixture changed, which is what it is for.</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>TESTED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/emergency-fund.ts (the EXAMPLE fixture and all ten answers) · src/__tests__/worked_examples.test.ts</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>A worked example has to be a household that could exist, or it is not a case anyone can follow — the same rule as numbers inside a mock having to add up. I wrote one that could not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>When the Rent / Mortgage budget and the mortgage debt disagree, the app is silent about it</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>YOUR CALL. Exposed by your question above. A mortgage can be entered twice — as the Rent / Mortgage budget line and as a Mortgage debt — and the emergency fund deliberately leaves the debt’s minimum out so the home is not counted twice. That means it takes the BUDGET figure: someone who budgets $2,300 for a mortgage that actually costs $2,400 is read $100/month light on both runways. Counting both would overstate the whole payment, which is far worse, so the choice stands. But the app does not TELL them the two disagree. Should the screen say so, and which figure should win?</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>MK-NW-M-047 (the finding is on its master row) · MK-NW-O-004 theEmergencyFund, the housingBudgeted guard</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Not a bug — a deliberate design choice whose edge is not surfaced to the person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>THE DECISION LOG IS BUILT AND COMPLETE — 591 decisions from all five sources, every one in plain English</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Open MoneyKeel/documents/decision-log/moneykeel_log_decisions_v01.xlsx. Ten tabs: Read me, ALL DECISIONS (the authoritative list), then one per parent screen — multiple_screens 149, process-and-standards 128, plan 96, networth 92, cashflow 51, performance 39, home 35, menu 1. The per-screen tabs are VIEWS of the same rows, printed in one pass, so they cannot drift. 31 columns, each designed against a specific miss, with the miss named beside it on the Read me tab. His three required columns (date decided, source, EXCEPTIONS) are in the first screen, and WHAT IS THE DECISION? sits immediately after his own words. ALL FIVE SOURCES ARE SWEPT: the design Changelog (every version), the retired rulings ledger, his -jj feedback and audit workbooks, the standards and the mocks, and the requirements workbooks. Nothing is edited in the workbook — it is printed from moneykeel_decisions.json at step A3 of the build.</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/decision-log/moneykeel_log_decisions_v01.xlsx · moneykeel_decisions.json (the source) · extract-decisions.py · build-decision-log.py · moneykeel_decision_schema.py · moneykeel_decision_tabs.py · check-rulings-in-file.py (re-pointed) · the naming standard, sub-folder 8 and type `log`</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>THREE FAULTS FOUND AND FIXED WHILE BUILDING IT, each recorded because each is a class: (1) the first key was the source FILE, which turned 251 decisions into 561 rows; (2) the feedback sweep read MY verdict column and added 285 rows whose whole content was ‘AGREE’ or ‘PARTLY’; (3) two rows took the wrong answer because a phrase appeared deep in their body — a row about creating a folder took the hide-balances answer. Matching now requires the phrase in the row’s HEADLINE and the longest match wins, never whichever I typed first. A dead-key guard fails the build on a written sentence that reaches no row — it caught 26 on its first run, whose sentences existed and reached nobody.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>THE DECISION LOG’S OWN GAPS — 41 rows still need his wording, 248 name no test</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Two gaps remain, and both have their plan ON THE ROW. (1) 41 rows are CONFIDENCE LOW — the source recorded what I BUILT, not what he SAID. All four outstanding sources are now swept and none of them held his wording for these, so the next step is the short list that goes to him. (2) The proof column: rows naming no test are the number that matters most. THE FOUR SOURCES ARE NO LONGER OUTSTANDING — they are swept, and they added 184 decisions that were in no ledger plus a second source on 200 rows already there.</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>the confidence and proof columns of ALL DECISIONS · extract-decisions.py (sweep_changelog, sweep_rulings are written; four sweeps to add)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Said plainly so the file is not mistaken for complete: it holds every decision in the design Changelog and the rulings ledger, and none yet from the standards, requirements, audit or mock files. Decisions made only in chat and never written down are in none of these sources and remain the hole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>WHAT IS THE DECISION? — all 591 rows written in plain English, and the gate keeps it that way</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>DONE. Every one of the 591 rows is written in words a person can read, with several decisions in one row numbered 1. 2. 3. HIS OWN WORDS LEAD, VERBATIM — his instruction of 2026-09-29, ‘for these the text in " " is better to understand. leave that as is’ — and my explanation follows. The count is now a GATE, not a ratchet: a new row arriving unwritten fails the build.</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>CODED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>moneykeel_decision_plain.py (HAND_WRITTEN) · the WHAT IS THE DECISION? and 'Is the plain-English written?' columns of the decision log · moneykeel_decision_schema.py</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>I tried it mechanically first and threw it away: a glossary swapping each code word for plain ones turned his own example into ‘the rule for which figure an account’s balance comes from gains the adding up what the account holds instead’ — worse than the jargon. Swapping words is not writing a sentence. The numbering is mechanical; the sentences are written by hand, row by row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>PLAN — the 41 low-confidence decisions get his own words back (three steps, in order)</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>His question, 2026-09-28: “what’s the plan to improve the confidence?” The plan is on every one of those rows now, in the column HOW THIS ROW GETS HIS WORDS, so it is not a promise in a message. ALL 41 came from the design Changelog alone, which is the reason they are LOW: that file records what I BUILT. STEP 1 — sweep the four sources still outstanding (his -jj feedback workbooks and the audit files, the standards, the requirements workbooks, and the mock files’ ‘what changed’ blocks). His actual wording is very likely in one of them, and a match lifts the row to HIGH with NO question to him. STEP 2 — for the 6 rows dated July, look in the build-43 and build-47 feedback workbooks and the July device-test sheets, which is where his wording from before the ledger existed lives; for the 35 from August and September, his column I of the second-verification assessment. STEP 3 — only the residue goes to him: a short list, each row showing what I believe he decided, for a yes or a correction. Never all 41 — asking him to re-decide what he already wrote down is the fault, not the fix.</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>the confidence and 'HOW THIS ROW GETS HIS WORDS' columns of the decision log · moneykeel_decision_plain.py confidence_plan</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>41 rows: 6 from July, 28 from August, 7 from September. The count is a ratchet and falls as sources are swept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>PLAN — the 248 untested decisions get a test, worked BY KIND not one at a time</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>His question, 2026-09-28: “what’s the plan to test them?” On every untested row now, in the column HOW THIS GETS A TEST. Worked by kind, because one guard closes many rows at once:
+· 115 are DESIGN APPROVALS. Proof is not a unit test: it is a mock-match audit (every visible string, in order, diffed against the built screen) plus a row in the design record. Worked per SCREEN — one audit closes every design decision on that screen. Biggest batch, fewest passes.
+· 61 are COPY. Most of this class is ALREADY held by the one-term-per-concept guard, which reads the agreed word list rather than hard-coding it. The work is adding each row’s word to that list, in batches.
+· 30 are FIGURES. Proof is a WORKED EXAMPLE declared on the figure and run through the real door on every build — the machinery finished earlier today. DO THESE FIRST: a wrong number is the one thing that loses trust irrecoverably.
+· 24 are SCREENS. Held by a rendered-strings test or by guards that already exist (edge-to-edge bands, 20-point titles, the type floor). Several are already covered by a guard that does not name them; the work is naming it on the row.
+· 9 are FILES or PROCESS. An `expect` file-check — the mechanism already running for 38 decisions — or a gate script. One line each.
+· 9 NEED READING before anything can be claimed.
+ORDER: figures, then files and process (cheapest), then copy in batches, then screens, then the design audits per screen.</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>the 'HOW THIS GETS A TEST' column of the decision log · moneykeel_decision_plain.py proof_plan · worked_examples.test.ts · one_term_per_concept.test.ts · check-rulings-in-file.py</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>The classification is read from each row’s own words, not assigned by hand, so it stays right as rows change. 159 of the 407 already name a test; that count is the one to watch and it may only rise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>CONFIDENCE — 35 decisions need your wording; the list is ready and deliberately short</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Open MoneyKeel/documents/decision-log/moneykeel_log_wording-asks_v01.xlsx. 35 rows, each showing WHAT I BELIEVE YOU DECIDED in plain English, with two columns for you: YOUR WORDING, and YES / NO / CHANGE. If my version is right, ‘as written’ is the whole answer — you are not being asked to re-decide anything. WHY IT IS ONLY 35: all five sources were swept first and none held your wording for these; and SIX more turned out not to be decisions of yours at all — my own engineering, recorded under an approval column that said JJ for everything that day. Those six are named one by one in the log and are NOT on your list. Anything you leave blank stays marked as my reconstruction, which is honest.</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/decision-log/moneykeel_log_wording-asks_v01.xlsx · build-wording-asks.py · the confidence column of the decision log</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>41 were LOW; 6 are mine, 35 are yours. Each answer folds back against its Decision ID, your words verbatim, and the row moves to HIGH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>TESTING — 169 of 591 decisions name a test; 422 do not, and each carries its own plan</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>His question, 2026-09-28: ‘what’s the plan to test them?’ STEP ONE IS DONE, and it was the honest one: before writing anything, the suite was read to find decisions ALREADY held by a guard that does not name them. 316 test files read; 10 found, and the link is now on the row. A match needed the test to name an identifier the decision names, or to contain 30+ characters of his own words — a shared ordinary word is not evidence, and a wrong link would report a decision as proved when nothing re-runs it.
+THE REMAINING 422, by what would prove each (classified from the PLAIN sentence, because the raw changelog text named files and numbers and sent the plan at the wrong work):
+· 94 COPY — most already held by the one-term-per-concept guard; the work is adding each word to the list it reads. Closes in BATCHES.
+· 69 FIGURES — a worked example declared on the figure and run through the real orchestrator every build. DO THESE FIRST: a wrong number is the one thing that loses trust irrecoverably.
+· 65 are QUESTIONS HE ASKED, not decisions — nothing to test until each is answered and the answer is its own row.
+· 64 DESIGN APPROVALS — a mock-match audit per SCREEN, which closes every design decision on that screen at once.
+· 63 SCREENS — a rendered-strings test, or a guard that already exists.
+· 16 FILE or PROCESS — an `expect` file-check, one line each.
+· 15 THINGS HE FOUND — a test that fails if the defect returns, written against his own case.
+· 36 NEED READING before anything can be claimed.
+ORDER: figures, then files and process, then copy in batches, then screens, then the design audits per screen.</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>find-tests-for-decisions.py · the proof and HOW THIS GETS A TEST columns of the decision log</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Only 10 were found already covered, which is a small number and worth saying plainly: the matcher is narrow on purpose. 65 of the 422 are questions rather than decisions, so the real body of work is nearer 357.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$177</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F175"/>
+  <dimension ref="A1:F177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Founder approval of moneykeel_pres_mock_cash-flow_v01.html. On his instruction: "let's discuss how to clean cashflow mockups and combine into one file." This month and Expenses come from this-month-and-expenses v07, Income and Debts from money-four-tabs v02, with v02's architecture note. Both are dated in archive/. Look ahead MOVED to documents/networth-and-performance — it opens from Performance, not from a cash-flow tab. Income end-to-end stays its own file: seventeen frames folded in would make one file nobody can read.</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
+          <t>APPROVED by him 2026-09-28: "Approved." moneykeel_pres_mock_cash-flow_v01.html is the cash-flow design. Recorded in the decision log. What remains is building the screens to it, and the mock-match audit that proves they match.</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>RULED, NOT CODED</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>YOUR CALL. Exposed by your question above. A mortgage can be entered twice — as the Rent / Mortgage budget line and as a Mortgage debt — and the emergency fund deliberately leaves the debt’s minimum out so the home is not counted twice. That means it takes the BUDGET figure: someone who budgets $2,300 for a mortgage that actually costs $2,400 is read $100/month light on both runways. Counting both would overstate the whole payment, which is far worse, so the choice stands. But the app does not TELL them the two disagree. Should the screen say so, and which figure should win?</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
+          <t>ANSWERED by him 2026-09-29: "Yes, ask User to correct, if not input from user, use the budget." CODED THE SAME DAY: MK-NW-O-004 theEmergencyFund returns housingDisagreement {budgeted, owed, difference} where the two differ, and null where they agree or where one is missing — asking somebody to reconcile a figure they never entered is a worse question than no question. The BUDGET figure still drives the arithmetic, so no number moved; only what the person is told. DEC-0471, held by a test. STILL TO DO, mine: the screen has to actually ASK — the door reports it, no screen shows it yet.</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>TESTED, NOT VERIFIED</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Not a bug — a deliberate design choice whose edge is not surfaced to the person.</t>
+          <t>The in-chat decision hole is closed with it: moneykeel_decisions_in_chat.json is the sixth source, and the log now carries what he says in conversation the same day.</t>
         </is>
       </c>
     </row>
@@ -5667,8 +5667,72 @@
         </is>
       </c>
     </row>
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>LAUNCH ANSWER LIST — 61 things need you for Net worth, Cash flow and Performance to be launch-ready</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>His ask, 2026-09-29: ‘Give me a list of files, tabs, and rows I need to answer for NW, CF, Performance sections of the app to be complete.’ Open MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx. Five tabs: Read me, EVERYTHING, and one per module. Every line names its FILE, its TAB and its ROW, the column to type in, and what it blocks. 61 items: 33 Net worth, 18 Cash flow, 10 Performance. It is REBUILT from the master file, the decision log and this plan as they are on disk, never hand-maintained — re-run the script and it is current. THE ORDER I would take it in: the unanswered questions first (they block figures moving behind their doors), then the questions HE asked that nobody answered (not decisions until answered), then the decisions recorded in my words (‘as written’ clears one), then the VERIFIED marks — the longest, and the only part nobody can do for him.</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx · build-launch-answer-list.py</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>The big number underneath is the VERIFIED marks: 48 Net worth rows, 53 Cash flow, 12 Performance are TESTED but not VERIFIED. A test proves a figure is what the code gives; it can never prove it is the figure he wanted, which is why his ladder has that rung and why launch-ready cannot be claimed without it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>BEFORE THE NEXT BUILD — review and correct every underlying calculation for Net worth, Cash flow and Performance</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>His instruction, 2026-09-29: ‘before next build let’s review and correct all underlying calculations for NW, CF and Performance modules.’ NOT STARTED. What it means concretely: walk every figure on those three modules against its formula, its inputs and its worked example, and correct what disagrees — the file-and-code rule, both or neither. 93 Net worth decisions, 52 Cash flow, 39 Performance are in the log; 123 of those have no test. This is mine, not his — his half is the answer list above.</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>the master file's networth / cashflow / performance tabs · the decision log · MoneyKeel/functions/</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Gates the next build. No build is cut without his explicit ‘cut the build’ to a presented checklist.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F175"/>
+  <autoFilter ref="A1:F177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,15 +459,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F177"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -754,7 +754,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Build 45 root causes; July-24 audit → standing order: same-day changelog row for every approval</t>
@@ -782,7 +782,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr"/>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Builds 46 and 47 item walks; standing order: full-surface done (coverage line on every done-claim)</t>
@@ -866,7 +866,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Standing order: mock-match audit — string-by-string diff, order, nesting, alignment, appearance</t>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr"/>
     </row>
-    <row r="22" ht="45" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Standing orders: identifiers everywhere; no blanket decisions — each case to you with its specifics</t>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr"/>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Your comments on the master (column W): questions Q01–Q33 recorded; rulings Q06, Q07, Q08, Q09, A15, A46, A47 and the bond display rule</t>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr"/>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Bond display rule (nine facts on a bond; value = current, else cost, else face) — ruled, not coded; three specifics open as Q38</t>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr"/>
     </row>
-    <row r="35" ht="60" customHeight="1">
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Your -jj comments on the master (20) and typed answers (7) folded into the master on their rows; the four wrong-number findings fixed</t>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr"/>
     </row>
-    <row r="37" ht="60" customHeight="1">
+    <row r="37" ht="45" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Per-asset-class capture list — 15 items NOT CAPTURED, 4 DERIVED but blocked, 1 rule pending, 1 wrong until Q42 (options), display currency Q43</t>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr"/>
     </row>
-    <row r="42" ht="60" customHeight="1">
+    <row r="42" ht="45" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Status on every tab and every row of the three working files, one vocabulary; rules for CODED / TESTED / VERIFIED; JJ-feedback-archive folders</t>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr"/>
     </row>
-    <row r="48" ht="45" customHeight="1">
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>One stale header: MK-CF-F-123 (the retired local-date helper) carries a header but has no master row</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr"/>
     </row>
-    <row r="50" ht="45" customHeight="1">
+    <row r="50" ht="30" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Build 55 — release gate: scope complete, audits closed, journey pass, checklist presented</t>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr"/>
     </row>
-    <row r="55" ht="60" customHeight="1">
+    <row r="55" ht="45" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>One-door architecture — step 2, the photograph: every figure two people see on eight screens recorded before any function moves behind a door</t>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr"/>
     </row>
-    <row r="96" ht="60" customHeight="1">
+    <row r="96" ht="45" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>The master's STATUS column said NOTHING OPEN on the eight cash flow rows that wait on your verdict (MK-CF-M-047 to MK-CF-M-054, Row status DRAFT)</t>
@@ -5731,8 +5731,232 @@
         </is>
       </c>
     </row>
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Performance pass 1 — every figure on the screen has a door, and an example that runs</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-30 (4476da5). Four figures were calculated inside PerformanceScreen — the category earnings table, 24 lines of arithmetic with no row, no example and nothing able to check it. MK-PF-M-006/007/008/009 now live behind categoryEarnings() in the door and the screen calls it. Coverage: 12 of 12 Performance figures declared; 11 of 12 carry a worked example a test RUNS.</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/performance.ts · src/screens/PerformanceScreen.tsx · src/__tests__/worked_examples.test.ts</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>The not-yet-worked ratchet fell 9 → 8. Full suite green at the commit: 319 suites, 2,993 tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Performance pass 2 — THE HEADLINE RETURN HAD NO ROW, and Home and Performance disagreed about the same month</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-30. Three things, each found by asking every figure which screen shows it. (1) B-112: the same month read +3.57% on Home and +3.69% on Performance, one tap apart — Home counted price change only, Performance counted the dividends. It is B-97, the defect he found on Performance on 2026-09-25, never swept to its class. Home now asks the same door. (2) The return itself had NO declared figure: MK-XS-M-004 has been in the old metric register from the start and no door declared it, so there was nothing for a cross-screen guard to compare — that is WHY the disagreement survived. It is declared now, with a worked example. (3) B-113: MK-PF-M-008 said it was on /invest and is on /home; MK-PF-M-009 said /invest and is on no screen at all (mock v14 removed that card), so its row is gone.</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>docs/finwise-bug-ledger.md B-112 · B-113 · B-114 · src/__tests__/guard_d3_screens_agree.test.tsx</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>The pin is RED on the old code (+3.57%) and green on the fixed code — checked, not assumed. FOR HIM, two things: (a) Home's “ahead by” compares a return that counts dividends against an index return that does not, because we hold no dividend record for an index; (b) MK-PF-F-026 moneyWeightedReturn (a true XIRR) is now reached by no screen — delete it, or give it a screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Performance pass 3 — THE WINDOW THE SCREEN OPENS ON SHOWED A FLAT WALK AND NO RETURN (B-115)</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-30. Comparing an account's own page with the Performance tab's band for the SAME account found it. A window's beginning is read at the day BEFORE it opens, and “Since” opened ON the record's first day — so it asked the record for the day before the record began, got nothing, and back-solved the beginning from the ending. On a household that went $100,000 → $130,000 over a month of daily records, Performance read “$130,000 became $130,000” with no return, while the account page read $100,000 → $130,000, +30.00%. It is his B-98 ruling broken: THE BEGINNING IS READ, NEVER BACK-FILLED. Fixed in MK-NW-F-090 windowStartKey; the account page's own copy of the rule is deleted and calls the door.</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>docs/finwise-bug-ledger.md B-115 · MoneyKeel/functions/networth-and-performance/performance.test.ts</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him. The account page was right all along and the Performance tab — the screen that OPENS on this window — was wrong, which is why nobody saw it: the walk looked tidy, it just said nothing happened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>I TYPED THREE IDENTIFIERS FROM MEMORY AND COLLIDED WITH THREE LIVE ONES — the guard saw one of three</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>FIXED 2026-09-30, and the guard is widened. I named three new functions MK-PF-F-031/032/033 without reading the register, which had issued MK-NW-F-090/091/092 — and 031/032/033 already belong to three other live functions in src/domain/performance. The existing guard matches an identifier followed by a NAME, so it caught the ONE reference written that way and was blind to the three doc headers, which write the identifier followed by a middle dot. A second test now pairs every doc header with the function declared beneath it, and BOTH tests state how many pairs they read (600 and 400) so they cannot report clean while seeing a fraction. Checked red before green.</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>src/__tests__/guard_identifiers_match_register.test.ts · Calculation Module code/scripts/moneykeel_function_register.json</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>THE LESSON IS THE SAME ONE AS B6 AND B5: I read my memory instead of the data, inside the same week I wrote the rule about it. The control that holds is the widened guard, not the intention. One command reads the register: python3 -c "import json;print(json.load(open('Calculation Module code/scripts/moneykeel_function_register.json'))['issued']['&lt;name&gt;'])"</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Performance pass 4 — every decision on every figure re-run, and NAMED BY ITS IDENTIFIER</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-30. Twelve figures carry sixteen decisions. Before today ONE test in the whole repository named a Performance figure by its identifier — the decisions were held, but no test said WHICH FIGURE it was holding, so a decision could be dropped from a row and every test would stay green. MoneyKeel/functions/networth-and-performance/performance-decisions.test.ts now carries 22 tests, one per decision, each named for its figure, each re-running the decision against the real function. It asserts that every figure the two doors declare is named in it, so a new figure without a test goes red. IT FOUND A DEFECT WHILE BEING WRITTEN — B-116.</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/performance-decisions.test.ts · docs/finwise-bug-ledger.md B-116</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>B-116: interest on a hand-entered bond or CD was shown under Stocks / Funds. His decision on that figure already covered it — 'interest comes from a bond' — but the code applied it only when a record had NO ticker, not when it had one we hold nothing priced for. Balance-only accounts are exactly that cohort. That is what pass 4 is for: the decision was on the row, the code half-honoured it, and nothing re-ran it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>The suite went red because the machine was busy — the flake logged as B-90 since 2026-07-12</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>FIXED 2026-09-30. mock_match_dump renders 28 screens; React Native Testing Library's automatic afterEach cleanup unmounts all of them, and Jest's DEFAULT 5,000 ms applies to hooks as well as tests. Under a full parallel run that cleanup tipped over 5,000 ms and the file failed while passing in isolation. The ui project now sets testTimeout 30,000. A real hang still fails; it just fails honestly.</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>jest.config.js · docs/finwise-bug-ledger.md B-90 (WATCH)</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>This matters beyond tidiness: a green suite is a BUILD GATE here. A gate that goes red because the machine was busy is a gate nobody can trust, and the habit of re-running until green is how a real failure gets waved through.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>TWO QUESTIONS FOR YOU from the Performance review — Q51 and Q52</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Q51 (on MK-PF-M-008 market +X%, Home): Home reads “you +3.69% · market +2.83% · ahead by 0.85%”. The two sides are NOT measured the same way — yours counts the dividends and interest you received (your ruling of 2026-09-25), the market's is the index's PRICE only, because no feed we have gives an index's dividends. So “ahead by” flatters you by roughly the dividend yield. Three ways out: (a) leave it and say underneath that the market figure is price only; (b) compare price against price, which makes Home disagree with Performance again; (c) buy a total-return index feed. Q52 (on MK-XS-M-004 Return): MK-PF-F-026 moneyWeightedReturn is a true personal return — it solves for the rate that makes what you paid in, on the days you paid it in, equal what you have now. Built, correct, and reached by NO SCREEN: the card that showed it was removed by the Performance design you approved on 2026-09-25. Delete it, or give it a screen?</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>moneykeel_calc_master_calculation-master_v01.xlsx · performance tab · MK-PF-M-008 and MK-XS-M-004, column 'YOUR ANSWER — use the same number' · also on the launch answer list</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Neither blocks the Performance passes; both block calling Performance launch-ready, because a figure a person reads either says what it means or it does not.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F177"/>
+  <autoFilter ref="A1:F184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5955,8 +5955,40 @@
         </is>
       </c>
     </row>
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>HE FOUND A SUPERSEDED DECISION STILL BEING ASKED ABOUT — DEC-0004 on the wording-asks file</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>FIXED 2026-09-30. His words: “decision log-ask-v01 still has DEC004. Have you update the file?” — and no, I had not. I marked DEC-0004 OLD in the decision log (superseded by DEC-0440, the Expenses tab) and committed it, but the wording-asks file is BUILT from the same rows and its builder selected on CONFIDENCE alone, never reading whether a decision is still in force. Two dead rows were on it: DEC-0004 and DEC-0037 (SnapTrade, superseded by DEC-0038 for Plaid). The launch answer list carried both too — DEC-0037 under Net worth, DEC-0004 under Cash flow. Both builders now read in_use and status; the asks file is 35 → 33 rows and the answer list's 'my words' counts are 8→7 Net worth and 7→6 Cash flow. src/__tests__/guard_no_dead_decision_asked.test.ts reads BOTH WORKBOOKS as he opens them and fails on any superseded identifier, asserting how many cells it read.</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/decision-log/moneykeel_log_wording-asks_v01.xlsx · MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx · src/__tests__/guard_no_dead_decision_asked.test.ts</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>WHY IT MATTERS MORE THAN WASTED TIME: an answer from him to a superseded row would have ruled a dead decision back into life. This is the PFS failure in miniature — the ruling reached the decision log and not the files built beside it — and it is the fourth time he, not a gate, has found a stale file. The guard is checked red before green.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F184"/>
+  <autoFilter ref="A1:F185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$188</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5987,8 +5987,104 @@
         </is>
       </c>
     </row>
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Q51 RULED and built — Home says WHICH return counts your income</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>His words 2026-09-30: “make it you +3.69% (including dividend), market +2.83%, ahead by 0.85%”, then “including dividend and interest”. Built and pinned. ONE WORD DIFFERS FROM HIS: “dividends” plural, the word the walk, the category table and the glossary already use — say the word to switch it to his singular. DEC-0595.</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>TESTED, NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/HomeScreen.tsx · src/__tests__/guard_d3_screens_agree.test.tsx · decision log DEC-0595</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Without the clarifier the gap read as skill, when part of it is income the market side cannot see — no feed we hold gives an index’s dividends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Q52 RULED — option B: when the Return refuses, show the exact rate in its place. NOT BUILT.</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>His words 2026-09-30: “Q52 - use option B”. NEXT STEP IS A MOCK, not code (mock-first standing order): both states on one sheet — the Return answering, and the Return refusing with the money-weighted rate in place of the refusal sentence. Nothing is coded until he approves it. DEC-0596.</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>RULED, NOT CODED</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/networth-and-performance/ (mock to be drawn, from v14) · MK-NW-O-008 thePerformance · MK-PF-F-026 moneyWeightedReturn · decision log DEC-0596</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Measured: the two methods agree to 0.018 of a percentage point wherever the Return answers (7.6161% vs 7.6341% on ,000 with ,000 added mid-year), so this fills the gap the refusal leaves and never contradicts it. One return visible at a time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>REWRITING A DECISION’S WORDING WAS RE-MINTING ITS IDENTIFIER — two rows lost in one afternoon</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>FIXED 2026-09-30. For a decision with no quoted words of his, the key that says “already recorded” was a hash of the date plus MY plain-English summary — so improving a summary moved the key, the sweep stopped recognising the row, and added it again under a fresh number. His rule is that an identifier is issued once and never re-pointed; my own editing was re-pointing them. DEC-0008 came back as DEC-0517 when I rewrote it on his font question; DEC-0002 was re-minted when I deleted a line I thought was dead. THREE FIXES: (1) a row is recognised by the SOURCE’s own words when the key misses, so my editing cannot create a duplicate; (2) the merge step no longer folds a split row into its sibling — both halves inherit his words “cashflow. Approve.” verbatim, matched at ratio 1.0, and were silently re-merged on every run, UNDOING THE SPLIT HE ASKED FOR; (3) the split step keeps each half’s key and never re-splits an already-split row. Proved stable over three consecutive runs: nothing lost, nothing gained.</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/extract-decisions.py · moneykeel_decisions.json</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>build-all.sh had been broken since this morning — the pipeline stopped with a bare KeyError on any second run. Nobody would have seen it until the next full build.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F185"/>
+  <autoFilter ref="A1:F188"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F188"/>
+  <dimension ref="A1:F189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6083,8 +6083,40 @@
         </is>
       </c>
     </row>
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Q52 MOCK DRAWN — performance v15, waiting on your yes</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_performance_v15.html. TWO PHONES: the first IS v14 with its change marks removed, so you can see nothing else moved; the second is the ONE state that changes — the Return cell reads 7.46%/year where it used to read an em-dash, and the note says which kind of rate it is. Mark 16a draws the alternative (cell stays an em-dash, rate in the note alone); I recommend 16. Every figure is computed by the real function, not typed: the walk closes 100,000 + 15,000 − 0 + 8,000 = 123,000, the income closes 1,800 + 400 + 5,800 = 8,000, and the rate is what the solver returns over 364 days. NO CODE WRITTEN.</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_performance_v15.html · decision log DEC-0596</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>SEPARATE FINDING ON THE SAME PAGE, needing its own word from you: three of v14’s colours do not match the app’s own tokens — a gain is #178F6B in the mock and #006300 in the app, a fall #C2483A against #A32D2D, an amber #B97F10 against #854F0B. v15 is drawn in v14’s colours ON PURPOSE so the only visible change is the one you ruled. Bringing every mock onto the app’s tokens is its own change.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F188"/>
+  <autoFilter ref="A1:F189"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -6086,12 +6086,12 @@
     <row r="189" ht="60" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Q52 MOCK DRAWN — performance v15, waiting on your yes</t>
+          <t>Q52 MOCK — performance v15, SEVEN phones, app colours, v14 archived. Waiting on your yes.</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_performance_v15.html. TWO PHONES: the first IS v14 with its change marks removed, so you can see nothing else moved; the second is the ONE state that changes — the Return cell reads 7.46%/year where it used to read an em-dash, and the note says which kind of rate it is. Mark 16a draws the alternative (cell stays an em-dash, rate in the note alone); I recommend 16. Every figure is computed by the real function, not typed: the walk closes 100,000 + 15,000 − 0 + 8,000 = 123,000, the income closes 1,800 + 400 + 5,800 = 8,000, and the rate is what the solver returns over 364 days. NO CODE WRITTEN.</t>
+          <t>REDRAWN 2026-09-30 after four corrections of his: (1) “match the color with the app colors” — twelve stylesheet rules read from theme.ts: gain #178F6B→#006300, fall #C2483A→#A32D2D, amber #B97F10 on #FDF1DC→#854F0B on #FAEEDA, grey #9A9891 and #8A8A84→#76766F, secondary #66655F→#6B6B66, screen #F4F3EC→#F6F7F5, axis labels 8.5pt→ 11pt. #178F6B STAYS where the app really uses Colors.primary — wordmark, link, value line. (2) “phone 2 missing institution level details” — phone 6 now carries the per-account walks, same structure as phone 1. (3) “recreate all slides as return is on all screens” — all five of v14’s screens are recreated, plus the two refusing states: SEVEN phones. (4) “move v14 to archive, which you did not” — done, archive/2026-09-30_moneykeel_pres_mock_performance_v14.html, and the four records naming it re-pointed (CLAUDE.md, design-each-screen-was-built-from, review-decisions-against-mocks.py, account_detail_v14.test.tsx).</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>SEPARATE FINDING ON THE SAME PAGE, needing its own word from you: three of v14’s colours do not match the app’s own tokens — a gain is #178F6B in the mock and #006300 in the app, a fall #C2483A against #A32D2D, an amber #B97F10 against #854F0B. v15 is drawn in v14’s colours ON PURPOSE so the only visible change is the one you ruled. Bringing every mock onto the app’s tokens is its own change.</t>
+          <t>HIS WORDS: “Pay attention to details so I don’t have to spoon feed everything.” The household on phone 6 is chosen so THREE cases sit on one screen: all accounts refuses (6.96–8.00% on timing) → 7.46%/year; Vanguard refuses (6.32–7.50%) → 6.88%/year; E*TRADE had nothing added so it answers normally → +10.00%. Every sum closes. My own audit before sending caught four faults of mine: three unbalanced divs, two stale greys, a retired “/yr” I typed in the window selector, and leftover v14 change marks.</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,12 +459,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F189"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
@@ -6115,8 +6115,72 @@
         </is>
       </c>
     </row>
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Net worth pass 1 — the WHOLE LEDGER was worked out on the screen</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-30 (d31209e). 48 rows on the master networth tab, 42 printed from the code; the last six were hand-typed. MK-NW-M-006 was the one that mattered: its own row said “this section total is computed on the screen itself” (written by hand 2026-09-08) and it named NO function. NetWorthScreen grouped every account and totalled each band with an inline reduce over balances. It is ledgerGroups in the door now. Coverage: 48 of 48 declared · 48 of 48 with a worked example · 0 hand-typed · 0 naming no function · 0 computed on a screen.</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/net-worth.ts · net-worth.test.ts · src/screens/NetWorthScreen.tsx</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Two things now checkable that never were: both groupings add to the SAME total (,200 either way), and the bands add to what the door says you own. An account with no institution groups under “No institution set” rather than vanishing. The ratchet fell 7 → 6; Net worth and Performance are both at full worked-example coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Net worth pass 3 — B-117: the emergency-fund warning was SUPPRESSED for the people who needed it</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>FIXED 2026-09-30. Insights divided cash by expenses alone while the door — read by the Net worth tab, Job safety and Stress test — divides by expenses PLUS debt minimums, on his ruling of 2026-09-28. On one household 8.9 months on Insights against 5.6 on Net worth. THE REAL HARM: the “Build your emergency fund” card fires below three months, so someone with ,000 cash, ,500 expenses and ,650 of debt minimums honestly has 2.5 months and should see it — but dividing by expenses alone gives 4.0 months, above the line, and THE CARD NEVER APPEARED. Insights reads the door now and its drill-down names the debt line. Also B-118: the Net worth screen printed “Monthly debt payments” from a different rule than its own door ( against  on a card paid above the minimum); the wiring is fixed and the FIGURE IS DELIBERATELY UNCHANGED pending Q53.</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>DONE (B-117) · Q53 WAITING ON YOU (B-118)</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>docs/finwise-bug-ledger.md B-117 · B-118 · src/__tests__/guard_d3_screens_agree.test.tsx · net-worth.test.ts</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Both pins checked RED on the genuine pre-fix code — my first red-check was invalid (I substituted a door field that already counted the debt) and I redid it with the real old call. Three guards caught faults of mine in one sitting: the canon guard on my own wording, the identifier register, and the rule-11 ratchet on two money lines I added without identifiers (they were MK-NW-M-047 and MK-NW-M-048 all along).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F189"/>
+  <autoFilter ref="A1:F191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6179,8 +6179,168 @@
         </is>
       </c>
     </row>
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>PFS DONE — all 33 wording asks answered by him and folded in; the asks file is now EMPTY</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>His instruction 2026-09-30: “Decision-log-ask-v01-jj - all questions answered. Record them in decision log, any other file needed to be updated (PFS).” COVERAGE: 33 of 33 rows read and folded — 24 confirmed my summary as written (“yes”), 9 replaced it with his own wording, word for word. Confidence across the whole log: 35 LOW → 2 LOW (the two remaining are DEC-0004 and DEC-0037, superseded, so they were correctly never asked). FILES UPDATED: moneykeel_decisions_answers.json (new, his words verbatim) · extract-decisions.py (apply_answers) · the decision log workbook · the wording-asks file (33 rows → 0) · the master calculation file · the launch answer list (no “recorded in MY words” items remain) · the file-and-folder standard and CLAUDE.md (DEC-0011) · archived as JJ-feedback-archive/2026-09-30_folded-in_moneykeel_log_wording-asks_v01-jj.xlsx.</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/decision-log/ · Calculation Module code/scripts/moneykeel_decisions_answers.json</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>NINE OF HIS ANSWERS CORRECTED MY PARAPHRASE MATERIALLY. Checked against the code, four were already built exactly as he describes (DEC-0009 Plan→Prepare holds all six rows in his words; DEC-0052 no donut, bars under BOTH what you own and what you owe; DEC-0211 the sim runs 1,000 and the screen says so; DEC-0197 his trim of my sentence). DEC-0011 changed a rule and is now in the standard: the DECISION LOG is the one consolidated master and the changelog is IN ADDITION to it — my summary had it backwards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>DEC-0028 — “Plan screens to be finalized next.”</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>HIS SEQUENCING DECISION, 2026-09-30, replacing my paraphrase (which said a big-costs mock was approved and built into build 48). After Net worth, Cash flow and Performance are launch-ready, PLAN SCREENS ARE NEXT. Not started.</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>decision log DEC-0028 · the Plan screens</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>It also answers the sequencing question that row 122 has been carrying: whether the Plan tab is built against its doors or in front of them. Finalising the DESIGN first is what he has now said.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>DEC-0033 — “Menu to be re-designed once all sectioned are launch ready”</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>HIS SEQUENCING DECISION, 2026-09-30, replacing my paraphrase (which said three items come off the menu for the 55-70 audience). The menu is redesigned AFTER every section is launch-ready — nothing comes off it now.</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>TO DO — after the sections</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>decision log DEC-0033 · src/components/TopBar.tsx</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>My paraphrase would have had me remove menu items now. His answer says the opposite: leave it, redesign it once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="60" customHeight="1">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>DEC-0201 — “Use latest mockup version of income screen”</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>HIS INSTRUCTION, 2026-09-30. The latest is MoneyKeel/documents/cashflow/moneykeel_pres_mock_income-end-to-end_v07.html. NOT YET CHECKED: whether the built income screen matches v07 in every state. That comparison is the first step of Cash flow’s passes, and it starts from this mock — not from today’s code (start-from-the-last-approved-design rule).</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>decision log DEC-0201 · MoneyKeel/documents/cashflow/moneykeel_pres_mock_income-end-to-end_v07.html</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>The design record says the income rebuild shipped in Build 54 against filing-status v02 and base-pay v07 — it does NOT say the income screen was traced to income-end-to-end v07. So the gap is real until measured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="60" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>DEC-0030 — “As of now park this.” ONE WORD NEEDED FROM HIM</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>HIS ANSWER, 2026-09-30, on whether the “what if I had moved this money” card stays on the holding page. My paraphrase said it stays; he says park it. THE CODE STILL HAS IT: HoldingDetailScreen line 291 has a working button that opens /look-back pre-filled. I have NOT removed it — parking a decision is not the same as deleting working code, and removing a door he can still see is a change he did not ask for. Say “remove it” or “leave it” and it is one commit either way.</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>decision log DEC-0030 · src/screens/HoldingDetailScreen.tsx:291 · MK-PF-M-010 / 011 / 012</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>If it is removed, MK-PF-M-010, 011 and 012 lose their only door from a holding page — /look-back is still reached from Account detail and Contribution room, so nothing would be stranded.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F191"/>
+  <autoFilter ref="A1:F196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,15 +459,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F196"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -754,7 +754,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Build 45 root causes; July-24 audit → standing order: same-day changelog row for every approval</t>
@@ -782,7 +782,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Builds 46 and 47 item walks; standing order: full-surface done (coverage line on every done-claim)</t>
@@ -866,7 +866,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Standing order: mock-match audit — string-by-string diff, order, nesting, alignment, appearance</t>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr"/>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Standing orders: identifiers everywhere; no blanket decisions — each case to you with its specifics</t>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr"/>
     </row>
-    <row r="25" ht="45" customHeight="1">
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Your comments on the master (column W): questions Q01–Q33 recorded; rulings Q06, Q07, Q08, Q09, A15, A46, A47 and the bond display rule</t>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr"/>
     </row>
-    <row r="26" ht="45" customHeight="1">
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Bond display rule (nine facts on a bond; value = current, else cost, else face) — ruled, not coded; three specifics open as Q38</t>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr"/>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Your -jj comments on the master (20) and typed answers (7) folded into the master on their rows; the four wrong-number findings fixed</t>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr"/>
     </row>
-    <row r="37" ht="45" customHeight="1">
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Per-asset-class capture list — 15 items NOT CAPTURED, 4 DERIVED but blocked, 1 rule pending, 1 wrong until Q42 (options), display currency Q43</t>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr"/>
     </row>
-    <row r="42" ht="45" customHeight="1">
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Status on every tab and every row of the three working files, one vocabulary; rules for CODED / TESTED / VERIFIED; JJ-feedback-archive folders</t>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="45" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>One stale header: MK-CF-F-123 (the retired local-date helper) carries a header but has no master row</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr"/>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" ht="45" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Build 55 — release gate: scope complete, audits closed, journey pass, checklist presented</t>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr"/>
     </row>
-    <row r="55" ht="45" customHeight="1">
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>One-door architecture — step 2, the photograph: every figure two people see on eight screens recorded before any function moves behind a door</t>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr"/>
     </row>
-    <row r="96" ht="45" customHeight="1">
+    <row r="96" ht="60" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>The master's STATUS column said NOTHING OPEN on the eight cash flow rows that wait on your verdict (MK-CF-M-047 to MK-CF-M-054, Row status DRAFT)</t>
@@ -5734,613 +5734,37 @@
     <row r="178" ht="60" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Performance pass 1 — every figure on the screen has a door, and an example that runs</t>
+          <t>Net worth module — compliance validation against every decision that touches it</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>DONE 2026-09-30 (4476da5). Four figures were calculated inside PerformanceScreen — the category earnings table, 24 lines of arithmetic with no row, no example and nothing able to check it. MK-PF-M-006/007/008/009 now live behind categoryEarnings() in the door and the screen calls it. Coverage: 12 of 12 Performance figures declared; 11 of 12 carry a worked example a test RUNS.</t>
+          <t>His instruction, 2026-10-01: "validate does existing screen mock ups, metrics, functions, code comply with these decisions or not — go module by module, first Net worth (all screens, all metrics, all functions, every line of code)." DONE for Net worth: 205 decisions checked against 10 screens, 8 doors, 69 figures and 7 approved mocks by validate-module-complies.py. FOUR BREACHES FOUND AND FIXED, each with a guard that counts what it read: DEC-0104/DEC-0109 (the odds sentence had split again — Cash flow said "{chance}% odds of lasting" with no age, and the gauge hand-typed its half); DEC-0036 (his own-math reword was live in 1 of 4 places, the other three still cited the ~4% guideline); DEC-0301 (the source chip printed a raw ISO date on every linked account, fresh or stale, and "stale" was defined three times over). Also built the missing back-link: every code header now names the decisions its arithmetic answers to — 126 decision ids in the code, up from 3 — so a wrong number traces to his ruling (objective 4).</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>DONE — Net worth. Performance and Cash flow next, same validator.</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/functions/networth-and-performance/performance.ts · src/screens/PerformanceScreen.tsx · src/__tests__/worked_examples.test.ts</t>
+          <t>Calculation Module code/scripts/validate-module-complies.py · moneykeel_validation_networth.json · src/__tests__/one_wording_for_the_odds.test.ts · own_math_not_a_rule_of_thumb.test.ts · source_always_date_only_when_stale.test.ts</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>The not-yet-worked ratchet fell 9 → 8. Full suite green at the commit: 319 suites, 2,993 tests.</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="60" customHeight="1">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>Performance pass 2 — THE HEADLINE RETURN HAD NO ROW, and Home and Performance disagreed about the same month</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>DONE 2026-09-30. Three things, each found by asking every figure which screen shows it. (1) B-112: the same month read +3.57% on Home and +3.69% on Performance, one tap apart — Home counted price change only, Performance counted the dividends. It is B-97, the defect he found on Performance on 2026-09-25, never swept to its class. Home now asks the same door. (2) The return itself had NO declared figure: MK-XS-M-004 has been in the old metric register from the start and no door declared it, so there was nothing for a cross-screen guard to compare — that is WHY the disagreement survived. It is declared now, with a worked example. (3) B-113: MK-PF-M-008 said it was on /invest and is on /home; MK-PF-M-009 said /invest and is on no screen at all (mock v14 removed that card), so its row is gone.</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>docs/finwise-bug-ledger.md B-112 · B-113 · B-114 · src/__tests__/guard_d3_screens_agree.test.tsx</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>The pin is RED on the old code (+3.57%) and green on the fixed code — checked, not assumed. FOR HIM, two things: (a) Home's “ahead by” compares a return that counts dividends against an index return that does not, because we hold no dividend record for an index; (b) MK-PF-F-026 moneyWeightedReturn (a true XIRR) is now reached by no screen — delete it, or give it a screen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="60" customHeight="1">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>Performance pass 3 — THE WINDOW THE SCREEN OPENS ON SHOWED A FLAT WALK AND NO RETURN (B-115)</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>DONE 2026-09-30. Comparing an account's own page with the Performance tab's band for the SAME account found it. A window's beginning is read at the day BEFORE it opens, and “Since” opened ON the record's first day — so it asked the record for the day before the record began, got nothing, and back-solved the beginning from the ending. On a household that went $100,000 → $130,000 over a month of daily records, Performance read “$130,000 became $130,000” with no return, while the account page read $100,000 → $130,000, +30.00%. It is his B-98 ruling broken: THE BEGINNING IS READ, NEVER BACK-FILLED. Fixed in MK-NW-F-090 windowStartKey; the account page's own copy of the rule is deleted and calls the door.</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>docs/finwise-bug-ledger.md B-115 · MoneyKeel/functions/networth-and-performance/performance.test.ts</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>Nothing for him. The account page was right all along and the Performance tab — the screen that OPENS on this window — was wrong, which is why nobody saw it: the walk looked tidy, it just said nothing happened.</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="60" customHeight="1">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>I TYPED THREE IDENTIFIERS FROM MEMORY AND COLLIDED WITH THREE LIVE ONES — the guard saw one of three</t>
-        </is>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>FIXED 2026-09-30, and the guard is widened. I named three new functions MK-PF-F-031/032/033 without reading the register, which had issued MK-NW-F-090/091/092 — and 031/032/033 already belong to three other live functions in src/domain/performance. The existing guard matches an identifier followed by a NAME, so it caught the ONE reference written that way and was blind to the three doc headers, which write the identifier followed by a middle dot. A second test now pairs every doc header with the function declared beneath it, and BOTH tests state how many pairs they read (600 and 400) so they cannot report clean while seeing a fraction. Checked red before green.</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
-        <is>
-          <t>src/__tests__/guard_identifiers_match_register.test.ts · Calculation Module code/scripts/moneykeel_function_register.json</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t>THE LESSON IS THE SAME ONE AS B6 AND B5: I read my memory instead of the data, inside the same week I wrote the rule about it. The control that holds is the widened guard, not the intention. One command reads the register: python3 -c "import json;print(json.load(open('Calculation Module code/scripts/moneykeel_function_register.json'))['issued']['&lt;name&gt;'])"</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="60" customHeight="1">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>Performance pass 4 — every decision on every figure re-run, and NAMED BY ITS IDENTIFIER</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>DONE 2026-09-30. Twelve figures carry sixteen decisions. Before today ONE test in the whole repository named a Performance figure by its identifier — the decisions were held, but no test said WHICH FIGURE it was holding, so a decision could be dropped from a row and every test would stay green. MoneyKeel/functions/networth-and-performance/performance-decisions.test.ts now carries 22 tests, one per decision, each named for its figure, each re-running the decision against the real function. It asserts that every figure the two doors declare is named in it, so a new figure without a test goes red. IT FOUND A DEFECT WHILE BEING WRITTEN — B-116.</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t>MoneyKeel/functions/networth-and-performance/performance-decisions.test.ts · docs/finwise-bug-ledger.md B-116</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F182" s="2" t="inlineStr">
-        <is>
-          <t>B-116: interest on a hand-entered bond or CD was shown under Stocks / Funds. His decision on that figure already covered it — 'interest comes from a bond' — but the code applied it only when a record had NO ticker, not when it had one we hold nothing priced for. Balance-only accounts are exactly that cohort. That is what pass 4 is for: the decision was on the row, the code half-honoured it, and nothing re-ran it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="60" customHeight="1">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>The suite went red because the machine was busy — the flake logged as B-90 since 2026-07-12</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>FIXED 2026-09-30. mock_match_dump renders 28 screens; React Native Testing Library's automatic afterEach cleanup unmounts all of them, and Jest's DEFAULT 5,000 ms applies to hooks as well as tests. Under a full parallel run that cleanup tipped over 5,000 ms and the file failed while passing in isolation. The ui project now sets testTimeout 30,000. A real hang still fails; it just fails honestly.</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
-        <is>
-          <t>jest.config.js · docs/finwise-bug-ledger.md B-90 (WATCH)</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>This matters beyond tidiness: a green suite is a BUILD GATE here. A gate that goes red because the machine was busy is a gate nobody can trust, and the habit of re-running until green is how a real failure gets waved through.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="60" customHeight="1">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>TWO QUESTIONS FOR YOU from the Performance review — Q51 and Q52</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>Q51 (on MK-PF-M-008 market +X%, Home): Home reads “you +3.69% · market +2.83% · ahead by 0.85%”. The two sides are NOT measured the same way — yours counts the dividends and interest you received (your ruling of 2026-09-25), the market's is the index's PRICE only, because no feed we have gives an index's dividends. So “ahead by” flatters you by roughly the dividend yield. Three ways out: (a) leave it and say underneath that the market figure is price only; (b) compare price against price, which makes Home disagree with Performance again; (c) buy a total-return index feed. Q52 (on MK-XS-M-004 Return): MK-PF-F-026 moneyWeightedReturn is a true personal return — it solves for the rate that makes what you paid in, on the days you paid it in, equal what you have now. Built, correct, and reached by NO SCREEN: the card that showed it was removed by the Performance design you approved on 2026-09-25. Delete it, or give it a screen?</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>moneykeel_calc_master_calculation-master_v01.xlsx · performance tab · MK-PF-M-008 and MK-XS-M-004, column 'YOUR ANSWER — use the same number' · also on the launch answer list</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>Neither blocks the Performance passes; both block calling Performance launch-ready, because a figure a person reads either says what it means or it does not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="60" customHeight="1">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>HE FOUND A SUPERSEDED DECISION STILL BEING ASKED ABOUT — DEC-0004 on the wording-asks file</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>FIXED 2026-09-30. His words: “decision log-ask-v01 still has DEC004. Have you update the file?” — and no, I had not. I marked DEC-0004 OLD in the decision log (superseded by DEC-0440, the Expenses tab) and committed it, but the wording-asks file is BUILT from the same rows and its builder selected on CONFIDENCE alone, never reading whether a decision is still in force. Two dead rows were on it: DEC-0004 and DEC-0037 (SnapTrade, superseded by DEC-0038 for Plaid). The launch answer list carried both too — DEC-0037 under Net worth, DEC-0004 under Cash flow. Both builders now read in_use and status; the asks file is 35 → 33 rows and the answer list's 'my words' counts are 8→7 Net worth and 7→6 Cash flow. src/__tests__/guard_no_dead_decision_asked.test.ts reads BOTH WORKBOOKS as he opens them and fails on any superseded identifier, asserting how many cells it read.</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/decision-log/moneykeel_log_wording-asks_v01.xlsx · MoneyKeel/documents/other/moneykeel_calc_plan_launch-answer-list_v01.xlsx · src/__tests__/guard_no_dead_decision_asked.test.ts</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F185" s="2" t="inlineStr">
-        <is>
-          <t>WHY IT MATTERS MORE THAN WASTED TIME: an answer from him to a superseded row would have ruled a dead decision back into life. This is the PFS failure in miniature — the ruling reached the decision log and not the files built beside it — and it is the fourth time he, not a gate, has found a stale file. The guard is checked red before green.</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="60" customHeight="1">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>Q51 RULED and built — Home says WHICH return counts your income</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>His words 2026-09-30: “make it you +3.69% (including dividend), market +2.83%, ahead by 0.85%”, then “including dividend and interest”. Built and pinned. ONE WORD DIFFERS FROM HIS: “dividends” plural, the word the walk, the category table and the glossary already use — say the word to switch it to his singular. DEC-0595.</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>TESTED, NOT VERIFIED</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>src/screens/HomeScreen.tsx · src/__tests__/guard_d3_screens_agree.test.tsx · decision log DEC-0595</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F186" s="2" t="inlineStr">
-        <is>
-          <t>Without the clarifier the gap read as skill, when part of it is income the market side cannot see — no feed we hold gives an index’s dividends.</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="60" customHeight="1">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>Q52 RULED — option B: when the Return refuses, show the exact rate in its place. NOT BUILT.</t>
-        </is>
-      </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>His words 2026-09-30: “Q52 - use option B”. NEXT STEP IS A MOCK, not code (mock-first standing order): both states on one sheet — the Return answering, and the Return refusing with the money-weighted rate in place of the refusal sentence. Nothing is coded until he approves it. DEC-0596.</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>RULED, NOT CODED</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/networth-and-performance/ (mock to be drawn, from v14) · MK-NW-O-008 thePerformance · MK-PF-F-026 moneyWeightedReturn · decision log DEC-0596</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F187" s="2" t="inlineStr">
-        <is>
-          <t>Measured: the two methods agree to 0.018 of a percentage point wherever the Return answers (7.6161% vs 7.6341% on ,000 with ,000 added mid-year), so this fills the gap the refusal leaves and never contradicts it. One return visible at a time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="60" customHeight="1">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>REWRITING A DECISION’S WORDING WAS RE-MINTING ITS IDENTIFIER — two rows lost in one afternoon</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>FIXED 2026-09-30. For a decision with no quoted words of his, the key that says “already recorded” was a hash of the date plus MY plain-English summary — so improving a summary moved the key, the sweep stopped recognising the row, and added it again under a fresh number. His rule is that an identifier is issued once and never re-pointed; my own editing was re-pointing them. DEC-0008 came back as DEC-0517 when I rewrote it on his font question; DEC-0002 was re-minted when I deleted a line I thought was dead. THREE FIXES: (1) a row is recognised by the SOURCE’s own words when the key misses, so my editing cannot create a duplicate; (2) the merge step no longer folds a split row into its sibling — both halves inherit his words “cashflow. Approve.” verbatim, matched at ratio 1.0, and were silently re-merged on every run, UNDOING THE SPLIT HE ASKED FOR; (3) the split step keeps each half’s key and never re-splits an already-split row. Proved stable over three consecutive runs: nothing lost, nothing gained.</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>Calculation Module code/scripts/extract-decisions.py · moneykeel_decisions.json</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>build-all.sh had been broken since this morning — the pipeline stopped with a bare KeyError on any second run. Nobody would have seen it until the next full build.</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="60" customHeight="1">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>Q52 MOCK — performance v15, SEVEN phones, app colours, v14 archived. Waiting on your yes.</t>
-        </is>
-      </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>REDRAWN 2026-09-30 after four corrections of his: (1) “match the color with the app colors” — twelve stylesheet rules read from theme.ts: gain #178F6B→#006300, fall #C2483A→#A32D2D, amber #B97F10 on #FDF1DC→#854F0B on #FAEEDA, grey #9A9891 and #8A8A84→#76766F, secondary #66655F→#6B6B66, screen #F4F3EC→#F6F7F5, axis labels 8.5pt→ 11pt. #178F6B STAYS where the app really uses Colors.primary — wordmark, link, value line. (2) “phone 2 missing institution level details” — phone 6 now carries the per-account walks, same structure as phone 1. (3) “recreate all slides as return is on all screens” — all five of v14’s screens are recreated, plus the two refusing states: SEVEN phones. (4) “move v14 to archive, which you did not” — done, archive/2026-09-30_moneykeel_pres_mock_performance_v14.html, and the four records naming it re-pointed (CLAUDE.md, design-each-screen-was-built-from, review-decisions-against-mocks.py, account_detail_v14.test.tsx).</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_performance_v15.html · decision log DEC-0596</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F189" s="2" t="inlineStr">
-        <is>
-          <t>HIS WORDS: “Pay attention to details so I don’t have to spoon feed everything.” The household on phone 6 is chosen so THREE cases sit on one screen: all accounts refuses (6.96–8.00% on timing) → 7.46%/year; Vanguard refuses (6.32–7.50%) → 6.88%/year; E*TRADE had nothing added so it answers normally → +10.00%. Every sum closes. My own audit before sending caught four faults of mine: three unbalanced divs, two stale greys, a retired “/yr” I typed in the window selector, and leftover v14 change marks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="60" customHeight="1">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>Net worth pass 1 — the WHOLE LEDGER was worked out on the screen</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>DONE 2026-09-30 (d31209e). 48 rows on the master networth tab, 42 printed from the code; the last six were hand-typed. MK-NW-M-006 was the one that mattered: its own row said “this section total is computed on the screen itself” (written by hand 2026-09-08) and it named NO function. NetWorthScreen grouped every account and totalled each band with an inline reduce over balances. It is ledgerGroups in the door now. Coverage: 48 of 48 declared · 48 of 48 with a worked example · 0 hand-typed · 0 naming no function · 0 computed on a screen.</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
-        <is>
-          <t>MoneyKeel/functions/networth-and-performance/net-worth.ts · net-worth.test.ts · src/screens/NetWorthScreen.tsx</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t>Two things now checkable that never were: both groupings add to the SAME total (,200 either way), and the bands add to what the door says you own. An account with no institution groups under “No institution set” rather than vanishing. The ratchet fell 7 → 6; Net worth and Performance are both at full worked-example coverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="60" customHeight="1">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>Net worth pass 3 — B-117: the emergency-fund warning was SUPPRESSED for the people who needed it</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>FIXED 2026-09-30. Insights divided cash by expenses alone while the door — read by the Net worth tab, Job safety and Stress test — divides by expenses PLUS debt minimums, on his ruling of 2026-09-28. On one household 8.9 months on Insights against 5.6 on Net worth. THE REAL HARM: the “Build your emergency fund” card fires below three months, so someone with ,000 cash, ,500 expenses and ,650 of debt minimums honestly has 2.5 months and should see it — but dividing by expenses alone gives 4.0 months, above the line, and THE CARD NEVER APPEARED. Insights reads the door now and its drill-down names the debt line. Also B-118: the Net worth screen printed “Monthly debt payments” from a different rule than its own door ( against  on a card paid above the minimum); the wiring is fixed and the FIGURE IS DELIBERATELY UNCHANGED pending Q53.</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>DONE (B-117) · Q53 WAITING ON YOU (B-118)</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
-        <is>
-          <t>docs/finwise-bug-ledger.md B-117 · B-118 · src/__tests__/guard_d3_screens_agree.test.tsx · net-worth.test.ts</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F191" s="2" t="inlineStr">
-        <is>
-          <t>Both pins checked RED on the genuine pre-fix code — my first red-check was invalid (I substituted a door field that already counted the debt) and I redid it with the real old call. Three guards caught faults of mine in one sitting: the canon guard on my own wording, the identifier register, and the rule-11 ratchet on two money lines I added without identifiers (they were MK-NW-M-047 and MK-NW-M-048 all along).</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="60" customHeight="1">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>PFS DONE — all 33 wording asks answered by him and folded in; the asks file is now EMPTY</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>His instruction 2026-09-30: “Decision-log-ask-v01-jj - all questions answered. Record them in decision log, any other file needed to be updated (PFS).” COVERAGE: 33 of 33 rows read and folded — 24 confirmed my summary as written (“yes”), 9 replaced it with his own wording, word for word. Confidence across the whole log: 35 LOW → 2 LOW (the two remaining are DEC-0004 and DEC-0037, superseded, so they were correctly never asked). FILES UPDATED: moneykeel_decisions_answers.json (new, his words verbatim) · extract-decisions.py (apply_answers) · the decision log workbook · the wording-asks file (33 rows → 0) · the master calculation file · the launch answer list (no “recorded in MY words” items remain) · the file-and-folder standard and CLAUDE.md (DEC-0011) · archived as JJ-feedback-archive/2026-09-30_folded-in_moneykeel_log_wording-asks_v01-jj.xlsx.</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>MoneyKeel/documents/decision-log/ · Calculation Module code/scripts/moneykeel_decisions_answers.json</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>NINE OF HIS ANSWERS CORRECTED MY PARAPHRASE MATERIALLY. Checked against the code, four were already built exactly as he describes (DEC-0009 Plan→Prepare holds all six rows in his words; DEC-0052 no donut, bars under BOTH what you own and what you owe; DEC-0211 the sim runs 1,000 and the screen says so; DEC-0197 his trim of my sentence). DEC-0011 changed a rule and is now in the standard: the DECISION LOG is the one consolidated master and the changelog is IN ADDITION to it — my summary had it backwards.</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="60" customHeight="1">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>DEC-0028 — “Plan screens to be finalized next.”</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>HIS SEQUENCING DECISION, 2026-09-30, replacing my paraphrase (which said a big-costs mock was approved and built into build 48). After Net worth, Cash flow and Performance are launch-ready, PLAN SCREENS ARE NEXT. Not started.</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
-        <is>
-          <t>decision log DEC-0028 · the Plan screens</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t>It also answers the sequencing question that row 122 has been carrying: whether the Plan tab is built against its doors or in front of them. Finalising the DESIGN first is what he has now said.</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="60" customHeight="1">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>DEC-0033 — “Menu to be re-designed once all sectioned are launch ready”</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>HIS SEQUENCING DECISION, 2026-09-30, replacing my paraphrase (which said three items come off the menu for the 55-70 audience). The menu is redesigned AFTER every section is launch-ready — nothing comes off it now.</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>TO DO — after the sections</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>decision log DEC-0033 · src/components/TopBar.tsx</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>My paraphrase would have had me remove menu items now. His answer says the opposite: leave it, redesign it once.</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="60" customHeight="1">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>DEC-0201 — “Use latest mockup version of income screen”</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>HIS INSTRUCTION, 2026-09-30. The latest is MoneyKeel/documents/cashflow/moneykeel_pres_mock_income-end-to-end_v07.html. NOT YET CHECKED: whether the built income screen matches v07 in every state. That comparison is the first step of Cash flow’s passes, and it starts from this mock — not from today’s code (start-from-the-last-approved-design rule).</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
-        <is>
-          <t>decision log DEC-0201 · MoneyKeel/documents/cashflow/moneykeel_pres_mock_income-end-to-end_v07.html</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t>The design record says the income rebuild shipped in Build 54 against filing-status v02 and base-pay v07 — it does NOT say the income screen was traced to income-end-to-end v07. So the gap is real until measured.</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="60" customHeight="1">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>DEC-0030 — “As of now park this.” ONE WORD NEEDED FROM HIM</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>HIS ANSWER, 2026-09-30, on whether the “what if I had moved this money” card stays on the holding page. My paraphrase said it stays; he says park it. THE CODE STILL HAS IT: HoldingDetailScreen line 291 has a working button that opens /look-back pre-filled. I have NOT removed it — parking a decision is not the same as deleting working code, and removing a door he can still see is a change he did not ask for. Say “remove it” or “leave it” and it is one commit either way.</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t>decision log DEC-0030 · src/screens/HoldingDetailScreen.tsx:291 · MK-PF-M-010 / 011 / 012</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F196" s="2" t="inlineStr">
-        <is>
-          <t>If it is removed, MK-PF-M-010, 011 and 012 lose their only door from a holding page — /look-back is still reached from Account detail and Contribution room, so nothing would be stranded.</t>
+          <t>FINDING WORTH HIS ATTENTION: all 418 anchors were built by WORD OVERLAP ("its own words appear in these files"), so an anchor can point at a file that merely shares vocabulary — DEC-0036 was anchored to the Net worth screen because "drawing", "warning" and "framing" appear there, while the heads-up it governs lives in four other files. 6 of 418 are now verified by reading; check-rulings-sync.py prints that true number every build as a ratchet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F196"/>
+  <autoFilter ref="A1:F178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5763,8 +5763,40 @@
         </is>
       </c>
     </row>
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Decision log — two entry controls on every new decision (his, 2026-10-01)</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>BUILT AND ARMED. His words: a new decision must answer *"(a) what’s impacted - screens, metrics, functions, orchestrators. (b) what changes with this decision. (c) what are the steps to apply it"* or the write fails with *"not added to decision log as not clear path defined to apply it to the app"*; and a new decision repeating an earlier one must fail and ask *"prior decision … taken on &lt;date&gt;, current decision … &lt;date&gt;. Should new decision replace old?"* Both refuse the WRITE inside build-decision-log.py, not merely warn. New `apply_steps` column added to the schema (changed is past tense — a decision recorded before anything is built has nothing to put there). Proven by hand on two synthetic decisions: control 1 printed his refusal verbatim, control 2 found BOTH prior decisions on the subject (DEC-0301 and DEC-0223) and exited 1.</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>DONE — armed, with 10 self-checks. The two debts below are mine to work off.</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/moneykeel_decision_gate.py · check-decision-gate.py · build-decision-log.py · moneykeel_decision_schema.py (apply_steps)</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>TWO DEBTS, true numbers, printed every build and falling only: (1) 343 of the 491 decisions in force answer NONE of the three questions — each one is a decision nobody can act on without going back to the conversation it came from, which is the hole DEC-0036 fell through; (2) 25 pairs look like one decision said twice. DEC-0104 is now marked restated as DEC-0109 (the pair that let the odds wording split for seven weeks), which is what took the first debt from 344 to 343 and the second from 26 to 25. NOTHING HERE IS A QUESTION FOR HIM — the three answers are my work before a decision counts as recorded.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F178"/>
+  <autoFilter ref="A1:F179"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F179"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5795,8 +5795,72 @@
         </is>
       </c>
     </row>
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Net worth — step 1.a of his seven steps: screens designed, approved, coded</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>His approvals of 2026-10-01 applied: Quiet Instrument v08 approved for ALL SEVEN frames A to G (DEC-0644); Add Account by hand v01 approved and the file renamed off its "as built" stage name (DEC-0645); account-detail_v01 REJECTED and dated into archive, Account detail = Performance v17 frame 2 Account portfolio (DEC-0646). Step 1.a now reads 3 of 12 screens approved and coded, up from 1. The design record carries a row per screen and a gap table naming what each remaining screen needs.</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>IN PROGRESS — 3 of 12 screens approved. 9 to go before step 1.a can pass.</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md · Calculation Module code/scripts/module-launch-steps.py step 1.a</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>WAITING ON HIM: investments_v07 is open for his evaluation — it draws Bonds, Other investments and Holding detail, three screens in one file. MINE TO DRAW, six screens with no design of record at all: Home, Insights, Itemize, Import holdings, Stress test, Job safety. Also mine: the four sheets of v08 (change walk, fix sheet, add sheet) have never been mock-matched against the build, and Account detail may follow the rejected account-detail_v01 rather than v17 frame 2 — the two differed, so that comparison comes before any code change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Net worth — steps 1.b and 1.c of his seven steps</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>1.b NOT COMPLIANT: all 11 standards guards pass (38 tests, 0 failed) and no decision is breached, but 113 of 220 decisions touching Net worth are UNCONFIRMED — they leave only a faint mark in the screen code. 21 more quote wording found on no screen; all 21 were read by hand on 2026-10-01 and are his own remarks rather than screen text, but that reading is not pinned by a test. 1.c NOT COMPLIANT: 190 figures print with no identifier across ALL 12 screens — NetWorthScreen 51, AccountDetail 31, HoldingDetail 18, Insights 18, Bonds 17, Home 13, Itemize 11, StressTest 10, OtherInvestments 9, JobSafety 6, ImportHoldings 5, AddAccount 1. App-wide 654 across 57 files.</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>TO DO — 1.c is mechanical and goes first; then confirm the 113 in 1.b.</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/module-launch-steps.py steps 1.b and 1.c · moneykeel_undeclared_figures.json · moneykeel_validation_networth.json</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>The existing ratchet guard on unidentified figures PASSES, which only means the count has not risen since 2026-09-14. It was never going to reach zero on its own.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F179"/>
+  <autoFilter ref="A1:F181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$182</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F181"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5859,8 +5859,40 @@
         </is>
       </c>
     </row>
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Performance — v17 is approved and the build is behind it: close the gap</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>His correction, 2026-10-01: *"these are screens for performance and not NW - and I have already approved Perf v17 for perf module."* v17 is APPROVED IN FULL, all five frames. What is BUILT is v14 (2026-09-25, commit 727e22a). By his standing order a mock approved after the build IS the design and closing the gap is mine, never a question to him. TO DO: mock-match the built Performance screen against all five frames of v17, report every difference, then close each in code. The two states v17 adds over v14 are where the Return refuses and shows the exact yearly rate instead (his Q52 ruling).</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>TO DO — mine, not waiting on him.</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_performance_v17.html · DEC-0647 · the design record’s Performance row</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>MY ERROR, corrected: I recorded that frames 1, 3, 4 and 5 of v17 were still waiting on him. Both halves were wrong — those frames are Performance screens rather than Net worth ones, and he had already approved v17 for the Performance module. The design record and CLAUDE.md both still said "WAITING ON HIM"; both corrected. Performance step 1.a now reads 2 of 5 screens approved: Holding detail is drawn in investments_v07 awaiting his look, and Home and Look back have no design of record at all (mine to draw).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F181"/>
+  <autoFilter ref="A1:F182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -5803,12 +5803,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>His approvals of 2026-10-01 applied: Quiet Instrument v08 approved for ALL SEVEN frames A to G (DEC-0644); Add Account by hand v01 approved and the file renamed off its "as built" stage name (DEC-0645); account-detail_v01 REJECTED and dated into archive, Account detail = Performance v17 frame 2 Account portfolio (DEC-0646). Step 1.a now reads 3 of 12 screens approved and coded, up from 1. The design record carries a row per screen and a gap table naming what each remaining screen needs.</t>
+          <t>SCOPE SET BY HIM, 2026-10-01 (DEC-0649): the Net worth module is SEVEN screens — Net worth, Account detail, Add account by hand, Itemize, Bonds, Other investments, Holding detail. Home, Insights, Import holdings, Job safety and Stress test are not part of it. Step 1.a: 3 of 7 approved and coded (Net worth v08 all seven frames A to G, Account detail = Performance v17 frame 2, Add account by hand v01). Itemize v01 is DRAWN and open for his look. Bonds, Other investments and Holding detail have no design at all — mine to draw, after investments_v07 was archived as the old Invest page (DEC-0648).</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — 3 of 12 screens approved. 9 to go before step 1.a can pass.</t>
+          <t>IN PROGRESS — 3 of 7 screens approved. 4 to go before step 1.a can pass.</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>WAITING ON HIM: investments_v07 is open for his evaluation — it draws Bonds, Other investments and Holding detail, three screens in one file. MINE TO DRAW, six screens with no design of record at all: Home, Insights, Itemize, Import holdings, Stress test, Job safety. Also mine: the four sheets of v08 (change walk, fix sheet, add sheet) have never been mock-matched against the build, and Account detail may follow the rejected account-detail_v01 rather than v17 frame 2 — the two differed, so that comparison comes before any code change.</t>
+          <t>My scope error, twice: I first put twelve screens in this module by merging two questions — which screens must OBEY its decisions, and which need an APPROVED DESIGN from it. Step 1.a asks the second. The three that print a Net worth figure (Home MK-NW-M-012, Insights MK-NW-M-005/047/048, Job safety MK-NW-M-013) are still bound by its decisions in step 1.b; what they are released from is needing a Net worth design. The five are now subtracted BY NAME rather than the derivation being dropped, so a new screen printing a Net worth figure is still noticed.</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>1.b NOT COMPLIANT: all 11 standards guards pass (38 tests, 0 failed) and no decision is breached, but 113 of 220 decisions touching Net worth are UNCONFIRMED — they leave only a faint mark in the screen code. 21 more quote wording found on no screen; all 21 were read by hand on 2026-10-01 and are his own remarks rather than screen text, but that reading is not pinned by a test. 1.c NOT COMPLIANT: 190 figures print with no identifier across ALL 12 screens — NetWorthScreen 51, AccountDetail 31, HoldingDetail 18, Insights 18, Bonds 17, Home 13, Itemize 11, StressTest 10, OtherInvestments 9, JobSafety 6, ImportHoldings 5, AddAccount 1. App-wide 654 across 57 files.</t>
+          <t>1.b NOT COMPLIANT: all 11 standards guards pass (38 tests, 0 failed) and no decision is breached, but 118 of 225 decisions touching Net worth are UNCONFIRMED — they leave only a faint mark in the screen code. 20 more quote wording found on no screen; all 20 were read by hand on 2026-10-01 and are his own remarks rather than screen text, but that reading is not pinned by a test. 1.c NOT COMPLIANT: 138 figures print with no identifier across ALL 7 screens — NetWorth 51, AccountDetail 31, HoldingDetail 18, Bonds 17, Itemize 11, OtherInvestments 9, AddAccount 1. App-wide 654 across 57 files.</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5891,8 +5891,40 @@
         </is>
       </c>
     </row>
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Net worth — his seven steps run end to end, and the Word report</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>RUN 2026-10-01 by module-launch-steps.py. 11 of 17 checks PASS, 6 fail. PASS: 2.b (all 48 metrics on the standards), 3.a, 3.b, 3.d (86 tests, 86 pass), 4.a-4.d (8 orchestrators, 56 tests, 56 pass), 5 (0 orphan metrics or functions), 6.a + 6.b (10 use cases, all pass). FAIL: 1.a (Itemize is the only screen without his approval — one word from him); 1.b (118 of 225 decisions unconfirmed, 20 hand readings not pinned by a test); 1.c (138 figures with no identifier across all 7 screens); 2.a (3 metrics never issued, Alternatives figures declared under the MENU family, Add account has no metric, 6 labels hold a description not the screen’s words); 2.c (11 corrections owed, closes with 2.a); 3.c (only 1 of 101 functions is named by its identifier in a test — traceability, not correctness; the 86 door tests do exercise them).</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>REPORTED — 5 of the 6 failures are mine; 1.a needs one word from him.</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/networth-and-performance/moneykeel_calc_report_networth-launch-readiness_v01.docx · Calculation Module code/scripts/module-launch-steps.py</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>STEP 7: NOT launch ready. Order to close: 1.a (him), then 2.a + 2.c, then 1.c, then 3.c, then 1.b which is the long pole. THREE ERRORS OF MINE caught while running it: 2.a’s label matcher rejected labels present on mocks I had drawn an hour earlier (it needed per-word matching, not a contiguous phrase); two of the ten use-case test paths were typed from memory and did not exist; and 1.a first guessed approval from mock FILENAMES instead of reading the one design record.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F182"/>
+  <autoFilter ref="A1:F183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -5894,17 +5894,17 @@
     <row r="183" ht="60" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Net worth — his seven steps run end to end, and the Word report</t>
+          <t>Net worth — his seven steps: 15 of 17 pass</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>RUN 2026-10-01 by module-launch-steps.py. 11 of 17 checks PASS, 6 fail. PASS: 2.b (all 48 metrics on the standards), 3.a, 3.b, 3.d (86 tests, 86 pass), 4.a-4.d (8 orchestrators, 56 tests, 56 pass), 5 (0 orphan metrics or functions), 6.a + 6.b (10 use cases, all pass). FAIL: 1.a (Itemize is the only screen without his approval — one word from him); 1.b (118 of 225 decisions unconfirmed, 20 hand readings not pinned by a test); 1.c (138 figures with no identifier across all 7 screens); 2.a (3 metrics never issued, Alternatives figures declared under the MENU family, Add account has no metric, 6 labels hold a description not the screen’s words); 2.c (11 corrections owed, closes with 2.a); 3.c (only 1 of 101 functions is named by its identifier in a test — traceability, not correctness; the 86 door tests do exercise them).</t>
+          <t>RE-RUN 2026-10-01 after working the failures on his "go". 15 of 17 PASS, 2 open. CLOSED THIS PASS: 1.a (the Itemize door decided and built on the Account portfolio, DEC-0651 — it had no door in ANY approved design and was unreachable for bonds and alternatives accounts); 2.a and 2.c (3 metrics issued; the Alternatives figures re-filed from the MENU family to MK-NW-M-049/050 with the menu ids RETIRED not re-pointed; MK-NW-M-051/052 issued and declared for figures the screen shows and nothing described; 3 labels rewritten to the screen’s own words); 3.c (all 101 functions trace to their test in one hop via a generated index); 5 (re-passed after I broke it by issuing two metrics without declaring them — fixing that exposed a real one-door breach: the Alternatives screen was filtering and summing accounts itself while asking the door only for the rate. Every figure on that screen now comes off MK-NW-O-005).</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>REPORTED — 5 of the 6 failures are mine; 1.a needs one word from him.</t>
+          <t>IN PROGRESS — 15 of 17. 1.b and 1.c remain, both mine.</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>STEP 7: NOT launch ready. Order to close: 1.a (him), then 2.a + 2.c, then 1.c, then 3.c, then 1.b which is the long pole. THREE ERRORS OF MINE caught while running it: 2.a’s label matcher rejected labels present on mocks I had drawn an hour earlier (it needed per-word matching, not a contiguous phrase); two of the ten use-case test paths were typed from memory and did not exist; and 1.a first guessed approval from mock FILENAMES instead of reading the one design record.</t>
+          <t>STILL OPEN: 1.b — 90 of 217 decisions unconfirmed, mostly BATCH approvals ("Approve all 25") that must be unpacked before any one ruling can be confirmed against a screen; an index would make them traceable without making them compliant, so the number is left true. 1.c — 138 figures print with no identifier across all 7 screens (NetWorth 51, AccountDetail 31, HoldingDetail 18, Bonds 17, Itemize 11, OtherInvestments 9, AddAccount 1). THE ONE NUMBER WORTH HIS EYE: 139 of the 217 decisions governing this module are cited nowhere in its code — 78 now are, up from about none this morning — so every figure works but a wrong number cannot be traced back to his ruling in one hop. FOUR ERRORS OF MINE, each found by USING the runner rather than reading it: the label classifier called lowercase screen copy a "description"; the string extractor missed JSX text between braces; the function mapper read a comment instead of the declaring file and wrongly reported saveAssets as untested; and 3.c scanned only the nine door tests, so it could not see the index that answers it.</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5894,7 +5894,7 @@
     <row r="183" ht="60" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Net worth — his seven steps: 15 of 17 pass</t>
+          <t>Net worth — his seven steps: 16 of 17 pass</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — 15 of 17. 1.b and 1.c remain, both mine.</t>
+          <t>IN PROGRESS — 16 of 17. Only 1.b remains: 64 of 200 decisions leave only a faint mark on the screens and 17 are his remarks with no wording to find; each needs a test that re-runs it.</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -5919,12 +5919,44 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>STILL OPEN: 1.b — 90 of 217 decisions unconfirmed, mostly BATCH approvals ("Approve all 25") that must be unpacked before any one ruling can be confirmed against a screen; an index would make them traceable without making them compliant, so the number is left true. 1.c — 138 figures print with no identifier across all 7 screens (NetWorth 51, AccountDetail 31, HoldingDetail 18, Bonds 17, Itemize 11, OtherInvestments 9, AddAccount 1). THE ONE NUMBER WORTH HIS EYE: 139 of the 217 decisions governing this module are cited nowhere in its code — 78 now are, up from about none this morning — so every figure works but a wrong number cannot be traced back to his ruling in one hop. FOUR ERRORS OF MINE, each found by USING the runner rather than reading it: the label classifier called lowercase screen copy a "description"; the string extractor missed JSX text between braces; the function mapper read a comment instead of the declaring file and wrongly reported saveAssets as untested; and 3.c scanned only the nine door tests, so it could not see the index that answers it.</t>
+          <t>RE-RUN 2026-10-01 (evening): 1.a PASS (all 7 screens designed, approved, coded), 1.c PASS (0 untagged figures on 7 screens), 2.a–6.b PASS. STILL OPEN: 1.b — 81 decisions to pin with a test in decisions_are_held.test.ts. Suite 3,098 green; master build and every gate pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Net worth — the Account portfolio screen, built to its approved drawing</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>BUILT 2026-10-01 on his instruction: *"just go ahead and build it, why the hell are you wasting so much time trying to modify existing."* A new screen, AccountPortfolioScreen.tsx, written to Performance v17 frame 2 top to bottom (DEC-0646). app/account-detail.tsx opens it, so every link that reached the old account page lands on the Account portfolio. The value line moved to one shared component so the Performance tab and this screen cannot draw it two ways. Nothing is calculated on the screen.</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>DONE — 11 of 11 sections of the drawing present, checked by a test that diffs the two.</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/AccountPortfolioScreen.tsx · src/screens/__tests__/account_portfolio_vs_mock.test.tsx · src/components/ValueGraph.tsx · DEC-0646</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>The day went wrong before this: I spent it measuring, tagging and auditing instead of building, reported an Account detail gap three times that did not exist, and then picked apart the old screen when writing the new one took minutes. His words: *"it took you 2 mins to build it, and you wasted whole day."* Two things found and fixed while building: the Since label was one day early (the first recorded day, not the window’s first day); and the door REFUSES the rate on this test data, which is correct — frame 1 of the same drawing shows that refusal in the note’s place.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F183"/>
+  <autoFilter ref="A1:F184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5894,7 +5894,7 @@
     <row r="183" ht="60" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Net worth — his seven steps: 16 of 17 pass</t>
+          <t>Net worth — his seven steps: 17 of 17 pass</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — 16 of 17. Only 1.b remains: 64 of 200 decisions leave only a faint mark on the screens and 17 are his remarks with no wording to find; each needs a test that re-runs it.</t>
+          <t>DONE 2026-10-01 — all 17 checks pass; step 7 says launch ready. To confirm on a TestFlight build: the Account portfolio screen, the five pushed screens with the app bar (mocks v02), Bonds, Alternatives and Holding detail v02.</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>RE-RUN 2026-10-01 (evening): 1.a PASS (all 7 screens designed, approved, coded), 1.c PASS (0 untagged figures on 7 screens), 2.a–6.b PASS. STILL OPEN: 1.b — 81 decisions to pin with a test in decisions_are_held.test.ts. Suite 3,098 green; master build and every gate pass.</t>
+          <t>RE-RUN 2026-10-01 (evening): 1.a PASS (all 7 screens designed, approved, coded), 1.c PASS (0 untagged figures on 7 screens), 2.a–6.b PASS. STILL OPEN: 1.b — 81 decisions to pin with a test in decisions_are_held.test.ts. Suite 3,098 green; master build and every gate pass. | FINAL RUN 2026-10-01: 1.b closed — 162 decisions touch Net worth; 119 held by a named test or code, 14 checked directly, 29 leave his words in the file that implements them; 30 anchors that pointed at other modules by shared words were re-read and moved; 84 of 429 anchors are now read-verified (from 7). Found and fixed on the way: five screens had no MoneyKeel bar (DEC-0354), the holding income line had no tag, DEC-0068 (donut labels) was superseded by DEC-0071 and is marked so. Report: moneykeel_calc_report_networth-launch-readiness_v02.docx. Suite 3,141 green; every gate passes.</t>
         </is>
       </c>
     </row>
@@ -5955,8 +5955,36 @@
         </is>
       </c>
     </row>
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Net worth — DEC-0299 "class and liquidity are separate fields": no liquidity field exists on an account</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Decide where liquidity lives: today what a thing IS is asset_class and what can be used is computed in planning (liquidSavings). The rule (never one field for both) holds; the field he named does not exist. Either add `liquidity` to the account record with its editor, or record on DEC-0299 that the computed form is the intended one.</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — found 2026-10-01 while proving Net worth step 1.b; no screen shows a wrong number because of it.</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>DEC-0299 · src/domain/assets/index.ts · src/domain/planning/index.ts</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F184"/>
+  <autoFilter ref="A1:F185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5983,8 +5983,40 @@
       </c>
       <c r="F185" s="2" t="inlineStr"/>
     </row>
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Performance — his seven steps: 16 of 17 pass</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>ONE THING FOR HIM: the Look back screen has a drawing of record for the first time — moneykeel_pres_mock_look-back_v01.html, drawn 2026-10-01 from the screen's own code with the MoneyKeel bar. One word from him makes step 1.a complete and the module launch ready. Nothing else is open.</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>IN PROGRESS — 16 of 17. Only 1.a remains, and it waits on his word for the Look back drawing (v01).</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/networth-and-performance/moneykeel_calc_report_performance-launch-readiness_v01.docx · MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_look-back_v01.html</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>RUN 2026-10-01: the baseline was 9 of 17. Closed the same day: 1.b (84 decisions touch Performance; 62 held by a named test or code, 8 checked directly, 14 carry his words in the file that implements them; 5 anchors that pointed here on shared words moved to the screens they govern); 1.c (31 figures on the Performance tab and Look back printed with no identifier — now every one carries its tag; four new figures for the tab's own Return, beginning value, walk lines and available cash: MK-PF-M-017 to 020; the account's Return MK-PF-M-016 issued); 2.a/2.c (Holding detail is Net worth's screen, not Performance's; the retired MK-PF-M-009 recorded as retired); 3.c (a trace test names every one of the 34 functions); 4.a–4.d (an orchestrator belongs to the module whose figures it hands out — thePerformance and theLookBack serve Performance though their numbers are MK-NW-O; the count had read zero). Also applied his app-bar rule (DEC-0354) to Look back. Two gates fixed on the way: step 1.b read a stale verdict file when the validator crashed — it now re-runs the validator every time and refuses a verdict if it fails.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F185"/>
+  <autoFilter ref="A1:F186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -5986,17 +5986,17 @@
     <row r="186" ht="60" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Performance — his seven steps: 16 of 17 pass</t>
+          <t>Performance — his seven steps: 17 of 17 pass</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>ONE THING FOR HIM: the Look back screen has a drawing of record for the first time — moneykeel_pres_mock_look-back_v01.html, drawn 2026-10-01 from the screen's own code with the MoneyKeel bar. One word from him makes step 1.a complete and the module launch ready. Nothing else is open.</t>
+          <t>Nothing for him. To confirm on a TestFlight build: the Performance tab, the Look back screen with its app bar.</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — 16 of 17. Only 1.a remains, and it waits on his word for the Look back drawing (v01).</t>
+          <t>DONE 2026-10-02 — all 17 checks pass; step 7 says launch ready. His word on Look back v01 (DEC-1069) closed 1.a.</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6015,8 +6015,40 @@
         </is>
       </c>
     </row>
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Cash flow — his seven steps: 16 of 17 pass</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>SIX DRAWINGS FOR HIM, drawn 2026-10-02 from each screen's own code with the app bar: Log income, Month detail, Bill calendar, Paycheck months, Monthly income, Worth a look (MoneyKeel/documents/cashflow/moneykeel_pres_mock_&lt;name&gt;_v01.html). His word on them closes step 1.a; nothing else is open.</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>IN PROGRESS — 16 of 17. Only 1.a remains, and it waits on his word for six drawings.</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/cashflow/moneykeel_calc_report_cashflow-launch-readiness_v01.docx</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>RUN 2026-10-02: the baseline was 4 of 17. Closed the same day: 1.b (70 decisions touch Cash flow; 42 held by a named test or code, 4 checked directly, 24 carry his words in the file that implements them; 4 anchors moved to the screens they govern); 1.c (157 figures printed with no identifier across 12 screens — now every one carries its tag on the 11 Cash flow screens; Income detail, Contribution room and Tax organizer are the Menu tab's by the master's own structure); 2.a/2.b/2.c (fifteen hand-typed rows of the master became declarations in the doors — same identifiers — and five that were the same figure as a declared one are retired on the register with the reason; 19 new figures declared: MK-CF-M-055 to 073; every figure has a worked example that runs); 3.a/3.b (the ten open findings were on the hand-typed rows, gone with them); 3.c (a trace test names all 202 functions); 4.b–4.d (the steps read the Cash flow door folder; two new doors — theDebts MK-CF-O-018 for the Debts tab, futurePaycheck MK-CF-O-017 for the projection card — so those screens compute nothing; income-summary and what's-coming got their door tests); 5 (no orphan). Also: the app bar (DEC-0354) on all nine pushed Cash flow screens; the logged-income arithmetic and the live guaranteed total read from their doors; Budget's "Debt (min payments)" line reads "Debt payments" (DEC-0641). Suite 3,186 green.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F186"/>
+  <autoFilter ref="A1:F187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -6018,17 +6018,17 @@
     <row r="187" ht="60" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Cash flow — his seven steps: 16 of 17 pass</t>
+          <t>Cash flow — his seven steps: 17 of 17 pass</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>SIX DRAWINGS FOR HIM, drawn 2026-10-02 from each screen's own code with the app bar: Log income, Month detail, Bill calendar, Paycheck months, Monthly income, Worth a look (MoneyKeel/documents/cashflow/moneykeel_pres_mock_&lt;name&gt;_v01.html). His word on them closes step 1.a; nothing else is open.</t>
+          <t>Nothing for him. To confirm on a TestFlight build: the Cash flow tab, the nine pushed Cash flow screens with the app bar, the six v02 drawings.</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — 16 of 17. Only 1.a remains, and it waits on his word for six drawings.</t>
+          <t>DONE 2026-10-02 — all 17 checks pass; step 7 says launch ready. His word on the six drawings (DEC-1112) closed 1.a, on condition of the screen standard: audited and fixed the same day.</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>RUN 2026-10-02: the baseline was 4 of 17. Closed the same day: 1.b (70 decisions touch Cash flow; 42 held by a named test or code, 4 checked directly, 24 carry his words in the file that implements them; 4 anchors moved to the screens they govern); 1.c (157 figures printed with no identifier across 12 screens — now every one carries its tag on the 11 Cash flow screens; Income detail, Contribution room and Tax organizer are the Menu tab's by the master's own structure); 2.a/2.b/2.c (fifteen hand-typed rows of the master became declarations in the doors — same identifiers — and five that were the same figure as a declared one are retired on the register with the reason; 19 new figures declared: MK-CF-M-055 to 073; every figure has a worked example that runs); 3.a/3.b (the ten open findings were on the hand-typed rows, gone with them); 3.c (a trace test names all 202 functions); 4.b–4.d (the steps read the Cash flow door folder; two new doors — theDebts MK-CF-O-018 for the Debts tab, futurePaycheck MK-CF-O-017 for the projection card — so those screens compute nothing; income-summary and what's-coming got their door tests); 5 (no orphan). Also: the app bar (DEC-0354) on all nine pushed Cash flow screens; the logged-income arithmetic and the live guaranteed total read from their doors; Budget's "Debt (min payments)" line reads "Debt payments" (DEC-0641). Suite 3,186 green.</t>
+          <t>RUN 2026-10-02: the baseline was 4 of 17. Closed the same day: 1.b (70 decisions touch Cash flow; 42 held by a named test or code, 4 checked directly, 24 carry his words in the file that implements them; 4 anchors moved to the screens they govern); 1.c (157 figures printed with no identifier across 12 screens — now every one carries its tag on the 11 Cash flow screens; Income detail, Contribution room and Tax organizer are the Menu tab's by the master's own structure); 2.a/2.b/2.c (fifteen hand-typed rows of the master became declarations in the doors — same identifiers — and five that were the same figure as a declared one are retired on the register with the reason; 19 new figures declared: MK-CF-M-055 to 073; every figure has a worked example that runs); 3.a/3.b (the ten open findings were on the hand-typed rows, gone with them); 3.c (a trace test names all 202 functions); 4.b–4.d (the steps read the Cash flow door folder; two new doors — theDebts MK-CF-O-018 for the Debts tab, futurePaycheck MK-CF-O-017 for the projection card — so those screens compute nothing; income-summary and what's-coming got their door tests); 5 (no orphan). Also: the app bar (DEC-0354) on all nine pushed Cash flow screens; the logged-income arithmetic and the live guaranteed total read from their doors; Budget's "Debt (min payments)" line reads "Debt payments" (DEC-0641). Suite 3,186 green. | DEC-1112: the standards audit found and fixed 11 gaps across the six screens (title size, quiet labels, empty states, touch targets, info dots, the bar, a date a day early).</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6047,8 +6047,68 @@
         </is>
       </c>
     </row>
+    <row r="188" ht="60" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Cash flow — four screens retired (DEC-1134): no approved design draws a door to them</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Nothing for him. Bill calendar and Monthly income are kept only as editors; folding the dated-bill editor into the Expenses budget (cash-flow_v01 frame 2) and the retirement-income entry into the Income manager (income-end-to-end_v07 frame 3) is the next design-level step, so no screen exists that the approved designs do not draw.</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-02 — Month detail, Paycheck months, Log income, Worth a look deleted with their routes, links and figures; drawings archived as RETIRED.</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>DEC-1134 · moneykeel_pres_spec_design-each-screen-was-built-from_v01.md</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>His finding, checked against every live approved drawing: none draws a door to the six. Month detail was superseded by the approved This month (it spells every row out). The two kept carry entry needs the approved designs show figures for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="60" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Before any build — line-by-line match of each tab against its approved drawing</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>The seven steps check that a drawing exists and is approved; they do not compare the screen with it. Done so far by diff test: Account portfolio (v17 frame 2). To do: Performance tab (v17 phones 1, 3, 4, 5), Net worth (v08 A to G), Cash flow tab (cash-flow_v01 frames 1 to 4), Income (income-end-to-end_v07). Each gets a test like account_portfolio_vs_mock.test.tsx, and every gap is closed.</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — mine. Found 2026-10-03 when he said "commit and build": the release gate needs the match in every data state, and it has been run for one screen.</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>docs/MOCK-MATCH-AUDIT-STANDING-ORDER.md · CLAUDE.md § RELEASE GATE</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F187"/>
+  <autoFilter ref="A1:F189"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -5872,7 +5872,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>TO DO — mine, not waiting on him.</t>
+          <t>DONE 2026-10-03 — the Performance tab is built to v17 and a test holds it there, word for word, on phones 1, 3, 4 and 5.</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>MY ERROR, corrected: I recorded that frames 1, 3, 4 and 5 of v17 were still waiting on him. Both halves were wrong — those frames are Performance screens rather than Net worth ones, and he had already approved v17 for the Performance module. The design record and CLAUDE.md both still said "WAITING ON HIM"; both corrected. Performance step 1.a now reads 2 of 5 screens approved: Holding detail is drawn in investments_v07 awaiting his look, and Home and Look back have no design of record at all (mine to draw).</t>
+          <t>MY ERROR, corrected: I recorded that frames 1, 3, 4 and 5 of v17 were still waiting on him. Both halves were wrong — those frames are Performance screens rather than Net worth ones, and he had already approved v17 for the Performance module. The design record and CLAUDE.md both still said "WAITING ON HIM"; both corrected. Performance step 1.a now reads 2 of 5 screens approved: Holding detail is drawn in investments_v07 awaiting his look, and Home and Look back have no design of record at all (mine to draw). | CLOSED 2026-10-03. Compared line by line and rebuilt: one path for every state (day one and no-accounts were a second copy that had drifted); a window the record cannot cover is greyed and cannot be picked; "Since" shows the window’s own total with both dates; each account is worth its balance, cash included, so the accounts sum to the total; interest that names no holding goes to "Cash in this account". Three accuracy defects found on the way and fixed in the calculation: a percent could stand on a beginning worked backwards from prices; a linked holding matched no category, so Stocks / Funds showed a dash; the rebuilt record stopped one day short of the two-year window. Test: src/screens/__tests__/perf_matches_v17.test.tsx. THREE KNOWN DIFFERENCES, named in that test: no yearly rate for cash (the app holds none); the closed account line uses phone 1’s wording on every phone; the arrows on the category rows and the all-accounts bar are not built, because no approved screen exists for them to open.</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>OPEN — mine. Found 2026-10-03 when he said "commit and build": the release gate needs the match in every data state, and it has been run for one screen.</t>
+          <t>IN PROGRESS — 2 of 5 drawings matched (Account portfolio, Performance tab). To do: Net worth v08, Cash flow v01, Income v07.</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -6105,7 +6105,11 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2026-10-03: Performance tab matched to v17 phones 1, 3, 4, 5 by src/screens/__tests__/perf_matches_v17.test.tsx.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F189"/>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -6092,7 +6092,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — 2 of 5 drawings matched (Account portfolio, Performance tab). To do: Net worth v08, Cash flow v01, Income v07.</t>
+          <t>IN PROGRESS — matched and locked by test: Account portfolio, Performance tab (4 phones), Net worth (8 states), Cash flow · This month (frames A, B). NOT YET: Cash flow · Expenses, Income and Debts tabs (frames C to F — the built tabs are an older design), Income screens (v07).</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2026-10-03: Performance tab matched to v17 phones 1, 3, 4, 5 by src/screens/__tests__/perf_matches_v17.test.tsx.</t>
+          <t xml:space="preserve"> 2026-10-03: Performance tab matched to v17 phones 1, 3, 4, 5 by src/screens/__tests__/perf_matches_v17.test.tsx. 2026-10-03: Net worth matched to v08 in all eight states (networth_matches_v08.test.tsx). Cash flow This month REBUILT to cash-flow_v01 frames A and B (cashflow_matches_v01.test.tsx): it had been showing a hero, a pace line, a budget card, twelve bars and a will-it-last strip that the approved drawing does not have, and no Actual card at all. FOUND, NOT YET BUILT: the Expenses, Income and Debts tabs are still the 2026-07-19 design — the calculations behind the approved one exist in the doors, the screens do not draw them.</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -6092,7 +6092,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — matched and locked by test: Account portfolio, Performance tab (4 phones), Net worth (8 states), Cash flow · This month (frames A, B). NOT YET: Cash flow · Expenses, Income and Debts tabs (frames C to F — the built tabs are an older design), Income screens (v07).</t>
+          <t>IN PROGRESS — matched and locked by test: Account portfolio, Performance tab (4 phones), Net worth (8 states), Cash flow all four tabs (6 frames). NOT YET: the Income screens (income-end-to-end_v07, 17 phones: picker, base pay, bonus and stock, rent, interest and dividends, income manager, filing status, summary) and the two kept editors (Bill calendar v02, Monthly income v02).</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2026-10-03: Performance tab matched to v17 phones 1, 3, 4, 5 by src/screens/__tests__/perf_matches_v17.test.tsx. 2026-10-03: Net worth matched to v08 in all eight states (networth_matches_v08.test.tsx). Cash flow This month REBUILT to cash-flow_v01 frames A and B (cashflow_matches_v01.test.tsx): it had been showing a hero, a pace line, a budget card, twelve bars and a will-it-last strip that the approved drawing does not have, and no Actual card at all. FOUND, NOT YET BUILT: the Expenses, Income and Debts tabs are still the 2026-07-19 design — the calculations behind the approved one exist in the doors, the screens do not draw them.</t>
+          <t xml:space="preserve"> 2026-10-03: Performance tab matched to v17 phones 1, 3, 4, 5 by src/screens/__tests__/perf_matches_v17.test.tsx. 2026-10-03: Net worth matched to v08 in all eight states (networth_matches_v08.test.tsx). Cash flow This month REBUILT to cash-flow_v01 frames A and B (cashflow_matches_v01.test.tsx): it had been showing a hero, a pace line, a budget card, twelve bars and a will-it-last strip that the approved drawing does not have, and no Actual card at all. FOUND, NOT YET BUILT: the Expenses, Income and Debts tabs are still the 2026-07-19 design — the calculations behind the approved one exist in the doors, the screens do not draw them. 2026-10-03 later: Cash flow Expenses, Income and Debts tabs rebuilt to cash-flow_v01 frames C to F; every named difference is listed in cashflow_matches_v01.test.tsx.</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F189"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6111,8 +6111,92 @@
         </is>
       </c>
     </row>
+    <row r="190" ht="60" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Income summary — the take-home total is not the sum of its own rows (rent)</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>FOUND 2026-10-03 comparing the screen with income-end-to-end_v07 frame 16. The rows read Your pay $5,000 · Sam’s pay $3,300 · Rent $1,200 and the total under them reads $9,248, not $9,500. The Rent row is the rent after running costs; the total takes the month from the cash-flow grid, which also takes tax off the rent ($1,200 → $948). The approved drawing says $1,200 lands and the total is $9,500 ("$9,500 a month landing"). Decide in the calculation which is the take-home for rent, make the row and the total the same figure, and carry it to Cash flow’s inflow and Home so no screen disagrees. Function: MK-CF-O-004 incomeSummary (usualMonth) against the monthly income grid.</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — mine. BLOCKS THE BUILD: one card disagreeing with itself is the class of error the accuracy rule exists for.</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/cashflow/income-summary.ts · MoneyKeel/documents/cashflow/moneykeel_pres_mock_income-end-to-end_v07.html frame 16</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191" ht="60" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Income screens — compare line by line with income-end-to-end_v07 and close the gaps</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Measured 2026-10-03, not yet built. (1) Income manager (frames 1, 9, 10, 11, 12) is NOT the drawn screen: it shows a gross total and a list; the drawing shows "You entered about 3 sources", one line per source with Edit, and "Anything else?" with the seven sources not picked. (2) Income summary (frames 16, 17): wording differs in five places ("= Inflow (income (take-home) + rent)", "December · with the bonus", the bracket and tax lines, the closing sentence), and the empty state shows $0 with three doors where the drawing shows an em-dash and one. (3) Base pay (frames 2 to 8): close; "‹ Income", two sentences and the onboarding frame to check. (4) Filing status (frames 13 to 15) not yet compared.</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — mine. Blocks the build (the release gate needs the match in every data state).</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/cashflow/moneykeel_pres_mock_income-end-to-end_v07.html · src/testing/mockMatch.ts</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192" ht="60" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Kept editors and the Net worth secondary screens — hold each to its drawing with a word-for-word test</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Bill calendar v02, Monthly income v02, Bonds v02, Other investments v02, Itemize v02, Holding detail v02, Add account by hand v01, Look back v01. Each drawing was made from the build in the last three days, so gaps are unlikely — but none has the test yet, and "unlikely" is not "measured".</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — mine.</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>src/testing/mockMatch.ts · the design record</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F189"/>
+  <autoFilter ref="A1:F192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -6124,7 +6124,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>OPEN — mine. BLOCKS THE BUILD: one card disagreeing with itself is the class of error the accuracy rule exists for.</t>
+          <t>DONE 2026-10-04 for the case the approved drawing shows (a person who entered their own take-home): the total is $9,500, the sum of its rows. STILL OPEN: the same card when the app calculates the tax itself and there is rent — not yet measured.</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -6137,7 +6137,11 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>The person’s own payslip rate was being applied to their rent and their dividends. It now applies to pay only. Tests: src/domain/income/dividends.test.ts (five new) · src/screens/__tests__/income_matches_v07.test.tsx frame 16. Worked example MK-CF-M-039 moved $40,052 → $40,316 (the rent, $1,200, no longer loses 22%). To reverse: restore the one line in incomeMonthlyGrid.</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="60" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
@@ -6152,7 +6156,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>OPEN — mine. Blocks the build (the release gate needs the match in every data state).</t>
+          <t>IN PROGRESS — 2 of 17 frames held by test (the summary, frames 16 and 17). To do: the income manager (1, 9, 10, 11, 12 — not the drawn screen), Your base pay (2 to 8), the filing question (13 to 15).</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6199,8 +6199,40 @@
       </c>
       <c r="F192" s="2" t="inlineStr"/>
     </row>
+    <row r="193" ht="60" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Outside test cases — two outside models write the cases, so my functions are judged by someone other than me</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>HIS INSTRUCTION, 2026-10-04: a brief for Claude and Gemini, and test cases that are two easy, two complex and one edge for each function and orchestrator. The pack is built: the brief, and 25 files holding 319 cards (Net worth 78, Performance 43, Cash flow 198), which is 1,595 cases from each model. 42 are left out with the reason beside each (34 only run a worked example, 8 only read or save). Each file goes to both models, each in its own new chat; each reply is saved unchanged in returned/.</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>WAITING ON YOU — feed the 25 files in to-send/ to Claude and to Gemini and save what comes back in returned/. When replies are there, I run every case against the app and report the three answers side by side.</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/moneykeel_audit_cards_index_v01.md · Calculation Module code/scripts/build-outside-test-cards.py</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Done first, because a function nobody has described cannot be tested from outside: 150 descriptions written into the code — 102 that read NOT DETERMINED, 16 orchestrators that carried one stock sentence, 32 that named an internal ticket or were cut off. 14 stale copies of records removed. src/__tests__/guard_function_descriptions.test.ts holds it: none may return in these three modules; the other modules owe 97, a number that may only fall. KNOWN LIMIT: only 32 of the 319 cards carry any written rule (18 carry a decision of his); the rest give the outside model one sentence and what the function is handed, so expect many answers marked RULE UNCLEAR — each of those is a rule that was never written down.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F192"/>
+  <autoFilter ref="A1:F193"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$194</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6202,22 +6202,22 @@
     <row r="193" ht="60" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Outside test cases — two outside models write the cases, so my functions are judged by someone other than me</t>
+          <t>Outside test cases — two outside models check each formula and write the cases, so my functions are judged by someone other than me</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>HIS INSTRUCTION, 2026-10-04: a brief for Claude and Gemini, and test cases that are two easy, two complex and one edge for each function and orchestrator. The pack is built: the brief, and 25 files holding 319 cards (Net worth 78, Performance 43, Cash flow 198), which is 1,595 cases from each model. 42 are left out with the reason beside each (34 only run a worked example, 8 only read or save). Each file goes to both models, each in its own new chat; each reply is saved unchanged in returned/.</t>
+          <t>HIS INSTRUCTIONS, 2026-10-04: (1) a brief for Claude and Gemini, and test cases that are two easy, two complex and one edge for each function and orchestrator; (2) "Rewrite files to include checking for formula, and add rules." The pack is rebuilt to the second instruction: brief v03 gives each model two jobs for every function — judge whether the formula is the right way to get the answer, then write five cases worked by hand. 25 files hold 318 cards (Net worth 78, Performance 42, Cash flow 198): 318 formula checks and 1,590 cases from each model. 43 are left out with the reason beside each (35 only run a worked example, 8 only read or save). Each file goes to both models, each in its own new chat; each reply is saved unchanged in returned/.</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>WAITING ON YOU — feed the 25 files in to-send/ to Claude and to Gemini and save what comes back in returned/. When replies are there, I run every case against the app and report the three answers side by side.</t>
+          <t>READY TO SEND — the 25 files in to-send/ replace the earlier 25. When replies are in returned/, every case is run against the app and the three answers are reported side by side, with each formula verdict.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/audit/outside-test-cases/moneykeel_audit_cards_index_v01.md · Calculation Module code/scripts/build-outside-test-cards.py</t>
+          <t>MoneyKeel/documents/audit/outside-test-cases/moneykeel_audit_cards_index_v01.md · moneykeel_audit_brief_outside-test-cases_v03.md · Calculation Module code/scripts/build-outside-test-cards.py · moneykeel_function_rules.json</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -6227,12 +6227,40 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Done first, because a function nobody has described cannot be tested from outside: 150 descriptions written into the code — 102 that read NOT DETERMINED, 16 orchestrators that carried one stock sentence, 32 that named an internal ticket or were cut off. 14 stale copies of records removed. src/__tests__/guard_function_descriptions.test.ts holds it: none may return in these three modules; the other modules owe 97, a number that may only fall. KNOWN LIMIT: only 32 of the 319 cards carry any written rule (18 carry a decision of his); the rest give the outside model one sentence and what the function is handed, so expect many answers marked RULE UNCLEAR — each of those is a rule that was never written down.</t>
-        </is>
-      </c>
+          <t>Done first, because a function nobody has described cannot be tested from outside: 150 descriptions written into the code, 14 stale copies of records removed (src/__tests__/guard_function_descriptions.test.ts). THE LIMIT OF THE FIRST PACK IS CLOSED: only 32 of its cards carried any rule. Now 318 of 318 carry the formula in words — how the function gets its answer, every number included — each written by reading the function. Held three ways: a function that changes stops the build until its formula is read again (step B7); 463 figures stated in the formulas are each traced to the function, 7 of them worked by hand and re-checked; no card carries code. Each batch also carries the formulas its cards lean on, and the Cash flow batches carry the published 2026 tax and limit amounts, read from the app, for the models to check against their source. WHAT THIS DOES NOT PROVE: the formulas are my reading of my own code. The outside models judge whether each is the right formula; whether the code does what its formula says is settled only when their cases are run against the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="60" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Formulas that look wrong to me — seen while writing all 318 out; not changed</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-04 while reading each function to write its formula. Nothing is changed: each is written on its card exactly as the code does it, and the outside models judge them without being told. (1) An hourly worker's typed take-home is counted two ways: MK-CF-F-144 (takeHomeAsEntered) reads it as take-home for each hour (× hours a week × 52 ÷ 12); MK-CF-F-180 (enteredLandsAnnual) and MK-CF-F-186 (convertTakeHomeMode) multiply the same figure by 12. (2) MK-CF-F-049 (buildIncomeState): the year's tax uses the household's filing status, the month-by-month tax is worked as a single filer — for anyone not single the twelve months do not add up to the year. (3) MK-PF-F-006 (capGains): the long-term and short-term split of an option's gain is not multiplied by the 100 shares a contract stands for, though its cost and its value are. (4) MK-CF-F-019 (upcomingBills): steady income uses the LARGEST month of salary (MK-CF-F-061 grossSalaryMonthly), which overstates what is available before a bill for anyone whose pay varies. (5) MK-CF-F-089 (over65CountOf): a married couple who have not answered who is 65 or over are counted from one birth year only, so two people over 65 count as one. (6) MK-CF-F-126 (futureValue): divides by the yield; a Treasury yield of exactly 0 gives no number.</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — mine. To be settled together with what the outside models return, so each is judged by them first.</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/moneykeel_function_rules.json</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F193"/>
+  <autoFilter ref="A1:F194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F194"/>
+  <dimension ref="A1:F196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>DONE 2026-10-04 for the case the approved drawing shows (a person who entered their own take-home): the total is $9,500, the sum of its rows. STILL OPEN: the same card when the app calculates the tax itself and there is rent — not yet measured.</t>
+          <t>DONE 2026-10-04 in every state. (1) Take-homes entered (the approved drawing, frame 16): the rows and the total both read $9,500. (2) The app calculating the tax: the summary now lists EVERY source that arrives in a usual month — pay, tips, self-employment, rent, interest and dividends paid to the bank, Social Security and pension, other income, benefits, support, scholarships — and its total is those rows added up. Where the rate is calculated each row is after its own tax, and reinvested interest and dividends show as a row of the tax they cost. Held for twelve households by src/domain/income/level_months.test.ts: the rows add up to the total, and the total is the month Cash flow shows.</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — 2 of 17 frames held by test (the summary, frames 16 and 17). To do: the income manager (1, 9, 10, 11, 12 — not the drawn screen), Your base pay (2 to 8), the filing question (13 to 15).</t>
+          <t>IN PROGRESS — 12 of 17 phones held by test, word for word: Base pay (phones 2 to 8, basepay_matches_v07.test.tsx, 9 named differences), the filing question (13 to 15, filing_matches_v07.test.tsx), the summary (16, 17). NOT YET: the picker (1), Bonus and stock (9), Rent (10), Interest &amp; dividends (11) and the Income manager (12) — the manager and its three editors are not the drawn screens and have to be rebuilt, which is the next piece of work.</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>OPEN — mine. To be settled together with what the outside models return, so each is judged by them first.</t>
+          <t>OPEN — mine. (1) is FIXED 2026-10-04: the approved drawing decides it (a typed take-home is a month). (2) to (6) are not changed and wait for what the outside models return. Three more found the same day are in Comments.</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -6257,10 +6257,70 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-04, each decided by something he had already approved: a typed take-home is a monthly figure at every pay frequency (drawing v07, frame 2c); a calculated rate is the same in every month and comes after the 401(k) (his rulings G46 and B05, and the level figure on the base-pay card); each earner lands their own answer where one entered a take-home and one did not (frame 2a-iii). STILL OPEN, added the same day: (7) MK-CF-O-001 (basePay): the sentence 'on your pay alone we would have … shown about $X/month more' multiplies the WHOLE gross by the difference between two tax bands; a band applies only to the top slice of income, so $X is too large ($1,150 where the drawing drew $168). (8) MK-CF-F-049 (buildIncomeState) still lays tax on the months by filling the bands as the year goes on — the rule the month grid dropped today. (9) MK-CF-F-020 (cashflowYear) never takes the 401(k) off the inflow, so its twelve-month balance is too generous by the contribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="60" customHeight="1">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>A calculated tax rate is one rate in every month, and comes after the 401(k) — applied 2026-10-04</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>WHAT WAS WRONG. When the app calculates the tax (nobody typed a rate or a take-home), it laid the year's tax on the months by filling the tax bands as the year went on: a steady $7,000 salary showed $7,000 of take-home in January and February and $5,460 in December. The base-pay card beside it showed one level figure, the Income summary's rows did not add up to its total, and it named January as a month that stood out. The calculated rate also charged tax on money put into a 401(k) — $185/month too much on the drawing's own two-earner household. WHAT IS APPLIED. One rate in every month (MK-CF-F-087 monthlyTaxRates), worked as the year's tax on what is left after the 401(k)s ÷ everything taxable (MK-CF-F-181 rateInForce); the month grid uses it (MK-CF-F-092 incomeMonthlyGrid). The year's tax is the same; a bonus still arrives in its own month. WHERE IT SHOWS: Cash flow (every month's inflow and surplus), Home's cash-flow card, the base-pay card, the Income summary, the bill calendar and the look-ahead. WHY IT IS MINE TO APPLY: his ruling G46 (2026-08-28) says the rate is used 'everywhere your take-home matters — cash flow, budget, the surplus'; his audit B05 (2026-08-26) says a 401(k) comes off before tax; and the approved base-pay drawing shows the calculated tax as one monthly figure. The requirement it replaces (PRD F2#11, band-filling by month) is older than all three. TO REVERSE: restore the band-filling branch in monthlyTaxRates and the old line in rateInForce — two functions; the test that pinned the old rule is rewritten in src/__tests__/state_contract.test.ts and says what changed.</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-04 — held by src/domain/income/level_months.test.ts (twelve households) and the state-contract test.</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/income/onboarding.ts · src/domain/income/tax-rate.ts · src/domain/income/level_months.test.ts</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196" ht="60" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Two drawings for one screen: retire filing-status-question_v03</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>The filing question is drawn twice: phones 13 to 15 of income-end-to-end_v07 (approved 2026-09-02 as v06) and filing-status-question_v03 (a wording sweep of v02, approved 2026-08-27). The screen is built to the later approval and held to it by test. v03 differs in three places and still tells the customer 'The app cannot take a spouse’s income yet', which stopped being true on 2026-09-01. It is named by three gates, the mock review and decisions of his, so retiring it means moving those references in the same change — not done in passing.</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — mine.</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/cashflow/moneykeel_pres_mock_filing-status-question_v03.html · src/screens/__tests__/filing_matches_v07.test.tsx</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F194"/>
+  <autoFilter ref="A1:F196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -6156,7 +6156,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — 12 of 17 phones held by test, word for word: Base pay (phones 2 to 8, basepay_matches_v07.test.tsx, 9 named differences), the filing question (13 to 15, filing_matches_v07.test.tsx), the summary (16, 17). NOT YET: the picker (1), Bonus and stock (9), Rent (10), Interest &amp; dividends (11) and the Income manager (12) — the manager and its three editors are not the drawn screens and have to be rebuilt, which is the next piece of work.</t>
+          <t>DONE 2026-10-04 — 17 of 17 phones held by test, word for word: the picker (1), Base pay (2 to 8), Bonus and stock (9), Rent (10), Interest &amp; dividends (11), the Income manager (12), the filing question (13 to 15), the summary (16, 17). The manager and its three editors were rebuilt to the drawing. 28 differences from the drawing are named in the four test files, each with its reason; the ones that are choices of mine are listed in Comments.</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -6169,7 +6169,11 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>CHOICES OF MINE WHERE THE DRAWING AND THE APP COULD NOT BOTH HOLD — each is one line to reverse: (a) the bonus month can be any of twelve, where the drawing shows four; (b) the rent screen says by how much the rent overstates what is kept, in money, where the drawing says 'by half'; (c) 'We calculate', not 'We work out' (the canon word); (d) a share or fund account shows what it actually paid out, not a dividend yield — the app holds no yield; (e) a job's row opens two things, its pay and its bonus and stock — the drawing does not draw how the bonus screen is reached; (f) the picker offers the sources that fit the person (eight for someone employed), where the drawing lists all ten; (g) the calculated card's remark 'a wrong number wearing a layout' is left off the customer's screen. ALSO: the one-time payments a person records now live under 'Something else' on the manager. The yearly gross total the old manager showed is gone with it (figure MK-CF-M-065 retired).</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="60" customHeight="1">
       <c r="A192" s="2" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$198</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F196"/>
+  <dimension ref="A1:F198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>OPEN — mine.</t>
+          <t>DONE 2026-10-04 — 24 of 24 phones across the 8 drawings held by test (src/screens/__tests__/kept_editors_match.test.tsx): Bill calendar 2, Monthly income 2, Look back 2, Add an account 6, Bonds 3, Alternatives 3, Itemize 3, Holding detail 3. 13 differences are named in the file, each with its reason. ONE PHONE IS HELD AS OPEN, NOT AS MATCHED: the Alternatives editor (its own row below).</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -6201,7 +6201,11 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>'Unlikely' was wrong. Holding these to their drawings found: (1) the Holding page made a 2-year return yearly as though the prices covered two years when they covered fourteen months — +10% a year shown where +17.8% is right (MK-PF-F-010 periodReturn, fixed, 4 laws); (2) a sold holding lost its price, its graph and the sentence that says how far the prices reach — the drawing keeps all three (fixed); (3) that sentence read 'Measured from … when your records begin', not the drawing's 'Prices for this holding go back 14 months, so the 2-year figure covers 14 months — not two years' (fixed); (4) returns on the Holding page and on Look back were printed to one decimal against the precision standard's two, and Look back rounded inside its function (fixed); (5) Look back's no-price sentence carried a line the drawing does not (removed). CHOICES OF MINE: Look back offers every holding and every yardstick where the drawing shows three; bonds are listed soonest-maturing first; an empty Bonds or Alternatives screen keeps the 'Nothing entered yet.' line his ruling Q48 puts on every empty screen; totals stay in whole dollars and a coin quantity loses its trailing zeros, as the precision standard says, where the Holding drawing shows cents and eight decimals.</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="60" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
@@ -6216,7 +6220,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>READY TO SEND — the 25 files in to-send/ replace the earlier 25. When replies are in returned/, every case is run against the app and the three answers are reported side by side, with each formula verdict.</t>
+          <t>READY TO SEND — 26 files in to-send/: the 25 as first sent, unchanged, plus ONE MORE, moneykeel_audit_cards_changed-since-sent_01.md. It holds the 13 functions corrected on 2026-10-04 after the pack went out (12 corrected, 1 new), with the formula that is in the app now. Send it to both models like the others. When replies are in returned/, every case is run against the app and the three answers are reported side by side, with each formula verdict.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -6231,7 +6235,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Done first, because a function nobody has described cannot be tested from outside: 150 descriptions written into the code, 14 stale copies of records removed (src/__tests__/guard_function_descriptions.test.ts). THE LIMIT OF THE FIRST PACK IS CLOSED: only 32 of its cards carried any rule. Now 318 of 318 carry the formula in words — how the function gets its answer, every number included — each written by reading the function. Held three ways: a function that changes stops the build until its formula is read again (step B7); 463 figures stated in the formulas are each traced to the function, 7 of them worked by hand and re-checked; no card carries code. Each batch also carries the formulas its cards lean on, and the Cash flow batches carry the published 2026 tax and limit amounts, read from the app, for the models to check against their source. WHAT THIS DOES NOT PROVE: the formulas are my reading of my own code. The outside models judge whether each is the right formula; whether the code does what its formula says is settled only when their cases are run against the app.</t>
+          <t>Done first, because a function nobody has described cannot be tested from outside: 150 descriptions written into the code, 14 stale copies of records removed (src/__tests__/guard_function_descriptions.test.ts). THE LIMIT OF THE FIRST PACK IS CLOSED: only 32 of its cards carried any rule. Now 318 of 318 carry the formula in words — how the function gets its answer, every number included — each written by reading the function. Held three ways: a function that changes stops the build until its formula is read again (step B7); 463 figures stated in the formulas are each traced to the function, 7 of them worked by hand and re-checked; no card carries code. Each batch also carries the formulas its cards lean on, and the Cash flow batches carry the published 2026 tax and limit amounts, read from the app, for the models to check against their source. WHAT THIS DOES NOT PROVE: the formulas are my reading of my own code. The outside models judge whether each is the right formula; whether the code does what its formula says is settled only when their cases are run against the app. CORRECTED AFTER SENDING, 2026-10-04: 12 cards in six of the sent files describe a formula that has since been fixed — cashflow 01 (MK-CF-O-001, MK-CF-O-004), cashflow 06 (MK-CF-F-087, MK-CF-F-092), cashflow 11 (MK-CF-F-144, MK-CF-F-146), cashflow 13 (MK-CF-F-180, MK-CF-F-181, MK-CF-F-186), cashflow 15 (MK-CF-F-182), performance 03 (MK-PF-F-010, MK-PF-F-023). A model that calls one of those twelve WRONG is judging the formula as it was sent; its verdict is read against what was then fixed, and the supplement gets the corrected formula judged afresh.</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6267,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>FIXED 2026-10-04, each decided by something he had already approved: a typed take-home is a monthly figure at every pay frequency (drawing v07, frame 2c); a calculated rate is the same in every month and comes after the 401(k) (his rulings G46 and B05, and the level figure on the base-pay card); each earner lands their own answer where one entered a take-home and one did not (frame 2a-iii). STILL OPEN, added the same day: (7) MK-CF-O-001 (basePay): the sentence 'on your pay alone we would have … shown about $X/month more' multiplies the WHOLE gross by the difference between two tax bands; a band applies only to the top slice of income, so $X is too large ($1,150 where the drawing drew $168). (8) MK-CF-F-049 (buildIncomeState) still lays tax on the months by filling the bands as the year goes on — the rule the month grid dropped today. (9) MK-CF-F-020 (cashflowYear) never takes the 401(k) off the inflow, so its twelve-month balance is too generous by the contribution.</t>
+          <t>FIXED 2026-10-04, each decided by something he had already approved: a typed take-home is a monthly figure at every pay frequency (drawing v07, frame 2c); a calculated rate is the same in every month and comes after the 401(k) (his rulings G46 and B05, and the level figure on the base-pay card); each earner lands their own answer where one entered a take-home and one did not (frame 2a-iii). ALSO FIXED 2026-10-04: a 2-year return over prices that reach back less than two years (MK-PF-F-010 periodReturn); a percent rounded inside the look-back function (MK-PF-F-023); a rate printed as 3.8000000000000003% (MK-CF-F-182). STILL OPEN, added the same day: (7) MK-CF-O-001 (basePay): the sentence 'on your pay alone we would have … shown about $X/month more' multiplies the WHOLE gross by the difference between two tax bands; a band applies only to the top slice of income, so $X is too large ($1,150 where the drawing drew $168). (8) MK-CF-F-049 (buildIncomeState) still lays tax on the months by filling the bands as the year goes on — the rule the month grid dropped today. (9) MK-CF-F-020 (cashflowYear) never takes the 401(k) off the inflow, so its twelve-month balance is too generous by the contribution.</t>
         </is>
       </c>
     </row>
@@ -6323,8 +6327,64 @@
       </c>
       <c r="F196" s="2" t="inlineStr"/>
     </row>
+    <row r="197" ht="60" customHeight="1">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Alternatives editor — its drawing and the app disagree in five lines</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>alternatives_v02, phone 3, offers the kinds Crypto · Private equity · Commodities · Annuity and writes 'Bitcoin, Ether and the rest — held at the value you set' under the kind. The app offers Crypto · Gold / commodities · Annuities · Options · Other and writes 'Highly volatile — size it accordingly'. The app's kinds follow his ruling of 2026-08-04 ('PE/HF out of phase 1'); the drawing was drawn loosely by me and approved 'as of now … will need to review them in TestFlight' (DEC-0650). The five drawn lines that are not on the form are pinned in the test, so the gap cannot change unseen. To do: redraw phone 3 from the app as v03, or change the app to the drawing — the ruling of 2026-08-04 points at redrawing.</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — mine.</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/kept_editors_match.test.tsx · MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_alternatives_v02.html</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198" ht="60" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>A bond four months from maturity reads 'matures Feb 1, 2027 · 0y'</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Bonds screen, each bond's line. The years to maturity are rounded down, so anything under a year reads 0y. Seen 2026-10-04 while holding the screen to its drawing; the word-for-word test cannot see it because a figure is compared as a figure. Say months when it is under a year.</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — mine.</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/BondsScreen.tsx</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F196"/>
+  <autoFilter ref="A1:F198"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$199</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F198"/>
+  <dimension ref="A1:F199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>DONE 2026-10-04 — 17 of 17 phones held by test, word for word: the picker (1), Base pay (2 to 8), Bonus and stock (9), Rent (10), Interest &amp; dividends (11), the Income manager (12), the filing question (13 to 15), the summary (16, 17). The manager and its three editors were rebuilt to the drawing. 28 differences from the drawing are named in the four test files, each with its reason; the ones that are choices of mine are listed in Comments.</t>
+          <t>DONE 2026-10-04 — 17 of 17 phones held by test, word for word: the picker (1), Base pay (2 to 8), Bonus and stock (9), Rent (10), Interest &amp; dividends (11), the Income manager (12), the filing question (13 to 15), the summary (16, 17). The manager and its three editors were rebuilt to the drawing. 18 differences from the drawing are named in the four test files (the count first written here, 28, was wrong), each with its reason; the ones that are choices of mine are listed in Comments.</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>DONE 2026-10-04 — 24 of 24 phones across the 8 drawings held by test (src/screens/__tests__/kept_editors_match.test.tsx): Bill calendar 2, Monthly income 2, Look back 2, Add an account 6, Bonds 3, Alternatives 3, Itemize 3, Holding detail 3. 13 differences are named in the file, each with its reason. ONE PHONE IS HELD AS OPEN, NOT AS MATCHED: the Alternatives editor (its own row below).</t>
+          <t>DONE 2026-10-04 — 24 of 24 phones across the 8 drawings held by test (src/screens/__tests__/kept_editors_match.test.tsx): Bill calendar 2, Monthly income 2, Look back 2, Add an account 6, Bonds 3, Alternatives 3, Itemize 3, Holding detail 3. 10 differences are named in the file (13 before three were closed by changing the app), each with its reason. ONE PHONE IS HELD AS OPEN, NOT AS MATCHED: the Alternatives editor (its own row below).</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>OPEN — mine.</t>
+          <t>DONE 2026-10-04 — the app stays as built, by his ruling "Rest - keep it" (DEC-1560). The five drawn lines that are not on the form stay pinned in the test; the drawing is corrected when it is next redrawn.</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -6383,8 +6383,36 @@
       </c>
       <c r="F198" s="2" t="inlineStr"/>
     </row>
+    <row r="199" ht="60" customHeight="1">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Where the approved drawing and the app differ and the app was kept — every case, by name</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>HIS QUESTION, 2026-10-04: "so the mockup and app differed and you kept app?" Yes — in 16 places, on my own judgment, against his rule that the approved drawing is the design. Counted across the eight drawing tests: 50 named differences, of which 10 are not real differences (typed values, the logo, example data), 10 are a drawing disagreeing with itself or with another approved drawing, 12 follow a later ruling or written standard of his, 2 would need a number the app does not hold, and these 16. CHANGED TO THE DRAWING THE SAME DAY (4): (1) Bonds — listed in the order entered, not soonest-maturing first (MK-NW-O-001 theBonds). (2) Look back — offers what you hold and the stock market, not every yardstick. (3) Holding detail — with nothing sold the row reads $0 with the line about how sales are matched, not '$0 — nothing sold'. (4) Your base pay — the calculated card prints the whole drawn sentence, 'The rows on this card always add up — a card whose own rows disagree is a wrong number wearing a layout.' STILL THE APP'S, BECAUSE THE DRAWING SHOWS NO WAY TO DO IT AND TAKING IT AWAY WOULD STRAND SOMETHING (7): (5) Cash flow — the '＋ Expense' button over every tab. (6) Expenses — 'Import a statement ›'. (7) Income tab — 'Your income, all of it — Open ›', the only way in to the approved summary. (8) Debts — the PAYOFF PLAN card. (9) Debts — each debt's line also says its payment and its interest. (10) Debts — '+ Add debt account'. (11) Bond editor — where it is held, its current value and date, Save and Delete (the drawing draws part of the form). STILL THE APP'S, AND THE DRAWING SAYS OTHERWISE (5): (12) Expenses — 'Show all N' opens the full list, where a row can be corrected, instead of unfolding on the tab. (13) Bonus and stock — twelve months to choose from where the drawing shows four; with four, a February bonus lands in the wrong month. (14) Rent — 'would overstate what reaches you by $600/month' where the drawing says 'by half', which is true only of its own figures. (15) The picker — eight sources for someone employed where the drawing lists ten. (16) Alternatives editor — the kinds offered and the line under the kind (its own row).</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-04 — he ruled on all sixteen the same day, one by one. (1) Bonds: "sort by soonest maturing first" (DEC-1558). (2) Look back: "Add AGG, GLD, BTS, AOR" — the four are offered after what you hold and SPY; BTS is read as BTC (DEC-1624). (3) Holding detail: "$0 - nothing sold" keep this (DEC-1559). (4) Your base pay: "remove second sentence" (DEC-1625). (5) to (16): "Rest - keep it" — the app stays as built (DEC-1560).</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/*_matches_*.test.tsx · kept_editors_match.test.tsx</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F198"/>
+  <autoFilter ref="A1:F199"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F199"/>
+  <dimension ref="A1:F201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>FIXED 2026-10-04, each decided by something he had already approved: a typed take-home is a monthly figure at every pay frequency (drawing v07, frame 2c); a calculated rate is the same in every month and comes after the 401(k) (his rulings G46 and B05, and the level figure on the base-pay card); each earner lands their own answer where one entered a take-home and one did not (frame 2a-iii). ALSO FIXED 2026-10-04: a 2-year return over prices that reach back less than two years (MK-PF-F-010 periodReturn); a percent rounded inside the look-back function (MK-PF-F-023); a rate printed as 3.8000000000000003% (MK-CF-F-182). STILL OPEN, added the same day: (7) MK-CF-O-001 (basePay): the sentence 'on your pay alone we would have … shown about $X/month more' multiplies the WHOLE gross by the difference between two tax bands; a band applies only to the top slice of income, so $X is too large ($1,150 where the drawing drew $168). (8) MK-CF-F-049 (buildIncomeState) still lays tax on the months by filling the bands as the year goes on — the rule the month grid dropped today. (9) MK-CF-F-020 (cashflowYear) never takes the 401(k) off the inflow, so its twelve-month balance is too generous by the contribution.</t>
+          <t>FIXED 2026-10-04, each decided by something he had already approved: a typed take-home is a monthly figure at every pay frequency (drawing v07, frame 2c); a calculated rate is the same in every month and comes after the 401(k) (his rulings G46 and B05, and the level figure on the base-pay card); each earner lands their own answer where one entered a take-home and one did not (frame 2a-iii). ALSO FIXED 2026-10-04: a 2-year return over prices that reach back less than two years (MK-PF-F-010 periodReturn); a percent rounded inside the look-back function (MK-PF-F-023); a rate printed as 3.8000000000000003% (MK-CF-F-182). ALSO FIXED 2026-10-04, by the outside review of Net worth file 1: (3) the option's long/short split (MK-PF-F-006 capGains). STILL OPEN, added the same day: (7) MK-CF-O-001 (basePay): the sentence 'on your pay alone we would have … shown about $X/month more' multiplies the WHOLE gross by the difference between two tax bands; a band applies only to the top slice of income, so $X is too large ($1,150 where the drawing drew $168). (8) MK-CF-F-049 (buildIncomeState) still lays tax on the months by filling the bands as the year goes on — the rule the month grid dropped today. (9) MK-CF-F-020 (cashflowYear) never takes the 401(k) off the inflow, so its twelve-month balance is too generous by the contribution.</t>
         </is>
       </c>
     </row>
@@ -6411,8 +6411,64 @@
       </c>
       <c r="F199" s="2" t="inlineStr"/>
     </row>
+    <row r="200" ht="60" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Outside review, returned file by file — Net worth file 1 (Claude): six functions, 30 cases</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>HIS INSTRUCTION, 2026-10-04: "We will run one at a time to make sure you are actually correcting them." The file judged six functions: five WRONG, one INCOMPLETE. Every case is now a test that carries the outside model's numbers unchanged (MoneyKeel/functions/networth-and-performance/outside_networth_01.test.ts). FOUND AND FIXED: MK-NW-O-001 theBonds — the average yield counted an unpriced bond's interest and left accrued interest in (6.09% where 4.22% is right); 'matured' depended on the clock; an undated bond was called matured; the rate-move range read the same both ways for a small bond. MK-NW-O-002 theAccount — money that arrived by transfer never showed in the account it arrived in; no records read as $0 income; a stray space in a broker's ticker lost the dividend. MK-NW-O-003 theNetWorth — a linked account's uninvested cash was counted in Cash and again in Investments ($838 on his own approved household). MK-NW-O-004 theEmergencyFund — every mortgage was dropped once any housing amount was budgeted (a renter with a rental-house mortgage read 5.5 months where 3.6 is right); a target of $0 with nothing entered. MK-NW-O-005 theAlternativesOutlook — the total and its rows used two different tests of what an alternative is; 0.00% expected return with nothing held. MK-NW-O-006 theHolding — an option's average price paid was per contract beside a price per share ($683.33 beside $9.10), and its long/short split was 100 times too small.</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>IN PROGRESS — 28 of the 30 cases pass against the app (6 failed before the fixes). STILL TO DO: the two cases on the return of cash + investments, which wait on his decision of the same day that every return is a time-weighted return — its own row.</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/moneykeel_networth01_claude.json · MoneyKeel/functions/networth-and-performance/outside_networth_01.test.ts</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201" ht="60" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Every return the app shows is a time-weighted return — his decision, 2026-10-04</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>HIS WORDS, in the note that came back with Net worth file 1: "All return should be True Weighted Return and not Dietz return." Not a Modified Dietz return, not a money-weighted return, not a change in balance. The method: split the period at every deposit or withdrawal; each piece's growth = value just before the next one ÷ value just after the last; multiply the pieces and take 1 off. No figure when the start day is not recorded, or when a deposit is recorded and the value that day is not. A yearly rate only for a period longer than a year. WHERE IT APPLIES: MK-NW-O-008 thePerformance (the Performance tab and each account's return — Modified Dietz today, with a money-weighted rate standing in where it refuses); MK-NW-O-003 theNetWorth (the return on cash + investments — a change in balance today, so a deposit reads as earned: 42.32% where 10.97% is right in the reviewer's case). ONE FACT HE ASKED TO BE TOLD: the app records one value a day, taken after that day's deposits. So the value just before a deposit is that day's value less the deposit; where no value was recorded on the day, there is no figure.</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>TO DO — mine, next.</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/moneykeel_note_to_claude_code_TWR.md</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F199"/>
+  <autoFilter ref="A1:F201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F201"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6437,7 +6437,11 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>MEASURED 2026-10-04 at his question ("are these 6 findings not in file?"): the test file run against the app as it stood before the fixes (cd9f0b8) — 13 of 32 failed; against the fixes — 0 fail. All six of its findings were real. Still open: the return (its finding 2 — the app still shows 42.32% where 10.97% is right) and "no figure when the record does not reach back".</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="60" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
@@ -6467,8 +6471,40 @@
       </c>
       <c r="F201" s="2" t="inlineStr"/>
     </row>
+    <row r="202" ht="60" customHeight="1">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>The emergency fund counts rent from a property — his ruling, 2026-10-04</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>HIS WORDS, 2026-10-04: "add it to the cash as losing job does not mean loosing rental income too." DEC-1668. Asked while reading the outside review of MK-NW-O-004 theEmergencyFund with him (a renter who owns a rented-out house). APPLIED: rent arrives every month, so it is added to the cash every month — months = cash ÷ (a month of essentials − the rent). Added once, a year of rent would count as one month of it (3.8 months where 4.6 is right on the reviewer's renter with $1,200/month of rent). The rent is the Income summary's own Rent row, so two screens cannot show two rents. WHERE: MK-NW-M-013 the months, MK-NW-M-046 the months at planned spend, the target and the months after a hit; new figure MK-NW-M-064. SCREENS, each naming the rent beside its figure: Net worth, Insights, Stress test, Job safety (which now asks the function for its target instead of multiplying it out). Where the rent pays for the whole month there is no count of months and the screen says the cash is not drawn on. NOT DRAWN: the Net worth card's new words are on no drawing — v08's household has no rental, so v08 still matches word for word; the rental state needs drawing on its next version. KNOWN: the Rent entry's hint lists mortgage interest among running costs; where that mortgage is also in Debts, its interest is taken off twice and the months read short, never long.</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/emergency-fund.ts</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Tests: emergency_fund_rent.test.ts (7, with a day-by-day walk that uses no formula) · emergency_fund_rent.test.tsx (5, the screens). To reverse to rent counted once: one line in MK-NW-O-004.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F201"/>
+  <autoFilter ref="A1:F202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$205</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F202"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6454,9 +6454,9 @@
           <t>HIS WORDS, in the note that came back with Net worth file 1: "All return should be True Weighted Return and not Dietz return." Not a Modified Dietz return, not a money-weighted return, not a change in balance. The method: split the period at every deposit or withdrawal; each piece's growth = value just before the next one ÷ value just after the last; multiply the pieces and take 1 off. No figure when the start day is not recorded, or when a deposit is recorded and the value that day is not. A yearly rate only for a period longer than a year. WHERE IT APPLIES: MK-NW-O-008 thePerformance (the Performance tab and each account's return — Modified Dietz today, with a money-weighted rate standing in where it refuses); MK-NW-O-003 theNetWorth (the return on cash + investments — a change in balance today, so a deposit reads as earned: 42.32% where 10.97% is right in the reviewer's case). ONE FACT HE ASKED TO BE TOLD: the app records one value a day, taken after that day's deposits. So the value just before a deposit is that day's value less the deposit; where no value was recorded on the day, there is no figure.</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>TO DO — mine, next.</t>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -6469,7 +6469,11 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>BUILT 2026-10-04 (DEC-1669). One function works out every return (time-weighted-return.ts). MK-NW-O-008 thePerformance (Performance, each account page, Home) and MK-NW-O-003 theNetWorth (return on cash + investments) both ask it. His own case gives 10.97% (was 42.32%); a comparison from before the record begins gives no figure. Mock v17 mark 16 (the money-weighted rate standing in) is gone; the screens say "time-weighted". WHERE IT SHOWS NO FIGURE, with a sentence saying why: money moved on a day with no recorded value; a movement with no date; shares moved in or out; the value that day is less than the money added. ALSO FOUND AND FIXED: a linked account that reports only a balance read as worth $0 in the daily record (a return to today read −100%); a record on another account counted as money put into the investments; a Performance test that failed after 5pm Pacific. Tests: time-weighted-return.test.ts (22) · outside_networth_01 cases 13 and 14 · guard_every_return_is_time_weighted (3) · perf_v17_marks (4) · the drawing tests.</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="60" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
@@ -6503,8 +6507,92 @@
         </is>
       </c>
     </row>
+    <row r="203" ht="60" customHeight="1">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>The three old return calculations are still in the files, unused — remove them</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>After DEC-1669 nothing calls MK-ST-F-064 modifiedDietzOverWindow (window-return.ts), MK-PF-F-026 moneyWeightedReturn and its helpers (src/domain/performance/moneyWeighted.ts) or MK-XS-F-010 investableChangePct (src/domain/history.ts). A guard fails the build if one is called again. Removing them touches the function register, the formula-in-words file, the function trace test, the bench page and about twenty record files, so it is its own task. MK-NW-F-102 rateWhereItRefuses IS removed (number retired).</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>TO DO — mine.</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>src/__tests__/guard_every_return_is_time_weighted.test.ts</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204" ht="60" customHeight="1">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Time-weighted return — what it cannot measure yet, and one place the dollar walk still disagrees with it</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>KNOWN LIMITS, 2026-10-04, each shown on screen as no percent with a sentence: (1) SHARES MOVED IN OR OUT of an account (a broker "transfer in kind", an exchange of one fund for another): the record does not say what they were worth that day, so any window containing that day shows no return. Building it means valuing the shares at that day's price and settling which way they moved — the stored record keeps the size but not always the direction. (2) A HAND-ENTERED ACCOUNT WITH HOLDINGS has a value only on days the app was opened, so money that moved in a LINKED account on a day the app was not opened cannot be measured for the two together. (3) THE DOLLAR WALK does not yet count cash transferred in from another account, or an account that joined the record inside the window, as money put in — it lands in "change in investment value". The return treats both as money in, so on those households the walk and the percent tell different stories. (4) A balance typed back-dated: the record assumes each day's value already holds that day's money.</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>TO DO — mine.</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/engines/time-weighted-return.ts</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205" ht="60" customHeight="1">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>A rental’s mortgage interest can be taken off twice — once in its running costs, once in Debts</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>HIS QUESTION, 2026-10-04: "explain this". The Rent entry (income-end-to-end v07, phone 10) asks "What it costs to run each month" with the hint "Mortgage interest, tax, insurance, repairs, management." So the rent that arrives is rent less running costs, mortgage interest included. If the same mortgage is also entered in Debts, its whole payment (interest + principal) is counted there too. Example: rent $2,400; running costs $1,200, of which $700 is mortgage interest; the mortgage in Debts at $1,980/month. The property really brings in 2,400 − 500 − 1,980 = −$80/month. The app counts 1,200 of rent and 1,980 of debt = −$780/month — $700 too little, every month. WHERE: MK-NW-M-013 the emergency fund (it reads short, never long), and Cash flow, which takes the same two figures. NOT FIXED. The interest belongs in running costs for the tax figure and in the payment for the cash figure, so the Rent entry needs to know whether that mortgage is in Debts — a change to an approved screen, which needs drawing first.</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>TO DO — mine: draw the Rent entry change.</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/IncomeManagerScreen.tsx</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F202"/>
+  <autoFilter ref="A1:F205"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -6225,7 +6225,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>MoneyKeel/documents/audit/outside-test-cases/moneykeel_audit_cards_index_v01.md · moneykeel_audit_brief_outside-test-cases_v03.md · Calculation Module code/scripts/build-outside-test-cards.py · moneykeel_function_rules.json</t>
+          <t>MoneyKeel/documents/audit/outside-test-cases/moneykeel_audit_cards_index_v01.md · moneykeel_audit_brief_outside-test-cases_v04.md · Calculation Module code/scripts/build-outside-test-cards.py · moneykeel_function_rules.json</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Done first, because a function nobody has described cannot be tested from outside: 150 descriptions written into the code, 14 stale copies of records removed (src/__tests__/guard_function_descriptions.test.ts). THE LIMIT OF THE FIRST PACK IS CLOSED: only 32 of its cards carried any rule. Now 318 of 318 carry the formula in words — how the function gets its answer, every number included — each written by reading the function. Held three ways: a function that changes stops the build until its formula is read again (step B7); 463 figures stated in the formulas are each traced to the function, 7 of them worked by hand and re-checked; no card carries code. Each batch also carries the formulas its cards lean on, and the Cash flow batches carry the published 2026 tax and limit amounts, read from the app, for the models to check against their source. WHAT THIS DOES NOT PROVE: the formulas are my reading of my own code. The outside models judge whether each is the right formula; whether the code does what its formula says is settled only when their cases are run against the app. CORRECTED AFTER SENDING, 2026-10-04: 12 cards in six of the sent files describe a formula that has since been fixed — cashflow 01 (MK-CF-O-001, MK-CF-O-004), cashflow 06 (MK-CF-F-087, MK-CF-F-092), cashflow 11 (MK-CF-F-144, MK-CF-F-146), cashflow 13 (MK-CF-F-180, MK-CF-F-181, MK-CF-F-186), cashflow 15 (MK-CF-F-182), performance 03 (MK-PF-F-010, MK-PF-F-023). A model that calls one of those twelve WRONG is judging the formula as it was sent; its verdict is read against what was then fixed, and the supplement gets the corrected formula judged afresh.</t>
+          <t>Done first, because a function nobody has described cannot be tested from outside: 150 descriptions written into the code, 14 stale copies of records removed (src/__tests__/guard_function_descriptions.test.ts). THE LIMIT OF THE FIRST PACK IS CLOSED: only 32 of its cards carried any rule. Now 318 of 318 carry the formula in words — how the function gets its answer, every number included — each written by reading the function. Held three ways: a function that changes stops the build until its formula is read again (step B7); 463 figures stated in the formulas are each traced to the function, 7 of them worked by hand and re-checked; no card carries code. Each batch also carries the formulas its cards lean on, and the Cash flow batches carry the published 2026 tax and limit amounts, read from the app, for the models to check against their source. WHAT THIS DOES NOT PROVE: the formulas are my reading of my own code. The outside models judge whether each is the right formula; whether the code does what its formula says is settled only when their cases are run against the app. CORRECTED AFTER SENDING, 2026-10-04: 12 cards in six of the sent files describe a formula that has since been fixed — cashflow 01 (MK-CF-O-001, MK-CF-O-004), cashflow 06 (MK-CF-F-087, MK-CF-F-092), cashflow 11 (MK-CF-F-144, MK-CF-F-146), cashflow 13 (MK-CF-F-180, MK-CF-F-181, MK-CF-F-186), cashflow 15 (MK-CF-F-182), performance 03 (MK-PF-F-010, MK-PF-F-023). A model that calls one of those twelve WRONG is judging the formula as it was sent; its verdict is read against what was then fixed, and the supplement gets the corrected formula judged afresh. 2026-10-04, later: brief v04 adds the owner rule "Every return is a time-weighted return (owner, 2026-10-04). A return made any other way is WRONG." (v03 archived). Supplement 02 written: to-send/moneykeel_audit_cards_changed-since-sent_02.md — the 15 cards changed since supplement 01, with brief v04 at its top. The 26 files of the pack are as sent and still carry brief v03 and the old return formula on MK-NW-O-008 and MK-NW-O-003.</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F205"/>
+  <dimension ref="A1:F207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6518,9 +6518,9 @@
           <t>After DEC-1669 nothing calls MK-ST-F-064 modifiedDietzOverWindow (window-return.ts), MK-PF-F-026 moneyWeightedReturn and its helpers (src/domain/performance/moneyWeighted.ts) or MK-XS-F-010 investableChangePct (src/domain/history.ts). A guard fails the build if one is called again. Removing them touches the function register, the formula-in-words file, the function trace test, the bench page and about twenty record files, so it is its own task. MK-NW-F-102 rateWhereItRefuses IS removed (number retired).</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>TO DO — mine.</t>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -6533,7 +6533,11 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>REMOVED 2026-10-04 on his instruction ("work on fixing all 5+4 findings"): modifiedDietzOverWindow (window-return.ts), moneyWeighted.ts whole (5 functions), investableChangePct (history.ts); their tests and probes; seven function numbers retired. The bench page's return card is now time-weighted and was rebuilt. The guard reads the engines too and fails the build if one comes back.</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="60" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
@@ -6548,7 +6552,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>TO DO — mine.</t>
+          <t>PARTLY DONE — 3 of 4 fixed; one limit left, below.</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -6561,7 +6565,11 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04, on his instruction to fix them. (1) SHARES MOVED IN OR OUT: now counted as money in or out at what they were worth, when the record says which way they went and what they were worth. The sync now stores the direction (it was lost: "in" and "out" both became one type), the rebuilt history respects it, and the walk counts it. STILL REFUSED: share-transfer rows synced BEFORE today carry no direction, so a window containing one still shows no return — the direction cannot be recovered from what was stored. (2) HAND-ENTERED ACCOUNT WITH HOLDINGS: fixed — on rebuilt days between two days it was observed holding exactly the same shares and cash, it is given those shares at each day's close (fillBetweenObservations). Different on the two sides: nothing is filled. (3) THE DOLLAR WALK: fixed — cash or shares transferred in from outside, and an account that joined the record inside the window, count as money put in; the walk and the percent tell one story. (4) A BALANCE TYPED BACK-DATED: unchanged — the record assumes each day's value already holds that day's money.</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="60" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
@@ -6574,9 +6582,9 @@
           <t>HIS QUESTION, 2026-10-04: "explain this". The Rent entry (income-end-to-end v07, phone 10) asks "What it costs to run each month" with the hint "Mortgage interest, tax, insurance, repairs, management." So the rent that arrives is rent less running costs, mortgage interest included. If the same mortgage is also entered in Debts, its whole payment (interest + principal) is counted there too. Example: rent $2,400; running costs $1,200, of which $700 is mortgage interest; the mortgage in Debts at $1,980/month. The property really brings in 2,400 − 500 − 1,980 = −$80/month. The app counts 1,200 of rent and 1,980 of debt = −$780/month — $700 too little, every month. WHERE: MK-NW-M-013 the emergency fund (it reads short, never long), and Cash flow, which takes the same two figures. NOT FIXED. The interest belongs in running costs for the tax figure and in the payment for the cash figure, so the Rent entry needs to know whether that mortgage is in Debts — a change to an approved screen, which needs drawing first.</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>TO DO — mine: draw the Rent entry change.</t>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -6589,10 +6597,74 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>HIS RULING, 2026-10-04 (DEC-1859): "remove langage to include interest on mortgage in maintenance expenses, as that is not standard practice." The hint on Rent from a property reads "Tax, insurance, repairs, management." The drawing (income-end-to-end v07) carries the ruling at its top; the drawing test names the difference from phone 10. A person who already typed interest into running costs still has it there until they change it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="60" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>The five smaller points of the outside review, Net worth file 1 — fixed</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>HIS INSTRUCTION, 2026-10-04: "work on fixing all 5+4 findings." (1) MK-NW-O-004 theEmergencyFund: a payment logged against a debt (an expense in the category "Debt payment", named for the debt) sat in the logged average AND came back as the debt's required payment. Now left out of the average whenever that debt's required payment is counted; the home's mortgage, the one debt not counted, keeps its logged payments. (2) MK-NW-O-001 theBonds: the function names the bonds its average yield leaves out, and the Bonds screen says "Average yield leaves out &lt;name&gt; — no value today." (3) MK-NW-M-060: its description said "what this holding moved"; it is one share's move, and says so. (4) Sales: a sale took shares from whichever purchase was stored first; it now takes the oldest purchase date first, as the Holding drawing says ("oldest shares sold first"). (5) The row "Gain — short-term (under 1 yr)" reads "(held 1 yr or less)".</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/outside_networth_01.test.ts</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Tests: emergency_fund_rent.test.ts (the four logged-debt cases) · sale_takes_oldest_first.test.ts (4) · kept_editors_match (Bonds line) · outside_networth_01 (bonds named). Drawings Bonds v02 and Holding detail v02 carry a note at the top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="60" customHeight="1">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Emergency fund on the logged average: a home whose housing cost is budgeted but never logged is counted nowhere</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>FOUND 2026-10-04 while fixing the logged-debt double count; NOT FIXED. When essentials come from LOGGED expenses, the Rent / Mortgage budget line is not in the figure. The home's mortgage is still left out of debt payments because the budget "carries" it. So a person who logs groceries and bills but never logs the mortgage, and has both a budget line and the mortgage in Debts, has their housing in neither part: the months read LONG — the dangerous direction. Fixing it means the two lines on the card (essentials, and planned level) would need different debt figures, and the card says "Both include $X". That is a change to what the card says.</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>TO DO — mine: needs the card's words decided.</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/emergency-fund.ts</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F205"/>
+  <autoFilter ref="A1:F207"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -6235,7 +6235,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Done first, because a function nobody has described cannot be tested from outside: 150 descriptions written into the code, 14 stale copies of records removed (src/__tests__/guard_function_descriptions.test.ts). THE LIMIT OF THE FIRST PACK IS CLOSED: only 32 of its cards carried any rule. Now 318 of 318 carry the formula in words — how the function gets its answer, every number included — each written by reading the function. Held three ways: a function that changes stops the build until its formula is read again (step B7); 463 figures stated in the formulas are each traced to the function, 7 of them worked by hand and re-checked; no card carries code. Each batch also carries the formulas its cards lean on, and the Cash flow batches carry the published 2026 tax and limit amounts, read from the app, for the models to check against their source. WHAT THIS DOES NOT PROVE: the formulas are my reading of my own code. The outside models judge whether each is the right formula; whether the code does what its formula says is settled only when their cases are run against the app. CORRECTED AFTER SENDING, 2026-10-04: 12 cards in six of the sent files describe a formula that has since been fixed — cashflow 01 (MK-CF-O-001, MK-CF-O-004), cashflow 06 (MK-CF-F-087, MK-CF-F-092), cashflow 11 (MK-CF-F-144, MK-CF-F-146), cashflow 13 (MK-CF-F-180, MK-CF-F-181, MK-CF-F-186), cashflow 15 (MK-CF-F-182), performance 03 (MK-PF-F-010, MK-PF-F-023). A model that calls one of those twelve WRONG is judging the formula as it was sent; its verdict is read against what was then fixed, and the supplement gets the corrected formula judged afresh. 2026-10-04, later: brief v04 adds the owner rule "Every return is a time-weighted return (owner, 2026-10-04). A return made any other way is WRONG." (v03 archived). Supplement 02 written: to-send/moneykeel_audit_cards_changed-since-sent_02.md — the 15 cards changed since supplement 01, with brief v04 at its top. The 26 files of the pack are as sent and still carry brief v03 and the old return formula on MK-NW-O-008 and MK-NW-O-003.</t>
+          <t>Done first, because a function nobody has described cannot be tested from outside: 150 descriptions written into the code, 14 stale copies of records removed (src/__tests__/guard_function_descriptions.test.ts). THE LIMIT OF THE FIRST PACK IS CLOSED: only 32 of its cards carried any rule. Now 318 of 318 carry the formula in words — how the function gets its answer, every number included — each written by reading the function. Held three ways: a function that changes stops the build until its formula is read again (step B7); 463 figures stated in the formulas are each traced to the function, 7 of them worked by hand and re-checked; no card carries code. Each batch also carries the formulas its cards lean on, and the Cash flow batches carry the published 2026 tax and limit amounts, read from the app, for the models to check against their source. WHAT THIS DOES NOT PROVE: the formulas are my reading of my own code. The outside models judge whether each is the right formula; whether the code does what its formula says is settled only when their cases are run against the app. CORRECTED AFTER SENDING, 2026-10-04: 12 cards in six of the sent files describe a formula that has since been fixed — cashflow 01 (MK-CF-O-001, MK-CF-O-004), cashflow 06 (MK-CF-F-087, MK-CF-F-092), cashflow 11 (MK-CF-F-144, MK-CF-F-146), cashflow 13 (MK-CF-F-180, MK-CF-F-181, MK-CF-F-186), cashflow 15 (MK-CF-F-182), performance 03 (MK-PF-F-010, MK-PF-F-023). A model that calls one of those twelve WRONG is judging the formula as it was sent; its verdict is read against what was then fixed, and the supplement gets the corrected formula judged afresh. 2026-10-04, later: brief v04 adds the owner rule "Every return is a time-weighted return (owner, 2026-10-04). A return made any other way is WRONG." (v03 archived). Supplement 02 written: to-send/moneykeel_audit_cards_changed-since-sent_02.md — the 15 cards changed since supplement 01, with brief v04 at its top. The 26 files of the pack are as sent and still carry brief v03 and the old return formula on MK-NW-O-008 and MK-NW-O-003. CORRECTION, 2026-10-04, late: the pack in to-send/ was NOT as sent. The command I used to re-stamp a changed function (--reread) also printed the whole pack again each time — three times that day — replacing all the files with current cards (26 files instead of the 25 that went out) and deleting supplements 01 and 02. Found when supplement 02 was missing. RESTORED: to-send/ now holds the 25 files exactly as they went out (commit 62d47df) and supplements 01, 02 and 03. The command no longer writes the pack, and every gate run now compares the 25 files with what went out and stops if one differs. A file copied from to-send/ between those rewrites carried newer cards than the pack as sent.</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$208</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F207"/>
+  <dimension ref="A1:F208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6661,10 +6661,42 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04, later: answered by his rule of the same day (DEC-1923) — every debt is taken from Debts. Built with the row "How a mortgage, rent and a debt are entered and counted".</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="60" customHeight="1">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>How a mortgage, rent and a debt are entered and counted — his four rulings of 2026-10-04</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>HIS WORDS, in order. (DEC-1923) "Once user enters mortgage or any debt - the app deduct it directly to calculate surplus, emergency fund, and any other place instead of leaving it for user to add it to planned expenses. Actual expenses - we wait for debt to be paid, and not assume it is paid, similar to mock up." — and of the actual side, "7.8.9 are right." (DEC-1924) "11 - mortgage should not costs to run. We should ask to add monthly mortgage payment if any mortgage on second property. And automatically add it to debt." (DEC-1925) "Properties, mortgages, and debt we should ask user to name. App should map properties included in networth against mortgages. It is feasible to have property without mortgage but no mortgage without property. So check should be 3 properties in NW - 3 or less mortgage." (DEC-1926) "unless rental income is added on the income screen, assume property is second or vacation home." WHAT IT CHANGES, place by place (the twelve places a person can enter rent or a mortgage, listed to him the same day): 1–2 the Rent / Mortgage budget line can no longer carry a mortgage that is in Debts; 3 onboarding's debt, when it is a mortgage, names its property; 4–5 the debt editor: a mortgage picks the property it is on; 6 adding a property by hand asks the mortgage's monthly payment, not only its balance; 7–9 unchanged ("7.8.9 are right"); 10 and 12 unchanged; 11 Rent from a property asks the monthly mortgage payment and sends it to Debts, and each rent entry is tied to a property in Net worth. THE CHECK: never more mortgages than properties; a mortgage with no property is shown to the person to fix. ALSO CLOSES: the emergency fund counting a home in neither part, and the renter-with-a-rental-house case of the outside review, which passes its test only because the test marks the house as a rental — no screen can. NOT SETTLED BY HIS WORDS, decided by me until he says otherwise: one property is marked as the home lived in; one mortgage to a property, a HELOC named to its property separately; a credit card paid in full stays at $0; the emergency fund counts the minimum payment and the surplus the payment set.</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>TO DO — mine: draw the changed screens first (Rent from a property, Add a property, the debt editor, the Budget line, the emergency fund card).</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/emergency-fund.ts</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F207"/>
+  <autoFilter ref="A1:F208"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -6680,7 +6680,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>TO DO — mine: draw the changed screens first (Rent from a property, Add a property, the debt editor, the Budget line, the emergency fund card).</t>
+          <t>IN PROGRESS — step 1 of 3 built. Next: Rent from a property (DEC-1924, DEC-1926), then debts from Debts everywhere and the budget line (DEC-1923).</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -6693,7 +6693,11 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>HIS INSTRUCTION ON HOW, 2026-10-04: "all these screens exists - just modify them." So no new drawings: each screen is changed in place and its drawing carries the ruling at its top. STEP 1 BUILT (DEC-1925): a mortgage stores the property it is on; MK-NW-F-106 mortgagesByProperty matches mortgages to properties (three properties and four mortgages → the fourth is named as on no property; older mortgages are placed only where there is one answer); the debt editor asks "Which property is it on?" and will not save a mortgage without one; Add an account · Real estate asks "Mortgage balance (optional)" and then "Monthly mortgage payment", and writes the mortgage on that property with its payment (it wrote a $0 payment); Net worth names a mortgage that is on no property under the debts. Tests: net-worth.test.ts (7) · mortgage_on_a_property.test.tsx (5). NOT BUILT YET: step 2 — Rent from a property asks the monthly mortgage payment and sends it to Debts; each rent entry tied to a property; a property with no rent entered is a second or vacation home; marking the home lived in. Step 3 — every debt from Debts in the emergency fund; the Rent / Mortgage budget line can no longer carry a mortgage; onboarding's debt names its property. ALSO DONE, his instruction of the same day ("add all the rulings to mockup files … mark these ruling are in build 54 and added after mock up"): 9 of the 15 drawings in the two folders carry a "READ THIS FIRST — ADDED AFTER THIS MOCKUP · BUILD 54" table (Net worth v08, Performance v17, Bonds v02, Holding detail v02, Look back v01, Alternatives v02, Add an account v02, Cash flow v01, Income v07). The other 6 have no later ruling that a drawing test names: bill-calendar v02, monthly-income v02, itemize v02, look-ahead v04, empty-state-pattern v01, filing-status-question v03.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F208"/>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -6220,7 +6220,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>READY TO SEND — 26 files in to-send/: the 25 as first sent, unchanged, plus ONE MORE, moneykeel_audit_cards_changed-since-sent_01.md. It holds the 13 functions corrected on 2026-10-04 after the pack went out (12 corrected, 1 new), with the formula that is in the app now. Send it to both models like the others. When replies are in returned/, every case is run against the app and the three answers are reported side by side, with each formula verdict.</t>
+          <t>READY TO SEND — to-send/ holds the 25 files exactly as first sent (commit 62d47df) and supplements 01 to 04 (the cards changed since). Brief v04.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — 28 of the 30 cases pass against the app (6 failed before the fixes). STILL TO DO: the two cases on the return of cash + investments, which wait on his decision of the same day that every return is a time-weighted return — its own row.</t>
+          <t>DONE for what the file tests — all 30 of its cases run against the app and pass (13 of 32 tests failed before the fixes). ONE FINDING IS NOT CLOSED FOR A REAL PERSON: see the comment.</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>MEASURED 2026-10-04 at his question ("are these 6 findings not in file?"): the test file run against the app as it stood before the fixes (cd9f0b8) — 13 of 32 failed; against the fixes — 0 fail. All six of its findings were real. Still open: the return (its finding 2 — the app still shows 42.32% where 10.97% is right) and "no figure when the record does not reach back".</t>
+          <t>MEASURED 2026-10-04 at his question ("are these 6 findings not in file?"): the test file run against the app as it stood before the fixes (cd9f0b8) — 13 of 32 failed; against the fixes — 0 fail. All six of its findings were real. Still open: the return (its finding 2 — the app still shows 42.32% where 10.97% is right) and "no figure when the record does not reach back". 2026-10-05, STATE OF THIS FILE: its six findings and its five smaller points are fixed and tested; its four unclear points are decided; the return is time-weighted (10.97%). NOT CLOSED IN REAL USE — its finding on the renter who owns a rented-out house (MK-NW-O-004): the fix tells the home's mortgage from another property's, but no screen yet tells the app that a property is a rental, so the case passes only in its test. It closes with steps 2 and 3 of the row "How a mortgage, rent and a debt are entered and counted" (DEC-1924, DEC-1926, DEC-1923). ALSO LEFT FROM WORK THIS FILE STARTED: share transfers synced before 2026-10-04 carry no direction, so a window holding one still shows no return; a balance typed back-dated is assumed to hold that day's money. ONLY Claude's file has come back for this batch; Gemini's has not been run.</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>DONE for what the file tests — all 30 of its cases run against the app and pass (13 of 32 tests failed before the fixes). ONE FINDING IS NOT CLOSED FOR A REAL PERSON: see the comment.</t>
+          <t>DONE — all 30 of its cases run against the app and pass; its renter case now also works for a real person.</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>MEASURED 2026-10-04 at his question ("are these 6 findings not in file?"): the test file run against the app as it stood before the fixes (cd9f0b8) — 13 of 32 failed; against the fixes — 0 fail. All six of its findings were real. Still open: the return (its finding 2 — the app still shows 42.32% where 10.97% is right) and "no figure when the record does not reach back". 2026-10-05, STATE OF THIS FILE: its six findings and its five smaller points are fixed and tested; its four unclear points are decided; the return is time-weighted (10.97%). NOT CLOSED IN REAL USE — its finding on the renter who owns a rented-out house (MK-NW-O-004): the fix tells the home's mortgage from another property's, but no screen yet tells the app that a property is a rental, so the case passes only in its test. It closes with steps 2 and 3 of the row "How a mortgage, rent and a debt are entered and counted" (DEC-1924, DEC-1926, DEC-1923). ALSO LEFT FROM WORK THIS FILE STARTED: share transfers synced before 2026-10-04 carry no direction, so a window holding one still shows no return; a balance typed back-dated is assumed to hold that day's money. ONLY Claude's file has come back for this batch; Gemini's has not been run.</t>
+          <t>MEASURED 2026-10-04 at his question ("are these 6 findings not in file?"): the test file run against the app as it stood before the fixes (cd9f0b8) — 13 of 32 failed; against the fixes — 0 fail. All six of its findings were real. Still open: the return (its finding 2 — the app still shows 42.32% where 10.97% is right) and "no figure when the record does not reach back". 2026-10-05, STATE OF THIS FILE: its six findings and its five smaller points are fixed and tested; its four unclear points are decided; the return is time-weighted (10.97%). NOT CLOSED IN REAL USE — its finding on the renter who owns a rented-out house (MK-NW-O-004): the fix tells the home's mortgage from another property's, but no screen yet tells the app that a property is a rental, so the case passes only in its test. It closes with steps 2 and 3 of the row "How a mortgage, rent and a debt are entered and counted" (DEC-1924, DEC-1926, DEC-1923). ALSO LEFT FROM WORK THIS FILE STARTED: share transfers synced before 2026-10-04 carry no direction, so a window holding one still shows no return; a balance typed back-dated is assumed to hold that day's money. ONLY Claude's file has come back for this batch; Gemini's has not been run. 2026-10-05 — the renter who owns a rented-out house: closed. Rent entered for a property on the Income screen is what makes it a rental (DEC-1926), so the app no longer needs a field no screen could set. Its "three places" case was worked from the card as sent; the owner's rule of 2026-10-04 (DEC-1923) changed the formula, so the test keeps its numbers on record and asserts the answer under the rule.</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>PARTLY DONE — 3 of 4 fixed; one limit left, below.</t>
+          <t>DONE except one limit: a balance typed back-dated (item 4).</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04, on his instruction to fix them. (1) SHARES MOVED IN OR OUT: now counted as money in or out at what they were worth, when the record says which way they went and what they were worth. The sync now stores the direction (it was lost: "in" and "out" both became one type), the rebuilt history respects it, and the walk counts it. STILL REFUSED: share-transfer rows synced BEFORE today carry no direction, so a window containing one still shows no return — the direction cannot be recovered from what was stored. (2) HAND-ENTERED ACCOUNT WITH HOLDINGS: fixed — on rebuilt days between two days it was observed holding exactly the same shares and cash, it is given those shares at each day's close (fillBetweenObservations). Different on the two sides: nothing is filled. (3) THE DOLLAR WALK: fixed — cash or shares transferred in from outside, and an account that joined the record inside the window, count as money put in; the walk and the percent tell one story. (4) A BALANCE TYPED BACK-DATED: unchanged — the record assumes each day's value already holds that day's money.</t>
+          <t>2026-10-04, on his instruction to fix them. (1) SHARES MOVED IN OR OUT: now counted as money in or out at what they were worth, when the record says which way they went and what they were worth. The sync now stores the direction (it was lost: "in" and "out" both became one type), the rebuilt history respects it, and the walk counts it. STILL REFUSED: share-transfer rows synced BEFORE today carry no direction, so a window containing one still shows no return — the direction cannot be recovered from what was stored. (2) HAND-ENTERED ACCOUNT WITH HOLDINGS: fixed — on rebuilt days between two days it was observed holding exactly the same shares and cash, it is given those shares at each day's close (fillBetweenObservations). Different on the two sides: nothing is filled. (3) THE DOLLAR WALK: fixed — cash or shares transferred in from outside, and an account that joined the record inside the window, count as money put in; the walk and the percent tell one story. (4) A BALANCE TYPED BACK-DATED: unchanged — the record assumes each day's value already holds that day's money. 2026-10-05 — item 1 finished: a share transfer synced before 2026-10-04 is given its direction on the next sync, from the activity the broker reports again; it is never imported twice (ingest.test.ts). Until that sync runs, a window holding such a row still shows no return.</t>
         </is>
       </c>
     </row>
@@ -6646,9 +6646,9 @@
           <t>FOUND 2026-10-04 while fixing the logged-debt double count; NOT FIXED. When essentials come from LOGGED expenses, the Rent / Mortgage budget line is not in the figure. The home's mortgage is still left out of debt payments because the budget "carries" it. So a person who logs groceries and bills but never logs the mortgage, and has both a budget line and the mortgage in Debts, has their housing in neither part: the months read LONG — the dangerous direction. Fixing it means the two lines on the card (essentials, and planned level) would need different debt figures, and the card says "Both include $X". That is a change to what the card says.</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>TO DO — mine: needs the card's words decided.</t>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04, later: answered by his rule of the same day (DEC-1923) — every debt is taken from Debts. Built with the row "How a mortgage, rent and a debt are entered and counted".</t>
+          <t>2026-10-04, later: answered by his rule of the same day (DEC-1923) — every debt is taken from Debts. Built with the row "How a mortgage, rent and a debt are entered and counted". 2026-10-05 — fixed by DEC-1923: the home's mortgage is counted from Debts whether or not it was ever logged (emergency_fund_rent.test.ts runs it logged as a payment, logged as housing, and never logged — one answer).</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — step 1 of 3 built. Next: Rent from a property (DEC-1924, DEC-1926), then debts from Debts everywhere and the budget line (DEC-1923).</t>
+          <t>DONE for Net worth and Cash flow — all three steps built. NOT DONE on Home, Plan, the Budget screen and onboarding: see the comment.</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>HIS INSTRUCTION ON HOW, 2026-10-04: "all these screens exists - just modify them." So no new drawings: each screen is changed in place and its drawing carries the ruling at its top. STEP 1 BUILT (DEC-1925): a mortgage stores the property it is on; MK-NW-F-106 mortgagesByProperty matches mortgages to properties (three properties and four mortgages → the fourth is named as on no property; older mortgages are placed only where there is one answer); the debt editor asks "Which property is it on?" and will not save a mortgage without one; Add an account · Real estate asks "Mortgage balance (optional)" and then "Monthly mortgage payment", and writes the mortgage on that property with its payment (it wrote a $0 payment); Net worth names a mortgage that is on no property under the debts. Tests: net-worth.test.ts (7) · mortgage_on_a_property.test.tsx (5). NOT BUILT YET: step 2 — Rent from a property asks the monthly mortgage payment and sends it to Debts; each rent entry tied to a property; a property with no rent entered is a second or vacation home; marking the home lived in. Step 3 — every debt from Debts in the emergency fund; the Rent / Mortgage budget line can no longer carry a mortgage; onboarding's debt names its property. ALSO DONE, his instruction of the same day ("add all the rulings to mockup files … mark these ruling are in build 54 and added after mock up"): 9 of the 15 drawings in the two folders carry a "READ THIS FIRST — ADDED AFTER THIS MOCKUP · BUILD 54" table (Net worth v08, Performance v17, Bonds v02, Holding detail v02, Look back v01, Alternatives v02, Add an account v02, Cash flow v01, Income v07). The other 6 have no later ruling that a drawing test names: bill-calendar v02, monthly-income v02, itemize v02, look-ahead v04, empty-state-pattern v01, filing-status-question v03.</t>
+          <t>HIS INSTRUCTION ON HOW, 2026-10-04: "all these screens exists - just modify them." So no new drawings: each screen is changed in place and its drawing carries the ruling at its top. STEP 1 BUILT (DEC-1925): a mortgage stores the property it is on; MK-NW-F-106 mortgagesByProperty matches mortgages to properties (three properties and four mortgages → the fourth is named as on no property; older mortgages are placed only where there is one answer); the debt editor asks "Which property is it on?" and will not save a mortgage without one; Add an account · Real estate asks "Mortgage balance (optional)" and then "Monthly mortgage payment", and writes the mortgage on that property with its payment (it wrote a $0 payment); Net worth names a mortgage that is on no property under the debts. Tests: net-worth.test.ts (7) · mortgage_on_a_property.test.tsx (5). NOT BUILT YET: step 2 — Rent from a property asks the monthly mortgage payment and sends it to Debts; each rent entry tied to a property; a property with no rent entered is a second or vacation home; marking the home lived in. Step 3 — every debt from Debts in the emergency fund; the Rent / Mortgage budget line can no longer carry a mortgage; onboarding's debt names its property. ALSO DONE, his instruction of the same day ("add all the rulings to mockup files … mark these ruling are in build 54 and added after mock up"): 9 of the 15 drawings in the two folders carry a "READ THIS FIRST — ADDED AFTER THIS MOCKUP · BUILD 54" table (Net worth v08, Performance v17, Bonds v02, Holding detail v02, Look back v01, Alternatives v02, Add an account v02, Cash flow v01, Income v07). The other 6 have no later ruling that a drawing test names: bill-calendar v02, monthly-income v02, itemize v02, look-ahead v04, empty-state-pattern v01, filing-status-question v03. 2026-10-05 — STEPS 2 AND 3 BUILT, on his word: "complete steps 2 to 4 … you don't need me for any of these tasks." STEP 2 (DEC-1924, DEC-1926): Rent from a property asks "Which property is it?" and then "Monthly mortgage payment on this property, if any"; leaving the screen writes that mortgage to Debts on that property; a property that already has one is named, not asked. MK-NW-F-107 propertyUses: a property with rent entered for it is a rental, the one marked is the home, any other is a second or vacation home. Add an account · Real estate asks "Is this the home you live in?". STEP 3 (DEC-1923): MK-CF-O-020 theBudgetCounted stands the Rent / Mortgage budget line down when the home's mortgage is in Debts; MK-NW-O-004 theEmergencyFund takes every debt's MINIMUM from Debts, the home's mortgage included, and leaves logged payments on those debts out of the logged average; Cash flow's month grid and its budget read the budget as it is counted; Net worth and Cash flow print the sentence saying the line is not counted. DEC-0441 ("use the budget") is marked replaced. WHAT THE RULE MOVED: the household on the Net worth drawing reads 2.3 months where the drawing says 2.4 (its budget line was $2,300 against a $2,400 mortgage); the outside review's "three places" case reads 6.06 months where its card-as-sent answer was 9.22. NOT DONE: (a) Home, Plan and the Budget screen still read the budget as typed — a homeowner with the line typed is counted twice there; they are outside this build. (b) Onboarding's rental step asks no mortgage, and onboarding's one debt names no property — there is no property in Net worth at that point; the mortgage is named on Net worth afterwards for the person to place. (c) Where a mortgage is on no property, the budget line is not stood down and both are counted until the person places it.</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$209</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F208"/>
+  <dimension ref="A1:F209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>READY TO SEND — to-send/ holds the 25 files exactly as first sent (commit 62d47df) and supplements 01 to 04 (the cards changed since). Brief v04.</t>
+          <t>READY TO SEND — to-send/ holds the 25 files exactly as first sent (commit 62d47df), supplements 01 to 06, and the final audit of Net worth batch 1 for Gemini. Brief v04.</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Done first, because a function nobody has described cannot be tested from outside: 150 descriptions written into the code, 14 stale copies of records removed (src/__tests__/guard_function_descriptions.test.ts). THE LIMIT OF THE FIRST PACK IS CLOSED: only 32 of its cards carried any rule. Now 318 of 318 carry the formula in words — how the function gets its answer, every number included — each written by reading the function. Held three ways: a function that changes stops the build until its formula is read again (step B7); 463 figures stated in the formulas are each traced to the function, 7 of them worked by hand and re-checked; no card carries code. Each batch also carries the formulas its cards lean on, and the Cash flow batches carry the published 2026 tax and limit amounts, read from the app, for the models to check against their source. WHAT THIS DOES NOT PROVE: the formulas are my reading of my own code. The outside models judge whether each is the right formula; whether the code does what its formula says is settled only when their cases are run against the app. CORRECTED AFTER SENDING, 2026-10-04: 12 cards in six of the sent files describe a formula that has since been fixed — cashflow 01 (MK-CF-O-001, MK-CF-O-004), cashflow 06 (MK-CF-F-087, MK-CF-F-092), cashflow 11 (MK-CF-F-144, MK-CF-F-146), cashflow 13 (MK-CF-F-180, MK-CF-F-181, MK-CF-F-186), cashflow 15 (MK-CF-F-182), performance 03 (MK-PF-F-010, MK-PF-F-023). A model that calls one of those twelve WRONG is judging the formula as it was sent; its verdict is read against what was then fixed, and the supplement gets the corrected formula judged afresh. 2026-10-04, later: brief v04 adds the owner rule "Every return is a time-weighted return (owner, 2026-10-04). A return made any other way is WRONG." (v03 archived). Supplement 02 written: to-send/moneykeel_audit_cards_changed-since-sent_02.md — the 15 cards changed since supplement 01, with brief v04 at its top. The 26 files of the pack are as sent and still carry brief v03 and the old return formula on MK-NW-O-008 and MK-NW-O-003. CORRECTION, 2026-10-04, late: the pack in to-send/ was NOT as sent. The command I used to re-stamp a changed function (--reread) also printed the whole pack again each time — three times that day — replacing all the files with current cards (26 files instead of the 25 that went out) and deleting supplements 01 and 02. Found when supplement 02 was missing. RESTORED: to-send/ now holds the 25 files exactly as they went out (commit 62d47df) and supplements 01, 02 and 03. The command no longer writes the pack, and every gate run now compares the 25 files with what went out and stops if one differs. A file copied from to-send/ between those rewrites carried newer cards than the pack as sent.</t>
+          <t>Done first, because a function nobody has described cannot be tested from outside: 150 descriptions written into the code, 14 stale copies of records removed (src/__tests__/guard_function_descriptions.test.ts). THE LIMIT OF THE FIRST PACK IS CLOSED: only 32 of its cards carried any rule. Now 318 of 318 carry the formula in words — how the function gets its answer, every number included — each written by reading the function. Held three ways: a function that changes stops the build until its formula is read again (step B7); 463 figures stated in the formulas are each traced to the function, 7 of them worked by hand and re-checked; no card carries code. Each batch also carries the formulas its cards lean on, and the Cash flow batches carry the published 2026 tax and limit amounts, read from the app, for the models to check against their source. WHAT THIS DOES NOT PROVE: the formulas are my reading of my own code. The outside models judge whether each is the right formula; whether the code does what its formula says is settled only when their cases are run against the app. CORRECTED AFTER SENDING, 2026-10-04: 12 cards in six of the sent files describe a formula that has since been fixed — cashflow 01 (MK-CF-O-001, MK-CF-O-004), cashflow 06 (MK-CF-F-087, MK-CF-F-092), cashflow 11 (MK-CF-F-144, MK-CF-F-146), cashflow 13 (MK-CF-F-180, MK-CF-F-181, MK-CF-F-186), cashflow 15 (MK-CF-F-182), performance 03 (MK-PF-F-010, MK-PF-F-023). A model that calls one of those twelve WRONG is judging the formula as it was sent; its verdict is read against what was then fixed, and the supplement gets the corrected formula judged afresh. 2026-10-04, later: brief v04 adds the owner rule "Every return is a time-weighted return (owner, 2026-10-04). A return made any other way is WRONG." (v03 archived). Supplement 02 written: to-send/moneykeel_audit_cards_changed-since-sent_02.md — the 15 cards changed since supplement 01, with brief v04 at its top. The 26 files of the pack are as sent and still carry brief v03 and the old return formula on MK-NW-O-008 and MK-NW-O-003. CORRECTION, 2026-10-04, late: the pack in to-send/ was NOT as sent. The command I used to re-stamp a changed function (--reread) also printed the whole pack again each time — three times that day — replacing all the files with current cards (26 files instead of the 25 that went out) and deleting supplements 01 and 02. Found when supplement 02 was missing. RESTORED: to-send/ now holds the 25 files exactly as they went out (commit 62d47df) and supplements 01, 02 and 03. The command no longer writes the pack, and every gate run now compares the 25 files with what went out and stops if one differs. A file copied from to-send/ between those rewrites carried newer cards than the pack as sent. 2026-10-05 — HIS INSTRUCTION: "write another brief for Gemini for NW-01 to conduct one final audit before we move to NW-02." WRITTEN: to-send/moneykeel_audit_final_networth01_for-gemini_v01.md — brief v04, then 9 cards as the functions stand today: the six of the batch (MK-NW-O-001 to O-006) and three added while correcting it (MK-NW-F-106 mortgagesByProperty, MK-NW-F-107 propertyUses, MK-CF-O-020 theBudgetCounted), with 11 formulas they lean on. It quotes the seven rulings of his made since, asks for the two jobs of the brief, and adds a third: say whether the batch can be closed ("ready_to_close", "still_open"). Nothing of Claude's review is in it, and no answer the app gives. The builder writes such a file with --final-audit &lt;batch&gt; --for &lt;who&gt; --also &lt;ids&gt;.</t>
         </is>
       </c>
     </row>
@@ -6699,8 +6699,40 @@
         </is>
       </c>
     </row>
+    <row r="209" ht="60" customHeight="1">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Post Feedback Sync, 2026-10-05 — his two feedback files folded in and archived</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>HIS INSTRUCTION, 2026-10-05: "make sure to execute on PFS." TWO FILES, both waiting since the end of September. (1) THE LAUNCH ANSWER LIST (moneykeel_calc_plan_launch-answer-list_v01-jj.xlsx): four answer cells on the Net worth tab, holding seven answers. Q17 "Money paid should not be counted as a gain. The formula is incorrect and should be corrected. Formula Time weighted return." — built on 2026-10-04 from his later words (DEC-1669); now on record as said here first. Q32 "Don't understand the question - what trend are your referring to?" — answered on its row: the trend is the net worth line chart; decided without asking again that the chart shows and a figure the daily record cannot cover says so. Q10 "Draft order is correct" — NOT BUILT: my draft put the institution's class field first, which contradicts his brief B7 ("name first, broker tag as fallback only", 2026-08-20) and his rule of 2026-08-04; the code stays on B7 and the conflict is put to him by name. Q11 "Refuse the line and ask" — BUILT: a holding nothing can class is in no class, shows as Unclassified, and Net worth asks. Q12 "user entry stays … cost basis should not be overwritten in future sync" — BUILT: a sync keeps a cost the person set and a holding they added. Q13 "incomplete question" — the question had been cut off; put in full on its row and decided as built (GLD is an alternative; physical metal is a hand-entered value). Q14 "Call an account by it's name" — the Net worth rows already do; one older list fixed. (2) THE MASTER (moneykeel_calc_master_calculation-master_v01-jj.xlsx, returned 2026-09-28): 14 cells of his in the answer and verified columns; 13 are word for word in the master today; the 14th, Q30 "rise with inflation each year", sat on a row retired on 2026-10-02 — recorded in the decision log; the draw is already shown in today's dollars. COVERAGE: 2 of 2 files · 21 answers and typed cells read · 13 already in the original · 8 newly recorded in his words · 3 rulings built and tested the same day (Q11, Q12, Q14) · 1 already built (Q17) · 3 answered or decided on the row (Q13, Q32, Q30) · 1 not built, held for him (Q10) · 2 files archived as 2026-10-05_folded-in_…</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>DONE — except Q10, which waits on him: his two rulings disagree.</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/other/JJ-feedback-archive/</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>The gate that printed "PFS pending: 2 files" is clear. check-questions-answered: every answer of his reaches the master, and none is still being asked.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F208"/>
+  <autoFilter ref="A1:F209"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$216</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F209"/>
+  <dimension ref="A1:F216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6731,8 +6731,212 @@
         </is>
       </c>
     </row>
+    <row r="210" ht="60" customHeight="1">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Outside review, returned file by file — Net worth file 2 (Claude): fifteen functions, 75 cases</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>HIS INSTRUCTION, 2026-10-04: "We will run one at a time to make sure you are actually correcting them." He handed over file 2 on 2026-10-05. THE FILE judged fifteen functions: 7 WRONG, 5 INCOMPLETE, 3 RIGHT. MEASURED: its 75 answers run against the app as it stood (commit c78d0de) — the app disagreed with 14; against the fixes — it disagrees with 2, both held on purpose (MK-NW-F-004, its own row below). FIXED, each by name. (1) MK-NW-F-003 valueFreshness: counted month names crossed, so "still right?" came up to a month early; it counts months fully passed. (2) MK-NW-F-005 accountAllowsTicker: an account that already lists holdings can take a ticker, whatever its class. (3) MK-NW-F-010 wrapperAccount: a Roth 401(k) has its own choice (a 401(k) by kind, Roth by tax); the card's words now name every kind. (4) MK-NW-F-011 assetClassOf: a maturity date outranks the name (his rule of 2026-08-04); a property whose kind is not a house is Personal property. (5) MK-NW-F-012 taxTreatmentOf: a 529 is tax-free; new MK-NW-F-108 taxWordsOf gives a 529 and an HSA their own words on the account page. (6) MK-NW-F-016 cashTotal and MK-NW-F-027 accountClassBreakdown: cash an account built by hand records for itself is cash; a holding with no price is filed under its class, never as cash. (7) MK-NW-F-021 investmentsTotal: it is the Investments line of Net worth, read from the class split, and MK-NW-O-003 theNetWorth calls it; cash + investments = cash and investments together, always. MK-NW-F-017 to F-020 (the four class totals) read the same split. (8) MK-NW-F-026 accountDisplayNames: no two accounts are ever shown by the same name; the order is the same on every device. (9) MK-NW-F-028 classPortionLabel: three kinds read "1 CD, 1 Treasury &amp; 2 bonds"; it counts by new MK-NW-F-109 holdingClassOf, the same test the dollars are split by. ALREADY FIXED with file 1: MK-NW-F-001 isAlternative. RIGHT, nothing changed: MK-NW-F-007 assetKind, MK-NW-F-009 maturityClass, MK-NW-F-022 investableAssets. WHERE IT WROTE "RULE UNCLEAR", decided without asking: a private-equity stake with an end date is a bond (his rule of 2026-08-04; no screen can give a stake a maturity date); a kind is matched exactly (only the app writes kinds); accounts with one name are numbered in the order of their ids read as text.</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>DONE — 73 of its 75 answers are the app's; 2 are held at the app's answer and named on the next row.</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/moneykeel_networth02_claude.json · MoneyKeel/functions/networth-and-performance/outside_networth_02.test.ts (75) · outside_networth_02_found.test.ts (23) · src/screens/__tests__/outside_networth_02.test.tsx (6)</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Not pushed. The two drawings carry the changes at their top, in a second table marked as not his rulings: Net worth v08 (8 lines), Performance v17 (5 lines).</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="60" customHeight="1">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>MK-NW-F-004 portfolioActualReturn — the outside reviewer called it WRONG; kept as it is, and why</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>THE REVIEWER'S POINT: the card said "value-weighted", and the function weighs each account by the amount set aside for retirement — so a brokerage saved for a house deposit (0% for retirement) that lost 4.2% is not in "your return". DECIDED BY ME, NOT ASKED: kept. The function is what the money set aside for retirement returned; the Retirement plan grows that money and nothing else, and compares it with a benchmark weighted the same way (MK-NW-F-037 blendedReturn). Weighing whole accounts would grow the retirement money at the return of money that is not in it. WHAT WAS WRONG was the card's words: they now say "what the money set aside for retirement returned". The two cases that rest on whole-account weights are held at the app's answer in the test file, each with its sum written out: 9.18% (its answer 10.07%) and 5.95% (its answer 3.51%). ITS OTHER TWO POINTS HOLD ALREADY: a reported return of 0 counts; one not reported is left out. TO REVERSE: one line in MK-NW-F-004 (weigh by balance) — and the benchmark beside it would have to change the same way. STILL OPEN, FOR THE MENU BUILD: Insights prints this figure as "Your 12-mo return" beside "Benchmark"; both are the retirement money's, and the label does not say so.</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>DONE — kept by my decision; one line reverses it. The Insights label is open for the Menu build.</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts (MK-NW-F-004) · src/screens/InsightsScreen.tsx (the behind-benchmark insight) · MoneyKeel/functions/networth-and-performance/outside_networth_02.test.ts</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212" ht="60" customHeight="1">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Home's investments figure and Performance's "Ending value" differed by the cash sitting uninvested in a linked account</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>FOUND 2026-10-05 while fixing MK-NW-F-021. On 2026-10-04 the Investments line of Net worth was corrected to leave a linked account's uninvested cash to the Cash line (the approved drawing: $354,314). Home read that line for its investments figure AND handed it to the performance function as today's value, while Performance handed in the accounts counted whole ($355,152). For the drawing's household: two figures $838 apart, a tap apart, and Home's dollars earned for the month were $838 lower than Performance's. FIXED: MK-NW-O-008 thePerformance reads what the measured accounts are worth from the accounts handed to it, so no screen can hand it a figure of its own; Home prints that figure. Net worth's Investments line is unchanged. The test that pinned Home to Performance used a household with no such cash, so it could not see this; a second test renders both screens in that state.</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/performance.ts (MK-NW-O-008) · src/screens/HomeScreen.tsx · src/screens/PerformanceScreen.tsx · src/screens/__tests__/outside_networth_02.test.tsx · src/screens/__tests__/fcc_agreement.test.tsx</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>DECIDED BY ME: Home's figure is the one Performance shows, not Net worth's Investments line — it sits beside Performance's return and opens Performance. To reverse: one line in HomeScreen.tsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="60" customHeight="1">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>A money-market fund the broker marks as "cash equivalent" was in neither the holdings nor the cash</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>FOUND 2026-10-05 while checking the reviewer's point that MK-NW-F-027's card still said money market goes under cash. The classifier has filed a money-market fund under Stocks / Funds since his rule of 2026-08-04 (DEC-0051) — but the sync dropped every holding the broker flags as cash-equivalent, and took it out of the cash as well. Run through the real sync: a $50,000 fund was in no holdings list, and the account was marked as not adding up to the broker's total by $50,000; a $900 fund was counted as $900 of cash, which the emergency fund then counted; where the broker sent no total, the balance worked out by the app left the fund out. A test from 2026-08-14 acted the defect out and passed. FIXED: the fund stays in the holdings (Stocks / Funds); the cash is still net of it, so it is counted once. HIS OWN ACCOUNTS: his brokers do not set this flag (recorded 2026-07-19), so his figures do not move.</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>src/services/sync/ingest.ts (MK-XS-F-102 ingestSync) · src/services/sync/f6_money_market.test.ts · src/services/sync/ingest.test.ts</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214" ht="60" customHeight="1">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>An account added by hand as Roth or 401(k) / IRA was shown as "Brokerage"</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>FOUND 2026-10-05 while checking the reviewer's point on MK-NW-F-010 (the kind must follow the tax wrapper). The by-hand form asks "Taxable · 401(k) / IRA · Roth" and records the answer as the tax bucket on a plain brokerage kind, so a Roth at Vanguard read "Vanguard Brokerage" — against his naming rule of 2026-08-11 (a tax-advantaged account always shows what it is). FIXED in MK-NW-F-025 accountDisplayName: where the kind says only Brokerage, the word is the tax answer — "Vanguard Roth", "Fidelity 401(k) / IRA". DECIDED BY ME: the two words are the form's own. To reverse or reword: one line. NOT DONE: the form has one choice for a 401(k) and an IRA, so nothing later can tell which of the two such an account is.</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>DONE for the name. OPEN: the by-hand form has one choice for 401(k) and IRA.</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts (MK-NW-F-025) · src/screens/AddAccountScreen.tsx · MoneyKeel/functions/networth-and-performance/outside_networth_02_found.test.ts</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215" ht="60" customHeight="1">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Three more found on file 2, each fixed: the person's own class answer, the account page's class test, a 529's name</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>FOUND 2026-10-05. (1) The split of a linked account let a holding's NAME outrank the class the person gave it: GLD they had classed as Stocks / Funds was still counted under Alternatives. Their answer now wins (new MK-NW-F-109 holdingClassOf). (2) The class of a holding was worked out three ways — in the split, in the words under the account, and on the account's page — so a CD the broker tags as cash was in the Bonds &amp; CDs dollars and missing from the words and the page list. All three ask the one function. A holding nobody has classed shows under an Unclassified band on its account's page, only when there is one. (3) A 529 at an institution read "Vanguard -1234"; it reads "Vanguard 529 -1234".</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts (MK-NW-F-109, MK-NW-F-027, MK-NW-F-028, MK-NW-F-012) · src/screens/AccountPortfolioScreen.tsx</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216" ht="60" customHeight="1">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Plan and the tax on money coming out — an HSA is treated as a 401(k), a 529 as taxable</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>FROM THE OUTSIDE REVIEW of MK-NW-F-010 and MK-NW-F-012 (file 2). The account page now says in words what makes a 529 and an HSA tax-free. NOT DONE, and not in this build: the Retirement plan reads an account's tax bucket, where an HSA is pre-tax (taxed when it comes out, like a 401(k)) and a 529 is taxable. Money taken from an HSA for medical costs is not taxed (IRS Publication 969), so a plan that draws on an HSA overstates its tax. It belongs with the Plan build.</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — mine, for the Plan build.</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts (MK-NW-F-012, MK-NW-F-108) · src/domain/decumulation · src/domain/retirement</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F209"/>
+  <autoFilter ref="A1:F216"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$217</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F216"/>
+  <dimension ref="A1:F217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6935,8 +6935,36 @@
       </c>
       <c r="F216" s="2" t="inlineStr"/>
     </row>
+    <row r="217" ht="60" customHeight="1">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Plan build — the retirement money the Plan grows, and the rate it grows by, checked against his words of 2026-10-06</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>HIS WORDS, 2026-10-06: "Per Plan mockup - NW - primary home - car = retirement." and "all return should be TWR. what is reported 12-month return?" WHAT THE APP DOES TODAY. (1) Retirement money (MK-NW-F-033 retirementEarmarkedValue) = every account except the home lived in, the car driven and a 529, each counted whole unless a share is set — DEBTS ARE NOT TAKEN OFF. Net worth takes debts off, so if his Plan drawing starts from net worth the two differ by the debts. (2) The Plan grows that money by one of three rates chosen in the Plan: the blended benchmark (default — each kind's typical long-run return, weighted by the retirement money in it, MK-NW-F-037), 'your 12-month return' (figures the person TYPES per account as 'reported return (12 mo)', weighted the same way, MK-NW-F-004), or a scenario rate typed. No measured return feeds the Plan. MY RECOMMENDATION for the Plan build: 'your 12-month return' should be the app's own time-weighted one-year return per account (what Performance measures, MK-NW-O-008), typed figures only where the app cannot measure — so his rule that every return is time-weighted reaches the Plan. Not built: the Plan waits for the build after this one.</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — for the Plan build. Nothing changed.</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts (MK-NW-F-033, MK-NW-F-037, MK-NW-F-004) · src/domain/retirement/willItLast.ts (MK-PL-F-067) · src/screens/RetirementCockpit.tsx</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F216"/>
+  <autoFilter ref="A1:F217"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$218</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F217"/>
+  <dimension ref="A1:F218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6963,8 +6963,36 @@
       </c>
       <c r="F217" s="2" t="inlineStr"/>
     </row>
+    <row r="218" ht="60" customHeight="1">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Private equity and hedge funds are not offered in this phase — his ruling of 2026-10-06, applied to the two doors that still offered them</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>HIS WORDS, 2026-10-06: "this phase of app no longer has options for Private Equity and Hedge fund." His ruling of 2026-08-04 (DEC-0045) had trimmed the Net worth add sheet; the Add an account form (built later) still offered "Private stake", and the Alternatives screen's first-day sentence still named both. DONE: the chip is gone; the sentence reads crypto, commodities, annuities; a row saved earlier with either kind keeps it when edited. The two drawings carry the ruling at their top; the test that holds them names the difference (item 17).</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/AddAccountScreen.tsx · src/screens/OtherInvestmentsScreen.tsx · src/screens/__tests__/kept_editors_match.test.tsx · the two drawings</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F217"/>
+  <autoFilter ref="A1:F218"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$219</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F218"/>
+  <dimension ref="A1:F219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6991,8 +6991,36 @@
       </c>
       <c r="F218" s="2" t="inlineStr"/>
     </row>
+    <row r="219" ht="60" customHeight="1">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Outside review — Gemini's final audit of Net worth batch 1 (returned 2026-10-05): nine issues, thirty cases</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>HIS INSTRUCTION, 2026-10-05: "write another brief for Gemini for NW-01 to conduct one final audit before we move to NW-02." Gemini answered "Ready to Close: No" with nine issues. MEASURED: its thirty cases and nine issues as 36 tests (outside_networth_01_final_gemini.test.ts) — 34 passed before any change, 36 after two small fixes. REAL, FIXED: (6) MK-PF-F-006 capGains — a share bought on 29 February read short-term one day too long (the anniversary rolled to 1 March; it is the last day of February). (2) MK-NW-O-002 theAccount — the uninvested cash an account built by hand records for itself is now in its inside, with the rest under the account's class (the same split Net worth counts by since file 2). ALREADY SO, PROVED BY TEST: (1) a zero-coupon bond gets no rate-move figure and a bond with no maturity date gets no yield to maturity; (3) the time-weighted return measures from the first day something was held and gives no figure for a start below zero — no division by zero; (4) rent at or above essentials draws nothing from cash and shows no months; (5) an alternative worth $0 gives no rate and no growth. NOT SO: (9) the rate-move figure reprices the bond at the new yield — not a straight line, and closer than the duration shortcut it asked for; (7) the 2026 standard deduction $16,100 single / $32,200 married IS the IRS figure (Rev. Proc. 2025-32); (8) a mortgage is matched by its property first, then its name, then only when one property and one mortgage are left — never by balance; two alike are both flagged. Three of its nine named functions by ids that are not theirs (F-010, F-012, F-015); read as the functions it meant. One of its figures differs from the app by design: a linked checking account with a deposit and a withdrawal shows income $0, not no figure — the records are there and none is income.</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>DONE — 36 of 36. Net worth batch 1 is closed on my side; his word closes it.</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/NW-01-gemini.md · MoneyKeel/functions/networth-and-performance/outside_networth_01_final_gemini.test.ts</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F218"/>
+  <autoFilter ref="A1:F219"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$220</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F219"/>
+  <dimension ref="A1:F220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>DONE — all 30 of its cases run against the app and pass; its renter case now also works for a real person.</t>
+          <t>CLOSED on his word, 2026-10-07: "NW batch one close."</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>DONE — 73 of its 75 answers are the app's; 2 are held at the app's answer and named on the next row.</t>
+          <t>DONE — 73 of 75 its answers, 2 held and approved by him ("Rest I am good with.", 2026-10-06). Final audit for Gemini written 2026-10-07: to-send/moneykeel_audit_final_networth02_for-gemini_v01.md (24 cards: the 15 of the batch as they stand + 9 changed or added since).</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>DONE — 36 of 36. Net worth batch 1 is closed on my side; his word closes it.</t>
+          <t>CLOSED on his word, 2026-10-07: "NW batch one close." — 36 of 36.</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -7019,8 +7019,36 @@
       </c>
       <c r="F219" s="2" t="inlineStr"/>
     </row>
+    <row r="220" ht="60" customHeight="1">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Post Feedback Sync, 2026-10-07 — every file brought level with what batches 1 and 2 changed in the code</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>HIS QUESTION, 2026-10-07: "The objective of PFS is to update all files - standards, master calculation, decision-log, screens - to changes we are making directly in code. Have you done that for batch 1 and 2?" HONEST ANSWER: no — the master (printed from the code), the drawings (a change table at the top of six) and the tracker were level; the decision log held his rulings but not his two approvals; no standard carried the classification rules or the housing rulings; the design Changelog had no row since 2026-09-26; and the old taxonomy spec still said the opposite of his 2026-08-04 rule. DONE TODAY: (1) two standards written — how an account is classed, split, counted and named (the batch 2 rules, with DEC-0051, 0092, 0095, 0309, 0343, 0045, 2160, 2163, 2334 named as their source) and how a mortgage, rent and a debt are entered and counted (DEC-1923 to 1926, 1668, 1859); fourteen decisions now name the standard that carries them. (2) The decision log: his two approvals recorded — "Rest I am good with." (2026-10-06, batch 2) and "NW batch one close." (2026-10-07, batch 1). (3) The design Changelog: 52 rows backfilled, one per decision of his since 2026-09-27, in a dated copy (FCC-core-detailed-design-v1.3-2026-10-07.xlsx), each anchored to its decision. (4) docs/finwise-taxonomy-spec.md: its cash, bonds and property lines corrected and pointed at the standard. (5) The master: rebuilt from the code by the gates. STILL TRUE: a code change with no ruling of his reaches the standard and the tracker, and the decision log only when he approves it.</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/standards/moneykeel_calc_spec_how-an-account-is-classed-and-counted_v01.md · moneykeel_calc_spec_mortgage-rent-and-debt_v01.md · docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx · docs/finwise-taxonomy-spec.md</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F219"/>
+  <autoFilter ref="A1:F220"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -6439,7 +6439,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>MEASURED 2026-10-04 at his question ("are these 6 findings not in file?"): the test file run against the app as it stood before the fixes (cd9f0b8) — 13 of 32 failed; against the fixes — 0 fail. All six of its findings were real. Still open: the return (its finding 2 — the app still shows 42.32% where 10.97% is right) and "no figure when the record does not reach back". 2026-10-05, STATE OF THIS FILE: its six findings and its five smaller points are fixed and tested; its four unclear points are decided; the return is time-weighted (10.97%). NOT CLOSED IN REAL USE — its finding on the renter who owns a rented-out house (MK-NW-O-004): the fix tells the home's mortgage from another property's, but no screen yet tells the app that a property is a rental, so the case passes only in its test. It closes with steps 2 and 3 of the row "How a mortgage, rent and a debt are entered and counted" (DEC-1924, DEC-1926, DEC-1923). ALSO LEFT FROM WORK THIS FILE STARTED: share transfers synced before 2026-10-04 carry no direction, so a window holding one still shows no return; a balance typed back-dated is assumed to hold that day's money. ONLY Claude's file has come back for this batch; Gemini's has not been run. 2026-10-05 — the renter who owns a rented-out house: closed. Rent entered for a property on the Income screen is what makes it a rental (DEC-1926), so the app no longer needs a field no screen could set. Its "three places" case was worked from the card as sent; the owner's rule of 2026-10-04 (DEC-1923) changed the formula, so the test keeps its numbers on record and asserts the answer under the rule.</t>
+          <t>MEASURED 2026-10-04 at his question ("are these 6 findings not in file?"): the test file run against the app as it stood before the fixes (cd9f0b8) — 13 of 32 failed; against the fixes — 0 fail. All six of its findings were real. Still open: the return (its finding 2 — the app still shows 42.32% where 10.97% is right) and "no figure when the record does not reach back". 2026-10-05, STATE OF THIS FILE: its six findings and its five smaller points are fixed and tested; its four unclear points are decided; the return is time-weighted (10.97%). NOT CLOSED IN REAL USE — its finding on the renter who owns a rented-out house (MK-NW-O-004): the fix tells the home's mortgage from another property's, but no screen yet tells the app that a property is a rental, so the case passes only in its test. It closes with steps 2 and 3 of the row "How a mortgage, rent and a debt are entered and counted" (DEC-1924, DEC-1926, DEC-1923). ALSO LEFT FROM WORK THIS FILE STARTED: share transfers synced before 2026-10-04 carry no direction, so a window holding one still shows no return; a balance typed back-dated is assumed to hold that day's money. ONLY Claude's file has come back for this batch; Gemini's has not been run. 2026-10-05 — the renter who owns a rented-out house: closed. Rent entered for a property on the Income screen is what makes it a rental (DEC-1926), so the app no longer needs a field no screen could set. Its "three places" case was worked from the card as sent; the owner's rule of 2026-10-04 (DEC-1923) changed the formula, so the test keeps its numbers on record and asserts the answer under the rule. APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>REMOVED 2026-10-04 on his instruction ("work on fixing all 5+4 findings"): modifiedDietzOverWindow (window-return.ts), moneyWeighted.ts whole (5 functions), investableChangePct (history.ts); their tests and probes; seven function numbers retired. The bench page's return card is now time-weighted and was rebuilt. The guard reads the engines too and fails the build if one comes back.</t>
+          <t>REMOVED 2026-10-04 on his instruction ("work on fixing all 5+4 findings"): modifiedDietzOverWindow (window-return.ts), moneyWeighted.ts whole (5 functions), investableChangePct (history.ts); their tests and probes; seven function numbers retired. The bench page's return card is now time-weighted and was rebuilt. The guard reads the engines too and fails the build if one comes back. APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04, on his instruction to fix them. (1) SHARES MOVED IN OR OUT: now counted as money in or out at what they were worth, when the record says which way they went and what they were worth. The sync now stores the direction (it was lost: "in" and "out" both became one type), the rebuilt history respects it, and the walk counts it. STILL REFUSED: share-transfer rows synced BEFORE today carry no direction, so a window containing one still shows no return — the direction cannot be recovered from what was stored. (2) HAND-ENTERED ACCOUNT WITH HOLDINGS: fixed — on rebuilt days between two days it was observed holding exactly the same shares and cash, it is given those shares at each day's close (fillBetweenObservations). Different on the two sides: nothing is filled. (3) THE DOLLAR WALK: fixed — cash or shares transferred in from outside, and an account that joined the record inside the window, count as money put in; the walk and the percent tell one story. (4) A BALANCE TYPED BACK-DATED: unchanged — the record assumes each day's value already holds that day's money. 2026-10-05 — item 1 finished: a share transfer synced before 2026-10-04 is given its direction on the next sync, from the activity the broker reports again; it is never imported twice (ingest.test.ts). Until that sync runs, a window holding such a row still shows no return.</t>
+          <t>2026-10-04, on his instruction to fix them. (1) SHARES MOVED IN OR OUT: now counted as money in or out at what they were worth, when the record says which way they went and what they were worth. The sync now stores the direction (it was lost: "in" and "out" both became one type), the rebuilt history respects it, and the walk counts it. STILL REFUSED: share-transfer rows synced BEFORE today carry no direction, so a window containing one still shows no return — the direction cannot be recovered from what was stored. (2) HAND-ENTERED ACCOUNT WITH HOLDINGS: fixed — on rebuilt days between two days it was observed holding exactly the same shares and cash, it is given those shares at each day's close (fillBetweenObservations). Different on the two sides: nothing is filled. (3) THE DOLLAR WALK: fixed — cash or shares transferred in from outside, and an account that joined the record inside the window, count as money put in; the walk and the percent tell one story. (4) A BALANCE TYPED BACK-DATED: unchanged — the record assumes each day's value already holds that day's money. 2026-10-05 — item 1 finished: a share transfer synced before 2026-10-04 is given its direction on the next sync, from the activity the broker reports again; it is never imported twice (ingest.test.ts). Until that sync runs, a window holding such a row still shows no return. APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Tests: emergency_fund_rent.test.ts (the four logged-debt cases) · sale_takes_oldest_first.test.ts (4) · kept_editors_match (Bonds line) · outside_networth_01 (bonds named). Drawings Bonds v02 and Holding detail v02 carry a note at the top.</t>
+          <t>Tests: emergency_fund_rent.test.ts (the four logged-debt cases) · sale_takes_oldest_first.test.ts (4) · kept_editors_match (Bonds line) · outside_networth_01 (bonds named). Drawings Bonds v02 and Holding detail v02 carry a note at the top. APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>Not pushed. The two drawings carry the changes at their top, in a second table marked as not his rulings: Net worth v08 (8 lines), Performance v17 (5 lines).</t>
+          <t>Not pushed. The two drawings carry the changes at their top, in a second table marked as not his rulings: Net worth v08 (8 lines), Performance v17 (5 lines). APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,11 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="60" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
@@ -6819,7 +6823,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>DECIDED BY ME: Home's figure is the one Performance shows, not Net worth's Investments line — it sits beside Performance's return and opens Performance. To reverse: one line in HomeScreen.tsx.</t>
+          <t>DECIDED BY ME: Home's figure is the one Performance shows, not Net worth's Investments line — it sits beside Performance's return and opens Performance. To reverse: one line in HomeScreen.tsx. APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6853,11 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="60" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
@@ -6877,7 +6885,11 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="60" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
@@ -6905,7 +6917,11 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="60" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
@@ -7017,7 +7033,11 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="60" customHeight="1">
       <c r="A220" s="2" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$221</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F220"/>
+  <dimension ref="A1:F221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7067,8 +7067,40 @@
       </c>
       <c r="F220" s="2" t="inlineStr"/>
     </row>
+    <row r="221" ht="60" customHeight="1">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Outside review, returned file by file — Net worth file 3 (Claude): fifteen functions, 75 cases</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>He handed over file 3 on 2026-10-07. THE FILE judged fifteen functions: 9 WRONG, 4 INCOMPLETE, 2 RIGHT. MEASURED: its 75 answers run against the app as it stood — the app disagreed with 12 (10 of its cases failed; 2 more are held on purpose); against the fixes — it disagrees with the 2 held. FIXED, by name. (1) MK-NW-F-031 primaryCarIdOf: a jewellery collection worth more than the car was taken as 'the car you drive'; only a vehicle can be. (2) MK-NW-F-037 blendedReturn and MK-NW-F-035 blendedVolatility: the rate the retirement money grows at is blended over exactly the money the nest egg counts — property included where it is set aside (a rental at 100%) — and there is no figure when nothing is set aside; the 6% that stood there was invented. The Plan chooses its own 6% at its call site and says so. (3) MK-NW-F-039 buildAssetsState: no average return for a household that owns nothing (it said 7%). (4) MK-NW-F-041 monthlyContributionsFromOnboarding: money saved toward a property (an older setup question) is not a retirement contribution; a 401(k) figure is held at the year's elective limit for the person's age (the Roth answer is not held at the IRA limit — the question does not say Roth IRA or Roth 401(k), whose limits differ four-fold; held against the reviewer, one of its cases); nothing answered gives no figure, not $0. (5) MK-NW-F-046 historyCoverage: eighteen months of history read '2 years'; it reads '18 months' or '1 year 6 months', never rounded up, with the part month counted by its days. (6) MK-NW-F-051 itemizedResultTotal: a path that did not keep the rest as cash let a part-itemised $186,442 fall to $148,001; the total never falls below the entered total. (7) MK-NW-F-052 buildItemizedAccounts: a bond's face value is entered or nothing (the Itemize bond row has a new optional Face value field; the account page says 'not entered' and shows no yield to maturity without one — MK-NW-F-060); the new accounts carry the lump's retirement share, source and wrapper, so itemising no longer moves the nest egg. ALREADY FIXED with file 2: MK-NW-F-029 (a hand-built account's cash). RIGHT, nothing changed: MK-NW-F-032, F-033. WORDS ONLY (the card was silent, the code was right): MK-NW-F-034 and F-036 (a rate of exactly 0 counts as set; kinds match exactly), F-045 (no update on record reads 'not updated yet'), F-048 (which class goes to which group). HELD AGAINST THE REVIEWER, on his rule: MK-NW-F-030 earmarkDefault — the reviewer wanted a second car and valuables at 0% for retirement; his rule of 2026-08-11 (DEC-0100: 'all assets minus primary home and primary car') says they count. KEPT, on my reading: holdings that come to more than the lump raise the total — the screen shows the new total before Done is tapped, and that tap is the confirmation.</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>DONE — 72 of its 75 answers are the app's; 3 held (2 on his rule DEC-0100, 1 on the Roth limit). Not yet approved by him.</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/moneykeel_networth03_claude.json · MoneyKeel/functions/networth-and-performance/outside_networth_03.test.ts (75)</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Not pushed. Drawings carry the changes at their top: Itemize v02 (4 lines, new box), Performance v17 (2), Net worth v08 (1). The retirement figures the Plan prints move for a household with a rental or a second valuable item; the Plan waits for the next build. ON HOME: the insight "You're investing about 0% of your gross income toward retirement" no longer appears for a household that answered no contribution question — nothing answered is not 0%.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F220"/>
+  <autoFilter ref="A1:F221"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$222</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F221"/>
+  <dimension ref="A1:F222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7099,8 +7099,40 @@
         </is>
       </c>
     </row>
+    <row r="222" ht="60" customHeight="1">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Outside review, returned file by file — Net worth file 4 (Claude): fifteen functions, 75 cases</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>He handed over file 4 on 2026-10-07. THE FILE judged fifteen functions: 7 WRONG, 4 INCOMPLETE, 4 RIGHT. MEASURED: its 75 answers (71 tests) run against the app as it stood — the app disagreed with 11 (8 of its cases failed; 3 more are held on purpose); against the fixes — it disagrees with the 4 held. FIXED, by name. (1) MK-NW-F-094 ledgerGroups: the list under the class rows counted every account whole, so its Cash group read $8,000 while the Cash row above read $8,838 and Vanguard's mix showed one kind; it uses the same split as the class rows, and one institution typed two ways is one group. (2) MK-NW-F-002 alternativesSummary: growth read $0 when nothing was held; no figure. (3) MK-NW-F-008 incomeBearingClassOf: a money-market settlement fund is a fund (DEC-0051), read before the sweep words; a bond word inside a company name (Treasury Wine Estates Ltd) is not a bond. (4) MK-NW-F-013 realEstateUseOf and MK-NW-F-030 earmarkDefault: two properties with no use stated were both the home, so a second property fell out of the retirement money; the one entered first is the home (his rule DEC-1926 as built, new MK-NW-F-110 primaryHomeIdOf); a car has no use. (5) MK-NW-F-035 blendedVolatility: no figure when nothing is set aside (it said 12%). ALREADY FIXED with files 2 and 3: MK-NW-F-017, F-018, F-019 (the class totals read the split). RIGHT, nothing changed: MK-NW-F-055, F-073, F-014, F-020. WORDS ONLY: MK-NW-F-015, F-024. HELD AGAINST THE REVIEWER: MK-NW-F-025 — it wanted 'Chase Checking -4821'; his rule of 2026-08-11 (DEC-0083) is 'Vanguard -5738', the kind word only without digits; and with no digits and no kind word the person's own name is kept behind the institution. MK-NW-F-035 — it wanted the portfolio's volatility from a table of how the classes move together (its 0.2 for stocks and bonds); the app has no such table, so the weighted average stands until the Plan build decides one. MK-NW-F-015 — it wanted a count of accounts with no value; the data model keeps a balance on every account, and a linked account not yet updated says so on its chip.</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>DONE — 71 of its 75 answers are the app's; 4 held and named. Not yet approved by him.</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/moneykeel_networth04_claude.json · MoneyKeel/functions/networth-and-performance/outside_networth_04.test.ts (71)</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Not pushed. Drawings carry the changes at their top: Net worth v08 (3 lines), Alternatives v02 (1). The standard "how an account is classed, split, counted and named" gained §8 to §11 (what counts toward retirement and its rate; itemising; the list under the class rows; history shared). PLAN BUILD: a correlation table for the portfolio volatility (its suggestion), and the Plan saying "not entered" for contributions never answered.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F221"/>
+  <autoFilter ref="A1:F222"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -7080,7 +7080,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>DONE — 72 of its 75 answers are the app's; 3 held (2 on his rule DEC-0100, 1 on the Roth limit). Not yet approved by him.</t>
+          <t>DONE — 72 of its 75 answers are the app's; 3 held and named. APPROVED by him 2026-10-07 (DEC-2634).</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>DONE — 71 of its 75 answers are the app's; 4 held and named. Not yet approved by him.</t>
+          <t>DONE — 71 of its 75 answers are the app's; 4 held and named. APPROVED by him 2026-10-07 (DEC-2634); his word on the count of accounts with no value: "no" — not built.</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$223</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F222"/>
+  <dimension ref="A1:F223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7131,8 +7131,40 @@
         </is>
       </c>
     </row>
+    <row r="223" ht="60" customHeight="1">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Outside review, returned file by file — Net worth file 5 (Claude): fifteen functions, 75 cases</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>He handed over file 5 on 2026-10-07. THE FILE judged fifteen functions: 7 WRONG, 4 INCOMPLETE, 4 RIGHT. MEASURED: its 75 answers run against the app as it stood — 17 of its cases failed (5 of them because the app had no function for a saved record with no accounts); 5 more are held on purpose; against the fixes — 75 of 75 pass, the 5 held at the app's answer. FIXED, by name. (1) MK-NW-F-056 bondInfo: a face value or a rate never entered was read as $0 — a CD typed by its balance showed a yield to maturity of −274%; each is now blank when not entered, and bondInfo says whether the account is a CD. (2) MK-NW-F-057 annualCoupon, new MK-NW-F-112 yearlyInterest: one rule for a year's interest — face × rate; with no face, today's value × rate; with no rate, nothing. (3) MK-NW-F-062 couponIncomeAnnual and MK-NW-F-063 interestIncomeAnnual use it, so the Bonds screen and the income figure agree on a CD (one said $0, the other balance × rate); a matured bond adds no interest. (4) MK-NW-F-060 approxYTM: worked on the value less accrued interest, as the current yield is (3.76% read where 4.57% is right). (5) MK-NW-F-061 bondSummary: the average yield over bonds with a value and a rate, each by the one rule. (6) MK-NW-F-064 bondRateSensitivity: the change measured between two prices worked the same way (a 4.4-year Treasury read down about $1,000 where about $1,680 is right); a CD refused by the function itself. (7) MK-NW-F-058 yearsToMaturity: calendar days, not the clock. (8) MK-NW-F-054 reclassifyAccounts: an account the person confirmed is never re-classed. (9) MK-NW-F-044 getAssetsState, new MK-NW-F-111 assetsStateFrom: a saved record whose accounts were all deleted is nothing saved, not $0 with a 7% average. ON THE SCREENS: the Bonds screen says 'face value not entered' / 'coupon rate not entered' and names the bonds its totals leave out; an account's BOND FACTS card stands when only the face value is missing. HELD, with the reason: MK-NW-F-040 the retired flow's one 'Taxable + cash' question seeds one account (a setup-flow change, for that build); MK-NW-F-053 a money-market account is Stocks / Funds by his rule DEC-0051; MK-NW-F-054 a holding tagged bond with no bond or fund word in its name keeps its tag; MK-NW-F-061 a bond maturing today has matured and is not next (batch 1, approved); MK-NW-F-064 its figures rounded in proportion to the bond (batch 1, approved). His rule A46 stands: a bond with no rate counts $0 of interest, and says so.</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>DONE — 75 of its 75 cases pass, 5 held at the app's answer and named. APPROVED under his standing word of 2026-10-07 (DEC-2634).</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/networth05_claude.json · MoneyKeel/functions/networth-and-performance/outside_networth_05.test.ts (75) · src/screens/__tests__/outside_networth_05.test.tsx (4)</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Not pushed. Drawings carry the changes at their top: Bonds v02 (4 lines), Performance v17 (3). The standard 'how an account is classed, split, counted and named' gained §12 (a bond's or a CD's figures) and §13 (a saved record with no accounts), and a line in §1 on confirmed accounts. Gemini's final audit of batch 5 is in to-send/.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F222"/>
+  <autoFilter ref="A1:F223"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$224</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F223"/>
+  <dimension ref="A1:F224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7163,8 +7163,40 @@
         </is>
       </c>
     </row>
+    <row r="224" ht="60" customHeight="1">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Outside review, second round — Net worth batches 2, 3 and 4 (Claude): 295 cases</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>He handed over the three second-round files on 2026-10-07. MEASURED: 295 cases run against the app — 33 failed before the fixes; after, 295 of 295 pass, 11 held at the app's answer. FIXED (each its own decision row under DEC-3035): MK-NW-F-004 the retirement return weighs what was set aside when the year began (13.72% → 12.98% in its example); MK-NW-F-108 529/HSA words fixed, '(Roth)' only in the Roth bucket; MK-NW-F-027 a hand-built account split holding by holding (a T-bill is Bonds &amp; CDs); MK-NW-F-025 Roth 401(k) named so; MK-NW-F-109 a holding with nothing stored is Unclassified (DEC-2160); MK-NW-F-028 broker Treasury words; MK-NW-F-003 a month-only date shown as the 1st; MK-NW-O-008 no walk for a window whose record begins too late; MK-NW-F-036 a person's own rate is an estimate; MK-NW-F-041 a percent match after the limit; MK-NW-F-046 history rounded down; MK-NW-F-052 itemised accounts carry their class's rate; MK-NW-F-002 Other investments reads the class split; MK-NW-F-011 a property's name is not read, a covered-call fund is a fund; new MK-NW-F-117 propertyUseMap — one reading of what a property is for, rent-aware (DEC-1926). HELD, by name: MK-NW-F-015 no refusal for an account with no value (his 'no', DEC-2747); MK-NW-F-019 and MK-NW-O-003 nothing entered shows $0 with 'Nothing entered yet' (DEC-0260); MK-NW-F-035 no correlation table until the Plan build; MK-NW-F-036 a period of '—' not blank (four cases; the card says '—'); MK-NW-F-048 the group label 'Personal property' (drawing v08); MK-NW-F-073 a holding with no price cannot be entered on the Itemize screen; MK-NW-F-094 an account sits under its largest class (DEC-2747b).</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>DONE — 295 of 295 cases pass, 11 held and named. APPROVED under his standing word (DEC-2634), recorded as DEC-3035.</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/networth0{2,3,4}_final_claude.json · MoneyKeel/functions/networth-and-performance/outside_networth_0{2,3,4}_final.test.ts</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Not pushed. OPEN FOR THE PLAN BUILD: the Plan's retirement callers do not yet hand the Income screen's rent entries to the property rule, so there the stored use still decides; the correlation table for volatility. Drawings carry the changes at their top: Performance v17 (3 lines), Net worth v08 (3), Alternatives v02 (1). Standard: §1, §2, §3, §4, §5, §6, §8, §9, §11 extended.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F223"/>
+  <autoFilter ref="A1:F224"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$224</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F224"/>
+  <dimension ref="A1:F225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7195,8 +7195,40 @@
         </is>
       </c>
     </row>
+    <row r="225" ht="60" customHeight="1">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Net worth By class: each account under each class with its part (his ruling, DEC-3146)</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>His words, 2026-10-07: "build it per mockup 07 where under each class you list each account Vanguard-0008 $45000, Chase - 0333 $34000." The main Net worth list already did this; MK-NW-F-094 ledgerGroups and the step-by-step setup list did not (a split account sat once under its largest class at its whole balance). Fixed: rows carry each account's part; the setup list prints the part under the account's name. The batch 4 rule DEC-2747b is marked replaced.</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>DONE — test: the rows under each heading add up to it.</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/net-worth.ts MK-NW-F-094 · src/screens/NetWorthScreen.tsx · outside_networth_04_final.test.ts</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Not pushed. Drawing v08's batch 4 line struck through and marked replaced.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F224"/>
+  <autoFilter ref="A1:F225"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$226</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F225"/>
+  <dimension ref="A1:F226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7227,8 +7227,40 @@
         </is>
       </c>
     </row>
+    <row r="226" ht="60" customHeight="1">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Home's YOUR INVESTMENTS = Net worth's Investments line (DEC-0457, MK-XS-M-003)</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Re-check 2026-10-08. Home printed Performance's ending value ($355,152, Vanguard's $838 uninvested cash included) under 'YOUR INVESTMENTS'; his definition DEC-0457 says investments do not include cash, and MK-XS-M-003 is one figure on Home and Net worth ($354,314). My batch 2 choice reversed; its decision row marked replaced.</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>DONE — outside_networth_02.test.tsx renders both values; fcc_agreement pins each figure to its door.</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/HomeScreen.tsx · src/screens/__tests__/outside_networth_02.test.tsx · src/screens/__tests__/fcc_agreement.test.tsx</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Home is outside build 55's scope; fixed because the figure was wrong against his definition.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F225"/>
+  <autoFilter ref="A1:F226"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$226</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$227</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F226"/>
+  <dimension ref="A1:F227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7259,8 +7259,40 @@
         </is>
       </c>
     </row>
+    <row r="227" ht="60" customHeight="1">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Fix brief — Net worth batch 06 (outside review, Claude): eight functions</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Handed over 2026-10-08. Built: exact years and bond prices (HIGH), a solved yield, missing values never $0 (amber box names an account with no balance), exact itemise sums with a not-final flag, wrapper words, CD words, the accrued note, calendar dates. 23 acceptance tests added as written: 22 pass; test 1 left failing as instructed — the brief's own working gives 50,250.6958, not 50,250.6939 (full precision 50,250.6956). DEVIATIONS, reasoned: the yield is solved on the full value (accrued included), not value − accrued (A47 governs the current yield; subtracting here counts accrued twice); a CD yields its stated rate (a $10,000 CD at 5.05% read 11.30% priced as a coupon bond). Reviewer cases from batches 3 and 5 that tested the approximation or days ÷ 365.25 were moved to hand-checked exact values, each noted. CD placement (Cash → Investments, his rule DEC-0051) in its own commit.</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>DONE — 4,104 tests; brief test 1 reported.</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/fix_brief_networth_06.test.ts</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Not pushed. A47 found: DEC-0280 (2026-08-26) 'subtract accrued interest when known; say so when not'.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F226"/>
+  <autoFilter ref="A1:F227"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$228</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F227"/>
+  <dimension ref="A1:F228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7291,8 +7291,40 @@
         </is>
       </c>
     </row>
+    <row r="228" ht="60" customHeight="1">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Accrued interest added for the yield to maturity — his ruling DEC-3390 (replaces A47)</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>His words, 2026-10-09: 'I like your recommendation to add accrued interest. Say "Added estimated $1,119 in accrued interest to bond value at 4.5% coupon for 363 days to calculate YTM. If this is not accurate, enter actual accrued interest"'. Built: estimatedAccrued (MK-NW-F-119); the yield to maturity on value + accrued; the yield on today's value and the average yield on the value as entered; the note in his words with its star on the yield to maturity. Moved cases hand-checked (batches 1, 3, 5, brief 06 test 5 → −0.66%).</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/bonds/index.ts · src/domain/bonds/a46_a47_coupon_and_accrued.test.ts</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Not pushed. Bonds v02 drawing noted.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F227"/>
+  <autoFilter ref="A1:F228"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$229</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F228"/>
+  <dimension ref="A1:F229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7323,8 +7323,40 @@
         </is>
       </c>
     </row>
+    <row r="229" ht="60" customHeight="1">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Final outside test of the whole Net worth module — brief for OpenAI</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>His words, 2026-10-09: 'write one last brief for Open AI to run one last set of test across entire NW module to ensure all fixes are in, and all screens, and functions meet tenants.' Written from the code as it stands (build-outside-test-cards.py --module-audit NW --for OpenAI): the tenets; four jobs (formula check and five cases for every function; each decided rule HELD or NOT; each screen figure against the tenets); his settled rulings (A47 replaced by DEC-3390); the 67 rules decided in the outside reviews, in force, from the decision log; the 71 figures the Net worth screens print, from the figure register; 101 function cards in four parts.</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>WAITING ON HIM — to send to OpenAI</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/to-send/moneykeel_audit_module_nw_for-openai_v01.md + _cards-part-1..4-of-4.md</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Batch 06's full 60-case JSON was never returned — only its fix brief; the brief's 23 tests are in. Tenets are draft v01, not yet approved by him.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F228"/>
+  <autoFilter ref="A1:F229"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$230</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F229"/>
+  <dimension ref="A1:F230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7355,8 +7355,40 @@
         </is>
       </c>
     </row>
+    <row r="230" ht="60" customHeight="1">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI preliminary handoff on the Net worth module (2026-10-09): four review findings, no cases</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>(1) Rent entries 'not handed in' vs 'none recorded' — REAL: the cash-flow budget read a profile with no rent entries as unknown; now none recorded = an empty list (MK-CF-O-020). Working it through found a gap in MK-NW-F-117: a renter owning only a stored 'rental' with no rent must not get a home, and an old stored 'rental' beside an unmarked mortgaged house must not stop that house being the home (else its mortgage is counted in Debts and in the budget line). Both pinned in budget-counted.test.ts. (2) Home ordering — already one rule: all five functions read propertyUseMap; addAsset keeps newest first. (3) More mortgages than properties — already shown: theNetWorth's mortgage check lists a mortgage on no property and Net worth opens it to fix. (4) Bond value wording — REAL: the editor said 'Current value'; it now says 'Market value, as your statement shows it — without accrued interest' (DEC-3390); Bonds v02 noted. (5) No cases yet — the full audit is still to come from OpenAI.</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>DONE — waiting on OpenAI's full audit</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned (handoff not saved as a file)</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Not pushed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F229"/>
+  <autoFilter ref="A1:F230"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$231</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F230"/>
+  <dimension ref="A1:F231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7387,8 +7387,40 @@
         </is>
       </c>
     </row>
+    <row r="231" ht="60" customHeight="1">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI final audit of the whole Net worth module (2026-10-09): 505 cases on 101 cards, run against the app</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Run all 505 cases (done: 433 pass, 16 app errors, 15 OpenAI slips, 35 open, 6 cannot be mapped — tests outside_networth_final_openai_part1..4, results in returned/results/). Fixed under his existing rules: matured bond pays $0 everywhere (DEC-2748d), category return start-weighted (DEC-1669/3035b), class sweep keeps the person's class and reads maturity before name and never a property name (DEC-2748h/2484r/2484i/3035o), Gold holding stays Alternatives, 'government' not a Treasury word (DEC-3035g), one property-use reading (DEC-3035p), missing balance left out with no NaN and row 'not entered', debt with no balance named in the amber box (DEC-3279e), bond with no rate keeps its facts card (DEC-2748b/c), Plan screens told the home and the car (DEC-2747e/2746b), impossible dates, unpriced itemise refused. Still to decide: the 'open' points (rent data unknown vs none, '2k' read as $2, month before Mar 31, CD with balance only, MK-NW-F-091 gain on a hand-typed CD).</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>IN PROGRESS — 16 app errors fixed or held; open points to decide</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/ (moneykeel_nw_part1..4_audit.json, results/)</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>Not pushed. MK-NW-F-091 held: making an unknown gain 'unknown' blanks two states of the approved account page (v17 frame 2) for any hand-typed CD or bond.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F230"/>
+  <autoFilter ref="A1:F231"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$232</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F231"/>
+  <dimension ref="A1:F232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7419,8 +7419,40 @@
         </is>
       </c>
     </row>
+    <row r="232" ht="60" customHeight="1">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Risk swing for Will my money last: a weighted average of each account's swing overstates the mix (60/40 at 18%/6% reads 13.2%, about 11.5% is right)</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Decide the table of how investment types move together in the Plan build, then compute the mix's swing from it (MK-NW-F-035 blendedVolatility)</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>PARKED by him 2026-10-10 (DEC-4082) until the Plan module</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts (MK-NW-F-035 blendedVolatility) · decision log DEC-4082 point 6</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>His point 6 of DEC-4082, parked; nothing changed in the code. The figure stays the weighted average until the Plan build sets the table.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F231"/>
+  <autoFilter ref="A1:F232"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$236</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F232"/>
+  <dimension ref="A1:F236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7451,8 +7451,132 @@
         </is>
       </c>
     </row>
+    <row r="233" ht="60" customHeight="1">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Net worth line-by-line drawing check v02 (against c40588f3, then 1769410f)</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Every Net worth screen and state against its approved drawing and READ THIS FIRST rows; fix what the code gets wrong; correct the drawings' own errors by dated lines (DEC-4529).</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-11 — 10 code fixes over two runs; 8 correction lines on 4 drawings; empty Debts door 'Add your debts ›' (DEC-4528); a home's edit sheet no longer asks what it is invested in</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/moneykeel_audit_mock-match_networth_2026-10-11_v02.md</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>The account page (Performance v17 frame 2) does NOT match: nine elements differ and the drawing's own figures do not add up ($52,704 of categories vs $101,000). Needs a redraw before it is rebuilt — next Net worth task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="45" customHeight="1">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Account page: redraw Performance v17 frame 2 so its figures add up, then rebuild the page to it</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Draw from the code's census strings and tokens; one phone, final state; his approval; then rebuild and mock-match.</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>OPEN — next Net worth task</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_performance_v17.html</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr"/>
+    </row>
+    <row r="235" ht="60" customHeight="1">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Claude's outside audit of Performance (4 batches, 225 cases, 45 functions incl. the time-weighted-return engine)</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>Run every case against the app; fix what his existing rules settle; bring the rest to him one at a time — AFTER Net worth is launch-ready (his order, 2026-10-11).</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>PAUSED by his order (one module at a time) — 225 of 225 run: 170 pass; 40 app errors fixed under his rules; open: 6 decision points (unknown window name, prices starting late, the trend function, partly matched sale, typed balance missing on the last record day; 0% CD settled by his rule), whether a holding's return includes its dividends, and the Home market line's 'including dividends' wording</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/results/performance_claude_0{1..4}_results.json</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Briefs v02 in to-send/moneykeel_brief_performance_0N_claude-code_v02.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="60" customHeight="1">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Read-only audit of every function's inputs and use (his objectives a and b)</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Every input entered, decided, published, fed or derived; every function, orchestrator and metric used on a live screen.</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-11 — findings to act on module by module (Net worth first)</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/moneykeel_audit_inputs-and-use_v01.xlsx · …_summary_v01.md</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Net worth: option contract size (MK-XS-I-063) set by nothing; 6% / 7% / ±1% with no decision (MK-NW-F-034, F-040, F-064); 10 tests-only and 2 unused functions; 7 figures printed under another ID.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F232"/>
+  <autoFilter ref="A1:F236"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$237</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F236"/>
+  <dimension ref="A1:F237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>PAUSED by his order (one module at a time) — 225 of 225 run: 170 pass; 40 app errors fixed under his rules; open: 6 decision points (unknown window name, prices starting late, the trend function, partly matched sale, typed balance missing on the last record day; 0% CD settled by his rule), whether a holding's return includes its dividends, and the Home market line's 'including dividends' wording</t>
+          <t>IN PROGRESS — his answers of 2026-10-12 built (DEC-4640 … DEC-4646): the 6 decision points and the two dividend questions are closed — unknown window name refuses, prices starting late are measured and named, six unused functions removed, a partly matched sale counted once, the typed-balance case was the judge's double count (withdrawn), a holding's return carries its dividends once, the market figure's record corrected, option shares per contract</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>Briefs v02 in to-send/moneykeel_brief_performance_0N_claude-code_v02.md.</t>
+          <t>Briefs v02 in to-send/moneykeel_brief_performance_0N_claude-code_v02.md. 2026-10-12: 35 outside cases settled or removed (1 + 3 + 25 removed + 5 re-pointed + 1 + 1 + 1 brief wrong); results files carry a 'settled' line on each. Not committed.</t>
         </is>
       </c>
     </row>
@@ -7571,12 +7571,44 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>Net worth: option contract size (MK-XS-I-063) set by nothing; 6% / 7% / ±1% with no decision (MK-NW-F-034, F-040, F-064); 10 tests-only and 2 unused functions; 7 figures printed under another ID.</t>
+          <t>Net worth: option contract size (MK-XS-I-063) set by nothing; 6% / 7% / ±1% with no decision (MK-NW-F-034, F-040, F-064); 10 tests-only and 2 unused functions; 7 figures printed under another ID. 2026-10-12: option contract size (MK-XS-I-063) now set by the broker (mini option 10) or the person (DEC-4646); MK-PF-F-003 / 016 / 017 / 018 / 019 / 021 removed (DEC-4642).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="60" customHeight="1">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Performance decisions of 2026-10-12 — eight items, built (his: "1, 2 - approved." · "3,4, 8-approved.")</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>1 unknown window name refuses (DEC-4640) · 2 prices starting late: measured from the first price, the line wherever the figure shows (DEC-4641) · 3 six unused functions removed (DEC-4642) · 4 a sale bigger than the purchases counted once (DEC-4643) · 5 withdrawn: the judge double-counted the IRA (+2.00% is right) · 6 dividends counted once (DEC-4644, his existing rule) · 7 the market figure's 'price only' record corrected (DEC-4645) · 8 option shares per contract (DEC-4646)</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-12 — code, tests, function rules, standards, changelog, drawings' READ THIS FIRST lines; not committed</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/performance_decisions_2026_10_12.test.tsx · src/domain/performance/start_date_month_end.test.ts · src/domain/performance/realized.test.ts · MoneyKeel/documents/standards/moneykeel_calc_spec_precision-and-display_v01.md</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Found while applying item 1: 'Since' was read as today, so each holding's Since figure (the category returns under the walk) was one day's move. Since now hands over its own first day.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F236"/>
+  <autoFilter ref="A1:F237"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$238</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F237"/>
+  <dimension ref="A1:F238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7607,8 +7607,40 @@
         </is>
       </c>
     </row>
+    <row r="238" ht="60" customHeight="1">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Performance line-by-line drawing check (v17 phones 1, 3, 4, 5 · Look back v01 · Holding detail v02), against 02adb375</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Every visible word AND figure of each phone against the screen rendered on the drawing's own day; then colours, sizes, weights; fix what the code gets wrong, each with a test; drawing arithmetic checked (DEC-4529). Phone 2, the account page, is out of scope: it is the redraw row of 2026-10-11.</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-12 — 11 code fixes (window control colours, one-line notes, 13-point date and labels, walk weights, withdrawals not red, notes' grey, category table, graph dates over a year, gridlines that hold the line, day-one frame, Holding liquidated colour); no drawing arithmetic error found; not committed</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/moneykeel_audit_mock-match_performance_2026-10-12_v01.md · src/screens/__tests__/perf_mock_match_2026_10_12.test.tsx</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Phones 1 and 3 now match the drawing figure for figure, not only word for word: the test builds a household whose record gives the drawn $100,000 → $123,000, +0.41%, +4.90%, 7.46%, 6.88%, $38,000 → $52,704 and the rest.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F237"/>
+  <autoFilter ref="A1:F238"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$240</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F238"/>
+  <dimension ref="A1:F240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7639,8 +7639,72 @@
         </is>
       </c>
     </row>
+    <row r="239" ht="60" customHeight="1">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>DEC-5068 — Wealth generated and Return for every holding with a history, where the beginning is worked back (his ruling of 2026-10-13)</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>thePerformance keeps the walk and leaves out a holding with no price history; Return = the holdings with a history only; notIncludedSentence replaces cannotWorkBackSentence; account page and Performance cards print it; outside cases settled; rules, standard, Changelog, v17 note.</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-13 — built and tested; Return shown where the beginning is worked back; sentence on the account page and each account's card; not committed</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/dec_worked_back_known_holdings.test.ts · src/screens/__tests__/dec_worked_back_known_holdings.test.tsx · MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_performance_v17.html</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>$50,000 = VTI $40,000 (+10%) + Treasury 2031 $10,000 → Wealth generated $3,636, Return +10.00%, walk drawn (was —, —, no walk). Replaces DEC-3656 part 2 (DEC-3656b, now not in use).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="60" customHeight="1">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>DEC-5136 — the walk card's title is always HOW $&lt;beginning&gt; BECAME $&lt;ending&gt; · ALL ACCOUNTS (his ruling of 2026-10-13)</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Both screens title the walk the one way in every state; retire the day-one title from code, tests and mock-match expectations; READ THIS FIRST rows; Changelog.</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-13 — built and tested on both screens; READ THIS FIRST rows on v17 and Ways to add v10; not committed</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/PerformanceScreen.tsx · src/screens/AccountPortfolioScreen.tsx · src/screens/__tests__/perf_matches_v17.test.tsx · src/screens/__tests__/perf_mock_match_2026_10_12.test.tsx</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>Day one reads HOW $354,314 BECAME $354,314 · ALL ACCOUNTS (was HOW TODAY'S VALUE STANDS · ALL ACCOUNTS $354,314); the account page gains · THIS ACCOUNT as v17 frame 2 draws it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F238"/>
+  <autoFilter ref="A1:F240"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$240</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F240"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7703,8 +7703,40 @@
         </is>
       </c>
     </row>
+    <row r="241" ht="60" customHeight="1">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>DEC-5291 — let price history count: a window that starts before the daily record is worked back, not greyed (his "approved." of 2026-10-13)</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>thePerformance works back a record-too-late window when a holding has a history (DEC-3035i's refusal only where none has); mixed accounts = the cards added up; cash gains $0 unnamed; day-one line; tests settled; rules re-read, standards, Changelog, v17 READ THIS FIRST row.</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-13 — built and tested; Performance tab, account page and Home work a too-late window back from price history; DEC-3035i marked OLD, NOT IN USE; not committed</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/dec_price_history_counts.test.ts · src/screens/__tests__/dec_price_history_counts.test.tsx · MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_performance_v17.html</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>Vanguard linked today, VTI $40,000 (+10%) + Treasury 2031 $10,000 by hand: 1Y +10.00% (was greyed —), Wealth generated $3,636, Return +10.00%, sentence names Treasury 2031 (was "The record begins Oct 13, 2026, …"). Mixed: Fidelity $100,000→$112,000 + Vanguard worked back → summary $136,364→$152,000, +11.47% = the cards added up. Day-one line: "Day one: your value is real and your daily record starts today. Longer windows are worked back from each holding's price history."</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F240"/>
+  <autoFilter ref="A1:F241"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$242</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F241"/>
+  <dimension ref="A1:F242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7731,12 +7731,44 @@
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>Vanguard linked today, VTI $40,000 (+10%) + Treasury 2031 $10,000 by hand: 1Y +10.00% (was greyed —), Wealth generated $3,636, Return +10.00%, sentence names Treasury 2031 (was "The record begins Oct 13, 2026, …"). Mixed: Fidelity $100,000→$112,000 + Vanguard worked back → summary $136,364→$152,000, +11.47% = the cards added up. Day-one line: "Day one: your value is real and your daily record starts today. Longer windows are worked back from each holding's price history."</t>
+          <t>Vanguard linked today, VTI $40,000 (+10%) + Treasury 2031 $10,000 by hand: 1Y +10.00% (was greyed —), Wealth generated $3,636, Return +10.00%, sentence names Treasury 2031 (was "The record begins Oct 13, 2026, …"). Mixed: Fidelity $100,000→$112,000 + Vanguard worked back → summary $136,364→$152,000, +11.47% = the cards added up. Day-one line, in his words (DEC-5425, 2026-10-14): "You added your accounts today. Figures for 1M, 1Y and longer come from each holding's past prices." (the wording first proposed here was replaced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="60" customHeight="1">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>DEC-5425 — the Performance tab's day-one line in his words (his "approved." of 2026-10-14)</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>PerformanceScreen day-one line (where a window is worked back) reads his words; tests moved; DEC-5291's records re-quoted; standards; Changelog row; v17 READ THIS FIRST row.</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-14 — built and tested; not committed</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/PerformanceScreen.tsx · src/screens/__tests__/dec_price_history_counts.test.tsx · src/screens/__tests__/perf_matches_v17.test.tsx · src/screens/__tests__/perf_mock_match_2026_10_12.test.tsx · MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_performance_v17.html</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Before: "Day one: your value is real and your daily record starts today. Longer windows are worked back from each holding's price history." Now: "You added your accounts today. Figures for 1M, 1Y and longer come from each holding's past prices." Canon checked: no clash.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F241"/>
+  <autoFilter ref="A1:F242"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -3445,14 +3445,14 @@
           <t>Claude: draw it in the Net worth series (v09) for approval before building.</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>TO DO</t>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-18 — built and tested (commit 42048261 for the one door; the rest of state C not committed)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>src/screens/NetWorthScreen.tsx (seeded, no accounts) · src/screens/__tests__/empty_state_q48.test.tsx</t>
+          <t>src/screens/NetWorthScreen.tsx · src/screens/__tests__/nw_no_accounts_one_door.test.tsx · src/screens/__tests__/empty_state_q48.test.tsx</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -3460,7 +3460,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Before: a later visit with no account showed "Add your accounts ›" 3 times (hero, Cash, Investments), no Personal property, no emergency fund line, a dated title, and "＋ Add an account". Now: the same screen as the first day, Net worth v08 state C, word for word — "Add your accounts ›" once, the three ways to add once, "Add your debts" on Debts (DEC-4528). Ruled by DEC-0227. No new drawing: v08 state C is the approved drawing of this data state. The retirement line keeps state C's words only when all three answers are missing; with one or two given it names what is left (DEC-0086), e.g. "a sample, not your number — 2 answers make it yours: what you spend and what you have ›".</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="60" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
@@ -7571,7 +7575,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>Net worth: option contract size (MK-XS-I-063) set by nothing; 6% / 7% / ±1% with no decision (MK-NW-F-034, F-040, F-064); 10 tests-only and 2 unused functions; 7 figures printed under another ID. 2026-10-12: option contract size (MK-XS-I-063) now set by the broker (mini option 10) or the person (DEC-4646); MK-PF-F-003 / 016 / 017 / 018 / 019 / 021 removed (DEC-4642).</t>
+          <t>Net worth: option contract size (MK-XS-I-063) set by nothing; 6% / 7% / ±1% with no decision (MK-NW-F-034, F-040, F-064); 10 tests-only and 2 unused functions; 7 figures printed under another ID. 2026-10-12: option contract size (MK-XS-I-063) now set by the broker (mini option 10) or the person (DEC-4646); MK-PF-F-003 / 016 / 017 / 018 / 019 / 021 removed (DEC-4642). 2026-10-19: MK-NW-F-006 / 013 / 015 / 017 / 018 / 019 / 020 / 038 removed and their numbers retired (DEC-5758, his words: "Removing #4,5,6,7-10,11 - approved.") — 8 of 8.</t>
         </is>
       </c>
     </row>

--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$243</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F242"/>
+  <dimension ref="A1:F243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7771,8 +7771,40 @@
         </is>
       </c>
     </row>
+    <row r="243" ht="60" customHeight="1">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>DEC-6412 — a window that opens before the daily record begins is joined at the record's first day (his "approved." of 2026-10-19, amends DEC-5291)</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>thePerformance joins the days before the record (price history) to the record's own return; every caller hands over the price histories; the note under the summary; tests for the three cases and a mixed one; account-page drawing state A, side column, READ THIS FIRST row 43; Performance v17 READ THIS FIRST row; standards; Changelog row; function rules re-read.</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-19 — built and tested; not committed</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/performance.ts · MoneyKeel/functions/networth-and-performance/dec6412_join_at_record_start.test.ts · src/screens/AccountPortfolioScreen.tsx · src/screens/PerformanceScreen.tsx · src/screens/HomeScreen.tsx · src/screens/__tests__/account_page_drawing_states.test.tsx · src/screens/__tests__/perf_mock_match_2026_10_12.test.tsx · MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_account-page_v01.html · MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_performance_v17.html</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>Before: state A 1Y +7.12%, 2Y +9.57% (worked back whole); Performance v17 phone 1 1Y +6.10%, 2Y +11.10%. Now: state A 1Y +8.26% (= Since), 2Y +10.87% a year; phone 1 1Y +7.46% (= Since), 2Y +11.81% a year. States B to E unchanged.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F242"/>
+  <autoFilter ref="A1:F243"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$256</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F243"/>
+  <dimension ref="A1:F256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1185,9 +1185,9 @@
           <t>Founder: answer Q38 (bond fields and display); then Claude: mock, then code + test</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-20 — Q38 answered by the lead's decisions DEC-6615, DEC-6616 and DEC-6617 under DEC-0281; built and tested; not committed</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>What's the questions?</t>
+          <t>What's the questions? | ANSWERED 2026-10-21 (records): your question was which three things Q38 asked. (1) Is a bond's quantity its face amount or a count of bonds? — the face amount (DEC-6615). (2) Is earned interest the interest records for the bond? — yes, the interest and coupon records dated in the window, as DEC-6212 already counts (DEC-6616). (3) Is current price per $100 of face or a dollar value? — per $100 of face, worked out from the value and the face, never typed (DEC-6617). All three decided by the lead on 2026-10-20 without asking you; one word reverses any. Built: one value rule (market value, else what was paid, else face, else Value not entered) on Bonds, the account page and Net worth; What you paid and Price in BOND FACTS. Tests: bond_value_agreement.test.tsx 5 of 5, account_page_drawing_states.test.tsx 59 of 59, bond_units.test.ts 5 of 5 (2026-10-21).</t>
         </is>
       </c>
     </row>
@@ -1749,9 +1749,9 @@
           <t>Founder: confirm or redirect</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-09 — both calls settled by his later rulings: A47 replaced by DEC-3390; the strict reading of A46 held by DEC-2748b</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1764,7 +1764,11 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>CHECKED 2026-10-20: A47 → DEC-3390 (2026-10-09, accrued interest added for the yield to maturity, commit 9f9eda02); A46 read strictly → DEC-0279 with DEC-2748b (a rate never entered stays blank, no built-in yield stands in); test src/domain/bonds/a46_a47_coupon_and_accrued.test.ts.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="60" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -1917,9 +1921,9 @@
           <t>Founder: say whether each gets a new version on the canon now (old archived), or at its next change. Plan v05 already carries its list inside the file as mark 14 and is fixed when v06 is drawn.</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-20 — none of the eight mocks draws a retired word now: six are archived, the other two are clean in their frames</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1934,7 +1938,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Recounted 2026-09-26: the old row said five; the drawn-frame scan finds eight.</t>
+          <t>Recounted 2026-09-26: the old row said five; the drawn-frame scan finds eight. | CHECKED 2026-10-20: archived — cash-flow-this-month-and-spending_v06, look-ahead_v03, money-four-tabs_v01, filing-status-question_v02 and plan_v05 (cashflow/ and plan/archive/, 2026-09-26), account-detail_v01 (networth-and-performance/archive/, 2026-10-01, DEC-0646). Still live and clean in their drawn frames: income-end-to-end_v07 (none of "A usual month", "Gross a year", "In (take-home)", "spending") and empty-state-pattern_v01 (edited in place 2026-10-20: "spending" and "owe" now appear only in its dated note about the change). Nothing is left to ask him.</t>
         </is>
       </c>
     </row>
@@ -3241,9 +3245,9 @@
           <t>Claude: done 2026-09-14 — Build 53 files matched by exact content and recorded in MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md. Founder: (1) confirm Net worth = v5 + square corners; (2) say whether to draw Net worth v6 from the Build 53 code (v5 with square corners) so one picture matches what shipped; (3) say whether to move the Build 53 set out of archive/. Home, Cash flow and the other screens are still to be traced.</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-01 — his three asks are settled: Net worth v06 was confirmed (DEC-0219, 2026-09-14), then v08 was approved in full and built (DEC-0644, 2026-10-01)</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -3256,7 +3260,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>CHECKED 2026-10-20: the design record MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md names v08 for Net worth and the approved Cash flow drawings; src/screens/__tests__/networth_matches_v08.test.tsx holds the screen to v08. Asks (1) and (2) are answered by DEC-0219 then DEC-0644; ask (3), moving the Build 53 set out of archive/, is moot — v08 is the design of record. Tracing Home's Build 53 design is my own work, not a question for him (the record's own note, "Home and every screen opened from another screen still need their Build 53 design traced").</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="60" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -3301,9 +3309,9 @@
           <t>Founder: say yes to v08, or name a mark. Also: today's money for the retirement figures and tax on taxable withdrawals (recommended); whether dark/light bars replace the Plan tab's quiet labels. Claude: once approved, record v08 as the current Net worth design, archive v06, then build marks 1–4 and 10–14 with tests (odds exact and Linked / Link again are app-wide).</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-03 — v08 approved in full (DEC-0644, 2026-10-01: "Quite Instrument v08 - approved all screens from A to G.") and built; held word for word in all eight states</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -3318,7 +3326,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 founder reviewed v07: odds exact · return 2 decimals · keep Tight ⚠ · Linked unless stale · Linked / Link again · dark bars for sections, light-green for sub-headings · state C too much duplication · asked whether the retirement figures are right. v08 answers all of it.</t>
+          <t>2026-09-14 founder reviewed v07: odds exact · return 2 decimals · keep Tight ⚠ · Linked unless stale · Linked / Link again · dark bars for sections, light-green for sub-headings · state C too much duplication · asked whether the retirement figures are right. v08 answers all of it. | CHECKED 2026-10-20: src/screens/__tests__/networth_matches_v08.test.tsx (commit f6c70644); v06 and v07 are in networth-and-performance/archive/. The two Plan asks on this row (today's money and tax on taxable withdrawals; the Plan tab's bars) belong to the row "The retirement sentence (Net worth, Plan, Home)…" and the Plan build.</t>
         </is>
       </c>
     </row>
@@ -3361,9 +3369,9 @@
           <t>Founder: say whether to show today's money and to tax taxable withdrawals (recommended). Claude: then write both as findings on the master rows (MK-XS-M-002 and the pot/leftover figures) before any code.</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>WAITING ON YOU</t>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-26 — ruled by DEC-0365: the retirement number stays before tax and as shipped; the present-value question moved to the row "Plan · present value vs future value"</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -3376,7 +3384,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>CHECKED 2026-10-20: DEC-0365, his words: "…to keep retirement number pre-tax, as we cannot determine tax accurately. The lengthly explanation is horrible."; proof MoneyKeel/documents/plan/moneykeel_pres_mock_plan_v06.html. This is a Plan row: the figures are the Plan's, printed also on Net worth and Home.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="60" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -3689,9 +3701,9 @@
           <t>Performance chips are fixed in mock v11 (mark 10). Sweep the other semicircle selectors and bring them to 12 points, screen by screen, each with its own mock.</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>TO DO</t>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — no button or choice app-wide has semicircle ends (DEC-0231 TESTED)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -3706,7 +3718,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Counted 2026-09-25.</t>
+          <t>Counted 2026-09-25. | 2026-10-20 (DEC-0231): the choice chips on Bonds, Alternatives, Itemize and Net worth (By category · By institution and the add sheet) now use the 12-point corner, with correction lines on their drawings. Still on the semicircle (Radii.pill), counted 2026-10-21 while another agent rounds the remaining action buttons app-wide: 11 uses — buttons and badges on Import holdings, Settings, the Retirement cockpit, the error screen, the UI badge, and Performance's period pills. Left open until that agent reports; DEC-0231 is marked TESTED then. | 2026-10-21 CLOSED: 8 button styles in 9 places and the onboarding Monthly · Yearly choice moved to the 12-point corner; 14 drawings carry a dated line. Test: src/__tests__/decisions_are_held.test.ts, 4 DEC-0231 tests, 123 of 123 pass.</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4271,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-26 — built and tested; since superseded by Performance v17 (DEC-0647) and the account-page drawing v01 (DEC-6457)</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -4274,7 +4286,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>B-108 to B-110. Found by comparing every static string mock v14 draws against every string the app can render.</t>
+          <t>B-108 to B-110. Found by comparing every static string mock v14 draws against every string the app can render. | CHECKED 2026-10-20: src/screens/__tests__/performance_mock_v14_gaps.test.tsx (first committed ac8114ca). AccountDetailScreen.tsx no longer exists: /account-detail opens AccountPortfolioScreen.tsx (041921af).</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4335,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-27 — the account page says "Cash in this account"; no screen says "sweep cash"</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -4338,7 +4350,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>B-111. The ruling lived in a changelog row with nothing enforcing it — that is why it was lost.</t>
+          <t>B-111. The ruling lived in a changelog row with nothing enforcing it — that is why it was lost. | CHECKED 2026-10-20: src/screens/AccountPortfolioScreen.tsx line 325 ("Cash in this account"); a search of src/, app/ and MoneyKeel/functions finds "sweep cash" only in a test name and comments.</t>
         </is>
       </c>
     </row>
@@ -4353,9 +4365,9 @@
           <t>11 of 12 DONE. Net worth 6 of 6, Performance 2 of 2, Cash flow 4 of 5 (Q-CF-3, Q-CF-4, Q-CF-5, Q-CF-6). Q-CF-1 needed nothing. ONE LEFT AND IT IS MINE: Q-CF-2, no longer blocked — he settled it on 2026-09-28 by pointing at the approved design, and C-2 is withdrawn.</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>TO DO</t>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-28 — 12 of 12 built: the last one, theMonth for Q-CF-2, is built</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -4370,7 +4382,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Each one: his row (done — he ruled all 13), the photograph, the door beside the old code, callers moved one at a time, old doors closed with a guard.</t>
+          <t>Each one: his row (done — he ruled all 13), the photograph, the door beside the old code, callers moved one at a time, old doors closed with a guard. | CHECKED 2026-10-20: MoneyKeel/functions/cashflow/the-month.ts (theMonth, MK-CF-O-010 in the code today) + the-month.test.ts; the twelve doors and their guard_one_door_* tests were first committed in ac8114ca.</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4527,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-28 — a bank CD gets no rates-move estimate; refined since by DEC-3837 (a CD bought through a broker is priced like a bond)</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -4530,7 +4542,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Found by his question on Q-NW-4: "CD rates don't move and one can do nothing if CD rates move." He was right. A real bond still gets the estimate — pinned by a test.</t>
+          <t>Found by his question on Q-NW-4: "CD rates don't move and one can do nothing if CD rates move." He was right. A real bond still gets the estimate — pinned by a test. | CHECKED 2026-10-20: src/domain/bonds/index.ts pricedLikeBond (MK-NW-F-131) · src/domain/bonds/dec3837_cd_bought.test.ts · MoneyKeel/functions/networth-and-performance/bonds.test.ts.</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4559,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-27 — the Alternatives total stays in "what am I worth"; EST. GROWTH /year has its own door</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -4562,7 +4574,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>His question on the answer sheet: "Not sure where on alternatives screen is the question what am I worth - provide more context?"</t>
+          <t>His question on the answer sheet: "Not sure where on alternatives screen is the question what am I worth - provide more context?" | CHECKED 2026-10-20: MoneyKeel/functions/networth-and-performance/alternatives-outlook.ts (theAlternativesOutlook — MK-NW-O-005 in the code today, not O-006 as written above) + alternatives-outlook.test.ts; first committed ac8114ca.</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4591,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-27 — canon row 14 matches capitals; both labels read /year</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -4594,7 +4606,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Third hole found in the same canon row this week: the spaced form, the curly quotes, now the capitals.</t>
+          <t>Third hole found in the same canon row this week: the spaced form, the curly quotes, now the capitals. | CHECKED 2026-10-20: row 14 of moneykeel_naming_spec_calculation-vocabulary_v01.md carries the /i flag; src/screens/BondsScreen.tsx line 71 "COUPON /year", src/screens/OtherInvestmentsScreen.tsx line 74 "EST. GROWTH /year"; guard src/__tests__/one_term_per_concept.test.ts.</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4687,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-27 — built and tested; the Bonds screen and the account page read one door</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -4690,7 +4702,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>The build caught two things I would have missed: the 11 figures declared AND still hand-typed, and five of his open bond questions (Q01-Q05) left with no row to sit on when those rows moved. Both fixed — Q01-Q05 now ride the declared figures.</t>
+          <t>The build caught two things I would have missed: the 11 figures declared AND still hand-typed, and five of his open bond questions (Q01-Q05) left with no row to sit on when those rows moved. Both fixed — Q01-Q05 now ride the declared figures. | CHECKED 2026-10-20: MoneyKeel/functions/networth-and-performance/bonds.ts (MK-NW-O-001 theBonds) + bonds.test.ts + src/__tests__/guard_one_door_bonds.test.ts; first committed ac8114ca. The account page is now AccountPortfolioScreen.tsx.</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4719,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-27 — built and tested</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -4722,7 +4734,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>The build again caught a question with no row to sit on (Q15, the institution-word rule) and it was re-homed on MK-NW-M-019 Income.</t>
+          <t>The build again caught a question with no row to sit on (Q15, the institution-word rule) and it was re-homed on MK-NW-M-019 Income. | CHECKED 2026-10-20: MoneyKeel/functions/networth-and-performance/account.ts (MK-NW-O-002 theAccount) + account.test.ts + src/__tests__/guard_one_door_account.test.ts; first committed ac8114ca.</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4751,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-27 — built and tested</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -4754,7 +4766,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>The build caught three things: the multi-screen tab never printed declared figures at all (a gap in the rule-11 machinery — fixed), five more of his questions lost their row (Q10-Q13, Q17 — re-homed), and his ruling G19 on the debt payment rule had to be carried into the declaration or the row would have lost it.</t>
+          <t>The build caught three things: the multi-screen tab never printed declared figures at all (a gap in the rule-11 machinery — fixed), five more of his questions lost their row (Q10-Q13, Q17 — re-homed), and his ruling G19 on the debt payment rule had to be carried into the declaration or the row would have lost it. | CHECKED 2026-10-20: MoneyKeel/functions/networth-and-performance/net-worth.ts (MK-NW-O-003 theNetWorth) + net-worth.test.ts + src/__tests__/guard_one_door_net_worth.test.ts; first committed ac8114ca.</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4783,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-27 — built and tested</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -4786,7 +4798,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>My own file failed the canon guard — I had written "cushion", "must-pay bills" and "you typed". The door is named theEmergencyFund now.</t>
+          <t>My own file failed the canon guard — I had written "cushion", "must-pay bills" and "you typed". The door is named theEmergencyFund now. | CHECKED 2026-10-20: MoneyKeel/functions/networth-and-performance/emergency-fund.ts (MK-NW-O-004 theEmergencyFund) + emergency-fund.test.ts + src/__tests__/guard_one_door_emergency_fund.test.ts; first committed ac8114ca.</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4815,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-28 — both runways and the debt payments are shown; how debts are counted has since changed (DEC-1923: every debt from Debts)</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -4818,7 +4830,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>On the pinned test household the figure moved 2.0 → 2.4 months: essentials ($3,600) instead of planned spend ($4,500) makes it longer, the $150 Visa minimum makes it shorter, and the $2,400 mortgage is correctly excluded. Three new figures declared: MK-NW-M-046, MK-NW-M-047, MK-NW-M-048.</t>
+          <t>On the pinned test household the figure moved 2.0 → 2.4 months: essentials ($3,600) instead of planned spend ($4,500) makes it longer, the $150 Visa minimum makes it shorter, and the $2,400 mortgage is correctly excluded. Three new figures declared: MK-NW-M-046, MK-NW-M-047, MK-NW-M-048. | CHECKED 2026-10-20: src/screens/NetWorthScreen.tsx prints MK-NW-M-013, MK-NW-M-046 and MK-NW-M-047 ("Both include … of debt payments you cannot stop"); MoneyKeel/functions/networth-and-performance/emergency-fund.test.ts.</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4847,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-28 — fixed and tested; since DEC-1923 the mortgage is counted from Debts</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -4850,7 +4862,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Same class as the canon guard misses this week: a rule written against a shape the data does not have.</t>
+          <t>Same class as the canon guard misses this week: a rule written against a shape the data does not have. | CHECKED 2026-10-20: emergency-fund.test.ts, the test "a mortgage is never counted twice — and since 2026-10-04 it is counted from Debts, not from the budget line (DEC-1923)".</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4879,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-28 — built and tested</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -4882,7 +4894,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>10 more figures moved out of the hand-typed lists; three of his questions (Q07, Q20, Q21) re-homed on the figures they ask about. 2,917 tests green.</t>
+          <t>10 more figures moved out of the hand-typed lists; three of his questions (Q07, Q20, Q21) re-homed on the figures they ask about. 2,917 tests green. | CHECKED 2026-10-20: holding.ts (theHolding — MK-NW-O-006 in the code today) + holding.test.ts + src/__tests__/guard_one_door_holding.test.ts; alternatives-outlook.ts (theAlternativesOutlook — MK-NW-O-005 today) + alternatives-outlook.test.ts; the two numbers in the title are the other way round from the code; first committed ac8114ca.</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5135,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-28 — all twelve doors built, each with its tests and a guard</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -5138,7 +5150,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>2,947 tests green, every gate passing, nothing committed.</t>
+          <t>2,947 tests green, every gate passing, nothing committed. | CHECKED 2026-10-20: MoneyKeel/functions/networth-and-performance/ and MoneyKeel/functions/cashflow/; guards src/__tests__/guard_one_door_account, _bonds, _cashflow, _emergency_fund, _holding, _net_worth, _performance, _will_it_last (.test.ts); first committed ac8114ca. Phases 3 to 6 of the orchestrator plan are their own rows.</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5167,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-28 — fixed, with a guard</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -5170,7 +5182,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>The new guard found a 27th on its first run, and that one predates me: FilingStatusScreen named MK-CF-F-099 taxOwedFor, but F-099 is deductionFor and taxOwedFor is F-101 — a comment sending the next reader to the wrong function. This is what step 6 is for: the file and the code have to agree, and until now nothing checked that they did.</t>
+          <t>The new guard found a 27th on its first run, and that one predates me: FilingStatusScreen named MK-CF-F-099 taxOwedFor, but F-099 is deductionFor and taxOwedFor is F-101 — a comment sending the next reader to the wrong function. This is what step 6 is for: the file and the code have to agree, and until now nothing checked that they did. | CHECKED 2026-10-20: src/__tests__/guard_identifiers_match_register.test.ts (first committed ac8114ca); moneykeel_function_register.json records renames and retirements ("renamed", "retired").</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5199,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>CODED, NOT VERIFIED</t>
+          <t>DONE 2026-09-28 — the worked examples run through the real doors on every build</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -5202,7 +5214,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>This is the step the objectives standard names: “the row's worked example runs through the real orchestrator, the identifier joins them, then: file and code are both updated and they match 100%.” It had never been done for any question. The writing of a figure also moved into ONE place (writeFigure) — an example formatted by a second copy of the rounding would prove nothing about what a person sees.</t>
+          <t>This is the step the objectives standard names: “the row's worked example runs through the real orchestrator, the identifier joins them, then: file and code are both updated and they match 100%.” It had never been done for any question. The writing of a figure also moved into ONE place (writeFigure) — an example formatted by a second copy of the rounding would prove nothing about what a person sees. | CHECKED 2026-10-20: src/__tests__/worked_examples.test.ts (first committed ac8114ca).</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5391,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>TESTED, NOT VERIFIED</t>
+          <t>DONE 2026-09-28 — the example household budgets and owes the same $2,400</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -5394,7 +5406,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>A worked example has to be a household that could exist, or it is not a case anyone can follow — the same rule as numbers inside a mock having to add up. I wrote one that could not.</t>
+          <t>A worked example has to be a household that could exist, or it is not a case anyone can follow — the same rule as numbers inside a mock having to add up. I wrote one that could not. | CHECKED 2026-10-20: MoneyKeel/functions/networth-and-performance/emergency-fund.ts, the EXAMPLE fixture (Rent / Mortgage $2,400 and a $2,400 mortgage debt); src/__tests__/worked_examples.test.ts.</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5423,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>TESTED, NOT VERIFIED</t>
+          <t>DONE 2026-10-05 — closed by a later ruling: DEC-0441 ("use the budget") was replaced by DEC-1923, so the two figures can no longer disagree and there is nothing left for a screen to ask</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -5426,7 +5438,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>The in-chat decision hole is closed with it: moneykeel_decisions_in_chat.json is the sixth source, and the log now carries what he says in conversation the same day.</t>
+          <t>The in-chat decision hole is closed with it: moneykeel_decisions_in_chat.json is the sixth source, and the log now carries what he says in conversation the same day. | CHECKED 2026-10-20: since DEC-1923 every debt is counted from Debts and the Rent / Mortgage budget line stands down when the home's mortgage is in Debts (MoneyKeel/functions/cashflow/budget-counted.ts + budget-counted.test.ts); housingDisagreement was removed in a398a5aa. The decision above is DEC-0441, not DEC-0471 as written.</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5824,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — 3 of 7 screens approved. 4 to go before step 1.a can pass.</t>
+          <t>DONE 2026-10-01 — 7 of 7 screens designed, approved and coded; step 1.a passes</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -5827,7 +5839,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>My scope error, twice: I first put twelve screens in this module by merging two questions — which screens must OBEY its decisions, and which need an APPROVED DESIGN from it. Step 1.a asks the second. The three that print a Net worth figure (Home MK-NW-M-012, Insights MK-NW-M-005/047/048, Job safety MK-NW-M-013) are still bound by its decisions in step 1.b; what they are released from is needing a Net worth design. The five are now subtracted BY NAME rather than the derivation being dropped, so a new screen printing a Net worth figure is still noticed.</t>
+          <t>My scope error, twice: I first put twelve screens in this module by merging two questions — which screens must OBEY its decisions, and which need an APPROVED DESIGN from it. Step 1.a asks the second. The three that print a Net worth figure (Home MK-NW-M-012, Insights MK-NW-M-005/047/048, Job safety MK-NW-M-013) are still bound by its decisions in step 1.b; what they are released from is needing a Net worth design. The five are now subtracted BY NAME rather than the derivation being dropped, so a new screen printing a Net worth figure is still noticed. | CHECKED 2026-10-20: the evening re-run on the row "Net worth — his seven steps: 17 of 17 pass" (1.a PASS); approvals DEC-0644 (Net worth v08), DEC-0645 (Add account by hand), DEC-0646 (Account detail = the Account portfolio screen), DEC-0650 (Bonds, Other investments, Holding detail), DEC-0651 (Itemize); report moneykeel_calc_report_networth-launch-readiness_v02.docx. The account page has since its own approved drawing (DEC-6457).</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5856,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>TO DO — 1.c is mechanical and goes first; then confirm the 113 in 1.b.</t>
+          <t>DONE 2026-10-01 — step 1.b closed and step 1.c passes (no untagged figure on the 7 screens)</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -5859,7 +5871,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>The existing ratchet guard on unidentified figures PASSES, which only means the count has not risen since 2026-09-14. It was never going to reach zero on its own.</t>
+          <t>The existing ratchet guard on unidentified figures PASSES, which only means the count has not risen since 2026-09-14. It was never going to reach zero on its own. | CHECKED 2026-10-20: the final run on the row "Net worth — his seven steps: 17 of 17 pass" (1.b: 162 decisions, each held by a named test, checked directly or carrying his words in its file; 1.c: PASS); src/__tests__/decisions_are_held.test.ts; report moneykeel_calc_report_networth-launch-readiness_v02.docx.</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5984,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>OPEN — found 2026-10-01 while proving Net worth step 1.b; no screen shows a wrong number because of it.</t>
+          <t>DECIDED 2026-10-20 — option A, his words: "A. This was a question you asked me without knowing why and where to use it. So, go with option A." The liquidity field is left out of this phase and is added when a screen needs it.</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -5985,7 +5997,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Option A: the account record gets no liquidity field in this phase; it is added when a screen needs one (for example "money you can reach within 30 days" on the emergency fund). No screen uses it and no number is wrong without it. DEC-0299's rule stands: class and liquidity are never one field. Decision row written 2026-10-20 to moneykeel_decisions_in_chat.json (governs DEC-0299); it takes its DEC id when the decision log is next built. DEC-0313 (liquidity tiers — Liquid / Sellable / Locked / Not spendable) needs this field, so it waits with DEC-0299; nothing is decided for DEC-0313 here.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="60" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
@@ -6096,7 +6112,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>IN PROGRESS — matched and locked by test: Account portfolio, Performance tab (4 phones), Net worth (8 states), Cash flow all four tabs (6 frames). NOT YET: the Income screens (income-end-to-end_v07, 17 phones: picker, base pay, bonus and stock, rent, interest and dividends, income manager, filing status, summary) and the two kept editors (Bill calendar v02, Monthly income v02).</t>
+          <t>DONE 2026-10-04 — every tab and screen named here is held to its drawing by a word-for-word test</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -6111,7 +6127,7 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2026-10-03: Performance tab matched to v17 phones 1, 3, 4, 5 by src/screens/__tests__/perf_matches_v17.test.tsx. 2026-10-03: Net worth matched to v08 in all eight states (networth_matches_v08.test.tsx). Cash flow This month REBUILT to cash-flow_v01 frames A and B (cashflow_matches_v01.test.tsx): it had been showing a hero, a pace line, a budget card, twelve bars and a will-it-last strip that the approved drawing does not have, and no Actual card at all. FOUND, NOT YET BUILT: the Expenses, Income and Debts tabs are still the 2026-07-19 design — the calculations behind the approved one exist in the doors, the screens do not draw them. 2026-10-03 later: Cash flow Expenses, Income and Debts tabs rebuilt to cash-flow_v01 frames C to F; every named difference is listed in cashflow_matches_v01.test.tsx.</t>
+          <t xml:space="preserve"> 2026-10-03: Performance tab matched to v17 phones 1, 3, 4, 5 by src/screens/__tests__/perf_matches_v17.test.tsx. 2026-10-03: Net worth matched to v08 in all eight states (networth_matches_v08.test.tsx). Cash flow This month REBUILT to cash-flow_v01 frames A and B (cashflow_matches_v01.test.tsx): it had been showing a hero, a pace line, a budget card, twelve bars and a will-it-last strip that the approved drawing does not have, and no Actual card at all. FOUND, NOT YET BUILT: the Expenses, Income and Debts tabs are still the 2026-07-19 design — the calculations behind the approved one exist in the doors, the screens do not draw them. 2026-10-03 later: Cash flow Expenses, Income and Debts tabs rebuilt to cash-flow_v01 frames C to F; every named difference is listed in cashflow_matches_v01.test.tsx. | CHECKED 2026-10-20: src/screens/__tests__/networth_matches_v08, perf_matches_v17, cashflow_matches_v01, income_matches_v07 (cf7e218a), income_manager_matches_v07, basepay_matches_v07, filing_matches_v07, kept_editors_match (b7f1d4ed). The account page, found not to match on 2026-10-11, is the row "Account page: redraw …" (rebuilt 2026-10-19, not committed).</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6388,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>OPEN — mine.</t>
+          <t>DONE 2026-10-11 — ruled by DEC-4529: "0y" is right; the years left are rounded to the nearest whole year</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -6385,7 +6401,11 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>CHECKED 2026-10-20: DEC-4529 (his "agree - leave the drawing, add line detailing correction … ok"): the Bonds v02 READ THIS FIRST line gives this exact bond, Chase 12-month CD matures Feb 1, 2027 = 123 days = 0.34 year → 0y; src/screens/BondsScreen.tsx rounds with Math.round.</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="60" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
@@ -6556,7 +6576,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>DONE except one limit: a balance typed back-dated (item 4).</t>
+          <t>DONE — item 4 closed 2026-10-20: a balance typed with an earlier Value-as-of date is booked on that date (DEC-6619)</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -6571,7 +6591,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04, on his instruction to fix them. (1) SHARES MOVED IN OR OUT: now counted as money in or out at what they were worth, when the record says which way they went and what they were worth. The sync now stores the direction (it was lost: "in" and "out" both became one type), the rebuilt history respects it, and the walk counts it. STILL REFUSED: share-transfer rows synced BEFORE today carry no direction, so a window containing one still shows no return — the direction cannot be recovered from what was stored. (2) HAND-ENTERED ACCOUNT WITH HOLDINGS: fixed — on rebuilt days between two days it was observed holding exactly the same shares and cash, it is given those shares at each day's close (fillBetweenObservations). Different on the two sides: nothing is filled. (3) THE DOLLAR WALK: fixed — cash or shares transferred in from outside, and an account that joined the record inside the window, count as money put in; the walk and the percent tell one story. (4) A BALANCE TYPED BACK-DATED: unchanged — the record assumes each day's value already holds that day's money. 2026-10-05 — item 1 finished: a share transfer synced before 2026-10-04 is given its direction on the next sync, from the activity the broker reports again; it is never imported twice (ingest.test.ts). Until that sync runs, a window holding such a row still shows no return. APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
+          <t>2026-10-04, on his instruction to fix them. (1) SHARES MOVED IN OR OUT: now counted as money in or out at what they were worth, when the record says which way they went and what they were worth. The sync now stores the direction (it was lost: "in" and "out" both became one type), the rebuilt history respects it, and the walk counts it. STILL REFUSED: share-transfer rows synced BEFORE today carry no direction, so a window containing one still shows no return — the direction cannot be recovered from what was stored. (2) HAND-ENTERED ACCOUNT WITH HOLDINGS: fixed — on rebuilt days between two days it was observed holding exactly the same shares and cash, it is given those shares at each day's close (fillBetweenObservations). Different on the two sides: nothing is filled. (3) THE DOLLAR WALK: fixed — cash or shares transferred in from outside, and an account that joined the record inside the window, count as money put in; the walk and the percent tell one story. (4) A BALANCE TYPED BACK-DATED: unchanged — the record assumes each day's value already holds that day's money. 2026-10-05 — item 1 finished: a share transfer synced before 2026-10-04 is given its direction on the next sync, from the activity the broker reports again; it is never imported twice (ingest.test.ts). Until that sync runs, a window holding such a row still shows no return. APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved." | 2026-10-20, ITEM 4 CLOSED (DEC-6619, the lead's decision under DEC-0013 and DEC-0230): a value typed with an earlier Value-as-of date now replaces the old value on each recorded day from that date to today that still holds it, and the daily totals move with it — $24,900 retyped Oct 20 as of Sep 30 reads September +$250, October $0. A new account with a past date is not written back (DEC-6620); the month records are not moved (DEC-6621). Test: MoneyKeel/functions/networth-and-performance/typed_value_on_its_date.test.ts 13 of 13 (2026-10-21).</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6736,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>DONE — except Q10, which waits on him: his two rulings disagree.</t>
+          <t>DONE — Q10 ruled by him 2026-10-20 (DEC-6614: “always the class broker sends.”) and built the same day</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -6731,7 +6751,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>The gate that printed "PFS pending: 2 files" is clear. check-questions-answered: every answer of his reaches the master, and none is still being asked.</t>
+          <t>The gate that printed "PFS pending: 2 files" is clear. check-questions-answered: every answer of his reaches the master, and none is still being asked. | 2026-10-20, Q10 CLOSED: put to him as the conflict between B7 (name first) and his Q10 answer (the broker's class first); his word: “always the class broker sends.” (DEC-6614). Built: classifyHoldingClass (holding-class.ts) asks the person's own class, then the class the broker sends, then the name. Test: Calculation Module code/engines/__tests__/holding-class.test.ts 13 of 13 (2026-10-21).</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6896,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>DONE for the name. OPEN: the by-hand form has one choice for 401(k) and IRA.</t>
+          <t>DONE 2026-10-20 — the name, and the one 401(k) / IRA choice: Held in now offers the one list of six (DEC-2441, DEC-2484h)</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -6891,7 +6911,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved."</t>
+          <t>APPROVED BY HIM, 2026-10-07: "all the code changes, findings and changes - for batch one and two - I approved." | 2026-10-20: the open half is closed — Add an account, the Bonds and Alternatives editors and Net worth's add sheet offer Held in as one list of six (Taxable, 401(k), Traditional IRA, Roth IRA, Roth 401(k), HSA); a Vanguard 401(k) typed by hand is named Vanguard 401(k) and compared with AOR. Tests: held_in_and_bond_forms.test.tsx 17 of 17, kept_editors_match.test.tsx 42 of 42 (2026-10-21).</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7360,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>WAITING ON HIM — to send to OpenAI</t>
+          <t>DONE 2026-10-09 — sent; OpenAI's audit came back the same day and was run against the app</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -7355,7 +7375,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>Batch 06's full 60-case JSON was never returned — only its fix brief; the brief's 23 tests are in. Tenets are draft v01, not yet approved by him.</t>
+          <t>Batch 06's full 60-case JSON was never returned — only its fix brief; the brief's 23 tests are in. Tenets are draft v01, not yet approved by him. | CHECKED 2026-10-20: brief commit 409f2a69 (tenets added 8f791996); audit run in e7da11ae (505 of 505 cases); the re-run brief v02 followed (f477e05b, 0cd68f22).</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7439,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>Not pushed. MK-NW-F-091 held: making an unknown gain 'unknown' blanks two states of the approved account page (v17 frame 2) for any hand-typed CD or bond.</t>
+          <t>Not pushed. MK-NW-F-091 held: making an unknown gain 'unknown' blanks two states of the approved account page (v17 frame 2) for any hand-typed CD or bond. | NOTE 2026-10-20: left open — the UNCLEAR outside cases still to decide are being classified now, one by one; the row closes when each is settled. Done so far: open points settled by DEC-3656, DEC-3657, DEC-3768b, DEC-3768c, DEC-3769, DEC-3837, DEC-4036b–k, DEC-4059b–d, DEC-4082, DEC-4105; re-run parts 1–4 (51a1fa67, 0f7adefa, 0e12a591); 10 cases classified in 7268efb4.</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7507,7 @@
         </is>
       </c>
     </row>
-    <row r="234" ht="45" customHeight="1">
+    <row r="234" ht="60" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
           <t>Account page: redraw Performance v17 frame 2 so its figures add up, then rebuild the page to it</t>
@@ -7500,7 +7520,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>OPEN — next Net worth task</t>
+          <t>DONE 2026-10-19 — drawing v01 approved (DEC-6457) and the page rebuilt to it in all five states, word for word: A 124 of 124 lines, B 65 of 65, C 83 of 83, D 89 of 89, E 71 of 71; not committed</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -7513,7 +7533,11 @@
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr"/>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Drawing: MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_account-page_v01.html. Held by src/screens/__tests__/account_page_drawing_states.test.tsx; audit MoneyKeel/documents/audit/moneykeel_audit_mock-match_account-page_2026-10-19_v01.md. Found on the way: the old match test read v17 phone 3 (the Performance tab), so the page carried the Performance tab's sections; the day-one lines never showed once Home wrote today's record; an account with no balance entered read −100.00%.</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="60" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
@@ -7803,8 +7827,424 @@
         </is>
       </c>
     </row>
+    <row r="244" ht="60" customHeight="1">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Net worth launch check, 2026-10-20 — six gaps fixed: one total function (DEC-0343), inputs built once (DEC-0345), the gap cards' ring (v08), MK-NW-M-015's label, the odds under MK-XS-M-002, a CD's rate on the add sheet</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>(1) DEC-0343: the section and institution totals are MK-NW-F-039 buildAssetsState over their accounts. (2) DEC-0345: the Net worth family's inputs are built once (MK-NW-F-145 netWorthInputs) and seven screens read them. (3) The fix sheet's gap cards carry v08's 1-point ring. (4) MK-NW-M-015 describes the sentence the card prints, and the records naming its old label are corrected. (5) The odds print under MK-XS-M-002 on Net worth, the Plan tab and Home. (6) A CD added on Net worth's sheet is asked its rate (DEC-6626).</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-20 — built and tested; not committed</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/nw_totals_one_function.test.tsx · src/screens/__tests__/networth_family_inputs.test.tsx · src/__tests__/guard_one_door_networth_inputs.test.ts · src/screens/__tests__/networth_matches_v08.test.tsx · src/screens/__tests__/networth_sheet_cd_rate_and_value_date.test.tsx · src/hooks/useNetWorthInputs.ts · src/screens/NetWorthScreen.tsx · src/components/DataGapsBanner.tsx</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>Added 2026-10-21 by the records job: the lead asked for the rows of these six to be closed, and none existed, so the work is recorded as one row, already done. Tests 2026-10-21: nw_totals_one_function 4 of 4, networth_family_inputs 8 of 8, guard_one_door_networth_inputs 3 of 3, networth_matches_v08 11 of 11, networth_sheet_cd_rate_and_value_date 7 of 7. DEC-0343 and DEC-0345 recorded TESTED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="60" customHeight="1">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>His ruling of 2026-10-20 — a linked or imported holding takes the class the broker sends first (DEC-6614, settles Q10 / DEC-2159 against brief B7)</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>classifyHoldingClass (holding-class.ts) asks the person's own class, then the class the broker sends (its cash-equivalent flag, else its type: SnapTrade's security type code or an import file's type column), then the name and the other automatic rules; the sync and the importer keep the broker's class on the saved holding (MK-XS-I-070); the class standard §2 and a Net worth v08 line say so; DEC-2159 answered; B7 narrowed.</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — built and tested; not committed</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/engines/holding-class.ts · Calculation Module code/engines/__tests__/holding-class.test.ts · src/services/sync/dec2159_broker_class.test.ts · src/screens/__tests__/dec2159_import_broker_type.test.tsx · MoneyKeel/documents/standards/moneykeel_calc_spec_how-an-account-is-classed-and-counted_v01.md</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>Worked example (Net worth v08 line, 2026-10-21): VMFXX $50,000 flagged cash-equivalent — Cash $10,000 becomes $60,000, the emergency fund 1.7 months becomes 10.0 months, what you own $160,000 either way. run 2026-10-21, all passing: holding-class.test.ts 13 of 13 · dec2159_import_broker_type.test.tsx 1 of 1 · dec2159_broker_class.test.ts 9 of 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="60" customHeight="1">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Sync: a reversed deposit and income with no amount (Performance re-run part 4)</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>(1) A broker's minus on a deposit kept as its direction (DEC-6672, DEC-6673). (2) Interest, a dividend or a coupon with no amount is unknown; the return refuses across its day (DEC-6674); a real $0 saved as 0 (DEC-6675).</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — built and tested; not committed</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/reversal_and_missing_amount.test.ts · src/screens/__tests__/reversal_and_missing_amount_screens.test.tsx · src/services/sync/ingest.ts · Calculation Module code/engines/ledger.ts · Calculation Module code/engines/time-weighted-return.ts</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: 17 of 17 and 6 of 6 pass. Drawings: account page v01 rows 53 and 54, Performance v17 line. Open follow-ups (code jobs): a dividend reversal or fee refund still loses its sign at sync; records saved before 2026-10-21 have no direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="60" customHeight="1">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>A holding worth $0 today dropped out of the worked-back figures (12 readers)</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Every reader keeps a holding's starting value at the window's start (DEC-6676..DEC-6681, under DEC-5068).</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — 12 of 12 readers fixed; built and tested; not committed</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/holding_worth_zero_counts.test.tsx · MoneyKeel/functions/networth-and-performance/performance.ts · src/domain/performance/index.ts</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: holding_worth_zero_counts.test.tsx 6 of 6. A $1,000 → $0, B $1,000 → $1,200: −40.00%, −$800; market +6.00%. No drawn figure moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="60" customHeight="1">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Holding page gains: five defects + spoken labels</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Undated purchase in neither part (DEC-6687); tax-advantaged accounts show Gain whole (DEC-6688); index options 60/40 (DEC-6689); no-price large figure = Total paid (DEC-6690); import keeps a missing date blank (DEC-6691); "not on record" (DEC-6692); spoken percents to two decimals (DEC-0264).</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — built and tested; not committed</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/holding_gains_if_sold_today.test.tsx · MoneyKeel/documents/networth-and-performance/moneykeel_pres_mock_holding-detail_v02.html</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: holding_gains_if_sold_today.test.tsx 17 of 17. Open (drawing wins): MK-NW-M-061#8 option purchase line reads "2 sh @" — to tell him.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="60" customHeight="1">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Performance outside re-run, part 1 (OpenAI) — 125 cases assessed</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Assess every case: agree, app wrong, reviewer wrong, ruling needed, blocked.</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — 125 of 125 assessed: 60 agree, 28 app wrong, 27 reviewer wrong, 7 need a ruling, 3 blocked; 30 were in flight (ZERO 12, ACCOUNT 11, GAINS 5, SYNC 2)</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/results/performance_openai_rerun_01_results.json</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>Still open, each its own job: the Net worth fix batch (D MK-NW-F-103, E and F MK-NW-O-008, H MK-NW-M-024); the Performance queue (MK-PF-F-040, MK-PF-M-003/015, -017, -020, head-of-household brackets); 7 rulings for the lead (MK-NW-F-084, MK-CF-M-051, MK-MN-M-003, MK-NW-M-029, MK-NW-M-035, MK-PF-M-001, MK-PF-M-016); disagreements #36-#38 and #43. | 2026-10-21 NWFIX CLOSED: MK-NW-F-103 (a blank balance is not a recorded day), MK-NW-O-008 ×2 (a record after today read on today, DEC-6824; a new account's first day), MK-NW-F-084 (Alternatives row, DEC-6825), MK-NW-M-029 (LAST CLOSE, DEC-6826), MK-NW-M-035 (a sale's fee, DEC-6827), the amber box (DEC-6828). MK-NW-M-024 kept: his DEC-2748c (face × rate; with no face, value × rate) stands, so test #18 is REVIEWER WRONG. Test: nwfix_performance_rerun_01.test.ts 16 of 17 (one amber-box test red while another agent edits the unpriced row).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="60" customHeight="1">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Dividend/fee sign class: a reversed dividend or a refunded fee lost its sign at sync (13 readers)</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Sync keeps the direction for all seven kinds (DEC-6796); one-time full re-fetch (DEC-6797); walk shows a net reversal as a minus (DEC-6798); outside case BRIEF WRONG (DEC-6799); isMoneyOut (DEC-6800); inverseOf (DEC-6801).</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — readers 13 of 13, kinds 7 of 7, re-fetch built; not committed</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/dividend_fee_signs.test.ts · src/screens/__tests__/dividend_fee_signs_screens.test.tsx · src/services/sync/signs_refetch.orch.test.ts · src/__tests__/guard_one_reader_for_stored_amounts.test.ts</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: 8 of 8, 4 of 4, 2 of 2, 2 of 2 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="60" customHeight="1">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Net worth figures from the Performance re-run part 1 screen checks (ACCOUNT, 8 fixes + the walk date)</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>DEC-6759 gap is cash · DEC-6760/DEC-6761 debt payment not entered · DEC-6765 Job safety · DEC-6764 CD asked · DEC-6763 Unclassified · DEC-6767 one date per window · DEC-6762 Home note · DEC-6766 concentration.</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — 8 of 8 fixed and the walk date; not committed</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/networth_rerun01_fixes.test.tsx · src/screens/__tests__/outside_performance_rerun_openai_01_screens.test.tsx · MoneyKeel/functions/networth-and-performance/outside_performance_rerun_openai_01_rules.test.ts</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: networth_rerun01_fixes.test.tsx 29 of 29. Home and Job safety have no recorded drawing — to tell him.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="60" customHeight="1">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>A stored $0 price paid read one way in every reader (cost 14 of 15, dates 7 of 7)</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>DEC-6768 tax gain share · DEC-6769 account balance · DEC-6770 sync cost · DEC-6771 window return · DEC-6772 daily record · DEC-6773 oldest-first sale.</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — 14 of 15 cost readers (the 15th with ACCOUNT), 7 of 7 date readers; not committed</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/paid_read_one_way_agreement.test.tsx</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: 11 of 11 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="45" customHeight="1">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Trade fee at sync: the broker's fee kept on record; realized gain takes it once; older trades fixed at next sync</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>DEC-6873 stored · DEC-6874 before or after · DEC-6875 purchase fee · DEC-6876 older trades.</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — built and tested; not committed</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/trade_fee_at_sync.test.tsx</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: 8 of 8. Drawing to make: the trade sheet's fee box — to tell him.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="45" customHeight="1">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Undo of a transfer moved the money twice (MK-CF-F-116 inverseOf)</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>DEC-6993: a transfer undo swaps accounts and keeps direction; others flip.</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — built and tested; not committed</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>src/domain/transactions/undo_round_trip.test.ts</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: 35 of 35; 17 kinds round-trip to the cent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="45" customHeight="1">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Class split scaled a bond twice and an option not at all (MK-NW-F-027)</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>A bond per $100 scaled once; an option price × 100. $195.08 → $9,900; $76.92 → $1,600.</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — fixed and tested; not committed</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/networth_rerun01_fixes.test.tsx (section 14)</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: 34 of 34. A fix under existing rulings, no new decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="30" customHeight="1">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Build check B7 read only the first 400 lines of a function</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Fingerprint each whole function; stop if a function is not closed.</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — built; not committed</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/build-outside-test-cards.py (body_of)</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>thePerformance (MK-NW-O-008) is now read whole.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F243"/>
+  <autoFilter ref="A1:F256"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
+++ b/MoneyKeel/documents/other/moneykeel_calc_plan_workplan_v01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Workplan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$256</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Workplan'!$A$1:$F$285</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F256"/>
+  <dimension ref="A1:F285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Claude: re-verify B07–B25 against the screen; Founder: decide B01 and B06</t>
+          <t>Claude: re-verify B07–B25 against the screen; B06 settled (DEC-1669); B01 stands</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1144,7 +1144,11 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 B06 SETTLED: "three return methods, one label" is settled by his DEC-1669 (2026-10-04, every return time-weighted), held by guard_every_return_is_time_weighted.test.ts; it is not his to decide again.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -1484,7 +1488,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 ANSWERED: Q34 (DEC-7170) and Q35 (DEC-7171) on 2026-10-21, Q36 by DEC-6618 (2026-10-20) — each the lead's decision under his rulings, printed in YOUR ANSWER; Q37 and Q38 were answered before. Still open on the master: Q39–Q45 and Q50.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -3970,7 +3978,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Performance was rebuilt in front of its door on 2026-09-25 (Q-PF-1 is still PROPOSED), so it will move again later — a recorded debt, not a surprise.</t>
+          <t>Performance was rebuilt in front of its door on 2026-09-25 (Q-PF-1 is still PROPOSED), so it will move again later — a recorded debt, not a surprise. | 2026-10-22 Q-PF-1: ruled "yes" on 2026-09-27 and built — the Performance tab, each account and Home ask MK-NW-O-008 thePerformance; TESTED in the rulings ledger (guard_one_door_performance.test.ts, 3 of 3). The Performance half of this debt is paid.</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4326,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Every other band in the app passes no door and is untouched.</t>
+          <t>Every other band in the app passes no door and is untouched. | 2026-10-22: the door is drawn on Performance v17 (approved in full, DEC-0647: "Tap ▾ to collapse · tap the name to open this account's portfolio ›") and opens the account page built to its drawing v01 (DEC-6457); the v14 test that holds it stays.</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5719,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>The big number underneath is the VERIFIED marks: 48 Net worth rows, 53 Cash flow, 12 Performance are TESTED but not VERIFIED. A test proves a figure is what the code gives; it can never prove it is the figure he wanted, which is why his ladder has that rung and why launch-ready cannot be claimed without it.</t>
+          <t>The big number underneath is the VERIFIED marks: 48 Net worth rows, 53 Cash flow, 12 Performance are TESTED but not VERIFIED. A test proves a figure is what the code gives; it can never prove it is the figure he wanted, which is why his ladder has that rung and why launch-ready cannot be claimed without it. | 2026-10-22 NOW: 11 things — 4 Net worth, 6 Cash flow, 1 Performance (VERIFY 26 rows; it was 5 on 2026-10-21: his four old questions DEC-0479, DEC-0483, DEC-0497 and DEC-0510 are answered on their rows). The 61 / "10 Performance" above is the count of 2026-09-29.</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5731,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>His instruction, 2026-09-29: ‘before next build let’s review and correct all underlying calculations for NW, CF and Performance modules.’ NOT STARTED. What it means concretely: walk every figure on those three modules against its formula, its inputs and its worked example, and correct what disagrees — the file-and-code rule, both or neither. 93 Net worth decisions, 52 Cash flow, 39 Performance are in the log; 123 of those have no test. This is mine, not his — his half is the answer list above.</t>
+          <t>His instruction, 2026-09-29: ‘before next build let’s review and correct all underlying calculations for NW, CF and Performance modules.’ STARTED 2026-10-20: Net worth done (committed 4698075c); Performance done on 2026-10-21 but for the items on the PF-A and PF-B rows; Cash flow next. What it means concretely: walk every figure on those three modules against its formula, its inputs and its worked example, and correct what disagrees — the file-and-code rule, both or neither. 93 Net worth decisions, 52 Cash flow, 39 Performance are in the log; 123 of those have no test. This is mine, not his — his half is the answer list above.</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
@@ -5743,7 +5751,7 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Gates the next build. No build is cut without his explicit ‘cut the build’ to a presented checklist.</t>
+          <t>Gates the next build. No build is cut without his explicit ‘cut the build’ to a presented checklist. | 2026-10-22 PERFORMANCE: every figure walked against the outside re-run (OpenAI parts 1 to 4 and tax, 1,180 tests) and fixed by PF-A and PF-B on 2026-10-21; what is left is on their rows.</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7575,7 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>Briefs v02 in to-send/moneykeel_brief_performance_0N_claude-code_v02.md. 2026-10-12: 35 outside cases settled or removed (1 + 3 + 25 removed + 5 re-pointed + 1 + 1 + 1 brief wrong); results files carry a 'settled' line on each. Not committed.</t>
+          <t>Briefs v02 in to-send/moneykeel_brief_performance_0N_claude-code_v02.md. 2026-10-12: 35 outside cases settled or removed (1 + 3 + 25 removed + 5 re-pointed + 1 + 1 + 1 brief wrong); results files carry a 'settled' line on each. Not committed. | 2026-10-22 STATE: 32 of 225 cases still carry no settled line (file 01: 11, 02: 7, 03: 10, 04: 4); the OpenAI re-run of 2026-10-21 covered the same functions and PF-A and PF-B fixed most of them. Five cases marked BRIEF WRONG and one superseded on 2026-10-22. Marking the 32 one by one is the next records job.</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8023,7 @@
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>Still open, each its own job: the Net worth fix batch (D MK-NW-F-103, E and F MK-NW-O-008, H MK-NW-M-024); the Performance queue (MK-PF-F-040, MK-PF-M-003/015, -017, -020, head-of-household brackets); 7 rulings for the lead (MK-NW-F-084, MK-CF-M-051, MK-MN-M-003, MK-NW-M-029, MK-NW-M-035, MK-PF-M-001, MK-PF-M-016); disagreements #36-#38 and #43. | 2026-10-21 NWFIX CLOSED: MK-NW-F-103 (a blank balance is not a recorded day), MK-NW-O-008 ×2 (a record after today read on today, DEC-6824; a new account's first day), MK-NW-F-084 (Alternatives row, DEC-6825), MK-NW-M-029 (LAST CLOSE, DEC-6826), MK-NW-M-035 (a sale's fee, DEC-6827), the amber box (DEC-6828). MK-NW-M-024 kept: his DEC-2748c (face × rate; with no face, value × rate) stands, so test #18 is REVIEWER WRONG. Test: nwfix_performance_rerun_01.test.ts 16 of 17 (one amber-box test red while another agent edits the unpriced row).</t>
+          <t>Still open, each its own job: the Net worth fix batch (D MK-NW-F-103, E and F MK-NW-O-008, H MK-NW-M-024); the Performance queue (MK-PF-F-040, MK-PF-M-003/015, -017, -020, head-of-household brackets); 7 rulings for the lead (MK-NW-F-084, MK-CF-M-051, MK-MN-M-003, MK-NW-M-029, MK-NW-M-035, MK-PF-M-001, MK-PF-M-016); disagreements #36-#38 and #43. | 2026-10-21 NWFIX CLOSED: MK-NW-F-103 (a blank balance is not a recorded day), MK-NW-O-008 ×2 (a record after today read on today, DEC-6824; a new account's first day), MK-NW-F-084 (Alternatives row, DEC-6825), MK-NW-M-029 (LAST CLOSE, DEC-6826), MK-NW-M-035 (a sale's fee, DEC-6827), the amber box (DEC-6828). MK-NW-M-024 kept: his DEC-2748c (face × rate; with no face, value × rate) stands, so test #18 is REVIEWER WRONG. Test: nwfix_performance_rerun_01.test.ts 16 of 17 (one amber-box test red while another agent edits the unpriced row). | 2026-10-22 PF CLOSED (marked in the results file): PF-A and PF-B fixed or decided #26, #29, #31, #33, #35, #41, #42, #43, #46 and the F-084 / F-128 cases; #36–#38 reviewer wrong (DEC-7220); #15 decided by DEC-6760; #6 and #52 settled (not launch items). Left: #3, #7 (MK-NW-F-091/127, second wave), #11, #14, #50 (Cash flow and Menu rounds); screens MK-PF-M-006 T1 (second wave), the Holding page wording (W-HOLDING), six Cash flow / Home checks, and MK-NW-M-024 T3, -026 T1, -028 T1 still in flight. | 2026-10-22 SECOND WAVE (marked in the results files): #3, #7 and rule 17 fixed (DEC-7323); screens MK-PF-M-006 T1 fixed (DEC-7324); MK-NW-M-030 T3, -031 T3, -034 T3, -061 T8 and F3 fixed (W-HOLDING). Left: #11, #14, #50 (Cash flow and Menu rounds), six Cash flow / Home screen checks, MK-NW-M-024 T3, -026 T1, -028 T1 still in flight.</t>
         </is>
       </c>
     </row>
@@ -8243,8 +8251,936 @@
         </is>
       </c>
     </row>
+    <row r="257" ht="60" customHeight="1">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Performance re-run: returns and windows (PF-A) — 9 app-wrong items and 7 rulings</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>Fix every open returns-and-windows item of the outside re-run. Decisions DEC-7216 (undated purchase), DEC-7217 (one yearly rate), DEC-7218 (value below $0), DEC-7219 (a close dated after today), DEC-7220 (Look back words), DEC-7221 (start from the shares held then).</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — 9 of 9 app-wrong fixed, plus 1 found; 7 of 7 rulings decided; not committed</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/returns_and_windows_agree.test.tsx · src/domain/performance/index.ts · Calculation Module code/engines/time-weighted-return.ts</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: returns_and_windows_agree.test.tsx 10 of 10; every outside file passes (1,180 tests, 4 skipped as BLOCKED). Left to the second wave: MK-NW-F-091 / MK-NW-F-127, a holding with shares added inside the window works its gain back as $420 where $320 is right (needs a start-shares field per row). | 2026-10-22 LEFT ITEM FIXED: MK-NW-F-091 / MK-NW-F-127 by W-START (DEC-7323): $420 → $320.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="60" customHeight="1">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Performance re-run: holdings, the market comparison, rows and labels (PF-B) — 17 of 22 app-wrong, 15 of 15 rulings</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Fix every open item of the re-run not about returns and windows. Decisions DEC-7222 (Home names the change's base), DEC-7223 (own dates), DEC-7224 (no yardstick → no market), DEC-7225 (sale after today), DEC-7226 (largest holding), DEC-7227 (a kind with no yardstick), DEC-7228 (two closes one day); Look back words with DEC-7220.</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — 17 of 22 app-wrong fixed, 15 of 15 rulings decided; not committed</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/pfb_cross_screen_agreement_2026_10_21.test.tsx · src/domain/performance/index.ts · src/screens/HomeScreen.tsx · MoneyKeel/functions/_figure-spec.ts (walkShown)</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: pfb_cross_screen_agreement_2026_10_21.test.tsx 10 of 10; the full suite 310 + 176 suites green at PF-B's end. Left (W-HOLDING): Holding page wording MK-NW-M-030, -031, -034, -061 and the "0 months" line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="60" customHeight="1">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Performance outside re-run, part 2 (OpenAI) — 87 items assessed</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Assess every case, formula check and still-open line; fix or decide each.</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — 87 of 87 assessed (59 agree, 19 app wrong, 4 reviewer wrong, 5 rulings, 8 in flight); every app-wrong item fixed and every ruling decided by PF-A and PF-B; marked 2026-10-22</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/results/performance_openai_rerun_02_results.json · MoneyKeel/functions/networth-and-performance/outside_performance_rerun_openai_02.test.ts</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: outside_performance_rerun_openai_02.test.ts 92 pass. Nothing left open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="60" customHeight="1">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Performance outside re-run, part 3 (OpenAI) — 87 items assessed</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Assess every case, formula check and still-open line; fix or decide each.</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — 87 of 87 assessed (56 agree, 14 app wrong, 6 reviewer wrong, 11 rulings); every app-wrong item fixed and every ruling decided by PF-A and PF-B; marked 2026-10-22</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/results/performance_openai_rerun_03_results.json · MoneyKeel/functions/networth-and-performance/outside_performance_rerun_openai_03.test.ts</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: outside_performance_rerun_openai_03.test.ts 94 pass. Nothing left open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="60" customHeight="1">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Performance outside re-run, part 4 (OpenAI) — 80 items assessed</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Assess every case, formula check and still-open line; fix or decide each.</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — 80 of 80 assessed; every app-wrong item fixed and every ruling decided by PF-A (and SYNC for MK-ST-F-082); marked 2026-10-22</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/results/performance_openai_rerun_04_results.json · MoneyKeel/functions/networth-and-performance/outside_performance_rerun_openai_04.test.ts</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-21: outside_performance_rerun_openai_04.test.ts 89 pass. Nothing left open. The file's own CHECKS table keeps the first verdict beside its FIXED / DECIDED reason, by design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="60" customHeight="1">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Performance outside re-run, tax sources and acceptance (OpenAI) — 29 items assessed</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Assess every item; fix or decide each.</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 for Performance — 29 of 29 assessed; the three Performance items fixed (2Y over a leap year, a 100% loss kept, Home's gap from one function); the blocked item settled 2026-10-22</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/documents/audit/outside-test-cases/returned/results/performance_openai_rerun_tax_results.json · MoneyKeel/functions/networth-and-performance/outside_performance_rerun_openai_tax.test.ts</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Left, with the Cash flow round: 2026 head-of-household brackets (24% and 32% tops), the senior deduction for a married couple both 65+ (cut once, not per person), and the register citing §2.15 where Rev. Proc. 2025-32 §4.14 is right — that last one needs the register line and its test.failing case changed together. | 2026-10-22 PF-TOOLS: the §2.15 citation is FIXED, read from the IRS text of Rev. Proc. 2025-32 (§4.14 Standard Deduction: $32,200 · $24,150 · $16,100 · $16,100; (3) aged or blind $1,650 / $2,050): register STANDARD_DEDUCTION §4.14 and TAX_TABLES §§4.01, 4.14; the master's Reference rows (§3.18 → §4.14; capital gains §3.03 → §4.03) and deductionFor's line in moneykeel_code_formula.py (§3.18 → §4.14). The test.failing case is now a passing test, the old citation pinned as test.failing. src/domain/income/tax.ts line 253 reprints at the next write-headers.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="60" customHeight="1">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>extract-decisions.py uses up about 22 decision numbers each run before merging them away</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>Merge reworded rows BEFORE a number is issued, so a merged row never takes one.</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/extract-decisions.py (add, merge_reworded)</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Found by NWQ, measured 2026-10-21: the run that recorded PF-A and PF-B issued DEC-7195 to DEC-7215 to rows it then merged into older ones (DEC-7195 → DEC-0125 and 21 more), so the 14 new decisions took DEC-7216 to DEC-7229. A number is never reused, so none is wrong — they are lost, and the highest number overstates the log (762 rows, highest 7230).</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="60" customHeight="1">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>The master file reads its own text back as his in ROW VERIFIED</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>moneykeel_keep.read: skip a ROW VERIFIED value that begins with the builder's own text (TESTED, NOT VERIFIED / RULED? NOT YET).</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 38 of 38 of his entries kept word for word; 201 of the build's own (179 ROW VERIFIED, 22 printed answers) no longer read back as his; not committed</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/moneykeel_keep.py · build-moneykeel-master.py (BUILDER_TEXT_IN_HIS_COLUMN)</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-21 by PF-RECORDS: the builder's line is carried forward as if he typed it, so its date goes stale — MK-NW-M-002, MK-NW-M-047, MK-PF-M-016 and MK-PF-M-017 say "you ruled on this row" on a date their Row status contradicts, and MK-PF-M-008 and MK-XS-M-004 still carry "RULED? NOT YET — read this row and say yes", a question in a file he opens, after they were ruled. Overriding that cell stops the build (his words changed), so the fix is the reader. | 2026-10-22 PF-TOOLS: moneykeel_keep.split takes the build's own sentence out of ROW VERIFIED and its printed answers out of YOUR ANSWER before anything is read back as his; 8 self-checks on made-up cells run at the start of every build and stop it (6 of them fail under the old reader). The build also stops if it writes a sentence in his columns the reader would not recognise (195 seen). A ruled date now also comes from a Row status override. Result: MK-PF-M-008 and MK-XS-M-004 read 'you ruled on this row 2026-09-30'; MK-NW-M-002, MK-NW-M-047, MK-PF-M-016, MK-PF-M-017 read 2026-10-04, as their Row status does; Q10, Q51, Q52 and Q53 print the decision log's answer. The same defect was in YOUR ANSWER, so both columns are fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="60" customHeight="1">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Master placeholder rows say "screen not yet read" for screens whose figures are declared</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>build-moneykeel-master.py: a route with declared figures prints READ and names them, not NOT STARTED.</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 60 of 60 screen lines derived from the declarations; 0 NOT STARTED; not committed</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/build-moneykeel-master.py (the NOT STARTED placeholder) · moneykeel_figures.json</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Performance audit item 13: on the performance tab /account-detail (21 figures declared), /bonds (11), /holding-detail (12), /itemize (3) and /look-back (3) read NOT STARTED; /add-account is right (no figure). The same rows repeat on the home, networth, plan and cashflow tabs. A row with no Metric ID cannot take an override, so the fix is in the builder. | 2026-10-22 PF-TOOLS: each line is built by column name from the declarations: 40 READ, naming each figure by ID and the tab it is printed on (/account-detail 25, /holding-detail 17, /bonds 11, /look-back 5, /itemize 3 …), 16 READ with no figure, 4 the same screen as /invest. The status had been landing in his 'Your name for it' column, two columns early; it is now in Row status and his column is empty on those lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="60" customHeight="1">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>The $0 empty-state refusal of Q48 still prints over declared figures' own refusals</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>Retire the 2026-09-09 Q48 overrides on rows whose declaration now carries its own refusal; keep Q48 where the screen shows $0 and the door.</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>TO DO</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/moneykeel_overrides.json (58 entries, "What it says when it cannot be computed")</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-21 by PF-RECORDS. Corrected for Performance's two percents, MK-PF-M-006 and MK-PF-M-008 (a percent cannot read $0). MK-PF-M-005 and MK-PF-M-007 to check against v17's first-day phone; the other 54 rows are Net worth, Cash flow, Menu, Plan and cross-screen figures, each checked with its module. | 2026-10-22 PF-TOOLS: Performance's part DONE — 4 of 4. MK-PF-M-005 and MK-PF-M-007's Q48 overrides retired; their master rows now print the declaration's own refusal, read against PerformanceScreen.tsx (005's was wrong, 'One account only…', and is rewritten as built: no account line while nothing is entered; 007's stands: no table when nothing was received). MK-PF-M-006 and MK-PF-M-008 were done 2026-10-21. Left for their own rounds, 54 rows: Net worth 18, Cash flow 15, Menu 12, Plan 5, cross-screen 4 — 37 of them declared with a refusal of their own, 16 on hand-typed rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="60" customHeight="1">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Every declared figure's Period column reads "as of today", window figures included</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Give a declaration its window (a period field), and print it in the master's Period column.</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 for Performance — 26 window figures name the window, 6 more carry their own period; Cash flow's this month waits; not committed</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/_figure-spec.ts · build-moneykeel-master.py (declared_row)</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Found 2026-10-21 by PF-RECORDS: on the performance tab every row reads "as of today", though Return, Wealth generated, the walk and the market figure are over the window picked. MK-PF-M-008's period is written by override (the 1M window) until the declaration carries it. | 2026-10-22 PF-TOOLS: moneykeel_period.py derives the Period from the declaration: its own period field first (none carry one yet), a month or a year (50), over a window when its words say window or the same dates (25 — each screen's choices read from its code: Performance Since · 1M · This year · 1Y · 2Y, Home 1M fixed, Look back 12 months ago · 2 years ago · 3 years ago, Holding page 1M to 2Y), else as of today (104). Bill calendar lists no window choices the build can read; its one row says so. Left: figures over a span that never say window (Cash flow's this month, since purchase, trailing twelve months, since the previous close) still read as of today — a period field on those declarations is the way. | 2026-10-22 PF-TOOLS, Performance's span figures: a period field on the declaration (_figure-spec.ts) now prints on the Period row — MK-NW-M-034 the trailing twelve months, MK-NW-M-035 every sale on record, MK-NW-M-059 and -067 since purchase, MK-NW-M-060 and -068 since the previous close (holding.ts); MK-PF-M-003, the walk's title, declares 'the window picked' and lists Performance's choices (performance.ts). Build: over a window 26 · own period 6 · a month or a year 50 · as of today 97.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="60" customHeight="1">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Records gaps from the Performance audit of 2026-10-21 (PF-RECORDS)</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Record PF-A, PF-B and NWQ; answer his four old questions on their rows; take MK-PF-M-008 out of DRAFT; mark the outside results; fix the design record and the stale plan rows.</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 14 decisions recorded, 32 Changelog rows, 186 results marks, 4 anchors re-mapped by reading; not committed</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/moneykeel_decisions_in_chat.json · moneykeel_decisions_anchors.json · moneykeel_overrides.json · moneykeel_rulings.json · docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx (Changelog) · MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Left for code (the lead): MK-PF-M-008's declaration in performance.ts needs ruled 2026-09-30 and the formula and refusal as built (the master carries them by override until then); the route comment in app/account-detail.tsx still says Performance v17 frame 2 (DEC-0646) — since DEC-6457 it is the account-page drawing v01. | 2026-10-22 UPDATE: the route comment in app/account-detail.tsx was fixed by W-SHEETS (gap 47). Q33's answer could not reach MK-PF-M-008's answer cell — his kept answer to Q51 was written back over it — so build-moneykeel-master.py now adds a decision-log answer under his kept text, his words unchanged at the top; check-questions-answered.py passes. | 2026-10-22 PASS 4: MK-PF-M-008's declaration now carries ruled 2026-09-30 (W-A11Y) and its Row status override is retired (PF-TOOLS); its other overrides go at the final pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="60" customHeight="1">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Holding page: the comparison band, units, the dividends line, a short history, the LAST CLOSE day, 2Y words, five IDs (W-HOLDING)</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Performance audit gaps 4, 5, 6, 9 and 10 for the Holding page, 34, the date check and PF-B's five Holding-page leftovers. Decisions DEC-7297 to DEC-7303.</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — finished 2026-10-22: 6 of 6 gaps, 5 of 5 leftovers, 9 of 9 rulings; not committed</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/holding_page_comparison_and_unknowns_2026_10_21.test.tsx · src/__tests__/last_close_day_on_persons_calendar.test.ts · MoneyKeel/functions/networth-and-performance/holding.ts · src/screens/HoldingDetailScreen.tsx</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-22 by W-HOLDING: 18 of 18 and 5 of 5; the outside screens file 455 of 455. Sent back, being fixed: MK-PF-M-023 and MK-NW-M-069 are one concept with two IDs; heldOnDay called from the account page (guard D1). | 2026-10-22 SENT BACK CLOSED: MK-NW-M-069 retired into MK-PF-M-023 (DEC-7369); heldOnDay had already moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="60" customHeight="1">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Performance: spoken words, every percent by ID, the screens agreeing (W-A11Y) — audit rows 9 and 28 to 33</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>Tag the untagged percents, give the graph and every figure a spoken form, fix a and an, set the accessibility counts true, pin the same figure across screens. Decisions DEC-7304 to DEC-7311.</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — finished 2026-10-22: 7 of 7 gaps, 8 of 8 calls; not committed</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/performance_spoken_and_agree_2026_10_21.test.tsx · src/domain/_shared/article.test.ts · src/__tests__/guard_figures_declared.test.ts · src/__tests__/a11y-baseline.json</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-22 09:15: 34 of 34 and 26 of 26. Sent back, being fixed: the account page and Holding page say "%/year" aloud; Home's left-out sentence shows dollars under hidden balances; the metric register collision; account_detail_journey. | 2026-10-22 SENT BACK CLOSED: the spoken "%/year" on the account page and Holding page; Home's left-out sentence under hidden balances; the register collision (each ID once); account_detail_journey passes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="60" customHeight="1">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Account page doors and the five sheets drawn from the code (W-SHEETS) — audit gaps 7, 8, 24 to 27 and 47</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>Open the trade sheet from the account page, remove the six sheets with no door, draw the five sheets from the code, hold the Holding page buttons and state F's look, test Look back empty, fix the route comment. Decisions DEC-7312 to DEC-7322.</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-21 — finished 2026-10-22: 7 of 7 gaps, 5 of 5 sheets drawn (35 states), 11 of 11 decisions; not committed</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/sheet_doors_2026_10_21.test.tsx · src/screens/__tests__/sheets_drawn_from_code.test.tsx · MoneyKeel/documents/standards/moneykeel_pres_spec_design-each-screen-was-built-from_v01.md</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-22: sheet_doors 10 of 10; sheets_drawn_from_code 42 of 42 at 08:59 — three drawings and the Update value sheet are being redrawn as v02 since 09:13. The five drawings wait for his approval. Sent back, being fixed: the date guard does not read a record's date; a 529 against DEC-2484g; Look back's empty sentence; Record a transaction against the canon word activity; "Net Worth" with a capital W; the edit sheet's save button fades to 50%. | 2026-10-22 SENT BACK CLOSED: all seven, by the W-SHEETS follow-ups row (DEC-7377, DEC-7379, DEC-7380, DEC-7381, DEC-7382; the 529 by his DEC-2484g).</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="60" customHeight="1">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Shares added inside the window: start, gain, category return (W-START)</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>With shares bought inside the window, the worked-back gain and start, and a category's return. Decisions DEC-7323 and DEC-7324; DEC-7221 now names classReturnOf, categoryEarnings and gainOfRow.</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 3 of 3 gaps, 8 of 8 outside marks; not committed</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/dec3656_shares_added_inside_window.test.ts · src/screens/__tests__/shares_added_inside_window_agree.test.tsx · MoneyKeel/documents/standards/moneykeel_calc_spec_how-an-account-is-classed-and-counted_v01.md</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-22 09:15: 12 of 12 and 8 of 8. Left: sales inside the window ($2,100 where $2,000 is right — needs the sale records replayed); a purchase with no price paid is named with "has no price history", the wrong reason; Home's market is weighed by starts while your return is split at each purchase. | 2026-10-22 SENT BACK CLOSED by W-START round 2: sales inside the window (DEC-7398); the true reason for a left-out holding (DEC-7400); Home's market on the same days (DEC-7399).</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="60" customHeight="1">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>Performance decisions read against the screen (PF-DECISIONS) — 186 of 186</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>Read every decision in Performance's scope against its screen, figure or function, with a test that runs today.</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — HELD 145 (36 moved to TESTED, 109 had it; test names added), SUPERSEDED 9 marked OLD, NOT PERFORMANCE 27 re-tagged, BREACHED 4 left for their fixes, DEC-0470 in flight (drawings made, approval his)</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/perf_decisions_held_1.test.tsx, _2, _3, _5 · MoneyKeel/functions/networth-and-performance/perf_decisions_held_4.test.ts, _6 · Calculation Module code/scripts/moneykeel_decisions.json (each row's status and proof)</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-22 09:15: perf_decisions_held_1 24 of 24, _2 16 of 16, _3 9 of 9, _4 9 of 9. Six anchors re-mapped by reading (DEC-0232, DEC-0233, DEC-0248, DEC-0088, DEC-0148, DEC-0159). DEC-6076's proof names its real file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="60" customHeight="1">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Four Performance decisions breached on the screen: DEC-0237 and DEC-0404 (2Y total), DEC-0346 (screens compute nothing), DEC-0402 (Home's market by ID)</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>Print the two years' own total beside a 2Y yearly rate on the summary and every account row; move the screen sums into functions; print Home's market, you and ahead by through their IDs.</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 4 of 4 fixed: DEC-0237 and DEC-0404 (PF-A), DEC-0346 (W-HOLDING), DEC-0402 (W-A11Y); each TESTED</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/PerformanceScreen.tsx · src/screens/AccountPortfolioScreen.tsx · src/screens/HomeScreen.tsx · perf_decisions_held_1 and _4 (the test.failing cases)</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>Found by the decisions read: in his v17 phone 1 household, 2Y reads +3.46% with no total; "All categories $2,200" is added on the screen; Home writes "market +2.83%" with its own formatter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="60" customHeight="1">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>One holding return, one ID; screens compute nothing on Performance (W-HOLDING follow-ups)</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>Merge the account page's and the Holding page's holding return; move the screen sums into functions; build guard D1b. Decisions DEC-7369, DEC-7370, DEC-7371, DEC-7372.</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 4 of 4; account page 10 places → 0, Performance tab 3 → 0; not committed</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/holding_return_one_figure_2026_10_22.test.tsx · MoneyKeel/functions/networth-and-performance/dec0346_screens_compute_nothing.test.ts · src/__tests__/guard_d1_nobody_in_the_kitchen.test.ts</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-22 14:09: 7 of 7, 13 of 13, 3 of 3. NEW: 10 shares at $100 + 10 at $110, $121 today, 1Y: account page +51.25% → +21.00%, as the Holding page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="60" customHeight="1">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>A share count not on record on the account page; screens compute nothing on Net worth (W-HOLDING round 3)</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>The lead's ruling (tenet 3) on a purchase with no share count, applied on the account page; DEC-0346 closed on Net worth, Itemize and Bonds; the Holding page's 2Y lines from the one writer. Decisions DEC-7373, DEC-7374, DEC-7375, DEC-7376.</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 3 of 3; D1b 75 places in 23 files, every Net worth and Performance screen at 0; not committed</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/holding_return_one_figure_2026_10_22.test.tsx · dec0346_screens_compute_nothing.test.ts · returns_and_windows_agree.test.tsx (section 2)</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Run by W-HOLDING: 3,791 pass, 1 fail not its (networth_family_inputs, since fixed by W-A11Y: 8 of 8). 10 shares at $40 + a purchase with no count: 10 shares / $500 → Not stated … / not stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="60" customHeight="1">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>W-SHEETS follow-ups — the seven items left open (date guard, 529, Look back words, Update value title, Record activity, Net worth case, one fade)</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>Close the seven items W-SHEETS left. Decisions DEC-7377, DEC-7378, DEC-7379, DEC-7380, DEC-7381, DEC-7382; the 529 applies his DEC-2484g.</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 7 of 7; four drawings redrawn as v02, v01s archived; not committed</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>src/__tests__/date_writer_guard.test.ts · src/screens/__tests__/sheets_drawn_from_code.test.tsx · sheet_doors_2026_10_21.test.tsx · src/__tests__/one_term_per_concept.test.ts</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-22 14:09: 3 of 3, 42 of 42, 10 of 10, 3 of 3. Canon rows 9 and 12 changed (note "Two more, 2026-10-22"). The sheet drawing generator was lost with /tmp; a redraw needs it rebuilt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="60" customHeight="1">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Look back fetches what it compares (W-SHEETS)</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>Fetch Look back's pairing, SPY and his four yardsticks (DEC-1624) through the one price refresh. Decisions DEC-7383, DEC-7384, DEC-7385.</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 1 of 1; not committed</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/look_back_fetches_what_it_compares.test.tsx · src/store/useStore.ts · src/screens/LookBackScreen.tsx</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-22 14:09: 5 of 5. Nothing held, AGG→SPY: Left in AGG it became $20,500; Moved to SPY $23,200; $2,700 more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="60" customHeight="1">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>DEC-0237 and DEC-0404: a 2Y yearly rate with the two years' own total beside it (PF-A)</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>Fix the two breaches: the summary and every account row over 2Y.</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 2 of 2 breaches, 2 of 2 pins flipped; DEC-0237 and DEC-0404 TESTED; not committed</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/perf_decisions_held_1.test.tsx · returns_and_windows_agree.test.tsx (test 7) · overTheYearsSentence (performance.ts)</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-22 14:09: 24 of 24, 11 of 11. His phone-1 household 2Y: +7.05% over the two years, which is +3.46%/year (before: +3.46% alone).</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="60" customHeight="1">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>W-A11Y follow-ups, the Home hero card and its nested door</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>DEC-0402 on Home, spoken words on the account page and Holding page, Home's left-out sentence masked, the hero card read line by line, its door spoken. Decisions DEC-7386, DEC-7387, DEC-7388, DEC-7389, DEC-7390, DEC-7391, DEC-7392.</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 7 of 7, 2 of 2, 1 of 1; DEC-0402 TESTED; not committed</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>src/screens/__tests__/performance_spoken_and_agree_2026_10_21.test.tsx (sections E to H) · perf_decisions_held_4.test.ts · src/components/SaidText.tsx</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-22 14:09: 48 of 48, 9 of 9. MK-PF-M-027 and MK-PF-M-002 on Home need master rows (the final build).</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="60" customHeight="1">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>Master file defects (PF-TOOLS, rounds 1 and 2)</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>The reader that kept the builder's text as his; stale ruled dates; screen lines from declarations; the Period column; two citations; Performance's $0 refusals; three overrides retired. Decisions DEC-7393, DEC-7394, DEC-7395, DEC-7396, DEC-7397, DEC-7402, DEC-7403, DEC-7404, DEC-7405.</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 4 of 4 and 3 of 3; his 38 cells word for word; not committed</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/moneykeel_keep.py · build-moneykeel-master.py · moneykeel_period.py · moneykeel_published_sources.json · moneykeel_overrides.json</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>Build exit 0; self-checks 8. Left for the final pass: MK-PF-M-008 overrides 393, 394 and 207 (the formula and refusal are now in the declaration, and W-START changed the formula) — retire or rewrite as built.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="60" customHeight="1">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Shares sold inside the window; Home's market on the same days as your return (W-START round 2)</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>Close W-START's three loose ends and the four red market cases. Decisions DEC-7398, DEC-7399, DEC-7400, DEC-7401; DEC-7399 amends DEC-7221 where money moved.</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 3 of 3, 4 of 4 market cases, 2 of 2 F-044 entries; not committed</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/dec3656_shares_added_inside_window.test.ts · src/screens/__tests__/shares_added_inside_window_agree.test.tsx · pfb_cross_screen_agreement_2026_10_21.test.tsx</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-22: 22 of 22, 15 of 15, 11 of 11. 20 held at $100, 10 sold at $110, 10 left at $121: $210 → $310, $2,100 → $2,000. Home market for one household +8.80% (start weights alone +8.00%). W-START is on three more leftovers (sold out inside the window, bought and sold inside it, sale fees). | 2026-10-22 LEFTOVERS CLOSED: sold out inside the window (DEC-7450), bought and sold inside it (DEC-7451), sale fees (DEC-7452).</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="45" customHeight="1">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Metric register: duplicate IDs already in HEAD (MK-CF-M-001 to 004, MK-MN-M-011 and 013, MK-PL-M-023)</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>Read each duplicate with its module and give each figure one ID.</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>TO DO — with Cash flow, Menu and Plan</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/moneykeel_metric_register.json</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>Found by W-A11Y on 2026-10-22 checking its own IDs; not Performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="60" customHeight="1">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>DEC-0641 lost its dollar amounts on 2026-09-30, and the scan for the same fault</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>Restore the amounts from their source and scan every record file for amounts eaten by a shell.</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — restored in 4 records; scan read 19,390 strings, 1 real case</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>Calculation Module code/scripts/moneykeel_decisions_in_chat.json · moneykeel_decisions.json · moneykeel_question_answers.json · docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-10-07.xlsx (Changelog row 270)</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>Source: src/screens/NetWorthScreen.tsx:538-541. "On a card with a $200 minimum paid at $600, it read $200 and now reads $600." The scan's other 67 hits are function brackets, his own "$" and drawn radio buttons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="60" customHeight="1">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Holdings sold in full or bought and sold inside the window; a sale's fee counted once (W-START round 3 and its correction)</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>Close W-START's three leftovers. Decisions DEC-7450, DEC-7451 (the correction's final rule, round 3's earlier wording noted on it), DEC-7452.</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>DONE 2026-10-22 — 3 of 3, and the correction in 2 of 2 places; not committed</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>MoneyKeel/functions/networth-and-performance/dec3656_shares_added_inside_window.test.ts · src/screens/__tests__/shares_added_inside_window_agree.test.tsx · soldOutPositions, eventPath (src/domain/performance/index.ts)</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>Run 2026-10-22: 56 of 56. 10 held at $100 sold at $110: +10.00%, gained $100 (round 3 first read +8.00%); bought and sold inside the window +30.00% (was +18.18%). No outside case covers these, so no results file is marked. Later, not wrong numbers: a sold-out Unclassified holding leaves Home with no market figure (tenet 3); a holding whose prices start late and is then sold in full is weighed from the window's first day.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F256"/>
+  <autoFilter ref="A1:F285"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>